--- a/MC 685.xlsx
+++ b/MC 685.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\ccnp 300-401\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\testing tools\ccnp_mc_test_online\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4398B68A-F584-45EA-8B59-A8A18555AC7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8AD147B-A6CA-45B7-8AE7-E63310C8A011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="285">
   <si>
     <t>Index</t>
   </si>
@@ -394,6 +394,495 @@
   </si>
   <si>
     <t>enable secret or enable password commands</t>
+  </si>
+  <si>
+    <t>ip dhcp relay</t>
+  </si>
+  <si>
+    <t>resolve reachability</t>
+  </si>
+  <si>
+    <t>control plane of P routers</t>
+  </si>
+  <si>
+    <t>RSVP, LDP</t>
+  </si>
+  <si>
+    <t>local-preference 99</t>
+  </si>
+  <si>
+    <t>router ospfv3 4 process</t>
+  </si>
+  <si>
+    <t>sequence 15</t>
+  </si>
+  <si>
+    <t>using customer edge</t>
+  </si>
+  <si>
+    <t>path trace</t>
+  </si>
+  <si>
+    <t>All, 1000</t>
+  </si>
+  <si>
+    <t>LA-message-digit,LA-message-digit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">traffic-filter </t>
+  </si>
+  <si>
+    <t>an AS path filter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">full access for the username </t>
+  </si>
+  <si>
+    <t>not run any privileged
+commands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">internal external </t>
+  </si>
+  <si>
+    <t xml:space="preserve">console global </t>
+  </si>
+  <si>
+    <t>interface E 0/2
+vrf forwarding Science</t>
+  </si>
+  <si>
+    <t>G0/0 in the incoming</t>
+  </si>
+  <si>
+    <t>Advertise the branch WAN interface</t>
+  </si>
+  <si>
+    <t>VPN routing information distributed</t>
+  </si>
+  <si>
+    <t>using of VPN target communities</t>
+  </si>
+  <si>
+    <t>service dhcp - R1， trust-all -R2</t>
+  </si>
+  <si>
+    <t>Tag the 10.1.1.0/24 prefix</t>
+  </si>
+  <si>
+    <t>point-to-point</t>
+  </si>
+  <si>
+    <t>gre multipoint ipv6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">optimize the reconvergence time </t>
+  </si>
+  <si>
+    <t>BFD</t>
+  </si>
+  <si>
+    <t>SCP service</t>
+  </si>
+  <si>
+    <t>R3 address-family ipv6</t>
+  </si>
+  <si>
+    <t>exceed action transmit</t>
+  </si>
+  <si>
+    <t>same autonomous system numbers</t>
+  </si>
+  <si>
+    <t>debug snmp packet, show snmp user</t>
+  </si>
+  <si>
+    <t>weekdays 8:00 to 16:30</t>
+  </si>
+  <si>
+    <t>feasible distance greater than the reported distance</t>
+  </si>
+  <si>
+    <t>area range command on the ABR</t>
+  </si>
+  <si>
+    <t>10.221.10.11</t>
+  </si>
+  <si>
+    <t>local</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> under a cyberattack</t>
+  </si>
+  <si>
+    <t>#terminal no monitor</t>
+  </si>
+  <si>
+    <t>R4 and R5</t>
+  </si>
+  <si>
+    <t>R4 R1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">engineering capabilities </t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique VPNv4 address </t>
+  </si>
+  <si>
+    <t>traffic segmentation, DMVPN</t>
+  </si>
+  <si>
+    <t>MPLS</t>
+  </si>
+  <si>
+    <t>lower than 23</t>
+  </si>
+  <si>
+    <t>le 23</t>
+  </si>
+  <si>
+    <t>test cable-diagnostics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1.100.10  configure ip summary </t>
+  </si>
+  <si>
+    <t>changed to 172.16.0.0/24</t>
+  </si>
+  <si>
+    <t>Remove sequence 20 and add it back</t>
+  </si>
+  <si>
+    <t>5 permit icmp host 10.10.10.1 host 10.66.66.66</t>
+  </si>
+  <si>
+    <t>Layer 2 and Layer 3</t>
+  </si>
+  <si>
+    <t>login authentication telnet</t>
+  </si>
+  <si>
+    <t>Permit ICMPv6 neighbor discovery, Remove the ACL entry 80</t>
+  </si>
+  <si>
+    <t>tunnel mode gre multipoint</t>
+  </si>
+  <si>
+    <t>works with address glean</t>
+  </si>
+  <si>
+    <t>no exec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisc0Us3r RO 20 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">static route for R2 loopback </t>
+  </si>
+  <si>
+    <t>R4 area 234, R2 area 234</t>
+  </si>
+  <si>
+    <t>match ip address 101 102</t>
+  </si>
+  <si>
+    <t>metric-type 1 at Site-A, metric-type 2 at Site-B</t>
+  </si>
+  <si>
+    <t>route-reflector-client</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modify the uRPF </t>
+  </si>
+  <si>
+    <t>ipv6 address autoconfig</t>
+  </si>
+  <si>
+    <t>interface Ethernet0/0</t>
+  </si>
+  <si>
+    <t>ipv6 access-class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">point-to-multipoint  both spoke </t>
+  </si>
+  <si>
+    <t>matching preshared key</t>
+  </si>
+  <si>
+    <t>track 700 ip sla 700      30 up 20</t>
+  </si>
+  <si>
+    <t>deny 10 permit 20</t>
+  </si>
+  <si>
+    <t>permit 10  set ip next-hop recursive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove the log and log-input </t>
+  </si>
+  <si>
+    <t>0.10.10.0 0.0.0.255</t>
+  </si>
+  <si>
+    <t>Redistribute the static metric</t>
+  </si>
+  <si>
+    <t>line con 0   authorization exec</t>
+  </si>
+  <si>
+    <t>no ip prefix-list</t>
+  </si>
+  <si>
+    <t>by RD</t>
+  </si>
+  <si>
+    <t>differentiate the IP address space</t>
+  </si>
+  <si>
+    <t>vrf forwarding BLUE   ip address 10.0.0.0 255.255.255.254</t>
+  </si>
+  <si>
+    <t>对应A1 -100 A2-200 以及 没有vrf</t>
+  </si>
+  <si>
+    <t>Change the R1 router ID</t>
+  </si>
+  <si>
+    <t>overcome a flapping link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">targeted hellos, hold-timer </t>
+  </si>
+  <si>
+    <t>Power cycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">service provider deployments, IPv6 snooping </t>
+  </si>
+  <si>
+    <t>set ip default next-hop</t>
+  </si>
+  <si>
+    <t>Increase the variance value</t>
+  </si>
+  <si>
+    <t>FILTER-IN permit 20</t>
+  </si>
+  <si>
+    <t>Allow file permissions</t>
+  </si>
+  <si>
+    <t>millisecond failure detection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">filters messages </t>
+  </si>
+  <si>
+    <t>DHCPv6 Guard</t>
+  </si>
+  <si>
+    <t>Include a valid source-interface</t>
+  </si>
+  <si>
+    <t>associated labels</t>
+  </si>
+  <si>
+    <t>Modify the interlace</t>
+  </si>
+  <si>
+    <t>only DHCP requests</t>
+  </si>
+  <si>
+    <t>hash sha</t>
+  </si>
+  <si>
+    <t>exceed-action transmit</t>
+  </si>
+  <si>
+    <t>label switch path       available</t>
+  </si>
+  <si>
+    <t>minimizes DoS attacks</t>
+  </si>
+  <si>
+    <t>Destination Guard</t>
+  </si>
+  <si>
+    <t>Stop sending a route matching</t>
+  </si>
+  <si>
+    <t>Mutual redistribution</t>
+  </si>
+  <si>
+    <t>R2:
+router eigrp 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> critical </t>
+  </si>
+  <si>
+    <t>R2 no auto-summary</t>
+  </si>
+  <si>
+    <t>lowest key-id</t>
+  </si>
+  <si>
+    <t>short           low</t>
+  </si>
+  <si>
+    <t>failure detection in BFD</t>
+  </si>
+  <si>
+    <t>Allow TCP</t>
+  </si>
+  <si>
+    <t>route filtering</t>
+  </si>
+  <si>
+    <t>no-unique</t>
+  </si>
+  <si>
+    <t>Insert a /24</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> secret , password-encryption</t>
+  </si>
+  <si>
+    <t>R2 and R3</t>
+  </si>
+  <si>
+    <t>in direction for area 20</t>
+  </si>
+  <si>
+    <t>up 60 down 60</t>
+  </si>
+  <si>
+    <t>130 120</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 65000, address-family ipv6 unicast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no ip next-hop-self </t>
+  </si>
+  <si>
+    <t>RD, MP-BGP</t>
+  </si>
+  <si>
+    <t>Disable split horizon</t>
+  </si>
+  <si>
+    <t>Create an inbound ACL</t>
+  </si>
+  <si>
+    <t>no snmp trap link-status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">package.conf file writable </t>
+  </si>
+  <si>
+    <t>adjust-mtu, after-encryption</t>
+  </si>
+  <si>
+    <t>route-map Router2V6 out</t>
+  </si>
+  <si>
+    <t>incoming, forward</t>
+  </si>
+  <si>
+    <t>hop-by-hop</t>
+  </si>
+  <si>
+    <t>MPLS LSP tunnel</t>
+  </si>
+  <si>
+    <t>2, 115</t>
+  </si>
+  <si>
+    <t>debug dateflme localtime</t>
+  </si>
+  <si>
+    <t>IGP does not have a route</t>
+  </si>
+  <si>
+    <t>filter the external routes</t>
+  </si>
+  <si>
+    <t>Upgrade the peer device IOS</t>
+  </si>
+  <si>
+    <t>Source Guard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">initially connecting to a switch port </t>
+  </si>
+  <si>
+    <t>subnets keyword</t>
+  </si>
+  <si>
+    <t>132.108.0.0 0.0.3.255 包含 108.1.0 108.2.0</t>
+  </si>
+  <si>
+    <t>TCP，pseudowire signaling</t>
+  </si>
+  <si>
+    <t>tunnel destination 192.168.10.1</t>
+  </si>
+  <si>
+    <t>FlowExporter1</t>
+  </si>
+  <si>
+    <t>MPLS LDP targeted session</t>
+  </si>
+  <si>
+    <t>label distribution session</t>
+  </si>
+  <si>
+    <t>OSPF sham-link</t>
+  </si>
+  <si>
+    <t>no access-list 100， service-policy input PM-COPP</t>
+  </si>
+  <si>
+    <t>correct OSPF backdoor routing ，PE-CE</t>
+  </si>
+  <si>
+    <t>ip, interface</t>
+  </si>
+  <si>
+    <t>msec option</t>
+  </si>
+  <si>
+    <t>ip helper-address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">redistribtute command toward a domain </t>
+  </si>
+  <si>
+    <t>process 1, and remove process 10 from the global configuration</t>
+  </si>
+  <si>
+    <t>consistent rate</t>
+  </si>
+  <si>
+    <t>IPv6 Prefix Guard</t>
+  </si>
+  <si>
+    <t>distance eigrp 10 170</t>
+  </si>
+  <si>
+    <t>trunk encapsulation dot1q</t>
+  </si>
+  <si>
+    <t>aaa group server radius RAD-SERV</t>
+  </si>
+  <si>
+    <t>receiving too many external routes</t>
+  </si>
+  <si>
+    <t>redistributing on ASBR</t>
   </si>
 </sst>
 </file>
@@ -429,7 +918,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -439,6 +928,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -724,7 +1216,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="47.77734375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="108.88671875" customWidth="1"/>
+    <col min="3" max="3" width="51.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -2028,16 +2520,28 @@
       <c r="A171">
         <v>204</v>
       </c>
+      <c r="C171" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>205</v>
       </c>
+      <c r="C172" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>206</v>
       </c>
+      <c r="B173" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C173" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174">
@@ -2054,882 +2558,1365 @@
         <v>209</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>210</v>
       </c>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C177" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>211</v>
       </c>
-    </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C178" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>212</v>
       </c>
-    </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C179" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>213</v>
       </c>
-    </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C180" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>214</v>
       </c>
-    </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C181" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>215</v>
       </c>
-    </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C182" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>216</v>
       </c>
-    </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C183" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>217</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>218</v>
       </c>
-    </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C185" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>219</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>220</v>
       </c>
-    </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C187" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>221</v>
       </c>
-    </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B188" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C188" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>222</v>
       </c>
-    </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C189" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>223</v>
       </c>
-    </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C190" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>224</v>
       </c>
-    </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C191" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>225</v>
       </c>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C192" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>226</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>227</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>228</v>
       </c>
-    </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C195" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>229</v>
       </c>
-    </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B196" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C196" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>230</v>
       </c>
-    </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C197" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>231</v>
       </c>
-    </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C198" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>232</v>
       </c>
-    </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C199" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>233</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>234</v>
       </c>
-    </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C201" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>235</v>
       </c>
-    </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C202" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>236</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>237</v>
       </c>
-    </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B204" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C204" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>238</v>
       </c>
-    </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C205" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>239</v>
       </c>
-    </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C206" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>240</v>
       </c>
-    </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C207" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>241</v>
       </c>
-    </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C208" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>242</v>
       </c>
-    </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C209" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>243</v>
       </c>
-    </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C210" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>244</v>
       </c>
-    </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C211" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>245</v>
       </c>
-    </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C212" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>246</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>247</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>248</v>
       </c>
-    </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C215" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>249</v>
       </c>
-    </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C216" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>250</v>
       </c>
-    </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B217" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C217" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>251</v>
       </c>
-    </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C218" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>252</v>
       </c>
-    </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C219" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>253</v>
       </c>
-    </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C220" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>254</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>255</v>
       </c>
-    </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C222" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>256</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>257</v>
       </c>
-    </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B224" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C224" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>258</v>
       </c>
-    </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B225" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C225" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>259</v>
       </c>
-    </row>
-    <row r="227" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C226" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>260</v>
       </c>
-    </row>
-    <row r="228" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C227" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>261</v>
       </c>
-    </row>
-    <row r="229" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C228" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>262</v>
       </c>
-    </row>
-    <row r="230" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C229" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>263</v>
       </c>
-    </row>
-    <row r="231" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C230" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>264</v>
       </c>
-    </row>
-    <row r="232" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C231" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>265</v>
       </c>
-    </row>
-    <row r="233" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C232" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>266</v>
       </c>
-    </row>
-    <row r="234" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C233" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>267</v>
       </c>
-    </row>
-    <row r="235" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C234" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>268</v>
       </c>
-    </row>
-    <row r="236" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C235" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>269</v>
       </c>
-    </row>
-    <row r="237" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C236" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>270</v>
       </c>
-    </row>
-    <row r="238" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C237" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>271</v>
       </c>
-    </row>
-    <row r="239" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C238" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>272</v>
       </c>
-    </row>
-    <row r="240" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C239" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>273</v>
       </c>
     </row>
-    <row r="241" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>274</v>
       </c>
-    </row>
-    <row r="242" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C241" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>275</v>
       </c>
-    </row>
-    <row r="243" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C242" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>276</v>
       </c>
-    </row>
-    <row r="244" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C243" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>277</v>
       </c>
-    </row>
-    <row r="245" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C244" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>278</v>
       </c>
-    </row>
-    <row r="246" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C245" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>279</v>
       </c>
     </row>
-    <row r="247" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>280</v>
       </c>
-    </row>
-    <row r="248" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C247" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>281</v>
       </c>
-    </row>
-    <row r="249" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C248" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>282</v>
       </c>
     </row>
-    <row r="250" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>283</v>
       </c>
-    </row>
-    <row r="251" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C250" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>284</v>
       </c>
-    </row>
-    <row r="252" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C251" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>285</v>
       </c>
     </row>
-    <row r="253" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>286</v>
       </c>
-    </row>
-    <row r="254" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C253" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>287</v>
       </c>
-    </row>
-    <row r="255" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C254" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>288</v>
       </c>
-    </row>
-    <row r="256" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C255" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>289</v>
       </c>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>290</v>
       </c>
-    </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C257" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>291</v>
       </c>
-    </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C258" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>292</v>
       </c>
-    </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C259" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>293</v>
       </c>
-    </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C260" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>294</v>
       </c>
-    </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C261" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>295</v>
       </c>
-    </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C262" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>296</v>
       </c>
-    </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B263" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C263" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>297</v>
       </c>
-    </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C264" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>298</v>
       </c>
-    </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C265" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>299</v>
       </c>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>300</v>
       </c>
     </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>301</v>
       </c>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>302</v>
       </c>
-    </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C269" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>303</v>
       </c>
-    </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B270" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C270" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>304</v>
       </c>
-    </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C271" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>305</v>
       </c>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>306</v>
       </c>
-    </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C273" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>307</v>
       </c>
-    </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C274" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>308</v>
       </c>
-    </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C275" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>309</v>
       </c>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>310</v>
       </c>
-    </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C277" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>311</v>
       </c>
-    </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C278" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>312</v>
       </c>
-    </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C279" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>313</v>
       </c>
-    </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B280" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C280" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>314</v>
       </c>
     </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>315</v>
       </c>
-    </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C282" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>316</v>
       </c>
     </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>317</v>
       </c>
-    </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C284" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>318</v>
       </c>
     </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>319</v>
       </c>
-    </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C286" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>320</v>
       </c>
-    </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C287" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>321</v>
       </c>
-    </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C288" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>322</v>
       </c>
-    </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C289" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>323</v>
       </c>
-    </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C290" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>324</v>
       </c>
     </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>325</v>
       </c>
-    </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C292" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>326</v>
       </c>
-    </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B293" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C293" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>327</v>
       </c>
-    </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C294" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>328</v>
       </c>
-    </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B295" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C295" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>329</v>
       </c>
-    </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C296" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>330</v>
       </c>
-    </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C297" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>331</v>
       </c>
-    </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C298" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>332</v>
       </c>
-    </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B299" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C299" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>333</v>
       </c>
-    </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C300" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>334</v>
       </c>
-    </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C301" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>335</v>
       </c>
-    </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C302" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>336</v>
       </c>
-    </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C303" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>337</v>
       </c>
     </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>338</v>
       </c>
     </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>339</v>
       </c>
-    </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C306" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>340</v>
       </c>
-    </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C307" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>341</v>
       </c>
-    </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C308" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>342</v>
       </c>
-    </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C309" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>343</v>
       </c>
-    </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C310" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>344</v>
       </c>
-    </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C311" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>345</v>
       </c>
-    </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C312" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>346</v>
       </c>
     </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>347</v>
       </c>
-    </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C314" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>348</v>
       </c>
-    </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C315" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>349</v>
       </c>
-    </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C316" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>350</v>
       </c>
-    </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C317" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>351</v>
       </c>
-    </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C318" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>352</v>
       </c>
-    </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C319" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>353</v>
       </c>
-    </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C320" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>354</v>
       </c>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>355</v>
       </c>
-    </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C322" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>356</v>
       </c>
-    </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B323" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C323" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>357</v>
       </c>
-    </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C324" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>358</v>
       </c>
-    </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C325" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>359</v>
       </c>
-    </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C326" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>360</v>
       </c>
-    </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C327" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>361</v>
       </c>
-    </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C328" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>362</v>
       </c>
-    </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B329" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C329" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>363</v>
       </c>
-    </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C330" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>364</v>
       </c>
-    </row>
-    <row r="332" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C331" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>365</v>
       </c>
-    </row>
-    <row r="333" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C332" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>366</v>
       </c>
-    </row>
-    <row r="334" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C333" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>367</v>
       </c>
     </row>
-    <row r="335" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>368</v>
       </c>
-    </row>
-    <row r="336" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C335" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>369</v>
       </c>
-    </row>
-    <row r="337" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B336" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C336" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>370</v>
       </c>
-    </row>
-    <row r="338" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B337" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C337" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>371</v>
       </c>
-    </row>
-    <row r="339" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C338" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>372</v>
       </c>
-    </row>
-    <row r="340" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C339" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>373</v>
       </c>
-    </row>
-    <row r="341" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C340" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>374</v>
       </c>
-    </row>
-    <row r="342" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C341" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>375</v>
       </c>
-    </row>
-    <row r="343" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C342" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>376</v>
       </c>
-    </row>
-    <row r="344" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C343" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>377</v>
       </c>
-    </row>
-    <row r="345" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C344" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>378</v>
       </c>
-    </row>
-    <row r="346" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C345" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>379</v>
       </c>
-    </row>
-    <row r="347" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C346" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>380</v>
       </c>
-    </row>
-    <row r="348" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C347" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>381</v>
       </c>
-    </row>
-    <row r="349" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C348" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>382</v>
       </c>
-    </row>
-    <row r="350" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B349" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C349" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>383</v>
       </c>
     </row>
-    <row r="351" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>384</v>
       </c>
     </row>
-    <row r="352" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>385</v>
       </c>

--- a/MC 685.xlsx
+++ b/MC 685.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\testing tools\ccnp_mc_test_online\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8AD147B-A6CA-45B7-8AE7-E63310C8A011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BADD233-815F-42D8-83B9-79B90B4B4AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="298">
   <si>
     <t>Index</t>
   </si>
@@ -883,6 +883,45 @@
   </si>
   <si>
     <t>redistributing on ASBR</t>
+  </si>
+  <si>
+    <t>source IP summarization</t>
+  </si>
+  <si>
+    <t>address ipv4 10.221.10.11</t>
+  </si>
+  <si>
+    <t>Ciscowruser RW 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crypto isakmp key </t>
+  </si>
+  <si>
+    <t>R3, ip verify unicast source</t>
+  </si>
+  <si>
+    <t>ssh -l user ip</t>
+  </si>
+  <si>
+    <t>redisdistributed prefixes,  Type 1</t>
+  </si>
+  <si>
+    <t>R3    no area 21 stub</t>
+  </si>
+  <si>
+    <t>router rip 1</t>
+  </si>
+  <si>
+    <t>Rome to inject</t>
+  </si>
+  <si>
+    <t>Bangkok, Ethernet0/2</t>
+  </si>
+  <si>
+    <t>Cape Town, Dubai,  Tokyo</t>
+  </si>
+  <si>
+    <t>包含 DDOS的选项</t>
   </si>
 </sst>
 </file>
@@ -3910,93 +3949,135 @@
       <c r="A350">
         <v>383</v>
       </c>
+      <c r="C350" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>384</v>
       </c>
+      <c r="C351" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>385</v>
       </c>
-    </row>
-    <row r="353" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C352" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>386</v>
       </c>
     </row>
-    <row r="354" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>387</v>
       </c>
-    </row>
-    <row r="355" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C354" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>388</v>
       </c>
-    </row>
-    <row r="356" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C355" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>389</v>
       </c>
-    </row>
-    <row r="357" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C356" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>390</v>
       </c>
-    </row>
-    <row r="358" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C357" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>391</v>
       </c>
     </row>
-    <row r="359" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>392</v>
       </c>
-    </row>
-    <row r="360" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C359" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>393</v>
       </c>
     </row>
-    <row r="361" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>394</v>
       </c>
-    </row>
-    <row r="362" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C361" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>395</v>
       </c>
-    </row>
-    <row r="363" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C362" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>396</v>
       </c>
-    </row>
-    <row r="364" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C363" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>397</v>
       </c>
-    </row>
-    <row r="365" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C364" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>398</v>
       </c>
     </row>
-    <row r="366" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>399</v>
       </c>
-    </row>
-    <row r="367" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C366" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>400</v>
       </c>
-    </row>
-    <row r="368" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C367" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>401</v>
       </c>

--- a/MC 685.xlsx
+++ b/MC 685.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\testing tools\ccnp_mc_test_online\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BADD233-815F-42D8-83B9-79B90B4B4AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D0397C0-8C3C-48A6-9823-76C53DA93597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="498">
   <si>
     <t>Index</t>
   </si>
@@ -922,6 +922,615 @@
   </si>
   <si>
     <t>包含 DDOS的选项</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prepend 200, in </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ip tacacs source-interface </t>
+  </si>
+  <si>
+    <t>R5, No area</t>
+  </si>
+  <si>
+    <t>ospf 10 metric</t>
+  </si>
+  <si>
+    <t>router ospf 1, summary-address</t>
+  </si>
+  <si>
+    <t>10.66.66.66</t>
+  </si>
+  <si>
+    <t>allowas-in and as-override at the PE_Hub</t>
+  </si>
+  <si>
+    <t>VTY lines with login local</t>
+  </si>
+  <si>
+    <t>set ip next-hop recursive,  没有permit 20</t>
+  </si>
+  <si>
+    <t>characteristic of IPv6 RA Guard</t>
+  </si>
+  <si>
+    <t>filters rogue RA broadcasts</t>
+  </si>
+  <si>
+    <t>interface index persistence</t>
+  </si>
+  <si>
+    <t>permitted by the IPv6 traffic filter</t>
+  </si>
+  <si>
+    <t>10 permit 10.0.0.0/8 le 32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">higher than 10.1.2.2 and lower than 10.1.1.2 </t>
+  </si>
+  <si>
+    <t>peer-group IBGP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R1, no periodic weekdays </t>
+  </si>
+  <si>
+    <t>ip vrf 1
+ip vrf 2, ip vrf forwarding 1
+ip address 1</t>
+  </si>
+  <si>
+    <t>stub summary connected</t>
+  </si>
+  <si>
+    <t>deny 10.10.10.0 0.0.0.255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adjust-mss </t>
+  </si>
+  <si>
+    <t>8-byte Route Distinguisher</t>
+  </si>
+  <si>
+    <t>18 update-source</t>
+  </si>
+  <si>
+    <t>A permit 20 statement</t>
+  </si>
+  <si>
+    <t>C!scoTACACS</t>
+  </si>
+  <si>
+    <t>router ospf 1 vrf Maths</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPv6 DHCP Guard feature </t>
+  </si>
+  <si>
+    <t>All client messages</t>
+  </si>
+  <si>
+    <t>Configure the network statement on the neighbor</t>
+  </si>
+  <si>
+    <t>threshold 800</t>
+  </si>
+  <si>
+    <t>R2, metric-type type-1</t>
+  </si>
+  <si>
+    <t>10.2.2.4 host 10.2.2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">access-list 100 permit ip any </t>
+  </si>
+  <si>
+    <t>ip address 172.16.81.1</t>
+  </si>
+  <si>
+    <t>Add a static route</t>
+  </si>
+  <si>
+    <t>BGP AS 100 and AS 200</t>
+  </si>
+  <si>
+    <t>NTP service is disabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configure the exec command </t>
+  </si>
+  <si>
+    <t>no sequence 30， sequence 10</t>
+  </si>
+  <si>
+    <t>120 on R3 E0/1</t>
+  </si>
+  <si>
+    <t>destination host， DHCP server</t>
+  </si>
+  <si>
+    <t>peer router</t>
+  </si>
+  <si>
+    <t>^111$</t>
+  </si>
+  <si>
+    <t>rip metric 1</t>
+  </si>
+  <si>
+    <t>FEC</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> exit from the same interface</t>
+  </si>
+  <si>
+    <t>Remove the traffic filtering rules</t>
+  </si>
+  <si>
+    <t>R12 and R13， 192.168.10.11</t>
+  </si>
+  <si>
+    <t>B and C interfaces</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ^300$</t>
+  </si>
+  <si>
+    <t>allow only devices</t>
+  </si>
+  <si>
+    <t>Route-reflector-client</t>
+  </si>
+  <si>
+    <t>10.10.10.0 0.0.0.255</t>
+  </si>
+  <si>
+    <t>blocking the Telnet</t>
+  </si>
+  <si>
+    <t>regardless of media type</t>
+  </si>
+  <si>
+    <t>next-hop recursive 10.4.4.4，没有permit 20</t>
+  </si>
+  <si>
+    <t>entire UDP destination port range</t>
+  </si>
+  <si>
+    <t>higher than 1023</t>
+  </si>
+  <si>
+    <t>admin local enable</t>
+  </si>
+  <si>
+    <t>current best path</t>
+  </si>
+  <si>
+    <t>SW1 interface G1/10</t>
+  </si>
+  <si>
+    <t>ospf 10 - area 0 ， ospf 20 -area 1</t>
+  </si>
+  <si>
+    <t>router eigrp 1</t>
+  </si>
+  <si>
+    <t>10.1.1.0 0.0.0.255, set ip next-hop recursive</t>
+  </si>
+  <si>
+    <t>Associate every IP SLA probe, Use a separate IP SLA probe</t>
+  </si>
+  <si>
+    <t>destination prefix</t>
+  </si>
+  <si>
+    <t>summary-address eigrp 100 172.16.8.0</t>
+  </si>
+  <si>
+    <t>ip nhrp redirect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">deny tcp host 1001:ABC:2011:7::1 host 400A:0:400C::1 </t>
+  </si>
+  <si>
+    <t>16000 informational</t>
+  </si>
+  <si>
+    <t>performs penultimate, reads the labels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Label Edge Router </t>
+  </si>
+  <si>
+    <t>create a database of label bindings</t>
+  </si>
+  <si>
+    <t>LDP used for in an LSR</t>
+  </si>
+  <si>
+    <t>EIGRP process on R3</t>
+  </si>
+  <si>
+    <t>route-map ENT</t>
+  </si>
+  <si>
+    <t>use as a source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summarize by using the area range </t>
+  </si>
+  <si>
+    <t>different RTs</t>
+  </si>
+  <si>
+    <t>authorized DHCP servers</t>
+  </si>
+  <si>
+    <t>ip http authentication aaa, max-connections 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">两个 ospfv3 1 ipv4 area 1 </t>
+  </si>
+  <si>
+    <t>ipv6 unicast-routing， network 2001:DB8:128::2/128
+neighbor 2001:DB8:1::1 activate</t>
+  </si>
+  <si>
+    <t>R2 Fa0/0 to 1500</t>
+  </si>
+  <si>
+    <t>222 admin distance</t>
+  </si>
+  <si>
+    <t>Configure the ip sla 6500</t>
+  </si>
+  <si>
+    <t>Add a route</t>
+  </si>
+  <si>
+    <t>Remove route-map sequence 20</t>
+  </si>
+  <si>
+    <t>key chain ospf</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MPLS Layer 3 VPN deployment</t>
+  </si>
+  <si>
+    <t>QoS provides performance</t>
+  </si>
+  <si>
+    <t>network non-broadcast，priority 100</t>
+  </si>
+  <si>
+    <t>neighbor 10.1.2.192</t>
+  </si>
+  <si>
+    <t>less than a second</t>
+  </si>
+  <si>
+    <t>只有 match route-type external</t>
+  </si>
+  <si>
+    <t>lost LDP adjacency，prefix mismatch</t>
+  </si>
+  <si>
+    <t>The last P router</t>
+  </si>
+  <si>
+    <t>optimize MPLS infrastructure</t>
+  </si>
+  <si>
+    <t>Fast-Reroute，IP LFA</t>
+  </si>
+  <si>
+    <t>access-list 120 permit tcp host 172.16.1.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disable EIGRP split honzon </t>
+  </si>
+  <si>
+    <t>Remove log-input keyword</t>
+  </si>
+  <si>
+    <t>10, 40， broadcast</t>
+  </si>
+  <si>
+    <t>PE devices, VPN route target communities</t>
+  </si>
+  <si>
+    <t>只包含ip sla responder</t>
+  </si>
+  <si>
+    <t>udp 68</t>
+  </si>
+  <si>
+    <t>without peer request</t>
+  </si>
+  <si>
+    <t>time-range timer</t>
+  </si>
+  <si>
+    <t>login default local</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the highest IP address </t>
+  </si>
+  <si>
+    <t>no auto-summary command</t>
+  </si>
+  <si>
+    <t>Replace the faulty cable</t>
+  </si>
+  <si>
+    <t>BGP，10.40.1.1</t>
+  </si>
+  <si>
+    <t>start-time now，track 2</t>
+  </si>
+  <si>
+    <t>P routers provide connectivity</t>
+  </si>
+  <si>
+    <t>match-any</t>
+  </si>
+  <si>
+    <t>VNI</t>
+  </si>
+  <si>
+    <t>eigrp stub</t>
+  </si>
+  <si>
+    <t>R6(config)#ip sla responder</t>
+  </si>
+  <si>
+    <t>udp-echo ipaddress 2.2.2.2</t>
+  </si>
+  <si>
+    <t>loose mode</t>
+  </si>
+  <si>
+    <t>两个area 3 stub</t>
+  </si>
+  <si>
+    <t>Configure a different interface</t>
+  </si>
+  <si>
+    <t>redistribute os[f, permit 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Increase the available bandwidth </t>
+  </si>
+  <si>
+    <t>两个 default-infoemation originate</t>
+  </si>
+  <si>
+    <t>没有permit 20</t>
+  </si>
+  <si>
+    <t>选择没有 接口 G的选项</t>
+  </si>
+  <si>
+    <t>no ip dhcp snooping information</t>
+  </si>
+  <si>
+    <t>包含Downstream</t>
+  </si>
+  <si>
+    <t>area 1 stub no-summary</t>
+  </si>
+  <si>
+    <t>http， 3000</t>
+  </si>
+  <si>
+    <t>Dampening in</t>
+  </si>
+  <si>
+    <t>wights 011100</t>
+  </si>
+  <si>
+    <t>mask 255.255.255.255 command</t>
+  </si>
+  <si>
+    <t>Add ipv6 dhcp server R1</t>
+  </si>
+  <si>
+    <t>on the physical interfaces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mtu ignore </t>
+  </si>
+  <si>
+    <t>permit host 172.16.4.4</t>
+  </si>
+  <si>
+    <t>R4, ip flow egress</t>
+  </si>
+  <si>
+    <t>takes an active role</t>
+  </si>
+  <si>
+    <t>higher IP address</t>
+  </si>
+  <si>
+    <t>R2,  key xyz123</t>
+  </si>
+  <si>
+    <t>logging console 2</t>
+  </si>
+  <si>
+    <t>^100$</t>
+  </si>
+  <si>
+    <t>passive-interface FastEthernet 1/0</t>
+  </si>
+  <si>
+    <t>VLAN100</t>
+  </si>
+  <si>
+    <t>router eigrp 100 redistribute rip</t>
+  </si>
+  <si>
+    <t>area 7 virtual-link 10.4.4.4, 10.1.9.0 0.0.0.3 area 5</t>
+  </si>
+  <si>
+    <t>replace nvram:startup-config</t>
+  </si>
+  <si>
+    <t>10.10.10.9 255.255.255.252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">modify the AAA policy </t>
+  </si>
+  <si>
+    <t>ip address 172.16.192.2 255.255.192.0</t>
+  </si>
+  <si>
+    <t>delay timer</t>
+  </si>
+  <si>
+    <t>virtual link in Area-110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">keyword subnets should be included </t>
+  </si>
+  <si>
+    <t>not sending the community value</t>
+  </si>
+  <si>
+    <t>OSPF external routes</t>
+  </si>
+  <si>
+    <t>not any DROTHER routers</t>
+  </si>
+  <si>
+    <t>BFD session is created</t>
+  </si>
+  <si>
+    <t>Remove the distance 10</t>
+  </si>
+  <si>
+    <t>set ip next-hop 10.0.0.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">via UDP port 3784 </t>
+  </si>
+  <si>
+    <t>area 7 nssa no-summary</t>
+  </si>
+  <si>
+    <t>ebgp-multihop 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolve tacacs+ server reachability </t>
+  </si>
+  <si>
+    <t>R2, R1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multicast packets are not reliably transmitted </t>
+  </si>
+  <si>
+    <t>ipv6 dhcp relay destination</t>
+  </si>
+  <si>
+    <t>exceed-action transmit, control-plane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enable loose mode </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Configure the username </t>
+  </si>
+  <si>
+    <t>Enable EIGRP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolve duplicate IP address </t>
+  </si>
+  <si>
+    <t>line console 0
+password cisco
+end</t>
+  </si>
+  <si>
+    <t>next-hop-self</t>
+  </si>
+  <si>
+    <t>enables label binding information</t>
+  </si>
+  <si>
+    <t>nhrp nhs</t>
+  </si>
+  <si>
+    <t>multicast</t>
+  </si>
+  <si>
+    <t>ip policy route-map CCNP, any, set ip next-hop 10.0.1.2</t>
+  </si>
+  <si>
+    <t>Enable default information</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change the EIGRP delay metric </t>
+  </si>
+  <si>
+    <t>mode transport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tunnel mode gre multipoint </t>
+  </si>
+  <si>
+    <t>Set tags</t>
+  </si>
+  <si>
+    <t>assigning CE-facing interfaces</t>
+  </si>
+  <si>
+    <t>route-map R1 permit 10
+set metric 200
+!
+route-map R2 permit 10
+set metric 100</t>
+  </si>
+  <si>
+    <t>area 0 authentication message-digest-key 1 md5 exam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">advertise the 0.0.0.0/0 default route </t>
+  </si>
+  <si>
+    <t>RIP V2</t>
+  </si>
+  <si>
+    <t>deny _65412$</t>
+  </si>
+  <si>
+    <t>Establish connectivity NTP server and the switch</t>
+  </si>
+  <si>
+    <t>Permit 10.0.1.0/24 address</t>
+  </si>
+  <si>
+    <t>Layer 2 ports</t>
+  </si>
+  <si>
+    <t>flow exporter under flow monitor</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> loopback 0 and redistribute</t>
+  </si>
+  <si>
+    <t>permit 20 statement</t>
+  </si>
+  <si>
+    <t>source-interface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R2, redistribute ospf 1 metric </t>
   </si>
 </sst>
 </file>
@@ -4081,1443 +4690,2064 @@
       <c r="A368">
         <v>401</v>
       </c>
-    </row>
-    <row r="369" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C368" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>402</v>
       </c>
-    </row>
-    <row r="370" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C369" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>403</v>
       </c>
     </row>
-    <row r="371" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>404</v>
       </c>
-    </row>
-    <row r="372" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C371" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>405</v>
       </c>
-    </row>
-    <row r="373" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C372" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>406</v>
       </c>
-    </row>
-    <row r="374" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C373" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>407</v>
       </c>
-    </row>
-    <row r="375" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C374" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>408</v>
       </c>
-    </row>
-    <row r="376" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C375" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>409</v>
       </c>
-    </row>
-    <row r="377" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C376" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>410</v>
       </c>
-    </row>
-    <row r="378" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C377" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>411</v>
       </c>
     </row>
-    <row r="379" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>412</v>
       </c>
-    </row>
-    <row r="380" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B379" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C379" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>413</v>
       </c>
-    </row>
-    <row r="381" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C380" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>414</v>
       </c>
-    </row>
-    <row r="382" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C381" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>415</v>
       </c>
-    </row>
-    <row r="383" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C382" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>416</v>
       </c>
-    </row>
-    <row r="384" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C383" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>417</v>
       </c>
-    </row>
-    <row r="385" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C384" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>418</v>
       </c>
     </row>
-    <row r="386" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>419</v>
       </c>
     </row>
-    <row r="387" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>420</v>
       </c>
     </row>
-    <row r="388" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>421</v>
       </c>
-    </row>
-    <row r="389" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C388" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>422</v>
       </c>
-    </row>
-    <row r="390" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C389" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>423</v>
       </c>
-    </row>
-    <row r="391" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C390" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>424</v>
       </c>
-    </row>
-    <row r="392" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C391" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>425</v>
       </c>
-    </row>
-    <row r="393" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C392" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>426</v>
       </c>
-    </row>
-    <row r="394" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C393" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>427</v>
       </c>
-    </row>
-    <row r="395" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C394" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>428</v>
       </c>
     </row>
-    <row r="396" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>429</v>
       </c>
-    </row>
-    <row r="397" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C396" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>430</v>
       </c>
-    </row>
-    <row r="398" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C397" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>431</v>
       </c>
     </row>
-    <row r="399" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>432</v>
       </c>
-    </row>
-    <row r="400" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C399" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>433</v>
       </c>
-    </row>
-    <row r="401" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B400" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C400" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>434</v>
       </c>
     </row>
-    <row r="402" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>435</v>
       </c>
-    </row>
-    <row r="403" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C402" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>436</v>
       </c>
-    </row>
-    <row r="404" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C403" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>437</v>
       </c>
     </row>
-    <row r="405" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>438</v>
       </c>
-    </row>
-    <row r="406" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C405" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>439</v>
       </c>
-    </row>
-    <row r="407" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C406" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>440</v>
       </c>
-    </row>
-    <row r="408" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C407" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>441</v>
       </c>
-    </row>
-    <row r="409" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C408" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>442</v>
       </c>
     </row>
-    <row r="410" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>443</v>
       </c>
-    </row>
-    <row r="411" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C410" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>444</v>
       </c>
-    </row>
-    <row r="412" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C411" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>445</v>
       </c>
-    </row>
-    <row r="413" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C412" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>446</v>
       </c>
     </row>
-    <row r="414" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>447</v>
       </c>
-    </row>
-    <row r="415" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C414" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>448</v>
       </c>
-    </row>
-    <row r="416" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C415" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>449</v>
       </c>
-    </row>
-    <row r="417" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C416" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>450</v>
       </c>
     </row>
-    <row r="418" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>451</v>
       </c>
     </row>
-    <row r="419" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>452</v>
       </c>
-    </row>
-    <row r="420" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C419" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>453</v>
       </c>
-    </row>
-    <row r="421" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C420" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>454</v>
       </c>
-    </row>
-    <row r="422" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C421" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="422" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>455</v>
       </c>
-    </row>
-    <row r="423" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C422" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="423" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>456</v>
       </c>
-    </row>
-    <row r="424" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B423" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C423" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="424" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>457</v>
       </c>
     </row>
-    <row r="425" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>458</v>
       </c>
-    </row>
-    <row r="426" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C425" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="426" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>459</v>
       </c>
-    </row>
-    <row r="427" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C426" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="427" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>460</v>
       </c>
     </row>
-    <row r="428" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>461</v>
       </c>
-    </row>
-    <row r="429" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C428" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>462</v>
       </c>
-    </row>
-    <row r="430" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C429" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>463</v>
       </c>
-    </row>
-    <row r="431" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B430" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C430" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>464</v>
       </c>
     </row>
-    <row r="432" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>465</v>
       </c>
     </row>
-    <row r="433" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>466</v>
       </c>
-    </row>
-    <row r="434" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C433" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>467</v>
       </c>
-    </row>
-    <row r="435" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C434" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>468</v>
       </c>
-    </row>
-    <row r="436" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C435" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>469</v>
       </c>
     </row>
-    <row r="437" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>470</v>
       </c>
-    </row>
-    <row r="438" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C437" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>471</v>
       </c>
-    </row>
-    <row r="439" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C438" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>472</v>
       </c>
-    </row>
-    <row r="440" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C439" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>473</v>
       </c>
-    </row>
-    <row r="441" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C440" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>474</v>
       </c>
-    </row>
-    <row r="442" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C441" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>475</v>
       </c>
-    </row>
-    <row r="443" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C442" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>476</v>
       </c>
-    </row>
-    <row r="444" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C443" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>477</v>
       </c>
-    </row>
-    <row r="445" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C444" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>478</v>
       </c>
-    </row>
-    <row r="446" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C445" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>479</v>
       </c>
-    </row>
-    <row r="447" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C446" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>480</v>
       </c>
-    </row>
-    <row r="448" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C447" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>481</v>
       </c>
-    </row>
-    <row r="449" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C448" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>482</v>
       </c>
-    </row>
-    <row r="450" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C449" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>483</v>
       </c>
-    </row>
-    <row r="451" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C450" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>484</v>
       </c>
-    </row>
-    <row r="452" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C451" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>485</v>
       </c>
-    </row>
-    <row r="453" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C452" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>486</v>
       </c>
     </row>
-    <row r="454" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>487</v>
       </c>
-    </row>
-    <row r="455" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B454" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C454" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>488</v>
       </c>
-    </row>
-    <row r="456" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B455" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C455" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>489</v>
       </c>
     </row>
-    <row r="457" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>490</v>
       </c>
-    </row>
-    <row r="458" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B457" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C457" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>491</v>
       </c>
     </row>
-    <row r="459" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A459">
         <v>492</v>
       </c>
-    </row>
-    <row r="460" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C459" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A460">
         <v>493</v>
       </c>
-    </row>
-    <row r="461" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C460" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A461">
         <v>494</v>
       </c>
-    </row>
-    <row r="462" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C461" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>495</v>
       </c>
     </row>
-    <row r="463" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A463">
         <v>496</v>
       </c>
-    </row>
-    <row r="464" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C463" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A464">
         <v>497</v>
       </c>
-    </row>
-    <row r="465" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C464" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A465">
         <v>498</v>
       </c>
-    </row>
-    <row r="466" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C465" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A466">
         <v>499</v>
       </c>
     </row>
-    <row r="467" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A467">
         <v>500</v>
       </c>
-    </row>
-    <row r="468" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C467" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A468">
         <v>501</v>
       </c>
-    </row>
-    <row r="469" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C468" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>502</v>
       </c>
     </row>
-    <row r="470" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>503</v>
       </c>
     </row>
-    <row r="471" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>504</v>
       </c>
     </row>
-    <row r="472" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A472">
         <v>505</v>
       </c>
-    </row>
-    <row r="473" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C472" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>506</v>
       </c>
-    </row>
-    <row r="474" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C473" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>507</v>
       </c>
-    </row>
-    <row r="475" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C474" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>508</v>
       </c>
-    </row>
-    <row r="476" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C475" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>509</v>
       </c>
-    </row>
-    <row r="477" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C476" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>510</v>
       </c>
-    </row>
-    <row r="478" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C477" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>511</v>
       </c>
-    </row>
-    <row r="479" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C478" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>512</v>
       </c>
     </row>
-    <row r="480" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>513</v>
       </c>
     </row>
-    <row r="481" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>514</v>
       </c>
     </row>
-    <row r="482" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>515</v>
       </c>
-    </row>
-    <row r="483" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C482" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>516</v>
       </c>
     </row>
-    <row r="484" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>517</v>
       </c>
-    </row>
-    <row r="485" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B484" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C484" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A485">
         <v>518</v>
       </c>
     </row>
-    <row r="486" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A486">
         <v>519</v>
       </c>
-    </row>
-    <row r="487" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C486" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>520</v>
       </c>
-    </row>
-    <row r="488" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C487" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>521</v>
       </c>
-    </row>
-    <row r="489" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C488" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>522</v>
       </c>
     </row>
-    <row r="490" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A490">
         <v>523</v>
       </c>
-    </row>
-    <row r="491" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C490" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>524</v>
       </c>
-    </row>
-    <row r="492" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C491" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>525</v>
       </c>
-    </row>
-    <row r="493" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C492" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>526</v>
       </c>
-    </row>
-    <row r="494" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B493" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C493" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>527</v>
       </c>
-    </row>
-    <row r="495" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C494" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>528</v>
       </c>
-    </row>
-    <row r="496" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C495" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>529</v>
       </c>
-    </row>
-    <row r="497" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C496" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>530</v>
       </c>
-    </row>
-    <row r="498" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C497" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A498">
         <v>531</v>
       </c>
-    </row>
-    <row r="499" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C498" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>532</v>
       </c>
     </row>
-    <row r="500" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>533</v>
       </c>
     </row>
-    <row r="501" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>534</v>
       </c>
-    </row>
-    <row r="502" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C501" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>535</v>
       </c>
-    </row>
-    <row r="503" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C502" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A503">
         <v>536</v>
       </c>
-    </row>
-    <row r="504" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C503" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A504">
         <v>537</v>
       </c>
-    </row>
-    <row r="505" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C504" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>538</v>
       </c>
-    </row>
-    <row r="506" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C505" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A506">
         <v>539</v>
       </c>
     </row>
-    <row r="507" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A507">
         <v>540</v>
       </c>
     </row>
-    <row r="508" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A508">
         <v>541</v>
       </c>
     </row>
-    <row r="509" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A509">
         <v>542</v>
       </c>
     </row>
-    <row r="510" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A510">
         <v>543</v>
       </c>
     </row>
-    <row r="511" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A511">
         <v>544</v>
       </c>
-    </row>
-    <row r="512" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C511" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A512">
         <v>545</v>
       </c>
-    </row>
-    <row r="513" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C512" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A513">
         <v>546</v>
       </c>
-    </row>
-    <row r="514" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C513" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A514">
         <v>547</v>
       </c>
-    </row>
-    <row r="515" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C514" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A515">
         <v>548</v>
       </c>
-    </row>
-    <row r="516" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C515" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A516">
         <v>549</v>
       </c>
     </row>
-    <row r="517" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A517">
         <v>550</v>
       </c>
     </row>
-    <row r="518" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A518">
         <v>551</v>
       </c>
-    </row>
-    <row r="519" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C518" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A519">
         <v>552</v>
       </c>
     </row>
-    <row r="520" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A520">
         <v>553</v>
       </c>
-    </row>
-    <row r="521" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C520" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A521">
         <v>554</v>
       </c>
-    </row>
-    <row r="522" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C521" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A522">
         <v>555</v>
       </c>
-    </row>
-    <row r="523" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C522" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A523">
         <v>556</v>
       </c>
-    </row>
-    <row r="524" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C523" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A524">
         <v>557</v>
       </c>
-    </row>
-    <row r="525" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C524" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A525">
         <v>558</v>
       </c>
-    </row>
-    <row r="526" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C525" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A526">
         <v>559</v>
       </c>
-    </row>
-    <row r="527" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C526" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A527">
         <v>560</v>
       </c>
-    </row>
-    <row r="528" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C527" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A528">
         <v>561</v>
       </c>
     </row>
-    <row r="529" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A529">
         <v>562</v>
       </c>
-    </row>
-    <row r="530" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C529" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A530">
         <v>563</v>
       </c>
-    </row>
-    <row r="531" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C530" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A531">
         <v>564</v>
       </c>
-    </row>
-    <row r="532" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C531" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A532">
         <v>565</v>
       </c>
     </row>
-    <row r="533" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A533">
         <v>566</v>
       </c>
-    </row>
-    <row r="534" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C533" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A534">
         <v>567</v>
       </c>
     </row>
-    <row r="535" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A535">
         <v>568</v>
       </c>
     </row>
-    <row r="536" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A536">
         <v>569</v>
       </c>
-    </row>
-    <row r="537" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C536" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A537">
         <v>570</v>
       </c>
-    </row>
-    <row r="538" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C537" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A538">
         <v>571</v>
       </c>
-    </row>
-    <row r="539" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C538" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A539">
         <v>572</v>
       </c>
     </row>
-    <row r="540" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A540">
         <v>573</v>
       </c>
-    </row>
-    <row r="541" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C540" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A541">
         <v>574</v>
       </c>
-    </row>
-    <row r="542" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C541" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A542">
         <v>575</v>
       </c>
     </row>
-    <row r="543" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A543">
         <v>576</v>
       </c>
-    </row>
-    <row r="544" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C543" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A544">
         <v>577</v>
       </c>
     </row>
-    <row r="545" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A545">
         <v>578</v>
       </c>
     </row>
-    <row r="546" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A546">
         <v>579</v>
       </c>
-    </row>
-    <row r="547" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C546" s="3" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A547">
         <v>580</v>
       </c>
     </row>
-    <row r="548" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A548">
         <v>581</v>
       </c>
     </row>
-    <row r="549" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A549">
         <v>582</v>
       </c>
     </row>
-    <row r="550" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A550">
         <v>583</v>
       </c>
     </row>
-    <row r="551" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A551">
         <v>584</v>
       </c>
     </row>
-    <row r="552" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A552">
         <v>585</v>
       </c>
     </row>
-    <row r="553" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A553">
         <v>586</v>
       </c>
-    </row>
-    <row r="554" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C553" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A554">
         <v>587</v>
       </c>
-    </row>
-    <row r="555" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C554" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A555">
         <v>588</v>
       </c>
     </row>
-    <row r="556" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A556">
         <v>589</v>
       </c>
-    </row>
-    <row r="557" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C556" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A557">
         <v>590</v>
       </c>
-    </row>
-    <row r="558" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C557" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A558">
         <v>591</v>
       </c>
     </row>
-    <row r="559" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A559">
         <v>592</v>
       </c>
-    </row>
-    <row r="560" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C559" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A560">
         <v>593</v>
       </c>
-    </row>
-    <row r="561" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C560" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A561">
         <v>594</v>
       </c>
-    </row>
-    <row r="562" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C561" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A562">
         <v>595</v>
       </c>
     </row>
-    <row r="563" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A563">
         <v>596</v>
       </c>
     </row>
-    <row r="564" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A564">
         <v>597</v>
       </c>
-    </row>
-    <row r="565" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B564" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="C564" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A565">
         <v>598</v>
       </c>
-    </row>
-    <row r="566" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C565" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A566">
         <v>599</v>
       </c>
-    </row>
-    <row r="567" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C566" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A567">
         <v>600</v>
       </c>
     </row>
-    <row r="568" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A568">
         <v>601</v>
       </c>
     </row>
-    <row r="569" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A569">
         <v>602</v>
       </c>
-    </row>
-    <row r="570" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C569" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A570">
         <v>603</v>
       </c>
     </row>
-    <row r="571" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A571">
         <v>604</v>
       </c>
     </row>
-    <row r="572" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A572">
         <v>605</v>
       </c>
     </row>
-    <row r="573" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A573">
         <v>606</v>
       </c>
     </row>
-    <row r="574" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A574">
         <v>607</v>
       </c>
     </row>
-    <row r="575" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A575">
         <v>608</v>
       </c>
-    </row>
-    <row r="576" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C575" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A576">
         <v>609</v>
       </c>
-    </row>
-    <row r="577" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C576" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A577">
         <v>610</v>
       </c>
     </row>
-    <row r="578" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A578">
         <v>611</v>
       </c>
-    </row>
-    <row r="579" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C578" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A579">
         <v>612</v>
       </c>
-    </row>
-    <row r="580" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C579" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A580">
         <v>613</v>
       </c>
     </row>
-    <row r="581" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A581">
         <v>614</v>
       </c>
     </row>
-    <row r="582" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A582">
         <v>615</v>
       </c>
-    </row>
-    <row r="583" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C582" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A583">
         <v>616</v>
       </c>
     </row>
-    <row r="584" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A584">
         <v>617</v>
       </c>
-    </row>
-    <row r="585" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C584" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A585">
         <v>618</v>
       </c>
-    </row>
-    <row r="586" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C585" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A586">
         <v>619</v>
       </c>
-    </row>
-    <row r="587" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C586" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A587">
         <v>620</v>
       </c>
-    </row>
-    <row r="588" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C587" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="588" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A588">
         <v>621</v>
       </c>
-    </row>
-    <row r="589" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C588" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A589">
         <v>622</v>
       </c>
-    </row>
-    <row r="590" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C589" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="590" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A590">
         <v>623</v>
       </c>
-    </row>
-    <row r="591" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C590" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="591" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A591">
         <v>624</v>
       </c>
-    </row>
-    <row r="592" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C591" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A592">
         <v>625</v>
       </c>
     </row>
-    <row r="593" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A593">
         <v>626</v>
       </c>
-    </row>
-    <row r="594" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C593" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A594">
         <v>627</v>
       </c>
-    </row>
-    <row r="595" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B594" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C594" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A595">
         <v>628</v>
       </c>
-    </row>
-    <row r="596" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C595" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A596">
         <v>629</v>
       </c>
-    </row>
-    <row r="597" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C596" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="597" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A597">
         <v>630</v>
       </c>
-    </row>
-    <row r="598" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C597" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A598">
         <v>631</v>
       </c>
-    </row>
-    <row r="599" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C598" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A599">
         <v>632</v>
       </c>
-    </row>
-    <row r="600" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C599" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="600" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A600">
         <v>633</v>
       </c>
     </row>
-    <row r="601" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A601">
         <v>634</v>
       </c>
-    </row>
-    <row r="602" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C601" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="602" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A602">
         <v>635</v>
       </c>
     </row>
-    <row r="603" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A603">
         <v>636</v>
       </c>
-    </row>
-    <row r="604" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C603" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A604">
         <v>637</v>
       </c>
-    </row>
-    <row r="605" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C604" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="605" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A605">
         <v>638</v>
       </c>
-    </row>
-    <row r="606" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C605" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A606">
         <v>639</v>
       </c>
-    </row>
-    <row r="607" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C606" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="607" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A607">
         <v>640</v>
       </c>
-    </row>
-    <row r="608" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C607" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A608">
         <v>641</v>
       </c>
-    </row>
-    <row r="609" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C608" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="609" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A609">
         <v>642</v>
       </c>
-    </row>
-    <row r="610" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C609" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="610" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A610">
         <v>643</v>
       </c>
-    </row>
-    <row r="611" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C610" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A611">
         <v>644</v>
       </c>
-    </row>
-    <row r="612" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C611" s="1" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="612" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A612">
         <v>645</v>
       </c>
-    </row>
-    <row r="613" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C612" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="613" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A613">
         <v>646</v>
       </c>
-    </row>
-    <row r="614" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C613" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A614">
         <v>647</v>
       </c>
-    </row>
-    <row r="615" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C614" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="615" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A615">
         <v>648</v>
       </c>
-    </row>
-    <row r="616" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C615" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="616" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A616">
         <v>649</v>
       </c>
-    </row>
-    <row r="617" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C616" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="617" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A617">
         <v>650</v>
       </c>
-    </row>
-    <row r="618" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C617" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="618" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A618">
         <v>651</v>
       </c>
-    </row>
-    <row r="619" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C618" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="619" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A619">
         <v>652</v>
       </c>
-    </row>
-    <row r="620" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C619" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="620" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A620">
         <v>653</v>
       </c>
-    </row>
-    <row r="621" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C620" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="621" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A621">
         <v>654</v>
       </c>
-    </row>
-    <row r="622" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C621" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="622" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A622">
         <v>655</v>
       </c>
-    </row>
-    <row r="623" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C622" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3" ht="72" x14ac:dyDescent="0.3">
       <c r="A623">
         <v>656</v>
       </c>
-    </row>
-    <row r="624" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C623" s="1" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="624" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A624">
         <v>657</v>
       </c>
-    </row>
-    <row r="625" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C624" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="625" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A625">
         <v>658</v>
       </c>
-    </row>
-    <row r="626" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C625" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A626">
         <v>659</v>
       </c>
-    </row>
-    <row r="627" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C626" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="627" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A627">
         <v>660</v>
       </c>
-    </row>
-    <row r="628" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C627" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="628" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A628">
         <v>661</v>
       </c>
-    </row>
-    <row r="629" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C628" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="629" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A629">
         <v>662</v>
       </c>
-    </row>
-    <row r="630" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C629" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A630">
         <v>663</v>
       </c>
-    </row>
-    <row r="631" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C630" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="631" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A631">
         <v>664</v>
       </c>
-    </row>
-    <row r="632" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C631" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="632" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A632">
         <v>665</v>
       </c>
-    </row>
-    <row r="633" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C632" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="633" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A633">
         <v>666</v>
       </c>
     </row>
-    <row r="634" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A634">
         <v>667</v>
       </c>
-    </row>
-    <row r="635" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C634" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A635">
         <v>668</v>
       </c>
     </row>
-    <row r="636" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A636">
         <v>669</v>
       </c>
-    </row>
-    <row r="637" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C636" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A637">
         <v>670</v>
       </c>
     </row>
-    <row r="638" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A638">
         <v>671</v>
       </c>
     </row>
-    <row r="639" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A639">
         <v>672</v>
       </c>
     </row>
-    <row r="640" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A640">
         <v>673</v>
       </c>
     </row>
-    <row r="641" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A641">
         <v>674</v>
       </c>
     </row>
-    <row r="642" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A642">
         <v>675</v>
       </c>
     </row>
-    <row r="643" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A643">
         <v>676</v>
       </c>
     </row>
-    <row r="644" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A644">
         <v>677</v>
       </c>
     </row>
-    <row r="645" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A645">
         <v>678</v>
       </c>
     </row>
-    <row r="646" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A646">
         <v>679</v>
       </c>
-    </row>
-    <row r="647" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C646" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A647">
         <v>680</v>
       </c>
-    </row>
-    <row r="648" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C647" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A648">
         <v>681</v>
       </c>
     </row>
-    <row r="649" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A649">
         <v>682</v>
       </c>
-    </row>
-    <row r="650" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C649" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A650">
         <v>683</v>
       </c>
     </row>
-    <row r="651" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A651">
         <v>684</v>
       </c>
     </row>
-    <row r="652" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A652">
         <v>685</v>
       </c>
     </row>
-    <row r="653" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A653">
         <v>686</v>
       </c>
     </row>
-    <row r="654" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A654">
         <v>687</v>
       </c>
     </row>
-    <row r="655" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A655">
         <v>688</v>
       </c>
     </row>
-    <row r="656" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A656">
         <v>689</v>
       </c>

--- a/MC 685.xlsx
+++ b/MC 685.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\testing tools\ccnp_mc_test_online\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D0397C0-8C3C-48A6-9823-76C53DA93597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8D1EFF-1685-494F-A0C0-B728A748A802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -686,9 +686,6 @@
     <t>Include a valid source-interface</t>
   </si>
   <si>
-    <t>associated labels</t>
-  </si>
-  <si>
     <t>Modify the interlace</t>
   </si>
   <si>
@@ -716,10 +713,6 @@
     <t>Mutual redistribution</t>
   </si>
   <si>
-    <t>R2:
-router eigrp 7</t>
-  </si>
-  <si>
     <t xml:space="preserve"> critical </t>
   </si>
   <si>
@@ -955,9 +948,6 @@
   </si>
   <si>
     <t>filters rogue RA broadcasts</t>
-  </si>
-  <si>
-    <t>interface index persistence</t>
   </si>
   <si>
     <t>permitted by the IPv6 traffic filter</t>
@@ -1043,9 +1033,6 @@
     <t>no sequence 30， sequence 10</t>
   </si>
   <si>
-    <t>120 on R3 E0/1</t>
-  </si>
-  <si>
     <t>destination host， DHCP server</t>
   </si>
   <si>
@@ -1203,25 +1190,16 @@
     <t>network non-broadcast，priority 100</t>
   </si>
   <si>
-    <t>neighbor 10.1.2.192</t>
-  </si>
-  <si>
     <t>less than a second</t>
   </si>
   <si>
     <t>只有 match route-type external</t>
   </si>
   <si>
-    <t>lost LDP adjacency，prefix mismatch</t>
-  </si>
-  <si>
     <t>The last P router</t>
   </si>
   <si>
     <t>optimize MPLS infrastructure</t>
-  </si>
-  <si>
-    <t>Fast-Reroute，IP LFA</t>
   </si>
   <si>
     <t>access-list 120 permit tcp host 172.16.1.17</t>
@@ -1532,13 +1510,183 @@
   <si>
     <t xml:space="preserve">R2, redistribute ospf 1 metric </t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>lost</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> LDP adjacency，prefix </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mismatch</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">interface </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>index persistence</t>
+    </r>
+  </si>
+  <si>
+    <t>stores</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">选项包含两个distribute-list 1 in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>s1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Fast-Reroute，IP LFA (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>IF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">neighbor </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10.1.2.192</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>120</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> E0/1</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1566,7 +1714,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1580,6 +1728,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1860,7 +2009,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D685"/>
+  <dimension ref="A1:D652"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="47.77734375" style="2" customWidth="1"/>
@@ -4027,8 +4176,8 @@
       <c r="A284">
         <v>317</v>
       </c>
-      <c r="C284" t="s">
-        <v>219</v>
+      <c r="C284" s="5" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
@@ -4049,7 +4198,7 @@
         <v>320</v>
       </c>
       <c r="C287" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.3">
@@ -4057,7 +4206,7 @@
         <v>321</v>
       </c>
       <c r="C288" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
@@ -4065,7 +4214,7 @@
         <v>322</v>
       </c>
       <c r="C289" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.3">
@@ -4073,7 +4222,7 @@
         <v>323</v>
       </c>
       <c r="C290" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.3">
@@ -4086,7 +4235,7 @@
         <v>325</v>
       </c>
       <c r="C292" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
@@ -4094,10 +4243,10 @@
         <v>326</v>
       </c>
       <c r="B293" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C293" t="s">
         <v>225</v>
-      </c>
-      <c r="C293" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
@@ -4105,18 +4254,18 @@
         <v>327</v>
       </c>
       <c r="C294" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="295" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>328</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>229</v>
+        <v>494</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
@@ -4124,7 +4273,7 @@
         <v>329</v>
       </c>
       <c r="C296" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.3">
@@ -4132,7 +4281,7 @@
         <v>330</v>
       </c>
       <c r="C297" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.3">
@@ -4140,7 +4289,7 @@
         <v>331</v>
       </c>
       <c r="C298" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
@@ -4148,10 +4297,10 @@
         <v>332</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C299" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
@@ -4159,7 +4308,7 @@
         <v>333</v>
       </c>
       <c r="C300" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
@@ -4167,7 +4316,7 @@
         <v>334</v>
       </c>
       <c r="C301" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.3">
@@ -4175,7 +4324,7 @@
         <v>335</v>
       </c>
       <c r="C302" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
@@ -4183,7 +4332,7 @@
         <v>336</v>
       </c>
       <c r="C303" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.3">
@@ -4201,7 +4350,7 @@
         <v>339</v>
       </c>
       <c r="C306" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
@@ -4209,7 +4358,7 @@
         <v>340</v>
       </c>
       <c r="C307" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
@@ -4217,7 +4366,7 @@
         <v>341</v>
       </c>
       <c r="C308" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.3">
@@ -4225,7 +4374,7 @@
         <v>342</v>
       </c>
       <c r="C309" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
@@ -4233,7 +4382,7 @@
         <v>343</v>
       </c>
       <c r="C310" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.3">
@@ -4241,7 +4390,7 @@
         <v>344</v>
       </c>
       <c r="C311" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.3">
@@ -4249,7 +4398,7 @@
         <v>345</v>
       </c>
       <c r="C312" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
@@ -4262,7 +4411,7 @@
         <v>347</v>
       </c>
       <c r="C314" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
@@ -4270,7 +4419,7 @@
         <v>348</v>
       </c>
       <c r="C315" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.3">
@@ -4278,7 +4427,7 @@
         <v>349</v>
       </c>
       <c r="C316" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
@@ -4286,7 +4435,7 @@
         <v>350</v>
       </c>
       <c r="C317" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.3">
@@ -4294,7 +4443,7 @@
         <v>351</v>
       </c>
       <c r="C318" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.3">
@@ -4302,7 +4451,7 @@
         <v>352</v>
       </c>
       <c r="C319" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
@@ -4310,7 +4459,7 @@
         <v>353</v>
       </c>
       <c r="C320" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
@@ -4323,7 +4472,7 @@
         <v>355</v>
       </c>
       <c r="C322" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.3">
@@ -4331,10 +4480,10 @@
         <v>356</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C323" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
@@ -4342,7 +4491,7 @@
         <v>357</v>
       </c>
       <c r="C324" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.3">
@@ -4350,7 +4499,7 @@
         <v>358</v>
       </c>
       <c r="C325" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.3">
@@ -4358,7 +4507,7 @@
         <v>359</v>
       </c>
       <c r="C326" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
@@ -4366,7 +4515,7 @@
         <v>360</v>
       </c>
       <c r="C327" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
@@ -4374,7 +4523,7 @@
         <v>361</v>
       </c>
       <c r="C328" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
@@ -4382,10 +4531,10 @@
         <v>362</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C329" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.3">
@@ -4393,7 +4542,7 @@
         <v>363</v>
       </c>
       <c r="C330" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
@@ -4401,7 +4550,7 @@
         <v>364</v>
       </c>
       <c r="C331" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.3">
@@ -4409,7 +4558,7 @@
         <v>365</v>
       </c>
       <c r="C332" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.3">
@@ -4417,7 +4566,7 @@
         <v>366</v>
       </c>
       <c r="C333" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
@@ -4430,7 +4579,7 @@
         <v>368</v>
       </c>
       <c r="C335" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.3">
@@ -4438,10 +4587,10 @@
         <v>369</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C336" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.3">
@@ -4449,10 +4598,10 @@
         <v>370</v>
       </c>
       <c r="B337" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C337" t="s">
         <v>270</v>
-      </c>
-      <c r="C337" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.3">
@@ -4460,7 +4609,7 @@
         <v>371</v>
       </c>
       <c r="C338" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.3">
@@ -4468,7 +4617,7 @@
         <v>372</v>
       </c>
       <c r="C339" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.3">
@@ -4476,7 +4625,7 @@
         <v>373</v>
       </c>
       <c r="C340" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.3">
@@ -4484,7 +4633,7 @@
         <v>374</v>
       </c>
       <c r="C341" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.3">
@@ -4492,7 +4641,7 @@
         <v>375</v>
       </c>
       <c r="C342" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.3">
@@ -4500,7 +4649,7 @@
         <v>376</v>
       </c>
       <c r="C343" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.3">
@@ -4508,7 +4657,7 @@
         <v>377</v>
       </c>
       <c r="C344" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.3">
@@ -4516,7 +4665,7 @@
         <v>378</v>
       </c>
       <c r="C345" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.3">
@@ -4524,7 +4673,7 @@
         <v>379</v>
       </c>
       <c r="C346" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.3">
@@ -4532,7 +4681,7 @@
         <v>380</v>
       </c>
       <c r="C347" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.3">
@@ -4540,7 +4689,7 @@
         <v>381</v>
       </c>
       <c r="C348" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.3">
@@ -4548,10 +4697,10 @@
         <v>382</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C349" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.3">
@@ -4559,7 +4708,7 @@
         <v>383</v>
       </c>
       <c r="C350" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.3">
@@ -4567,7 +4716,7 @@
         <v>384</v>
       </c>
       <c r="C351" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.3">
@@ -4575,7 +4724,7 @@
         <v>385</v>
       </c>
       <c r="C352" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.3">
@@ -4588,7 +4737,7 @@
         <v>387</v>
       </c>
       <c r="C354" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.3">
@@ -4596,7 +4745,7 @@
         <v>388</v>
       </c>
       <c r="C355" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.3">
@@ -4604,7 +4753,7 @@
         <v>389</v>
       </c>
       <c r="C356" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.3">
@@ -4612,7 +4761,7 @@
         <v>390</v>
       </c>
       <c r="C357" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.3">
@@ -4625,7 +4774,7 @@
         <v>392</v>
       </c>
       <c r="C359" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.3">
@@ -4638,7 +4787,7 @@
         <v>394</v>
       </c>
       <c r="C361" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.3">
@@ -4646,7 +4795,7 @@
         <v>395</v>
       </c>
       <c r="C362" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.3">
@@ -4654,7 +4803,7 @@
         <v>396</v>
       </c>
       <c r="C363" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.3">
@@ -4662,7 +4811,7 @@
         <v>397</v>
       </c>
       <c r="C364" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.3">
@@ -4675,7 +4824,7 @@
         <v>399</v>
       </c>
       <c r="C366" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.3">
@@ -4683,7 +4832,7 @@
         <v>400</v>
       </c>
       <c r="C367" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.3">
@@ -4691,7 +4840,7 @@
         <v>401</v>
       </c>
       <c r="C368" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.3">
@@ -4699,7 +4848,7 @@
         <v>402</v>
       </c>
       <c r="C369" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.3">
@@ -4712,7 +4861,7 @@
         <v>404</v>
       </c>
       <c r="C371" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.3">
@@ -4720,7 +4869,7 @@
         <v>405</v>
       </c>
       <c r="C372" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.3">
@@ -4728,7 +4877,7 @@
         <v>406</v>
       </c>
       <c r="C373" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.3">
@@ -4736,7 +4885,7 @@
         <v>407</v>
       </c>
       <c r="C374" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.3">
@@ -4744,7 +4893,7 @@
         <v>408</v>
       </c>
       <c r="C375" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.3">
@@ -4752,7 +4901,7 @@
         <v>409</v>
       </c>
       <c r="C376" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.3">
@@ -4760,7 +4909,7 @@
         <v>410</v>
       </c>
       <c r="C377" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.3">
@@ -4773,10 +4922,10 @@
         <v>412</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C379" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.3">
@@ -4784,7 +4933,7 @@
         <v>413</v>
       </c>
       <c r="C380" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.3">
@@ -4792,7 +4941,7 @@
         <v>414</v>
       </c>
       <c r="C381" t="s">
-        <v>309</v>
+        <v>492</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.3">
@@ -4800,7 +4949,7 @@
         <v>415</v>
       </c>
       <c r="C382" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.3">
@@ -4808,7 +4957,7 @@
         <v>416</v>
       </c>
       <c r="C383" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.3">
@@ -4816,7 +4965,7 @@
         <v>417</v>
       </c>
       <c r="C384" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.3">
@@ -4839,7 +4988,7 @@
         <v>421</v>
       </c>
       <c r="C388" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
@@ -4847,7 +4996,7 @@
         <v>422</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.3">
@@ -4855,7 +5004,7 @@
         <v>423</v>
       </c>
       <c r="C390" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.3">
@@ -4863,7 +5012,7 @@
         <v>424</v>
       </c>
       <c r="C391" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.3">
@@ -4871,7 +5020,7 @@
         <v>425</v>
       </c>
       <c r="C392" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.3">
@@ -4879,7 +5028,7 @@
         <v>426</v>
       </c>
       <c r="C393" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.3">
@@ -4887,7 +5036,7 @@
         <v>427</v>
       </c>
       <c r="C394" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.3">
@@ -4900,7 +5049,7 @@
         <v>429</v>
       </c>
       <c r="C396" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.3">
@@ -4908,7 +5057,7 @@
         <v>430</v>
       </c>
       <c r="C397" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.3">
@@ -4921,7 +5070,7 @@
         <v>432</v>
       </c>
       <c r="C399" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.3">
@@ -4929,10 +5078,10 @@
         <v>433</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C400" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.3">
@@ -4945,7 +5094,7 @@
         <v>435</v>
       </c>
       <c r="C402" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.3">
@@ -4953,7 +5102,7 @@
         <v>436</v>
       </c>
       <c r="C403" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.3">
@@ -4966,7 +5115,7 @@
         <v>438</v>
       </c>
       <c r="C405" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.3">
@@ -4974,7 +5123,7 @@
         <v>439</v>
       </c>
       <c r="C406" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.3">
@@ -4982,7 +5131,7 @@
         <v>440</v>
       </c>
       <c r="C407" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.3">
@@ -4990,7 +5139,7 @@
         <v>441</v>
       </c>
       <c r="C408" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.3">
@@ -5003,7 +5152,7 @@
         <v>443</v>
       </c>
       <c r="C410" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.3">
@@ -5011,7 +5160,7 @@
         <v>444</v>
       </c>
       <c r="C411" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.3">
@@ -5019,7 +5168,7 @@
         <v>445</v>
       </c>
       <c r="C412" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.3">
@@ -5032,7 +5181,7 @@
         <v>447</v>
       </c>
       <c r="C414" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.3">
@@ -5040,7 +5189,7 @@
         <v>448</v>
       </c>
       <c r="C415" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.3">
@@ -5048,7 +5197,7 @@
         <v>449</v>
       </c>
       <c r="C416" t="s">
-        <v>337</v>
+        <v>497</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.3">
@@ -5066,15 +5215,15 @@
         <v>452</v>
       </c>
       <c r="C419" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>453</v>
       </c>
-      <c r="C420" t="s">
-        <v>339</v>
+      <c r="C420" s="5" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.3">
@@ -5082,7 +5231,7 @@
         <v>454</v>
       </c>
       <c r="C421" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.3">
@@ -5090,7 +5239,7 @@
         <v>455</v>
       </c>
       <c r="C422" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.3">
@@ -5098,10 +5247,10 @@
         <v>456</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C423" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.3">
@@ -5114,7 +5263,7 @@
         <v>458</v>
       </c>
       <c r="C425" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.3">
@@ -5122,7 +5271,7 @@
         <v>459</v>
       </c>
       <c r="C426" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.3">
@@ -5135,7 +5284,7 @@
         <v>461</v>
       </c>
       <c r="C428" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.3">
@@ -5143,7 +5292,7 @@
         <v>462</v>
       </c>
       <c r="C429" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.3">
@@ -5151,10 +5300,10 @@
         <v>463</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C430" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.3">
@@ -5172,7 +5321,7 @@
         <v>466</v>
       </c>
       <c r="C433" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.3">
@@ -5180,7 +5329,7 @@
         <v>467</v>
       </c>
       <c r="C434" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.3">
@@ -5188,7 +5337,7 @@
         <v>468</v>
       </c>
       <c r="C435" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.3">
@@ -5201,7 +5350,7 @@
         <v>470</v>
       </c>
       <c r="C437" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.3">
@@ -5209,7 +5358,7 @@
         <v>471</v>
       </c>
       <c r="C438" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.3">
@@ -5217,7 +5366,7 @@
         <v>472</v>
       </c>
       <c r="C439" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.3">
@@ -5225,7 +5374,7 @@
         <v>473</v>
       </c>
       <c r="C440" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.3">
@@ -5233,7 +5382,7 @@
         <v>474</v>
       </c>
       <c r="C441" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.3">
@@ -5241,7 +5390,7 @@
         <v>475</v>
       </c>
       <c r="C442" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.3">
@@ -5249,7 +5398,7 @@
         <v>476</v>
       </c>
       <c r="C443" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.3">
@@ -5257,7 +5406,7 @@
         <v>477</v>
       </c>
       <c r="C444" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.3">
@@ -5265,7 +5414,7 @@
         <v>478</v>
       </c>
       <c r="C445" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.3">
@@ -5273,7 +5422,7 @@
         <v>479</v>
       </c>
       <c r="C446" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.3">
@@ -5281,7 +5430,7 @@
         <v>480</v>
       </c>
       <c r="C447" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.3">
@@ -5289,7 +5438,7 @@
         <v>481</v>
       </c>
       <c r="C448" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.3">
@@ -5297,7 +5446,7 @@
         <v>482</v>
       </c>
       <c r="C449" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.3">
@@ -5305,7 +5454,7 @@
         <v>483</v>
       </c>
       <c r="C450" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.3">
@@ -5313,7 +5462,7 @@
         <v>484</v>
       </c>
       <c r="C451" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.3">
@@ -5321,7 +5470,7 @@
         <v>485</v>
       </c>
       <c r="C452" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.3">
@@ -5337,7 +5486,7 @@
         <v>111</v>
       </c>
       <c r="C454" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.3">
@@ -5345,7 +5494,7 @@
         <v>488</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C455" t="s">
         <v>114</v>
@@ -5361,10 +5510,10 @@
         <v>490</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C457" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.3">
@@ -5377,7 +5526,7 @@
         <v>492</v>
       </c>
       <c r="C459" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.3">
@@ -5385,7 +5534,7 @@
         <v>493</v>
       </c>
       <c r="C460" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.3">
@@ -5393,7 +5542,7 @@
         <v>494</v>
       </c>
       <c r="C461" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.3">
@@ -5406,7 +5555,7 @@
         <v>496</v>
       </c>
       <c r="C463" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.3">
@@ -5422,7 +5571,7 @@
         <v>498</v>
       </c>
       <c r="C465" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.3">
@@ -5435,7 +5584,7 @@
         <v>500</v>
       </c>
       <c r="C467" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.3">
@@ -5443,7 +5592,7 @@
         <v>501</v>
       </c>
       <c r="C468" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.3">
@@ -5466,7 +5615,7 @@
         <v>505</v>
       </c>
       <c r="C472" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
@@ -5474,7 +5623,7 @@
         <v>506</v>
       </c>
       <c r="C473" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.3">
@@ -5482,7 +5631,7 @@
         <v>507</v>
       </c>
       <c r="C474" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.3">
@@ -5490,7 +5639,7 @@
         <v>508</v>
       </c>
       <c r="C475" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.3">
@@ -5498,7 +5647,7 @@
         <v>509</v>
       </c>
       <c r="C476" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.3">
@@ -5506,7 +5655,7 @@
         <v>510</v>
       </c>
       <c r="C477" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.3">
@@ -5514,7 +5663,7 @@
         <v>511</v>
       </c>
       <c r="C478" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.3">
@@ -5537,7 +5686,7 @@
         <v>515</v>
       </c>
       <c r="C482" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.3">
@@ -5550,10 +5699,10 @@
         <v>517</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C484" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.3">
@@ -5566,7 +5715,7 @@
         <v>519</v>
       </c>
       <c r="C486" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.3">
@@ -5574,7 +5723,7 @@
         <v>520</v>
       </c>
       <c r="C487" t="s">
-        <v>390</v>
+        <v>496</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.3">
@@ -5582,7 +5731,7 @@
         <v>521</v>
       </c>
       <c r="C488" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.3">
@@ -5595,7 +5744,7 @@
         <v>523</v>
       </c>
       <c r="C490" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.3">
@@ -5603,7 +5752,7 @@
         <v>524</v>
       </c>
       <c r="C491" t="s">
-        <v>393</v>
+        <v>491</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.3">
@@ -5611,7 +5760,7 @@
         <v>525</v>
       </c>
       <c r="C492" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.3">
@@ -5619,10 +5768,10 @@
         <v>526</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C493" t="s">
-        <v>396</v>
+        <v>495</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.3">
@@ -5630,7 +5779,7 @@
         <v>527</v>
       </c>
       <c r="C494" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.3">
@@ -5638,7 +5787,7 @@
         <v>528</v>
       </c>
       <c r="C495" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.3">
@@ -5646,7 +5795,7 @@
         <v>529</v>
       </c>
       <c r="C496" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.3">
@@ -5654,7 +5803,7 @@
         <v>530</v>
       </c>
       <c r="C497" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.3">
@@ -5662,7 +5811,7 @@
         <v>531</v>
       </c>
       <c r="C498" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.3">
@@ -5680,7 +5829,7 @@
         <v>534</v>
       </c>
       <c r="C501" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.3">
@@ -5688,7 +5837,7 @@
         <v>535</v>
       </c>
       <c r="C502" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.3">
@@ -5696,7 +5845,7 @@
         <v>536</v>
       </c>
       <c r="C503" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.3">
@@ -5704,7 +5853,7 @@
         <v>537</v>
       </c>
       <c r="C504" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.3">
@@ -5712,7 +5861,7 @@
         <v>538</v>
       </c>
       <c r="C505" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.3">
@@ -5745,7 +5894,7 @@
         <v>544</v>
       </c>
       <c r="C511" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.3">
@@ -5761,7 +5910,7 @@
         <v>546</v>
       </c>
       <c r="C513" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.3">
@@ -5769,7 +5918,7 @@
         <v>547</v>
       </c>
       <c r="C514" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.3">
@@ -5777,7 +5926,7 @@
         <v>548</v>
       </c>
       <c r="C515" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.3">
@@ -5795,7 +5944,7 @@
         <v>551</v>
       </c>
       <c r="C518" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.3">
@@ -5808,7 +5957,7 @@
         <v>553</v>
       </c>
       <c r="C520" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.3">
@@ -5816,7 +5965,7 @@
         <v>554</v>
       </c>
       <c r="C521" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.3">
@@ -5824,7 +5973,7 @@
         <v>555</v>
       </c>
       <c r="C522" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.3">
@@ -5832,7 +5981,7 @@
         <v>556</v>
       </c>
       <c r="C523" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.3">
@@ -5840,7 +5989,7 @@
         <v>557</v>
       </c>
       <c r="C524" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.3">
@@ -5848,7 +5997,7 @@
         <v>558</v>
       </c>
       <c r="C525" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.3">
@@ -5856,7 +6005,7 @@
         <v>559</v>
       </c>
       <c r="C526" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.3">
@@ -5864,7 +6013,7 @@
         <v>560</v>
       </c>
       <c r="C527" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.3">
@@ -5877,7 +6026,7 @@
         <v>562</v>
       </c>
       <c r="C529" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.3">
@@ -5885,7 +6034,7 @@
         <v>563</v>
       </c>
       <c r="C530" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.3">
@@ -5893,7 +6042,7 @@
         <v>564</v>
       </c>
       <c r="C531" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.3">
@@ -5906,7 +6055,7 @@
         <v>566</v>
       </c>
       <c r="C533" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.3">
@@ -5924,7 +6073,7 @@
         <v>569</v>
       </c>
       <c r="C536" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.3">
@@ -5932,7 +6081,7 @@
         <v>570</v>
       </c>
       <c r="C537" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.3">
@@ -5940,7 +6089,7 @@
         <v>571</v>
       </c>
       <c r="C538" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.3">
@@ -5953,7 +6102,7 @@
         <v>573</v>
       </c>
       <c r="C540" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.3">
@@ -5961,7 +6110,7 @@
         <v>574</v>
       </c>
       <c r="C541" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.3">
@@ -5974,7 +6123,7 @@
         <v>576</v>
       </c>
       <c r="C543" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.3">
@@ -5992,7 +6141,7 @@
         <v>579</v>
       </c>
       <c r="C546" s="3" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.3">
@@ -6030,7 +6179,7 @@
         <v>586</v>
       </c>
       <c r="C553" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.3">
@@ -6038,7 +6187,7 @@
         <v>587</v>
       </c>
       <c r="C554" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.3">
@@ -6051,7 +6200,7 @@
         <v>589</v>
       </c>
       <c r="C556" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.3">
@@ -6059,7 +6208,7 @@
         <v>590</v>
       </c>
       <c r="C557" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.3">
@@ -6072,7 +6221,7 @@
         <v>592</v>
       </c>
       <c r="C559" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.3">
@@ -6080,7 +6229,7 @@
         <v>593</v>
       </c>
       <c r="C560" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.3">
@@ -6088,7 +6237,7 @@
         <v>594</v>
       </c>
       <c r="C561" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.3">
@@ -6106,10 +6255,10 @@
         <v>597</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="C564" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.3">
@@ -6117,7 +6266,7 @@
         <v>598</v>
       </c>
       <c r="C565" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.3">
@@ -6125,7 +6274,7 @@
         <v>599</v>
       </c>
       <c r="C566" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.3">
@@ -6143,7 +6292,7 @@
         <v>602</v>
       </c>
       <c r="C569" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.3">
@@ -6176,7 +6325,7 @@
         <v>608</v>
       </c>
       <c r="C575" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.3">
@@ -6184,7 +6333,7 @@
         <v>609</v>
       </c>
       <c r="C576" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.3">
@@ -6197,7 +6346,7 @@
         <v>611</v>
       </c>
       <c r="C578" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.3">
@@ -6205,7 +6354,7 @@
         <v>612</v>
       </c>
       <c r="C579" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.3">
@@ -6223,7 +6372,7 @@
         <v>615</v>
       </c>
       <c r="C582" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.3">
@@ -6236,7 +6385,7 @@
         <v>617</v>
       </c>
       <c r="C584" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.3">
@@ -6244,7 +6393,7 @@
         <v>618</v>
       </c>
       <c r="C585" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.3">
@@ -6252,7 +6401,7 @@
         <v>619</v>
       </c>
       <c r="C586" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.3">
@@ -6260,7 +6409,7 @@
         <v>620</v>
       </c>
       <c r="C587" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.3">
@@ -6268,7 +6417,7 @@
         <v>621</v>
       </c>
       <c r="C588" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.3">
@@ -6276,7 +6425,7 @@
         <v>622</v>
       </c>
       <c r="C589" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.3">
@@ -6284,7 +6433,7 @@
         <v>623</v>
       </c>
       <c r="C590" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.3">
@@ -6305,7 +6454,7 @@
         <v>626</v>
       </c>
       <c r="C593" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.3">
@@ -6313,10 +6462,10 @@
         <v>627</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="C594" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.3">
@@ -6324,7 +6473,7 @@
         <v>628</v>
       </c>
       <c r="C595" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.3">
@@ -6332,7 +6481,7 @@
         <v>629</v>
       </c>
       <c r="C596" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.3">
@@ -6340,7 +6489,7 @@
         <v>630</v>
       </c>
       <c r="C597" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.3">
@@ -6348,7 +6497,7 @@
         <v>631</v>
       </c>
       <c r="C598" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.3">
@@ -6356,7 +6505,7 @@
         <v>632</v>
       </c>
       <c r="C599" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.3">
@@ -6369,7 +6518,7 @@
         <v>634</v>
       </c>
       <c r="C601" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.3">
@@ -6382,7 +6531,7 @@
         <v>636</v>
       </c>
       <c r="C603" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.3">
@@ -6390,7 +6539,7 @@
         <v>637</v>
       </c>
       <c r="C604" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.3">
@@ -6398,7 +6547,7 @@
         <v>638</v>
       </c>
       <c r="C605" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.3">
@@ -6406,7 +6555,7 @@
         <v>639</v>
       </c>
       <c r="C606" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.3">
@@ -6414,7 +6563,7 @@
         <v>640</v>
       </c>
       <c r="C607" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.3">
@@ -6422,7 +6571,7 @@
         <v>641</v>
       </c>
       <c r="C608" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.3">
@@ -6430,7 +6579,7 @@
         <v>642</v>
       </c>
       <c r="C609" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.3">
@@ -6438,7 +6587,7 @@
         <v>643</v>
       </c>
       <c r="C610" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
     </row>
     <row r="611" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
@@ -6446,7 +6595,7 @@
         <v>644</v>
       </c>
       <c r="C611" s="1" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.3">
@@ -6454,7 +6603,7 @@
         <v>645</v>
       </c>
       <c r="C612" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.3">
@@ -6462,7 +6611,7 @@
         <v>646</v>
       </c>
       <c r="C613" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.3">
@@ -6470,7 +6619,7 @@
         <v>647</v>
       </c>
       <c r="C614" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.3">
@@ -6478,7 +6627,7 @@
         <v>648</v>
       </c>
       <c r="C615" t="s">
-        <v>476</v>
+        <v>469</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.3">
@@ -6486,7 +6635,7 @@
         <v>649</v>
       </c>
       <c r="C616" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.3">
@@ -6494,7 +6643,7 @@
         <v>650</v>
       </c>
       <c r="C617" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.3">
@@ -6502,7 +6651,7 @@
         <v>651</v>
       </c>
       <c r="C618" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.3">
@@ -6510,7 +6659,7 @@
         <v>652</v>
       </c>
       <c r="C619" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.3">
@@ -6518,7 +6667,7 @@
         <v>653</v>
       </c>
       <c r="C620" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.3">
@@ -6526,7 +6675,7 @@
         <v>654</v>
       </c>
       <c r="C621" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.3">
@@ -6534,7 +6683,7 @@
         <v>655</v>
       </c>
       <c r="C622" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
     </row>
     <row r="623" spans="1:3" ht="72" x14ac:dyDescent="0.3">
@@ -6542,7 +6691,7 @@
         <v>656</v>
       </c>
       <c r="C623" s="1" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.3">
@@ -6550,7 +6699,7 @@
         <v>657</v>
       </c>
       <c r="C624" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.3">
@@ -6558,7 +6707,7 @@
         <v>658</v>
       </c>
       <c r="C625" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.3">
@@ -6566,7 +6715,7 @@
         <v>659</v>
       </c>
       <c r="C626" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.3">
@@ -6582,7 +6731,7 @@
         <v>661</v>
       </c>
       <c r="C628" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.3">
@@ -6590,7 +6739,7 @@
         <v>662</v>
       </c>
       <c r="C629" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.3">
@@ -6598,7 +6747,7 @@
         <v>663</v>
       </c>
       <c r="C630" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.3">
@@ -6606,7 +6755,7 @@
         <v>664</v>
       </c>
       <c r="C631" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.3">
@@ -6614,7 +6763,7 @@
         <v>665</v>
       </c>
       <c r="C632" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.3">
@@ -6627,7 +6776,7 @@
         <v>667</v>
       </c>
       <c r="C634" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.3">
@@ -6640,7 +6789,7 @@
         <v>669</v>
       </c>
       <c r="C636" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.3">
@@ -6693,7 +6842,7 @@
         <v>679</v>
       </c>
       <c r="C646" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.3">
@@ -6701,7 +6850,7 @@
         <v>680</v>
       </c>
       <c r="C647" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.3">
@@ -6714,7 +6863,7 @@
         <v>682</v>
       </c>
       <c r="C649" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.3">
@@ -6730,171 +6879,6 @@
     <row r="652" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A652">
         <v>685</v>
-      </c>
-    </row>
-    <row r="653" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A653">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="654" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A654">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="655" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A655">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="656" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A656">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="657" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A657">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="658" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A658">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="659" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A659">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="660" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A660">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="661" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A661">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="662" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A662">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="663" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A663">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="664" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A664">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="665" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A665">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="666" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A666">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="667" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A667">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="668" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A668">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="669" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A669">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="670" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A670">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="671" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A671">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="672" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A672">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="673" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A673">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="674" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A674">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="675" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A675">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="676" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A676">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="677" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A677">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="678" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A678">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="679" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A679">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="680" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A680">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="681" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A681">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="682" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A682">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="683" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A683">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="684" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A684">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="685" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A685">
-        <v>718</v>
       </c>
     </row>
   </sheetData>

--- a/MC 685.xlsx
+++ b/MC 685.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\testing tools\ccnp_mc_test_online\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A8D1EFF-1685-494F-A0C0-B728A748A802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CE38DFE-10ED-49F6-97FF-9FE4178C1ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="510">
   <si>
     <t>Index</t>
   </si>
@@ -929,9 +929,6 @@
     <t>ospf 10 metric</t>
   </si>
   <si>
-    <t>router ospf 1, summary-address</t>
-  </si>
-  <si>
     <t>10.66.66.66</t>
   </si>
   <si>
@@ -950,13 +947,7 @@
     <t>filters rogue RA broadcasts</t>
   </si>
   <si>
-    <t>permitted by the IPv6 traffic filter</t>
-  </si>
-  <si>
     <t>10 permit 10.0.0.0/8 le 32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">higher than 10.1.2.2 and lower than 10.1.1.2 </t>
   </si>
   <si>
     <t>peer-group IBGP</t>
@@ -1003,9 +994,6 @@
     <t>Configure the network statement on the neighbor</t>
   </si>
   <si>
-    <t>threshold 800</t>
-  </si>
-  <si>
     <t>R2, metric-type type-1</t>
   </si>
   <si>
@@ -1021,9 +1009,6 @@
     <t>Add a static route</t>
   </si>
   <si>
-    <t>BGP AS 100 and AS 200</t>
-  </si>
-  <si>
     <t>NTP service is disabled</t>
   </si>
   <si>
@@ -1033,9 +1018,6 @@
     <t>no sequence 30， sequence 10</t>
   </si>
   <si>
-    <t>destination host， DHCP server</t>
-  </si>
-  <si>
     <t>peer router</t>
   </si>
   <si>
@@ -1051,9 +1033,6 @@
     <t xml:space="preserve"> exit from the same interface</t>
   </si>
   <si>
-    <t>Remove the traffic filtering rules</t>
-  </si>
-  <si>
     <t>R12 and R13， 192.168.10.11</t>
   </si>
   <si>
@@ -1082,9 +1061,6 @@
   </si>
   <si>
     <t>entire UDP destination port range</t>
-  </si>
-  <si>
-    <t>higher than 1023</t>
   </si>
   <si>
     <t>admin local enable</t>
@@ -1181,24 +1157,12 @@
     <t>key chain ospf</t>
   </si>
   <si>
-    <t xml:space="preserve"> MPLS Layer 3 VPN deployment</t>
-  </si>
-  <si>
-    <t>QoS provides performance</t>
-  </si>
-  <si>
-    <t>network non-broadcast，priority 100</t>
-  </si>
-  <si>
     <t>less than a second</t>
   </si>
   <si>
     <t>只有 match route-type external</t>
   </si>
   <si>
-    <t>The last P router</t>
-  </si>
-  <si>
     <t>optimize MPLS infrastructure</t>
   </si>
   <si>
@@ -1322,9 +1286,6 @@
     <t>permit host 172.16.4.4</t>
   </si>
   <si>
-    <t>R4, ip flow egress</t>
-  </si>
-  <si>
     <t>takes an active role</t>
   </si>
   <si>
@@ -1346,9 +1307,6 @@
     <t>VLAN100</t>
   </si>
   <si>
-    <t>router eigrp 100 redistribute rip</t>
-  </si>
-  <si>
     <t>area 7 virtual-link 10.4.4.4, 10.1.9.0 0.0.0.3 area 5</t>
   </si>
   <si>
@@ -1404,9 +1362,6 @@
   </si>
   <si>
     <t>R2, R1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multicast packets are not reliably transmitted </t>
   </si>
   <si>
     <t>ipv6 dhcp relay destination</t>
@@ -1453,16 +1408,10 @@
     <t xml:space="preserve">Change the EIGRP delay metric </t>
   </si>
   <si>
-    <t>mode transport</t>
-  </si>
-  <si>
     <t xml:space="preserve">tunnel mode gre multipoint </t>
   </si>
   <si>
     <t>Set tags</t>
-  </si>
-  <si>
-    <t>assigning CE-facing interfaces</t>
   </si>
   <si>
     <t>route-map R1 permit 10
@@ -1475,22 +1424,13 @@
     <t>area 0 authentication message-digest-key 1 md5 exam</t>
   </si>
   <si>
-    <t xml:space="preserve">advertise the 0.0.0.0/0 default route </t>
-  </si>
-  <si>
     <t>RIP V2</t>
   </si>
   <si>
     <t>deny _65412$</t>
   </si>
   <si>
-    <t>Establish connectivity NTP server and the switch</t>
-  </si>
-  <si>
     <t>Permit 10.0.1.0/24 address</t>
-  </si>
-  <si>
-    <t>Layer 2 ports</t>
   </si>
   <si>
     <t>flow exporter under flow monitor</t>
@@ -1672,6 +1612,473 @@
       <t xml:space="preserve"> E0/1</t>
     </r>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>advantage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> MPLS Layer 3 VPN deployment</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>QoS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> provides performance</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>destination</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> host， </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DHCP server</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">assigning </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CE-facing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> interfaces</t>
+    </r>
+  </si>
+  <si>
+    <t>Layer 2 untrusted ports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICMPv6 </t>
+  </si>
+  <si>
+    <r>
+      <t>The</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> last P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> router</t>
+    </r>
+  </si>
+  <si>
+    <t>penultimate hop popping</t>
+  </si>
+  <si>
+    <t>default-metric</t>
+  </si>
+  <si>
+    <t>passive FTP</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">higher than </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1023</t>
+    </r>
+  </si>
+  <si>
+    <t>AS 100 and AS 200</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>advertise</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> the 0.0.0.0/0</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> default route </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Multicast packets</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> are not reliably transmitted </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">threshold </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>800</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">router </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ospf 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>summary-address</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">BGP peering </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Remove the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>traffic filtering</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> rules</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">mode </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>transport</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">extra bytes overhead </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Establish connectivity </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>NTP server and the switch</t>
+    </r>
+  </si>
+  <si>
+    <t>Excessive time lag</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">network </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>non-broadcast</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">，priority </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>100</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">monitoring device </t>
+  </si>
+  <si>
+    <t>copy an image file</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">destination PE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>device</t>
+    </r>
+  </si>
+  <si>
+    <t>MPLS Layer 3 VPN function</t>
+  </si>
+  <si>
+    <t>monitor all application server traffic</t>
+  </si>
+  <si>
+    <t>2/0</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Layer 2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ports</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>protected</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by IPv6 Source Guard</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">lower than 10.1.1.2 </t>
+  </si>
 </sst>
 </file>
 
@@ -1714,7 +2121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1729,6 +2136,10 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4177,7 +4588,7 @@
         <v>317</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>493</v>
+        <v>473</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
@@ -4265,7 +4676,7 @@
         <v>227</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>494</v>
+        <v>474</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
@@ -4877,7 +5288,7 @@
         <v>406</v>
       </c>
       <c r="C373" t="s">
-        <v>300</v>
+        <v>493</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.3">
@@ -4885,7 +5296,7 @@
         <v>407</v>
       </c>
       <c r="C374" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.3">
@@ -4893,7 +5304,7 @@
         <v>408</v>
       </c>
       <c r="C375" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.3">
@@ -4901,7 +5312,7 @@
         <v>409</v>
       </c>
       <c r="C376" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.3">
@@ -4909,7 +5320,7 @@
         <v>410</v>
       </c>
       <c r="C377" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.3">
@@ -4922,18 +5333,18 @@
         <v>412</v>
       </c>
       <c r="B379" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C379" t="s">
         <v>305</v>
-      </c>
-      <c r="C379" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>413</v>
       </c>
-      <c r="C380" t="s">
-        <v>307</v>
+      <c r="C380" s="5" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.3">
@@ -4941,7 +5352,7 @@
         <v>414</v>
       </c>
       <c r="C381" t="s">
-        <v>492</v>
+        <v>472</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.3">
@@ -4949,15 +5360,15 @@
         <v>415</v>
       </c>
       <c r="C382" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>416</v>
       </c>
-      <c r="C383" t="s">
-        <v>309</v>
+      <c r="C383" s="5" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.3">
@@ -4965,7 +5376,7 @@
         <v>417</v>
       </c>
       <c r="C384" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.3">
@@ -4988,7 +5399,7 @@
         <v>421</v>
       </c>
       <c r="C388" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
@@ -4996,7 +5407,7 @@
         <v>422</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.3">
@@ -5004,7 +5415,7 @@
         <v>423</v>
       </c>
       <c r="C390" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.3">
@@ -5012,7 +5423,7 @@
         <v>424</v>
       </c>
       <c r="C391" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.3">
@@ -5020,15 +5431,15 @@
         <v>425</v>
       </c>
       <c r="C392" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>426</v>
       </c>
-      <c r="C393" t="s">
-        <v>317</v>
+      <c r="C393" s="5" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.3">
@@ -5036,7 +5447,7 @@
         <v>427</v>
       </c>
       <c r="C394" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.3">
@@ -5049,7 +5460,7 @@
         <v>429</v>
       </c>
       <c r="C396" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.3">
@@ -5057,7 +5468,7 @@
         <v>430</v>
       </c>
       <c r="C397" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.3">
@@ -5070,7 +5481,7 @@
         <v>432</v>
       </c>
       <c r="C399" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.3">
@@ -5078,10 +5489,10 @@
         <v>433</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C400" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.3">
@@ -5094,7 +5505,7 @@
         <v>435</v>
       </c>
       <c r="C402" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.3">
@@ -5102,7 +5513,7 @@
         <v>436</v>
       </c>
       <c r="C403" t="s">
-        <v>324</v>
+        <v>492</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.3">
@@ -5115,7 +5526,7 @@
         <v>438</v>
       </c>
       <c r="C405" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.3">
@@ -5123,7 +5534,7 @@
         <v>439</v>
       </c>
       <c r="C406" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.3">
@@ -5131,7 +5542,7 @@
         <v>440</v>
       </c>
       <c r="C407" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.3">
@@ -5139,7 +5550,7 @@
         <v>441</v>
       </c>
       <c r="C408" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.3">
@@ -5152,15 +5563,15 @@
         <v>443</v>
       </c>
       <c r="C410" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>444</v>
       </c>
-      <c r="C411" t="s">
-        <v>330</v>
+      <c r="C411" s="5" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.3">
@@ -5168,7 +5579,7 @@
         <v>445</v>
       </c>
       <c r="C412" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.3">
@@ -5181,7 +5592,7 @@
         <v>447</v>
       </c>
       <c r="C414" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.3">
@@ -5189,7 +5600,7 @@
         <v>448</v>
       </c>
       <c r="C415" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.3">
@@ -5197,7 +5608,7 @@
         <v>449</v>
       </c>
       <c r="C416" t="s">
-        <v>497</v>
+        <v>477</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.3">
@@ -5215,7 +5626,7 @@
         <v>452</v>
       </c>
       <c r="C419" t="s">
-        <v>334</v>
+        <v>480</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.3">
@@ -5223,7 +5634,7 @@
         <v>453</v>
       </c>
       <c r="C420" s="5" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.3">
@@ -5231,7 +5642,7 @@
         <v>454</v>
       </c>
       <c r="C421" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.3">
@@ -5239,7 +5650,7 @@
         <v>455</v>
       </c>
       <c r="C422" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.3">
@@ -5247,10 +5658,10 @@
         <v>456</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C423" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.3">
@@ -5262,8 +5673,11 @@
       <c r="A425">
         <v>458</v>
       </c>
+      <c r="B425" s="2" t="s">
+        <v>494</v>
+      </c>
       <c r="C425" t="s">
-        <v>340</v>
+        <v>495</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.3">
@@ -5271,7 +5685,7 @@
         <v>459</v>
       </c>
       <c r="C426" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.3">
@@ -5284,7 +5698,7 @@
         <v>461</v>
       </c>
       <c r="C428" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.3">
@@ -5292,7 +5706,7 @@
         <v>462</v>
       </c>
       <c r="C429" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.3">
@@ -5300,7 +5714,7 @@
         <v>463</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="C430" t="s">
         <v>277</v>
@@ -5321,7 +5735,7 @@
         <v>466</v>
       </c>
       <c r="C433" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.3">
@@ -5329,7 +5743,7 @@
         <v>467</v>
       </c>
       <c r="C434" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.3">
@@ -5337,7 +5751,7 @@
         <v>468</v>
       </c>
       <c r="C435" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.3">
@@ -5350,7 +5764,7 @@
         <v>470</v>
       </c>
       <c r="C437" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.3">
@@ -5358,7 +5772,7 @@
         <v>471</v>
       </c>
       <c r="C438" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.3">
@@ -5366,15 +5780,18 @@
         <v>472</v>
       </c>
       <c r="C439" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>473</v>
       </c>
+      <c r="B440" s="2" t="s">
+        <v>487</v>
+      </c>
       <c r="C440" t="s">
-        <v>351</v>
+        <v>488</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.3">
@@ -5382,7 +5799,7 @@
         <v>474</v>
       </c>
       <c r="C441" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.3">
@@ -5390,7 +5807,7 @@
         <v>475</v>
       </c>
       <c r="C442" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.3">
@@ -5398,7 +5815,7 @@
         <v>476</v>
       </c>
       <c r="C443" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.3">
@@ -5406,7 +5823,7 @@
         <v>477</v>
       </c>
       <c r="C444" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.3">
@@ -5414,7 +5831,7 @@
         <v>478</v>
       </c>
       <c r="C445" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.3">
@@ -5422,7 +5839,7 @@
         <v>479</v>
       </c>
       <c r="C446" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.3">
@@ -5430,7 +5847,7 @@
         <v>480</v>
       </c>
       <c r="C447" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.3">
@@ -5438,7 +5855,7 @@
         <v>481</v>
       </c>
       <c r="C448" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.3">
@@ -5446,7 +5863,7 @@
         <v>482</v>
       </c>
       <c r="C449" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.3">
@@ -5454,7 +5871,7 @@
         <v>483</v>
       </c>
       <c r="C450" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.3">
@@ -5462,7 +5879,7 @@
         <v>484</v>
       </c>
       <c r="C451" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.3">
@@ -5470,7 +5887,7 @@
         <v>485</v>
       </c>
       <c r="C452" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.3">
@@ -5486,7 +5903,7 @@
         <v>111</v>
       </c>
       <c r="C454" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.3">
@@ -5494,7 +5911,7 @@
         <v>488</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="C455" t="s">
         <v>114</v>
@@ -5510,10 +5927,10 @@
         <v>490</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="C457" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.3">
@@ -5526,7 +5943,7 @@
         <v>492</v>
       </c>
       <c r="C459" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.3">
@@ -5534,7 +5951,7 @@
         <v>493</v>
       </c>
       <c r="C460" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.3">
@@ -5542,7 +5959,7 @@
         <v>494</v>
       </c>
       <c r="C461" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.3">
@@ -5555,7 +5972,7 @@
         <v>496</v>
       </c>
       <c r="C463" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.3">
@@ -5571,7 +5988,7 @@
         <v>498</v>
       </c>
       <c r="C465" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.3">
@@ -5584,7 +6001,7 @@
         <v>500</v>
       </c>
       <c r="C467" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.3">
@@ -5592,7 +6009,7 @@
         <v>501</v>
       </c>
       <c r="C468" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.3">
@@ -5615,7 +6032,7 @@
         <v>505</v>
       </c>
       <c r="C472" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
@@ -5623,7 +6040,7 @@
         <v>506</v>
       </c>
       <c r="C473" s="1" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.3">
@@ -5631,7 +6048,7 @@
         <v>507</v>
       </c>
       <c r="C474" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.3">
@@ -5639,7 +6056,7 @@
         <v>508</v>
       </c>
       <c r="C475" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.3">
@@ -5647,7 +6064,7 @@
         <v>509</v>
       </c>
       <c r="C476" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.3">
@@ -5655,7 +6072,7 @@
         <v>510</v>
       </c>
       <c r="C477" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.3">
@@ -5663,7 +6080,7 @@
         <v>511</v>
       </c>
       <c r="C478" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.3">
@@ -5686,7 +6103,7 @@
         <v>515</v>
       </c>
       <c r="C482" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.3">
@@ -5699,10 +6116,10 @@
         <v>517</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>383</v>
+        <v>478</v>
       </c>
       <c r="C484" t="s">
-        <v>384</v>
+        <v>479</v>
       </c>
     </row>
     <row r="485" spans="1:3" x14ac:dyDescent="0.3">
@@ -5714,8 +6131,11 @@
       <c r="A486">
         <v>519</v>
       </c>
+      <c r="B486" s="6" t="s">
+        <v>501</v>
+      </c>
       <c r="C486" t="s">
-        <v>385</v>
+        <v>500</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.3">
@@ -5723,7 +6143,7 @@
         <v>520</v>
       </c>
       <c r="C487" t="s">
-        <v>496</v>
+        <v>476</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.3">
@@ -5731,7 +6151,7 @@
         <v>521</v>
       </c>
       <c r="C488" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.3">
@@ -5744,7 +6164,7 @@
         <v>523</v>
       </c>
       <c r="C490" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.3">
@@ -5752,15 +6172,18 @@
         <v>524</v>
       </c>
       <c r="C491" t="s">
-        <v>491</v>
+        <v>471</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>525</v>
       </c>
+      <c r="B492" s="2" t="s">
+        <v>485</v>
+      </c>
       <c r="C492" t="s">
-        <v>388</v>
+        <v>484</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.3">
@@ -5768,10 +6191,10 @@
         <v>526</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="C493" t="s">
-        <v>495</v>
+        <v>475</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.3">
@@ -5779,7 +6202,7 @@
         <v>527</v>
       </c>
       <c r="C494" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.3">
@@ -5787,7 +6210,7 @@
         <v>528</v>
       </c>
       <c r="C495" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.3">
@@ -5795,7 +6218,7 @@
         <v>529</v>
       </c>
       <c r="C496" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.3">
@@ -5803,7 +6226,7 @@
         <v>530</v>
       </c>
       <c r="C497" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.3">
@@ -5811,13 +6234,19 @@
         <v>531</v>
       </c>
       <c r="C498" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>532</v>
       </c>
+      <c r="B499" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="C499" t="s">
+        <v>503</v>
+      </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A500">
@@ -5829,7 +6258,7 @@
         <v>534</v>
       </c>
       <c r="C501" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.3">
@@ -5837,7 +6266,7 @@
         <v>535</v>
       </c>
       <c r="C502" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.3">
@@ -5845,7 +6274,7 @@
         <v>536</v>
       </c>
       <c r="C503" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.3">
@@ -5853,7 +6282,7 @@
         <v>537</v>
       </c>
       <c r="C504" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.3">
@@ -5861,7 +6290,7 @@
         <v>538</v>
       </c>
       <c r="C505" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.3">
@@ -5894,7 +6323,7 @@
         <v>544</v>
       </c>
       <c r="C511" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.3">
@@ -5910,7 +6339,7 @@
         <v>546</v>
       </c>
       <c r="C513" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.3">
@@ -5918,7 +6347,7 @@
         <v>547</v>
       </c>
       <c r="C514" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.3">
@@ -5926,7 +6355,7 @@
         <v>548</v>
       </c>
       <c r="C515" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.3">
@@ -5944,7 +6373,7 @@
         <v>551</v>
       </c>
       <c r="C518" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.3">
@@ -5957,7 +6386,7 @@
         <v>553</v>
       </c>
       <c r="C520" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.3">
@@ -5965,7 +6394,7 @@
         <v>554</v>
       </c>
       <c r="C521" t="s">
-        <v>406</v>
+        <v>394</v>
       </c>
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.3">
@@ -5973,7 +6402,7 @@
         <v>555</v>
       </c>
       <c r="C522" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.3">
@@ -5981,7 +6410,7 @@
         <v>556</v>
       </c>
       <c r="C523" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.3">
@@ -5989,7 +6418,7 @@
         <v>557</v>
       </c>
       <c r="C524" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.3">
@@ -5997,7 +6426,7 @@
         <v>558</v>
       </c>
       <c r="C525" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.3">
@@ -6005,7 +6434,7 @@
         <v>559</v>
       </c>
       <c r="C526" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.3">
@@ -6013,7 +6442,7 @@
         <v>560</v>
       </c>
       <c r="C527" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.3">
@@ -6026,7 +6455,7 @@
         <v>562</v>
       </c>
       <c r="C529" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.3">
@@ -6034,7 +6463,7 @@
         <v>563</v>
       </c>
       <c r="C530" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.3">
@@ -6042,7 +6471,7 @@
         <v>564</v>
       </c>
       <c r="C531" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.3">
@@ -6055,7 +6484,7 @@
         <v>566</v>
       </c>
       <c r="C533" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.3">
@@ -6073,7 +6502,7 @@
         <v>569</v>
       </c>
       <c r="C536" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.3">
@@ -6081,7 +6510,7 @@
         <v>570</v>
       </c>
       <c r="C537" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.3">
@@ -6089,7 +6518,7 @@
         <v>571</v>
       </c>
       <c r="C538" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.3">
@@ -6102,7 +6531,7 @@
         <v>573</v>
       </c>
       <c r="C540" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.3">
@@ -6110,7 +6539,7 @@
         <v>574</v>
       </c>
       <c r="C541" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.3">
@@ -6123,7 +6552,7 @@
         <v>576</v>
       </c>
       <c r="C543" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.3">
@@ -6135,13 +6564,16 @@
       <c r="A545">
         <v>578</v>
       </c>
+      <c r="B545" s="6" t="s">
+        <v>482</v>
+      </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A546">
         <v>579</v>
       </c>
       <c r="C546" s="3" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.3">
@@ -6179,7 +6611,7 @@
         <v>586</v>
       </c>
       <c r="C553" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.3">
@@ -6187,7 +6619,7 @@
         <v>587</v>
       </c>
       <c r="C554" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.3">
@@ -6200,7 +6632,7 @@
         <v>589</v>
       </c>
       <c r="C556" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.3">
@@ -6208,7 +6640,7 @@
         <v>590</v>
       </c>
       <c r="C557" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.3">
@@ -6221,7 +6653,7 @@
         <v>592</v>
       </c>
       <c r="C559" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.3">
@@ -6229,15 +6661,18 @@
         <v>593</v>
       </c>
       <c r="C560" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A561">
         <v>594</v>
       </c>
-      <c r="C561" t="s">
-        <v>430</v>
+      <c r="B561" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="C561" s="7" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.3">
@@ -6255,10 +6690,10 @@
         <v>597</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="C564" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.3">
@@ -6266,7 +6701,7 @@
         <v>598</v>
       </c>
       <c r="C565" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.3">
@@ -6274,7 +6709,7 @@
         <v>599</v>
       </c>
       <c r="C566" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.3">
@@ -6292,7 +6727,7 @@
         <v>602</v>
       </c>
       <c r="C569" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.3">
@@ -6325,7 +6760,7 @@
         <v>608</v>
       </c>
       <c r="C575" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.3">
@@ -6333,7 +6768,7 @@
         <v>609</v>
       </c>
       <c r="C576" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.3">
@@ -6345,8 +6780,8 @@
       <c r="A578">
         <v>611</v>
       </c>
-      <c r="C578" t="s">
-        <v>438</v>
+      <c r="C578" s="5" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.3">
@@ -6354,7 +6789,7 @@
         <v>612</v>
       </c>
       <c r="C579" t="s">
-        <v>439</v>
+        <v>425</v>
       </c>
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.3">
@@ -6372,7 +6807,7 @@
         <v>615</v>
       </c>
       <c r="C582" t="s">
-        <v>440</v>
+        <v>426</v>
       </c>
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.3">
@@ -6385,7 +6820,7 @@
         <v>617</v>
       </c>
       <c r="C584" t="s">
-        <v>441</v>
+        <v>427</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.3">
@@ -6393,7 +6828,7 @@
         <v>618</v>
       </c>
       <c r="C585" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.3">
@@ -6401,7 +6836,7 @@
         <v>619</v>
       </c>
       <c r="C586" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.3">
@@ -6409,7 +6844,7 @@
         <v>620</v>
       </c>
       <c r="C587" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.3">
@@ -6417,7 +6852,7 @@
         <v>621</v>
       </c>
       <c r="C588" t="s">
-        <v>445</v>
+        <v>431</v>
       </c>
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.3">
@@ -6425,7 +6860,7 @@
         <v>622</v>
       </c>
       <c r="C589" t="s">
-        <v>446</v>
+        <v>432</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.3">
@@ -6433,7 +6868,7 @@
         <v>623</v>
       </c>
       <c r="C590" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.3">
@@ -6454,7 +6889,7 @@
         <v>626</v>
       </c>
       <c r="C593" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.3">
@@ -6462,10 +6897,10 @@
         <v>627</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="C594" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.3">
@@ -6473,7 +6908,7 @@
         <v>628</v>
       </c>
       <c r="C595" t="s">
-        <v>451</v>
+        <v>437</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.3">
@@ -6481,7 +6916,7 @@
         <v>629</v>
       </c>
       <c r="C596" t="s">
-        <v>452</v>
+        <v>438</v>
       </c>
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.3">
@@ -6489,7 +6924,7 @@
         <v>630</v>
       </c>
       <c r="C597" t="s">
-        <v>453</v>
+        <v>439</v>
       </c>
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.3">
@@ -6497,7 +6932,7 @@
         <v>631</v>
       </c>
       <c r="C598" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.3">
@@ -6505,7 +6940,7 @@
         <v>632</v>
       </c>
       <c r="C599" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.3">
@@ -6518,7 +6953,7 @@
         <v>634</v>
       </c>
       <c r="C601" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.3">
@@ -6531,7 +6966,7 @@
         <v>636</v>
       </c>
       <c r="C603" t="s">
-        <v>457</v>
+        <v>443</v>
       </c>
     </row>
     <row r="604" spans="1:3" x14ac:dyDescent="0.3">
@@ -6539,7 +6974,7 @@
         <v>637</v>
       </c>
       <c r="C604" t="s">
-        <v>458</v>
+        <v>491</v>
       </c>
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.3">
@@ -6547,7 +6982,7 @@
         <v>638</v>
       </c>
       <c r="C605" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.3">
@@ -6555,7 +6990,7 @@
         <v>639</v>
       </c>
       <c r="C606" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.3">
@@ -6563,7 +6998,7 @@
         <v>640</v>
       </c>
       <c r="C607" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.3">
@@ -6571,7 +7006,7 @@
         <v>641</v>
       </c>
       <c r="C608" t="s">
-        <v>462</v>
+        <v>447</v>
       </c>
     </row>
     <row r="609" spans="1:3" x14ac:dyDescent="0.3">
@@ -6579,7 +7014,7 @@
         <v>642</v>
       </c>
       <c r="C609" t="s">
-        <v>463</v>
+        <v>448</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.3">
@@ -6587,7 +7022,7 @@
         <v>643</v>
       </c>
       <c r="C610" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
     </row>
     <row r="611" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
@@ -6595,7 +7030,7 @@
         <v>644</v>
       </c>
       <c r="C611" s="1" t="s">
-        <v>465</v>
+        <v>450</v>
       </c>
     </row>
     <row r="612" spans="1:3" x14ac:dyDescent="0.3">
@@ -6603,7 +7038,7 @@
         <v>645</v>
       </c>
       <c r="C612" t="s">
-        <v>466</v>
+        <v>451</v>
       </c>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.3">
@@ -6611,7 +7046,7 @@
         <v>646</v>
       </c>
       <c r="C613" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.3">
@@ -6619,7 +7054,7 @@
         <v>647</v>
       </c>
       <c r="C614" t="s">
-        <v>468</v>
+        <v>453</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.3">
@@ -6627,7 +7062,7 @@
         <v>648</v>
       </c>
       <c r="C615" t="s">
-        <v>469</v>
+        <v>454</v>
       </c>
     </row>
     <row r="616" spans="1:3" x14ac:dyDescent="0.3">
@@ -6635,7 +7070,7 @@
         <v>649</v>
       </c>
       <c r="C616" t="s">
-        <v>470</v>
+        <v>455</v>
       </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.3">
@@ -6643,7 +7078,7 @@
         <v>650</v>
       </c>
       <c r="C617" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.3">
@@ -6651,15 +7086,18 @@
         <v>651</v>
       </c>
       <c r="C618" t="s">
-        <v>472</v>
+        <v>457</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A619">
         <v>652</v>
       </c>
+      <c r="B619" s="6" t="s">
+        <v>497</v>
+      </c>
       <c r="C619" t="s">
-        <v>473</v>
+        <v>496</v>
       </c>
     </row>
     <row r="620" spans="1:3" x14ac:dyDescent="0.3">
@@ -6667,7 +7105,7 @@
         <v>653</v>
       </c>
       <c r="C620" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
     </row>
     <row r="621" spans="1:3" x14ac:dyDescent="0.3">
@@ -6675,7 +7113,7 @@
         <v>654</v>
       </c>
       <c r="C621" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.3">
@@ -6683,7 +7121,7 @@
         <v>655</v>
       </c>
       <c r="C622" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="623" spans="1:3" ht="72" x14ac:dyDescent="0.3">
@@ -6691,7 +7129,7 @@
         <v>656</v>
       </c>
       <c r="C623" s="1" t="s">
-        <v>477</v>
+        <v>460</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.3">
@@ -6699,7 +7137,7 @@
         <v>657</v>
       </c>
       <c r="C624" t="s">
-        <v>478</v>
+        <v>461</v>
       </c>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.3">
@@ -6707,15 +7145,15 @@
         <v>658</v>
       </c>
       <c r="C625" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
     </row>
     <row r="626" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A626">
         <v>659</v>
       </c>
-      <c r="C626" t="s">
-        <v>480</v>
+      <c r="C626" s="5" t="s">
+        <v>462</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.3">
@@ -6731,15 +7169,18 @@
         <v>661</v>
       </c>
       <c r="C628" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A629">
         <v>662</v>
       </c>
+      <c r="B629" s="2" t="s">
+        <v>499</v>
+      </c>
       <c r="C629" t="s">
-        <v>482</v>
+        <v>498</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.3">
@@ -6747,15 +7188,18 @@
         <v>663</v>
       </c>
       <c r="C630" t="s">
-        <v>483</v>
+        <v>464</v>
       </c>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A631">
         <v>664</v>
       </c>
+      <c r="B631" s="2" t="s">
+        <v>508</v>
+      </c>
       <c r="C631" t="s">
-        <v>484</v>
+        <v>507</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.3">
@@ -6763,7 +7207,7 @@
         <v>665</v>
       </c>
       <c r="C632" t="s">
-        <v>485</v>
+        <v>465</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.3">
@@ -6776,7 +7220,7 @@
         <v>667</v>
       </c>
       <c r="C634" t="s">
-        <v>486</v>
+        <v>466</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.3">
@@ -6789,7 +7233,7 @@
         <v>669</v>
       </c>
       <c r="C636" t="s">
-        <v>487</v>
+        <v>467</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.3">
@@ -6842,15 +7286,18 @@
         <v>679</v>
       </c>
       <c r="C646" t="s">
-        <v>488</v>
+        <v>468</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A647">
         <v>680</v>
       </c>
-      <c r="C647" t="s">
-        <v>489</v>
+      <c r="B647" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="C647" s="5" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.3">
@@ -6863,7 +7310,7 @@
         <v>682</v>
       </c>
       <c r="C649" t="s">
-        <v>490</v>
+        <v>470</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.3">

--- a/MC 685.xlsx
+++ b/MC 685.xlsx
@@ -1,33 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\testing tools\ccnp_mc_test_online\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F41CAA-C65F-4362-9A77-6B0CF9A96068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="18345" windowHeight="17655"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="523">
   <si>
     <t>Index</t>
   </si>
@@ -722,8 +715,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">选项包含两个distribute-list 1 in </t>
@@ -733,8 +726,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>s1</t>
@@ -934,8 +927,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">   </t>
@@ -945,8 +938,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>no area 21 stub</t>
@@ -988,8 +981,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>ospf 1</t>
@@ -998,8 +991,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">, </t>
@@ -1009,8 +1002,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>summary-address, 252</t>
@@ -1039,8 +1032,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> broadcasts</t>
@@ -1054,8 +1047,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">interface </t>
@@ -1065,8 +1058,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>index persistence</t>
@@ -1080,8 +1073,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">, permit </t>
@@ -1091,8 +1084,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>10.0.0.0/8 le 32</t>
@@ -1150,8 +1143,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">threshold </t>
@@ -1161,8 +1154,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>800</t>
@@ -1201,8 +1194,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>120</t>
@@ -1211,8 +1204,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> on </t>
@@ -1222,8 +1215,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>R3</t>
@@ -1232,8 +1225,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> E0/1</t>
@@ -1248,8 +1241,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>destination</t>
@@ -1258,8 +1251,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> host， </t>
@@ -1269,8 +1262,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>DHCP server</t>
@@ -1303,8 +1296,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>traffic filtering</t>
@@ -1313,8 +1306,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -1324,8 +1317,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>rules</t>
@@ -1369,8 +1362,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">higher than </t>
@@ -1380,8 +1373,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>1023</t>
@@ -1401,9 +1394,6 @@
   </si>
   <si>
     <t>router eigrp 1</t>
-  </si>
-  <si>
-    <t>10.1.1.0 0.0.0.255, set ip next-hop recursive</t>
   </si>
   <si>
     <t>Associate every IP SLA probe, Use a separate IP SLA probe</t>
@@ -1468,8 +1458,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> ospfv3 1 ipv4 area 1</t>
@@ -1478,8 +1468,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -1516,8 +1506,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>advantage</t>
@@ -1526,8 +1516,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> MPLS Layer 3 VPN deployment</t>
@@ -1539,8 +1529,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>QoS</t>
@@ -1549,8 +1539,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> provides performance</t>
@@ -1568,8 +1558,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>non-broadcast</t>
@@ -1578,8 +1568,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">，priority </t>
@@ -1589,8 +1579,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>100</t>
@@ -1602,8 +1592,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">neighbor </t>
@@ -1612,8 +1602,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>10.1.2.192</t>
@@ -1631,8 +1621,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>lost</t>
@@ -1641,8 +1631,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> LDP adjacency，prefix </t>
@@ -1652,8 +1642,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>mismatch</t>
@@ -1667,8 +1657,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>The</t>
@@ -1678,8 +1668,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> last P</t>
@@ -1688,8 +1678,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> router</t>
@@ -1703,8 +1693,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Fast-Reroute，IP LFA (</t>
@@ -1714,8 +1704,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>IF</t>
@@ -1724,8 +1714,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>)</t>
@@ -1748,8 +1738,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> keyword</t>
@@ -1767,8 +1757,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">destination PE </t>
@@ -1777,8 +1767,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>device</t>
@@ -1813,8 +1803,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>ommand</t>
@@ -1890,9 +1880,6 @@
     <t>wights 011100</t>
   </si>
   <si>
-    <t>一个 match tag 200</t>
-  </si>
-  <si>
     <t>把手图</t>
   </si>
   <si>
@@ -1956,9 +1943,6 @@
     <t xml:space="preserve">modify the AAA policy </t>
   </si>
   <si>
-    <t>ip address 172.16.192.2 255.255.192.0</t>
-  </si>
-  <si>
     <t>delay timer</t>
   </si>
   <si>
@@ -1980,9 +1964,6 @@
     <t>not any DROTHER routers</t>
   </si>
   <si>
-    <t>Remove the distance 10</t>
-  </si>
-  <si>
     <t>set ip next-hop 10.0.0.2</t>
   </si>
   <si>
@@ -1990,9 +1971,6 @@
   </si>
   <si>
     <t>area 7 nssa no-summary</t>
-  </si>
-  <si>
-    <t>ebgp-multihop 2</t>
   </si>
   <si>
     <t xml:space="preserve">Resolve tacacs+ server reachability </t>
@@ -2006,8 +1984,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Multicast packets</t>
@@ -2016,8 +1994,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> are not reliably transmitted </t>
@@ -2075,8 +2053,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">mode </t>
@@ -2086,8 +2064,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>transport</t>
@@ -2104,8 +2082,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">assigning </t>
@@ -2115,8 +2093,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>CE-facing</t>
@@ -2125,8 +2103,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> interfaces</t>
@@ -2151,8 +2129,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>advertise</t>
@@ -2161,8 +2139,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> the 0.0.0.0/0</t>
@@ -2172,8 +2150,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> default route </t>
@@ -2193,8 +2171,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Establish connectivity </t>
@@ -2204,8 +2182,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>NTP server and the switch</t>
@@ -2220,8 +2198,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>protected</t>
@@ -2230,8 +2208,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> by IPv6 Source Guard</t>
@@ -2243,8 +2221,8 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">Layer 2 </t>
@@ -2253,8 +2231,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>ports</t>
@@ -2292,196 +2270,182 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> users</t>
     </r>
   </si>
   <si>
-    <t>no ip prefix-list Customer</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Remove</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> the distance 10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10.1.1.0 0.0.0.255</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, set ip next-hop </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>recursive</t>
+    </r>
+  </si>
+  <si>
+    <t>no ip prefix-list Customer, 192.168.1.1/32</t>
+  </si>
+  <si>
+    <t>RB,  ebgp-multihop 3</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">一个 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>match tag 200</t>
+    </r>
+  </si>
+  <si>
+    <t>BGP neighbor is not coming up</t>
+  </si>
+  <si>
+    <t>ebgp-multihop 2, toward the neighbor</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>migration</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> project</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ip address 172.16.192.2 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>255.255.192.0</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2494,194 +2458,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -2689,256 +2467,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2951,80 +2486,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -3282,24 +2775,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E652"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="47.775" style="3" customWidth="1"/>
-    <col min="3" max="3" width="51.3333333333333" customWidth="1"/>
+    <col min="2" max="2" width="47.77734375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="51.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -3310,7 +2803,7 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="4">
+      <c r="A2" s="3">
         <v>3</v>
       </c>
       <c r="C2" t="s">
@@ -3497,7 +2990,7 @@
       <c r="A25">
         <v>38</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C25" t="s">
@@ -3508,7 +3001,7 @@
       <c r="A26">
         <v>44</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C26" t="s">
@@ -3565,7 +3058,7 @@
       <c r="A32">
         <v>63</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C32" t="s">
@@ -3618,7 +3111,7 @@
       <c r="A39">
         <v>72</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C39" t="s">
@@ -3886,7 +3379,7 @@
       <c r="A74">
         <v>107</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C74" t="s">
@@ -3900,7 +3393,7 @@
       <c r="A75">
         <v>108</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C75" t="s">
@@ -3914,7 +3407,7 @@
       <c r="A76">
         <v>109</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C76" t="s">
@@ -3928,7 +3421,7 @@
       <c r="A77">
         <v>110</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C77" t="s">
@@ -3980,7 +3473,7 @@
       <c r="A82">
         <v>115</v>
       </c>
-      <c r="C82" s="5">
+      <c r="C82" s="4">
         <v>90</v>
       </c>
     </row>
@@ -4387,7 +3880,7 @@
       <c r="A137">
         <v>170</v>
       </c>
-      <c r="C137" s="5">
+      <c r="C137" s="4">
         <v>100.1</v>
       </c>
     </row>
@@ -4408,7 +3901,7 @@
       <c r="A140">
         <v>173</v>
       </c>
-      <c r="B140" s="3" t="s">
+      <c r="B140" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C140" t="s">
@@ -4612,7 +4105,7 @@
       <c r="A173">
         <v>206</v>
       </c>
-      <c r="B173" s="3" t="s">
+      <c r="B173" s="2" t="s">
         <v>125</v>
       </c>
       <c r="C173" t="s">
@@ -4716,11 +4209,11 @@
         <v>135</v>
       </c>
     </row>
-    <row r="188" ht="28.5" spans="1:3">
+    <row r="188" spans="1:3" ht="28.8">
       <c r="A188">
         <v>221</v>
       </c>
-      <c r="B188" s="6" t="s">
+      <c r="B188" s="5" t="s">
         <v>136</v>
       </c>
       <c r="C188" t="s">
@@ -4743,11 +4236,11 @@
         <v>139</v>
       </c>
     </row>
-    <row r="191" ht="28.5" spans="1:3">
+    <row r="191" spans="1:3" ht="28.8">
       <c r="A191">
         <v>224</v>
       </c>
-      <c r="C191" s="4" t="s">
+      <c r="C191" s="3" t="s">
         <v>140</v>
       </c>
     </row>
@@ -4781,7 +4274,7 @@
       <c r="A196">
         <v>229</v>
       </c>
-      <c r="B196" s="3" t="s">
+      <c r="B196" s="2" t="s">
         <v>143</v>
       </c>
       <c r="C196" t="s">
@@ -4842,7 +4335,7 @@
       <c r="A204">
         <v>237</v>
       </c>
-      <c r="B204" s="3" t="s">
+      <c r="B204" s="2" t="s">
         <v>149</v>
       </c>
       <c r="C204" t="s">
@@ -4943,7 +4436,7 @@
       <c r="A217">
         <v>250</v>
       </c>
-      <c r="B217" s="3" t="s">
+      <c r="B217" s="2" t="s">
         <v>161</v>
       </c>
       <c r="C217" t="s">
@@ -4996,7 +4489,7 @@
       <c r="A224">
         <v>257</v>
       </c>
-      <c r="B224" s="3" t="s">
+      <c r="B224" s="2" t="s">
         <v>167</v>
       </c>
       <c r="C224" t="s">
@@ -5007,7 +4500,7 @@
       <c r="A225">
         <v>258</v>
       </c>
-      <c r="B225" s="3" t="s">
+      <c r="B225" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C225" t="s">
@@ -5299,7 +4792,7 @@
       <c r="A263">
         <v>296</v>
       </c>
-      <c r="B263" s="3" t="s">
+      <c r="B263" s="2" t="s">
         <v>202</v>
       </c>
       <c r="C263" t="s">
@@ -5349,7 +4842,7 @@
       <c r="A270">
         <v>303</v>
       </c>
-      <c r="B270" s="3" t="s">
+      <c r="B270" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C270" t="s">
@@ -5426,7 +4919,7 @@
       <c r="A280">
         <v>313</v>
       </c>
-      <c r="B280" s="3" t="s">
+      <c r="B280" s="2" t="s">
         <v>216</v>
       </c>
       <c r="C280" t="s">
@@ -5455,7 +4948,7 @@
       <c r="A284">
         <v>317</v>
       </c>
-      <c r="C284" s="7" t="s">
+      <c r="C284" s="6" t="s">
         <v>219</v>
       </c>
     </row>
@@ -5468,7 +4961,7 @@
       <c r="A286">
         <v>319</v>
       </c>
-      <c r="C286" s="5">
+      <c r="C286" s="4">
         <v>25</v>
       </c>
     </row>
@@ -5521,7 +5014,7 @@
       <c r="A293">
         <v>326</v>
       </c>
-      <c r="B293" s="3" t="s">
+      <c r="B293" s="2" t="s">
         <v>225</v>
       </c>
       <c r="C293" t="s">
@@ -5540,10 +5033,10 @@
       <c r="A295">
         <v>328</v>
       </c>
-      <c r="B295" s="3" t="s">
+      <c r="B295" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C295" s="4" t="s">
+      <c r="C295" s="3" t="s">
         <v>229</v>
       </c>
     </row>
@@ -5575,7 +5068,7 @@
       <c r="A299">
         <v>332</v>
       </c>
-      <c r="B299" s="3" t="s">
+      <c r="B299" s="2" t="s">
         <v>233</v>
       </c>
       <c r="C299" t="s">
@@ -5758,7 +5251,7 @@
       <c r="A323">
         <v>356</v>
       </c>
-      <c r="B323" s="3" t="s">
+      <c r="B323" s="2" t="s">
         <v>254</v>
       </c>
       <c r="C323" t="s">
@@ -5809,7 +5302,7 @@
       <c r="A329">
         <v>362</v>
       </c>
-      <c r="B329" s="3" t="s">
+      <c r="B329" s="2" t="s">
         <v>261</v>
       </c>
       <c r="C329" t="s">
@@ -5865,7 +5358,7 @@
       <c r="A336">
         <v>369</v>
       </c>
-      <c r="B336" s="3" t="s">
+      <c r="B336" s="2" t="s">
         <v>268</v>
       </c>
       <c r="C336" t="s">
@@ -5876,7 +5369,7 @@
       <c r="A337">
         <v>370</v>
       </c>
-      <c r="B337" s="3" t="s">
+      <c r="B337" s="2" t="s">
         <v>270</v>
       </c>
       <c r="C337" t="s">
@@ -5975,7 +5468,7 @@
       <c r="A349">
         <v>382</v>
       </c>
-      <c r="B349" s="3" t="s">
+      <c r="B349" s="2" t="s">
         <v>283</v>
       </c>
       <c r="C349" t="s">
@@ -6061,12 +5554,12 @@
         <v>393</v>
       </c>
     </row>
-    <row r="361" s="1" customFormat="1" spans="1:3">
+    <row r="361" spans="1:3" s="1" customFormat="1">
       <c r="A361" s="1">
         <v>394</v>
       </c>
-      <c r="B361" s="8"/>
-      <c r="C361" s="9" t="s">
+      <c r="B361" s="7"/>
+      <c r="C361" s="8" t="s">
         <v>292</v>
       </c>
     </row>
@@ -6144,11 +5637,14 @@
         <v>300</v>
       </c>
     </row>
-    <row r="372" spans="1:3">
-      <c r="A372">
+    <row r="372" spans="1:3" s="1" customFormat="1">
+      <c r="A372" s="1">
         <v>405</v>
       </c>
-      <c r="C372" t="s">
+      <c r="B372" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="C372" s="13" t="s">
         <v>301</v>
       </c>
     </row>
@@ -6156,7 +5652,7 @@
       <c r="A373">
         <v>406</v>
       </c>
-      <c r="C373" s="10" t="s">
+      <c r="C373" t="s">
         <v>302</v>
       </c>
     </row>
@@ -6197,14 +5693,14 @@
         <v>411</v>
       </c>
     </row>
-    <row r="379" s="1" customFormat="1" spans="1:3">
+    <row r="379" spans="1:3" s="1" customFormat="1">
       <c r="A379" s="1">
         <v>412</v>
       </c>
-      <c r="B379" s="8" t="s">
+      <c r="B379" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="C379" s="9" t="s">
+      <c r="C379" s="8" t="s">
         <v>308</v>
       </c>
     </row>
@@ -6212,7 +5708,7 @@
       <c r="A380">
         <v>413</v>
       </c>
-      <c r="C380" s="7" t="s">
+      <c r="C380" s="6" t="s">
         <v>309</v>
       </c>
     </row>
@@ -6228,7 +5724,7 @@
       <c r="A382">
         <v>415</v>
       </c>
-      <c r="C382" s="7" t="s">
+      <c r="C382" s="6" t="s">
         <v>311</v>
       </c>
     </row>
@@ -6236,7 +5732,7 @@
       <c r="A383">
         <v>416</v>
       </c>
-      <c r="C383" s="7" t="s">
+      <c r="C383" s="6" t="s">
         <v>312</v>
       </c>
     </row>
@@ -6271,11 +5767,11 @@
         <v>314</v>
       </c>
     </row>
-    <row r="389" ht="42.75" spans="1:3">
+    <row r="389" spans="1:3" ht="43.2">
       <c r="A389">
         <v>422</v>
       </c>
-      <c r="C389" s="4" t="s">
+      <c r="C389" s="3" t="s">
         <v>315</v>
       </c>
     </row>
@@ -6307,7 +5803,7 @@
       <c r="A393">
         <v>426</v>
       </c>
-      <c r="C393" s="7" t="s">
+      <c r="C393" s="6" t="s">
         <v>319</v>
       </c>
     </row>
@@ -6357,7 +5853,7 @@
       <c r="A400">
         <v>433</v>
       </c>
-      <c r="B400" s="3" t="s">
+      <c r="B400" s="2" t="s">
         <v>324</v>
       </c>
       <c r="C400" t="s">
@@ -6377,11 +5873,11 @@
         <v>326</v>
       </c>
     </row>
-    <row r="403" s="1" customFormat="1" ht="13" customHeight="1" spans="1:3">
+    <row r="403" spans="1:3" s="1" customFormat="1" ht="13.05" customHeight="1">
       <c r="A403" s="1">
         <v>436</v>
       </c>
-      <c r="B403" s="8"/>
+      <c r="B403" s="7"/>
       <c r="C403" s="1" t="s">
         <v>327</v>
       </c>
@@ -6440,7 +5936,7 @@
       <c r="A411">
         <v>444</v>
       </c>
-      <c r="C411" s="7" t="s">
+      <c r="C411" s="6" t="s">
         <v>333</v>
       </c>
     </row>
@@ -6485,7 +5981,7 @@
       <c r="A417">
         <v>450</v>
       </c>
-      <c r="C417" s="7" t="s">
+      <c r="C417" s="6" t="s">
         <v>338</v>
       </c>
     </row>
@@ -6506,7 +6002,7 @@
       <c r="A420">
         <v>453</v>
       </c>
-      <c r="C420" s="7" t="s">
+      <c r="C420" s="6" t="s">
         <v>340</v>
       </c>
     </row>
@@ -6530,7 +6026,7 @@
       <c r="A423">
         <v>456</v>
       </c>
-      <c r="B423" s="3" t="s">
+      <c r="B423" s="2" t="s">
         <v>343</v>
       </c>
       <c r="C423" t="s">
@@ -6546,10 +6042,10 @@
       <c r="A425">
         <v>458</v>
       </c>
-      <c r="B425" s="3" t="s">
+      <c r="B425" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C425" s="10" t="s">
+      <c r="C425" t="s">
         <v>346</v>
       </c>
     </row>
@@ -6586,7 +6082,7 @@
       <c r="A430">
         <v>463</v>
       </c>
-      <c r="B430" s="3" t="s">
+      <c r="B430" s="2" t="s">
         <v>350</v>
       </c>
       <c r="C430" t="s">
@@ -6660,7 +6156,7 @@
       <c r="A440">
         <v>473</v>
       </c>
-      <c r="B440" s="3" t="s">
+      <c r="B440" s="2" t="s">
         <v>357</v>
       </c>
       <c r="C440" t="s">
@@ -6711,8 +6207,8 @@
       <c r="A446">
         <v>479</v>
       </c>
-      <c r="C446" t="s">
-        <v>364</v>
+      <c r="C446" s="12" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="447" spans="1:3">
@@ -6720,7 +6216,7 @@
         <v>480</v>
       </c>
       <c r="C447" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="448" spans="1:3">
@@ -6728,19 +6224,19 @@
         <v>481</v>
       </c>
       <c r="C448" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="449" s="1" customFormat="1" spans="1:5">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5" s="1" customFormat="1">
       <c r="A449" s="1">
         <v>482</v>
       </c>
-      <c r="B449" s="8"/>
+      <c r="B449" s="7"/>
       <c r="C449" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="E449" s="1" t="s">
         <v>367</v>
-      </c>
-      <c r="E449" s="1" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="450" spans="1:5">
@@ -6748,7 +6244,7 @@
         <v>483</v>
       </c>
       <c r="C450" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="451" spans="1:5">
@@ -6756,7 +6252,7 @@
         <v>484</v>
       </c>
       <c r="C451" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="452" spans="1:5">
@@ -6764,7 +6260,7 @@
         <v>485</v>
       </c>
       <c r="C452" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="453" spans="1:5">
@@ -6776,19 +6272,19 @@
       <c r="A454">
         <v>487</v>
       </c>
-      <c r="B454" s="3" t="s">
+      <c r="B454" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C454" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="455" spans="1:5">
       <c r="A455">
         <v>488</v>
       </c>
-      <c r="B455" s="3" t="s">
-        <v>373</v>
+      <c r="B455" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="C455" t="s">
         <v>67</v>
@@ -6803,11 +6299,11 @@
       <c r="A457">
         <v>490</v>
       </c>
-      <c r="B457" s="3" t="s">
+      <c r="B457" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C457" t="s">
         <v>374</v>
-      </c>
-      <c r="C457" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="458" spans="1:5">
@@ -6820,7 +6316,7 @@
         <v>492</v>
       </c>
       <c r="C459" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="460" spans="1:5">
@@ -6828,7 +6324,7 @@
         <v>493</v>
       </c>
       <c r="C460" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="461" spans="1:5">
@@ -6836,7 +6332,7 @@
         <v>494</v>
       </c>
       <c r="C461" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="462" spans="1:5">
@@ -6849,14 +6345,14 @@
         <v>496</v>
       </c>
       <c r="C463" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="464" spans="1:5">
       <c r="A464">
         <v>497</v>
       </c>
-      <c r="C464" s="5">
+      <c r="C464" s="4">
         <v>200</v>
       </c>
     </row>
@@ -6865,7 +6361,7 @@
         <v>498</v>
       </c>
       <c r="C465" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="466" spans="1:3">
@@ -6878,7 +6374,7 @@
         <v>500</v>
       </c>
       <c r="C467" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="468" spans="1:3">
@@ -6886,7 +6382,7 @@
         <v>501</v>
       </c>
       <c r="C468" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="469" spans="1:3">
@@ -6904,21 +6400,21 @@
         <v>504</v>
       </c>
     </row>
-    <row r="472" s="1" customFormat="1" spans="1:3">
+    <row r="472" spans="1:3" s="1" customFormat="1">
       <c r="A472" s="1">
         <v>505</v>
       </c>
-      <c r="B472" s="8"/>
-      <c r="C472" s="11" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="473" ht="28.5" spans="1:3">
+      <c r="B472" s="7"/>
+      <c r="C472" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" ht="28.8">
       <c r="A473">
         <v>506</v>
       </c>
-      <c r="C473" s="4" t="s">
-        <v>384</v>
+      <c r="C473" s="3" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="474" spans="1:3">
@@ -6926,7 +6422,7 @@
         <v>507</v>
       </c>
       <c r="C474" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="475" spans="1:3">
@@ -6934,7 +6430,7 @@
         <v>508</v>
       </c>
       <c r="C475" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="476" spans="1:3">
@@ -6942,18 +6438,18 @@
         <v>509</v>
       </c>
       <c r="C476" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="477" spans="1:3">
       <c r="A477">
         <v>510</v>
       </c>
-      <c r="B477" s="12" t="s">
+      <c r="B477" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="C477" s="6" t="s">
         <v>388</v>
-      </c>
-      <c r="C477" s="7" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="478" spans="1:3">
@@ -6961,7 +6457,7 @@
         <v>511</v>
       </c>
       <c r="C478" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="479" spans="1:3">
@@ -6984,7 +6480,7 @@
         <v>515</v>
       </c>
       <c r="C482" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="483" spans="1:3">
@@ -6996,11 +6492,11 @@
       <c r="A484">
         <v>517</v>
       </c>
-      <c r="B484" s="3" t="s">
+      <c r="B484" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C484" t="s">
         <v>392</v>
-      </c>
-      <c r="C484" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="485" spans="1:3">
@@ -7008,15 +6504,15 @@
         <v>518</v>
       </c>
     </row>
-    <row r="486" s="1" customFormat="1" spans="1:3">
+    <row r="486" spans="1:3" s="1" customFormat="1">
       <c r="A486" s="1">
         <v>519</v>
       </c>
-      <c r="B486" s="13" t="s">
+      <c r="B486" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C486" s="1" t="s">
         <v>394</v>
-      </c>
-      <c r="C486" s="11" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="487" spans="1:3">
@@ -7024,7 +6520,7 @@
         <v>520</v>
       </c>
       <c r="C487" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="488" spans="1:3">
@@ -7032,7 +6528,7 @@
         <v>521</v>
       </c>
       <c r="C488" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="489" spans="1:3">
@@ -7040,13 +6536,13 @@
         <v>522</v>
       </c>
     </row>
-    <row r="490" s="1" customFormat="1" spans="1:3">
+    <row r="490" spans="1:3" s="1" customFormat="1">
       <c r="A490" s="1">
         <v>523</v>
       </c>
-      <c r="B490" s="8"/>
+      <c r="B490" s="7"/>
       <c r="C490" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="491" spans="1:3">
@@ -7054,29 +6550,29 @@
         <v>524</v>
       </c>
       <c r="C491" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="492" spans="1:3">
       <c r="A492">
         <v>525</v>
       </c>
-      <c r="B492" s="3" t="s">
+      <c r="B492" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C492" t="s">
         <v>400</v>
       </c>
-      <c r="C492" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="493" s="1" customFormat="1" spans="1:3">
+    </row>
+    <row r="493" spans="1:3" s="1" customFormat="1">
       <c r="A493" s="1">
         <v>526</v>
       </c>
-      <c r="B493" s="8" t="s">
+      <c r="B493" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="C493" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="C493" s="1" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="494" spans="1:3">
@@ -7084,7 +6580,7 @@
         <v>527</v>
       </c>
       <c r="C494" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="495" spans="1:3">
@@ -7092,7 +6588,7 @@
         <v>528</v>
       </c>
       <c r="C495" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="496" spans="1:3">
@@ -7100,16 +6596,16 @@
         <v>529</v>
       </c>
       <c r="C496" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" s="1" customFormat="1">
+      <c r="A497" s="1">
+        <v>530</v>
+      </c>
+      <c r="B497" s="7"/>
+      <c r="C497" s="8" t="s">
         <v>406</v>
-      </c>
-    </row>
-    <row r="497" s="2" customFormat="1" spans="1:3">
-      <c r="A497" s="2">
-        <v>530</v>
-      </c>
-      <c r="B497" s="14"/>
-      <c r="C497" s="9" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="498" spans="1:3">
@@ -7117,18 +6613,18 @@
         <v>531</v>
       </c>
       <c r="C498" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="499" spans="1:3">
       <c r="A499">
         <v>532</v>
       </c>
-      <c r="B499" s="3" t="s">
+      <c r="B499" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C499" t="s">
         <v>409</v>
-      </c>
-      <c r="C499" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="500" spans="1:3">
@@ -7141,15 +6637,15 @@
         <v>534</v>
       </c>
       <c r="C501" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="502" spans="1:3">
       <c r="A502">
         <v>535</v>
       </c>
-      <c r="C502" s="7" t="s">
-        <v>412</v>
+      <c r="C502" s="6" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="503" spans="1:3">
@@ -7157,7 +6653,7 @@
         <v>536</v>
       </c>
       <c r="C503" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="504" spans="1:3">
@@ -7165,7 +6661,7 @@
         <v>537</v>
       </c>
       <c r="C504" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="505" spans="1:3">
@@ -7173,7 +6669,7 @@
         <v>538</v>
       </c>
       <c r="C505" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="506" spans="1:3">
@@ -7206,23 +6702,23 @@
         <v>544</v>
       </c>
       <c r="C511" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="512" spans="1:3">
       <c r="A512">
         <v>545</v>
       </c>
-      <c r="C512" s="7" t="s">
-        <v>417</v>
+      <c r="C512" s="6" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="513" spans="1:3">
       <c r="A513">
         <v>546</v>
       </c>
-      <c r="C513" s="7" t="s">
-        <v>418</v>
+      <c r="C513" s="6" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="514" spans="1:3">
@@ -7230,7 +6726,7 @@
         <v>547</v>
       </c>
       <c r="C514" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="515" spans="1:3">
@@ -7238,7 +6734,7 @@
         <v>548</v>
       </c>
       <c r="C515" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="516" spans="1:3">
@@ -7256,7 +6752,7 @@
         <v>551</v>
       </c>
       <c r="C518" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="519" spans="1:3">
@@ -7269,15 +6765,15 @@
         <v>553</v>
       </c>
       <c r="C520" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="521" spans="1:3">
       <c r="A521">
         <v>554</v>
       </c>
-      <c r="C521" s="7" t="s">
-        <v>423</v>
+      <c r="C521" s="6" t="s">
+        <v>422</v>
       </c>
     </row>
     <row r="522" spans="1:3">
@@ -7285,7 +6781,7 @@
         <v>555</v>
       </c>
       <c r="C522" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="523" spans="1:3">
@@ -7293,7 +6789,7 @@
         <v>556</v>
       </c>
       <c r="C523" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="524" spans="1:3">
@@ -7301,7 +6797,7 @@
         <v>557</v>
       </c>
       <c r="C524" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="525" spans="1:3">
@@ -7309,7 +6805,7 @@
         <v>558</v>
       </c>
       <c r="C525" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="526" spans="1:3">
@@ -7317,7 +6813,7 @@
         <v>559</v>
       </c>
       <c r="C526" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="527" spans="1:3">
@@ -7325,7 +6821,7 @@
         <v>560</v>
       </c>
       <c r="C527" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="528" spans="1:3">
@@ -7338,7 +6834,7 @@
         <v>562</v>
       </c>
       <c r="C529" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="530" spans="1:3">
@@ -7346,7 +6842,7 @@
         <v>563</v>
       </c>
       <c r="C530" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="531" spans="1:3">
@@ -7354,7 +6850,7 @@
         <v>564</v>
       </c>
       <c r="C531" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="532" spans="1:3">
@@ -7367,7 +6863,7 @@
         <v>566</v>
       </c>
       <c r="C533" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="534" spans="1:3">
@@ -7385,7 +6881,7 @@
         <v>569</v>
       </c>
       <c r="C536" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="537" spans="1:3">
@@ -7393,7 +6889,7 @@
         <v>570</v>
       </c>
       <c r="C537" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="538" spans="1:3">
@@ -7401,7 +6897,7 @@
         <v>571</v>
       </c>
       <c r="C538" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="539" spans="1:3">
@@ -7414,7 +6910,7 @@
         <v>573</v>
       </c>
       <c r="C540" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="541" spans="1:3">
@@ -7422,7 +6918,7 @@
         <v>574</v>
       </c>
       <c r="C541" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="542" spans="1:3">
@@ -7435,7 +6931,7 @@
         <v>576</v>
       </c>
       <c r="C543" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="544" spans="1:3">
@@ -7447,28 +6943,28 @@
       <c r="A545">
         <v>578</v>
       </c>
-      <c r="B545" s="12" t="s">
-        <v>440</v>
+      <c r="B545" s="9" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="546" spans="1:5">
       <c r="A546">
         <v>579</v>
       </c>
-      <c r="C546" s="5" t="s">
+      <c r="C546" s="4" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="547" spans="1:5" s="1" customFormat="1">
+      <c r="A547" s="1">
+        <v>580</v>
+      </c>
+      <c r="B547" s="7"/>
+      <c r="C547" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="E547" s="1" t="s">
         <v>441</v>
-      </c>
-    </row>
-    <row r="547" s="2" customFormat="1" spans="1:5">
-      <c r="A547" s="2">
-        <v>580</v>
-      </c>
-      <c r="B547" s="14"/>
-      <c r="C547" s="11" t="s">
-        <v>442</v>
-      </c>
-      <c r="E547" s="11" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="548" spans="1:5">
@@ -7501,16 +6997,16 @@
         <v>586</v>
       </c>
       <c r="C553" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="554" s="1" customFormat="1" spans="1:5">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="554" spans="1:5" s="1" customFormat="1">
       <c r="A554" s="1">
         <v>587</v>
       </c>
-      <c r="B554" s="8"/>
+      <c r="B554" s="7"/>
       <c r="C554" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="555" spans="1:5">
@@ -7523,7 +7019,7 @@
         <v>589</v>
       </c>
       <c r="C556" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="557" spans="1:5">
@@ -7531,7 +7027,7 @@
         <v>590</v>
       </c>
       <c r="C557" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="558" spans="1:5">
@@ -7544,7 +7040,7 @@
         <v>592</v>
       </c>
       <c r="C559" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="560" spans="1:5">
@@ -7552,18 +7048,18 @@
         <v>593</v>
       </c>
       <c r="C560" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="561" spans="1:3">
       <c r="A561">
         <v>594</v>
       </c>
-      <c r="B561" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="C561" s="16" t="s">
-        <v>451</v>
+      <c r="B561" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C561" s="11" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="562" spans="1:3">
@@ -7580,11 +7076,11 @@
       <c r="A564">
         <v>597</v>
       </c>
-      <c r="B564" s="3" t="s">
-        <v>452</v>
+      <c r="B564" s="2" t="s">
+        <v>450</v>
       </c>
       <c r="C564" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="565" spans="1:3">
@@ -7592,7 +7088,7 @@
         <v>598</v>
       </c>
       <c r="C565" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="566" spans="1:3">
@@ -7600,7 +7096,7 @@
         <v>599</v>
       </c>
       <c r="C566" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="567" spans="1:3">
@@ -7618,7 +7114,7 @@
         <v>602</v>
       </c>
       <c r="C569" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="570" spans="1:3">
@@ -7651,7 +7147,7 @@
         <v>608</v>
       </c>
       <c r="C575" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="576" spans="1:3">
@@ -7659,7 +7155,7 @@
         <v>609</v>
       </c>
       <c r="C576" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="577" spans="1:5">
@@ -7667,16 +7163,16 @@
         <v>610</v>
       </c>
     </row>
-    <row r="578" s="1" customFormat="1" spans="1:5">
+    <row r="578" spans="1:5" s="1" customFormat="1">
       <c r="A578" s="1">
         <v>611</v>
       </c>
-      <c r="B578" s="8"/>
-      <c r="C578" s="9" t="s">
-        <v>459</v>
+      <c r="B578" s="7"/>
+      <c r="C578" s="8" t="s">
+        <v>457</v>
       </c>
       <c r="E578" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="579" spans="1:5">
@@ -7684,7 +7180,7 @@
         <v>612</v>
       </c>
       <c r="C579" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="580" spans="1:5">
@@ -7702,7 +7198,7 @@
         <v>615</v>
       </c>
       <c r="C582" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="583" spans="1:5">
@@ -7715,7 +7211,7 @@
         <v>617</v>
       </c>
       <c r="C584" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="585" spans="1:5">
@@ -7723,15 +7219,16 @@
         <v>618</v>
       </c>
       <c r="C585" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="586" spans="1:5">
-      <c r="A586">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="586" spans="1:5" s="1" customFormat="1">
+      <c r="A586" s="1">
         <v>619</v>
       </c>
-      <c r="C586" t="s">
-        <v>464</v>
+      <c r="B586" s="7"/>
+      <c r="C586" s="17" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="587" spans="1:5">
@@ -7739,7 +7236,7 @@
         <v>620</v>
       </c>
       <c r="C587" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="588" spans="1:5">
@@ -7747,7 +7244,7 @@
         <v>621</v>
       </c>
       <c r="C588" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="589" spans="1:5">
@@ -7755,7 +7252,7 @@
         <v>622</v>
       </c>
       <c r="C589" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="590" spans="1:5">
@@ -7763,7 +7260,7 @@
         <v>623</v>
       </c>
       <c r="C590" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="591" spans="1:5">
@@ -7784,26 +7281,26 @@
         <v>626</v>
       </c>
       <c r="C593" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="594" spans="1:3">
       <c r="A594">
         <v>627</v>
       </c>
-      <c r="B594" s="3" t="s">
-        <v>470</v>
+      <c r="B594" s="2" t="s">
+        <v>467</v>
       </c>
       <c r="C594" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="595" spans="1:3">
       <c r="A595">
         <v>628</v>
       </c>
-      <c r="C595" t="s">
-        <v>472</v>
+      <c r="C595" s="12" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="596" spans="1:3">
@@ -7811,7 +7308,7 @@
         <v>629</v>
       </c>
       <c r="C596" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
     <row r="597" spans="1:3">
@@ -7819,23 +7316,27 @@
         <v>630</v>
       </c>
       <c r="C597" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="598" spans="1:3">
-      <c r="A598">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3" s="1" customFormat="1">
+      <c r="A598" s="1">
         <v>631</v>
       </c>
-      <c r="C598" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="599" spans="1:3">
-      <c r="A599">
+      <c r="B598" s="7"/>
+      <c r="C598" s="13" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3" s="1" customFormat="1">
+      <c r="A599" s="1">
         <v>632</v>
       </c>
-      <c r="C599" s="7" t="s">
-        <v>476</v>
+      <c r="B599" s="16" t="s">
+        <v>519</v>
+      </c>
+      <c r="C599" s="13" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="600" spans="1:3">
@@ -7848,7 +7349,7 @@
         <v>634</v>
       </c>
       <c r="C601" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
     </row>
     <row r="602" spans="1:3">
@@ -7861,7 +7362,7 @@
         <v>636</v>
       </c>
       <c r="C603" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
     </row>
     <row r="604" spans="1:3">
@@ -7869,7 +7370,7 @@
         <v>637</v>
       </c>
       <c r="C604" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
     </row>
     <row r="605" spans="1:3">
@@ -7877,7 +7378,7 @@
         <v>638</v>
       </c>
       <c r="C605" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
     </row>
     <row r="606" spans="1:3">
@@ -7885,7 +7386,7 @@
         <v>639</v>
       </c>
       <c r="C606" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
     </row>
     <row r="607" spans="1:3">
@@ -7893,16 +7394,16 @@
         <v>640</v>
       </c>
       <c r="C607" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="608" s="1" customFormat="1" spans="1:3">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3" s="1" customFormat="1">
       <c r="A608" s="1">
         <v>641</v>
       </c>
-      <c r="B608" s="8"/>
-      <c r="C608" s="9" t="s">
-        <v>483</v>
+      <c r="B608" s="7"/>
+      <c r="C608" s="8" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="609" spans="1:3">
@@ -7910,7 +7411,7 @@
         <v>642</v>
       </c>
       <c r="C609" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
     </row>
     <row r="610" spans="1:3">
@@ -7918,15 +7419,15 @@
         <v>643</v>
       </c>
       <c r="C610" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="611" ht="42.75" spans="1:3">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3" ht="43.2">
       <c r="A611">
         <v>644</v>
       </c>
-      <c r="C611" s="4" t="s">
-        <v>486</v>
+      <c r="C611" s="3" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="612" spans="1:3">
@@ -7934,23 +7435,23 @@
         <v>645</v>
       </c>
       <c r="C612" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="613" spans="1:3">
       <c r="A613">
         <v>646</v>
       </c>
-      <c r="C613" s="7" t="s">
-        <v>488</v>
+      <c r="C613" s="6" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="614" spans="1:3">
       <c r="A614">
         <v>647</v>
       </c>
-      <c r="C614" s="7" t="s">
-        <v>489</v>
+      <c r="C614" s="6" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="615" spans="1:3">
@@ -7958,7 +7459,7 @@
         <v>648</v>
       </c>
       <c r="C615" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
     <row r="616" spans="1:3">
@@ -7966,7 +7467,7 @@
         <v>649</v>
       </c>
       <c r="C616" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
     </row>
     <row r="617" spans="1:3">
@@ -7974,7 +7475,7 @@
         <v>650</v>
       </c>
       <c r="C617" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
     </row>
     <row r="618" spans="1:3">
@@ -7982,18 +7483,18 @@
         <v>651</v>
       </c>
       <c r="C618" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
     </row>
     <row r="619" spans="1:3">
       <c r="A619">
         <v>652</v>
       </c>
-      <c r="B619" s="12" t="s">
-        <v>494</v>
+      <c r="B619" s="9" t="s">
+        <v>489</v>
       </c>
       <c r="C619" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
     </row>
     <row r="620" spans="1:3">
@@ -8001,7 +7502,7 @@
         <v>653</v>
       </c>
       <c r="C620" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
     </row>
     <row r="621" spans="1:3">
@@ -8009,7 +7510,7 @@
         <v>654</v>
       </c>
       <c r="C621" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
     </row>
     <row r="622" spans="1:3">
@@ -8017,27 +7518,27 @@
         <v>655</v>
       </c>
       <c r="C622" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="623" ht="71.25" spans="1:3">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3" ht="72">
       <c r="A623">
         <v>656</v>
       </c>
-      <c r="B623" s="12" t="s">
-        <v>499</v>
-      </c>
-      <c r="C623" s="4" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="624" s="1" customFormat="1" spans="1:3">
+      <c r="B623" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="C623" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="624" spans="1:3" s="1" customFormat="1">
       <c r="A624" s="1">
         <v>657</v>
       </c>
-      <c r="B624" s="8"/>
-      <c r="C624" s="9" t="s">
-        <v>501</v>
+      <c r="B624" s="7"/>
+      <c r="C624" s="8" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="625" spans="1:3">
@@ -8045,22 +7546,22 @@
         <v>658</v>
       </c>
       <c r="C625" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="626" spans="1:3">
       <c r="A626">
         <v>659</v>
       </c>
-      <c r="C626" s="7" t="s">
-        <v>503</v>
+      <c r="C626" s="6" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="627" spans="1:3">
       <c r="A627">
         <v>660</v>
       </c>
-      <c r="C627" s="5">
+      <c r="C627" s="4">
         <v>7</v>
       </c>
     </row>
@@ -8069,18 +7570,18 @@
         <v>661</v>
       </c>
       <c r="C628" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
     </row>
     <row r="629" spans="1:3">
       <c r="A629">
         <v>662</v>
       </c>
-      <c r="B629" s="3" t="s">
-        <v>505</v>
+      <c r="B629" s="2" t="s">
+        <v>500</v>
       </c>
       <c r="C629" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
     </row>
     <row r="630" spans="1:3">
@@ -8088,18 +7589,18 @@
         <v>663</v>
       </c>
       <c r="C630" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
     </row>
     <row r="631" spans="1:3">
       <c r="A631">
         <v>664</v>
       </c>
-      <c r="B631" s="3" t="s">
-        <v>508</v>
+      <c r="B631" s="2" t="s">
+        <v>503</v>
       </c>
       <c r="C631" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
     </row>
     <row r="632" spans="1:3">
@@ -8107,7 +7608,7 @@
         <v>665</v>
       </c>
       <c r="C632" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
     </row>
     <row r="633" spans="1:3">
@@ -8120,7 +7621,7 @@
         <v>667</v>
       </c>
       <c r="C634" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
     </row>
     <row r="635" spans="1:3">
@@ -8133,7 +7634,7 @@
         <v>669</v>
       </c>
       <c r="C636" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
     </row>
     <row r="637" spans="1:3">
@@ -8161,7 +7662,7 @@
         <v>674</v>
       </c>
       <c r="E641" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="642" spans="1:5">
@@ -8189,18 +7690,18 @@
         <v>679</v>
       </c>
       <c r="C646" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
     </row>
     <row r="647" spans="1:5">
       <c r="A647">
         <v>680</v>
       </c>
-      <c r="B647" s="12" t="s">
-        <v>514</v>
-      </c>
-      <c r="C647" s="7" t="s">
-        <v>515</v>
+      <c r="B647" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="C647" s="6" t="s">
+        <v>510</v>
       </c>
     </row>
     <row r="648" spans="1:5">
@@ -8212,28 +7713,31 @@
       <c r="A649">
         <v>682</v>
       </c>
-      <c r="B649" s="12" t="s">
-        <v>516</v>
-      </c>
-      <c r="C649" s="7" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="650" s="1" customFormat="1" spans="1:5">
+      <c r="B649" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="C649" s="6" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="650" spans="1:5" s="1" customFormat="1">
       <c r="A650" s="1">
         <v>683</v>
       </c>
-      <c r="B650" s="13" t="s">
-        <v>518</v>
-      </c>
-      <c r="C650" s="9" t="s">
-        <v>519</v>
+      <c r="B650" s="10" t="s">
+        <v>513</v>
+      </c>
+      <c r="C650" s="13" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="651" spans="1:5">
       <c r="A651">
         <v>684</v>
       </c>
+      <c r="C651" s="14" t="s">
+        <v>517</v>
+      </c>
     </row>
     <row r="652" spans="1:5">
       <c r="A652">
@@ -8242,6 +7746,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/MC 685.xlsx
+++ b/MC 685.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\testing tools\ccnp_mc_test_online\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F41CAA-C65F-4362-9A77-6B0CF9A96068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF182984-A6BE-44F2-B13E-61D0910F7743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="545">
   <si>
     <t>Index</t>
   </si>
@@ -46,9 +46,6 @@
     <t>no the summary route is not generated</t>
   </si>
   <si>
-    <t>Change sequence 10</t>
-  </si>
-  <si>
     <t>participating BFD endpoints</t>
   </si>
   <si>
@@ -88,15 +85,6 @@
     <t>Set the administrative distance 100</t>
   </si>
   <si>
-    <t>weight value in another neighbor</t>
-  </si>
-  <si>
-    <t>ibgp 2</t>
-  </si>
-  <si>
-    <t>mode tunnel to mode transport, 0.0.0.0</t>
-  </si>
-  <si>
     <t>unique VPNv4 address</t>
   </si>
   <si>
@@ -112,15 +100,9 @@
     <t>Standard pings</t>
   </si>
   <si>
-    <t>control-plane</t>
-  </si>
-  <si>
     <t>flash</t>
   </si>
   <si>
-    <t>keyword localtime is not defined</t>
-  </si>
-  <si>
     <t>aaa new-model configuration</t>
   </si>
   <si>
@@ -184,9 +166,6 @@
     <t>Resource Reservation Protocol</t>
   </si>
   <si>
-    <t>OSPF and ISIS</t>
-  </si>
-  <si>
     <t>authentication port</t>
   </si>
   <si>
@@ -202,18 +181,6 @@
     <t>equal or longer prefix</t>
   </si>
   <si>
-    <t>SNMPv2c</t>
-  </si>
-  <si>
-    <t>Community String, no encryption, read-only</t>
-  </si>
-  <si>
-    <t>SNMPv3</t>
-  </si>
-  <si>
-    <t>username and password, authentiation, privileged</t>
-  </si>
-  <si>
     <t>Label Switch Router</t>
   </si>
   <si>
@@ -274,9 +241,6 @@
     <t>192.168.8.0/21</t>
   </si>
   <si>
-    <t xml:space="preserve">both options include access list 100 </t>
-  </si>
-  <si>
     <t>0.0.0.0   spokes</t>
   </si>
   <si>
@@ -298,12 +262,6 @@
     <t>both options include IP address and default gateway</t>
   </si>
   <si>
-    <t>E1 and E2 access list</t>
-  </si>
-  <si>
-    <t>Add the control disable option</t>
-  </si>
-  <si>
     <t>Fix IP Event Dampening</t>
   </si>
   <si>
@@ -325,9 +283,6 @@
     <t>the same tag on R2 to deny</t>
   </si>
   <si>
-    <t>overlapping IP addresses, private routing table</t>
-  </si>
-  <si>
     <t xml:space="preserve">172.16.1.0/24 is not redistributed </t>
   </si>
   <si>
@@ -352,12 +307,6 @@
     <t>sequence number 5 from the prefix list</t>
   </si>
   <si>
-    <t>Default metrics are not configured</t>
-  </si>
-  <si>
-    <t>DHCP option 66</t>
-  </si>
-  <si>
     <t>IPsec + mGRE</t>
   </si>
   <si>
@@ -379,9 +328,6 @@
     <t>ip helper-address &lt;dhcp server ip&gt;</t>
   </si>
   <si>
-    <t>both options include VPN</t>
-  </si>
-  <si>
     <t>eq 23, Ethernet0/3</t>
   </si>
   <si>
@@ -419,9 +365,6 @@
   </si>
   <si>
     <t>All, 1000</t>
-  </si>
-  <si>
-    <t>LA-message-digit,LA-message-digit</t>
   </si>
   <si>
     <t xml:space="preserve">traffic-filter </t>
@@ -495,9 +438,6 @@
     <t>weekdays 8:00 to 16:30</t>
   </si>
   <si>
-    <t>feasible distance greater than the reported distance</t>
-  </si>
-  <si>
     <t>area range command on the ABR</t>
   </si>
   <si>
@@ -543,15 +483,9 @@
     <t xml:space="preserve">10.1.100.10  configure ip summary </t>
   </si>
   <si>
-    <t>changed to 172.16.0.0/24</t>
-  </si>
-  <si>
     <t>Remove sequence 20 and add it back</t>
   </si>
   <si>
-    <t>5 permit icmp host 10.10.10.1 host 10.66.66.66</t>
-  </si>
-  <si>
     <t>Layer 2 and Layer 3</t>
   </si>
   <si>
@@ -588,9 +522,6 @@
     <t>route-reflector-client</t>
   </si>
   <si>
-    <t xml:space="preserve">Modify the uRPF </t>
-  </si>
-  <si>
     <t>ipv6 address autoconfig</t>
   </si>
   <si>
@@ -699,9 +630,6 @@
     <t>label switch path       available</t>
   </si>
   <si>
-    <t>minimizes DoS attacks</t>
-  </si>
-  <si>
     <t>Destination Guard</t>
   </si>
   <si>
@@ -767,9 +695,6 @@
     <t>R2 and R3</t>
   </si>
   <si>
-    <t>in direction for area 20</t>
-  </si>
-  <si>
     <t>up 60 down 60</t>
   </si>
   <si>
@@ -782,9 +707,6 @@
     <t xml:space="preserve">no ip next-hop-self </t>
   </si>
   <si>
-    <t>RD, MP-BGP</t>
-  </si>
-  <si>
     <t>Disable split horizon</t>
   </si>
   <si>
@@ -872,12 +794,6 @@
     <t>ip helper-address</t>
   </si>
   <si>
-    <t xml:space="preserve">redistribtute command toward a domain </t>
-  </si>
-  <si>
-    <t>process 1, and remove process 10 from the global configuration</t>
-  </si>
-  <si>
     <t>consistent rate</t>
   </si>
   <si>
@@ -1063,32 +979,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>index persistence</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, permit </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>10.0.0.0/8 le 32</t>
     </r>
   </si>
   <si>
@@ -1794,21 +1684,6 @@
   </si>
   <si>
     <t>ospf network point-to-point</t>
-  </si>
-  <si>
-    <r>
-      <t>no auto-summary c</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ommand</t>
-    </r>
   </si>
   <si>
     <t>Replace the faulty cable</t>
@@ -2190,9 +2065,6 @@
     </r>
   </si>
   <si>
-    <t>Permit 10.0.1.0/24 address</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -2287,29 +2159,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Remove</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> the distance 10</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>10.1.1.0 0.0.0.255</t>
     </r>
     <r>
@@ -2399,6 +2248,1162 @@
         <scheme val="minor"/>
       </rPr>
       <t>255.255.192.0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>redistribtute</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> command toward </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">a domain </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SNMP</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>v2c</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SNMP</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>v3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Community</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> String, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>no encryption</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>read-only</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CNR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">sername and password, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">uthentiation, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rivileged</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>uap</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>mark</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Permit </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10.0.1.0/24 address</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>process 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>remove</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> process 10 from the global configuration</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0.0.0.0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Default metrics</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> are not configured</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">两个 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">disable-connected-check </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MP-BGP</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">components，MPLS Layer 3 VPN </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>weight value</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>200</t>
+    </r>
+  </si>
+  <si>
+    <t>LDP autoconfiguration</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OSPF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ISIS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">R1 based on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ISE</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">keyword </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>localtime</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is not defined</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">SanFrancisco and Boston </t>
+  </si>
+  <si>
+    <t>network management system tools</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>not met, changed to 172</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.16.0.0/24</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Partial updates</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Scaling</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">minimizes </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DoS attacks</t>
+    </r>
+  </si>
+  <si>
+    <t>没有only的选项</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RD，64-bit route distinguisher </t>
+  </si>
+  <si>
+    <t>purposes， IPv4 and VPNv4 address-family configurations</t>
+  </si>
+  <si>
+    <t>Change sequence 10， from permit to deny</t>
+  </si>
+  <si>
+    <t>两个选项包含LA, message-digest</t>
+  </si>
+  <si>
+    <t>floating static route</t>
+  </si>
+  <si>
+    <t>BRANCH， 192.168.100.1</t>
+  </si>
+  <si>
+    <t>CLIENT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove sequence 10 </t>
+  </si>
+  <si>
+    <t>cannot Telnet </t>
+  </si>
+  <si>
+    <r>
+      <t>seq 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, permit </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10.0.0.0/8 le 32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DHCP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> option </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>66</t>
+    </r>
+  </si>
+  <si>
+    <t>DHCP server for Cisco IP phones</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TFTP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SNMP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> policy-map </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>control-plane</t>
+    </r>
+  </si>
+  <si>
+    <t>Remove the distance 10</t>
+  </si>
+  <si>
+    <r>
+      <t>选项包含</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>customer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VPN</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Add the</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> control disable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> option</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">both options include </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">access list 100 </t>
+    </r>
+  </si>
+  <si>
+    <t>poison reverse</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>overlapping</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> IP addresses, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>private routing table</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>E1 and E2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>access list</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>distribute-list</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 10 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>out</t>
+    </r>
+  </si>
+  <si>
+    <t>maximum-paths ibgp 2</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">from </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>strict to loose</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Apply CoPP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>control plane interface</t>
+    </r>
+  </si>
+  <si>
+    <t>syslog level 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downstream node signals </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>in</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>area 20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>feasible distance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>greater</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> than the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>reported distance</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">5 permit icmp host </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10.10.10.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> host </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10.66.66.66</t>
     </r>
   </si>
 </sst>
@@ -2406,12 +3411,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2444,6 +3456,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF31333F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2471,7 +3489,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2486,26 +3504,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2788,7 +3823,7 @@
     <col min="3" max="3" width="51.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2801,8 +3836,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="18" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="3">
         <v>3</v>
       </c>
@@ -2810,15 +3848,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="D3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>6</v>
       </c>
@@ -2826,7 +3867,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>7</v>
       </c>
@@ -2834,92 +3875,95 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>8</v>
       </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="C6" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>14</v>
       </c>
-      <c r="C11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="C11" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>17</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>19</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2927,7 +3971,7 @@
         <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2935,39 +3979,51 @@
         <v>21</v>
       </c>
       <c r="C18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" s="1" customFormat="1">
+      <c r="A19" s="1">
+        <v>23</v>
+      </c>
+      <c r="B19" s="7"/>
+      <c r="C19" s="8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19">
-        <v>23</v>
-      </c>
-      <c r="C19" t="s">
-        <v>21</v>
+      <c r="D19" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20">
         <v>24</v>
       </c>
-      <c r="C20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21">
+      <c r="C20" s="18" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="1" customFormat="1">
+      <c r="A21" s="1">
         <v>25</v>
       </c>
-      <c r="C21" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22">
+      <c r="B21" s="7"/>
+      <c r="C21" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="1" customFormat="1">
+      <c r="A22" s="1">
         <v>26</v>
       </c>
-      <c r="C22" t="s">
-        <v>24</v>
+      <c r="B22" s="7"/>
+      <c r="C22" s="20" t="s">
+        <v>499</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2975,7 +4031,7 @@
         <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2983,7 +4039,7 @@
         <v>28</v>
       </c>
       <c r="C24" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2991,21 +4047,24 @@
         <v>38</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" s="1" customFormat="1">
+      <c r="A26" s="1">
         <v>44</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" t="s">
-        <v>30</v>
+      <c r="B26" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>528</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -3013,26 +4072,27 @@
         <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28">
         <v>51</v>
       </c>
-      <c r="C28" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28">
+      <c r="C28" s="18" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" s="1" customFormat="1">
+      <c r="A29" s="1">
+        <v>57</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29">
-        <v>57</v>
-      </c>
-      <c r="C29" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -3040,18 +4100,19 @@
         <v>58</v>
       </c>
       <c r="C30" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" s="1" customFormat="1">
+      <c r="A31" s="1">
+        <v>59</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31" s="1">
         <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31">
-        <v>59</v>
-      </c>
-      <c r="C31" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -3059,417 +4120,369 @@
         <v>63</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>37</v>
-      </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="A33">
         <v>64</v>
       </c>
-      <c r="C33" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+      <c r="B33" s="19" t="s">
+        <v>510</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="A34">
         <v>65</v>
       </c>
       <c r="C34" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="A35">
         <v>68</v>
       </c>
       <c r="C35" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="A36">
         <v>69</v>
       </c>
-    </row>
-    <row r="37" spans="1:4">
+      <c r="C36" s="18" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="A37">
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:3">
       <c r="A38">
         <v>71</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:3">
       <c r="A39">
         <v>72</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C39" t="s">
-        <v>42</v>
-      </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="A40">
         <v>73</v>
       </c>
       <c r="C40" t="s">
-        <v>43</v>
-      </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="A41">
         <v>74</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:3">
       <c r="A42">
         <v>75</v>
       </c>
       <c r="C42" t="s">
-        <v>44</v>
-      </c>
-      <c r="D42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="A43">
         <v>76</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:3">
       <c r="A44">
         <v>77</v>
       </c>
       <c r="C44" t="s">
-        <v>45</v>
-      </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="A45">
         <v>78</v>
       </c>
       <c r="C45" t="s">
-        <v>46</v>
-      </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
       <c r="A46">
         <v>79</v>
       </c>
       <c r="C46" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47">
         <v>80</v>
       </c>
       <c r="C47" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48">
         <v>81</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:3">
       <c r="A49">
         <v>82</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:3">
       <c r="A50">
         <v>83</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:3">
       <c r="A51">
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:3">
       <c r="A52">
         <v>85</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:3">
       <c r="A53">
         <v>86</v>
       </c>
       <c r="C53" t="s">
-        <v>49</v>
-      </c>
-      <c r="D53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
       <c r="A54">
         <v>87</v>
       </c>
       <c r="C54" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55">
         <v>88</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:3">
       <c r="A56">
         <v>89</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:3">
       <c r="A57">
         <v>90</v>
       </c>
-      <c r="D57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
+    </row>
+    <row r="58" spans="1:3">
       <c r="A58">
         <v>91</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:3">
       <c r="A59">
         <v>92</v>
       </c>
-    </row>
-    <row r="60" spans="1:4">
+      <c r="C59" s="18" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
       <c r="A60">
         <v>93</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:3">
       <c r="A61">
         <v>94</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:3">
       <c r="A62">
         <v>95</v>
       </c>
       <c r="C62" t="s">
-        <v>51</v>
-      </c>
-      <c r="D62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
       <c r="A63">
         <v>96</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:3">
       <c r="A64">
         <v>97</v>
       </c>
       <c r="C64" t="s">
-        <v>52</v>
-      </c>
-      <c r="D64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
       <c r="A65">
         <v>98</v>
       </c>
       <c r="C65" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
       <c r="A66">
         <v>99</v>
       </c>
-      <c r="C66" t="s">
-        <v>54</v>
-      </c>
-      <c r="D66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
+      <c r="B66" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="C66" s="18" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
       <c r="A67">
         <v>100</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:3">
       <c r="A68">
         <v>101</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:3">
       <c r="A69">
         <v>102</v>
       </c>
       <c r="C69" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
       <c r="A70">
         <v>103</v>
       </c>
       <c r="C70" t="s">
-        <v>56</v>
-      </c>
-      <c r="D70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
       <c r="A71">
         <v>104</v>
       </c>
       <c r="C71" t="s">
-        <v>57</v>
-      </c>
-      <c r="D71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
       <c r="A72">
         <v>105</v>
       </c>
       <c r="C72" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
       <c r="A73">
         <v>106</v>
       </c>
       <c r="C73" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
       <c r="A74">
         <v>107</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C74" t="s">
-        <v>61</v>
-      </c>
-      <c r="D74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
+      <c r="B74" s="19" t="s">
+        <v>492</v>
+      </c>
+      <c r="C74" s="18" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
       <c r="A75">
         <v>108</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C75" t="s">
-        <v>63</v>
-      </c>
-      <c r="D75">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
+      <c r="B75" s="19" t="s">
+        <v>493</v>
+      </c>
+      <c r="C75" s="18" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
       <c r="A76">
         <v>109</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C76" t="s">
-        <v>65</v>
-      </c>
-      <c r="D76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
       <c r="A77">
         <v>110</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C77" t="s">
-        <v>67</v>
-      </c>
-      <c r="D77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
       <c r="A78">
         <v>111</v>
       </c>
       <c r="C78" t="s">
-        <v>68</v>
-      </c>
-      <c r="D78">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
       <c r="A79">
         <v>112</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:3">
       <c r="A80">
         <v>113</v>
       </c>
       <c r="C80" t="s">
-        <v>69</v>
-      </c>
-      <c r="D80">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
       <c r="A81">
         <v>114</v>
       </c>
       <c r="C81" t="s">
-        <v>70</v>
-      </c>
-      <c r="D81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
       <c r="A82">
         <v>115</v>
       </c>
@@ -3477,251 +4490,261 @@
         <v>90</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:3">
       <c r="A83">
         <v>116</v>
       </c>
       <c r="C83" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
       <c r="A84">
         <v>117</v>
       </c>
       <c r="C84" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
       <c r="A85">
         <v>118</v>
       </c>
       <c r="C85" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
       <c r="A86">
         <v>119</v>
       </c>
       <c r="C86" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
       <c r="A87">
         <v>120</v>
       </c>
       <c r="C87" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
       <c r="A88">
         <v>121</v>
       </c>
       <c r="C88" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
       <c r="A89">
         <v>122</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:3">
       <c r="A90">
         <v>123</v>
       </c>
       <c r="C90" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
       <c r="A91">
         <v>124</v>
       </c>
       <c r="C91" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
       <c r="A92">
         <v>125</v>
       </c>
       <c r="C92" t="s">
-        <v>79</v>
-      </c>
-      <c r="D92">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
       <c r="A93">
         <v>126</v>
       </c>
       <c r="C93" t="s">
-        <v>80</v>
-      </c>
-      <c r="D93">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
       <c r="A94">
         <v>127</v>
       </c>
-      <c r="C94" t="s">
-        <v>81</v>
-      </c>
-      <c r="D94">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
+      <c r="C94" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
       <c r="A95">
         <v>128</v>
       </c>
       <c r="C95" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
       <c r="A96">
         <v>129</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
+    <row r="97" spans="1:4">
       <c r="A97">
         <v>130</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
+    <row r="98" spans="1:4">
       <c r="A98">
         <v>131</v>
       </c>
       <c r="C98" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
       <c r="A99">
         <v>132</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
-      <c r="A100">
+    <row r="100" spans="1:4" s="1" customFormat="1">
+      <c r="A100" s="1">
         <v>133</v>
       </c>
-    </row>
-    <row r="101" spans="1:3">
-      <c r="A101">
+      <c r="B100" s="7"/>
+      <c r="C100" s="20" t="s">
+        <v>536</v>
+      </c>
+      <c r="D100" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" s="1" customFormat="1">
+      <c r="A101" s="1">
         <v>134</v>
       </c>
-      <c r="C101" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3">
+      <c r="B101" s="7"/>
+      <c r="C101" s="20" t="s">
+        <v>532</v>
+      </c>
+      <c r="D101" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
       <c r="A102">
         <v>135</v>
       </c>
       <c r="C102" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
       <c r="A103">
         <v>136</v>
       </c>
-      <c r="C103" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3">
+      <c r="C103" s="18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
       <c r="A104">
         <v>137</v>
       </c>
       <c r="C104" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
       <c r="A105">
         <v>138</v>
       </c>
     </row>
-    <row r="106" spans="1:3">
+    <row r="106" spans="1:4">
       <c r="A106">
         <v>139</v>
       </c>
       <c r="C106" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
       <c r="A107">
         <v>140</v>
       </c>
       <c r="C107" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
       <c r="A108">
         <v>141</v>
       </c>
       <c r="C108" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
       <c r="A109">
         <v>142</v>
       </c>
       <c r="C109" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3">
-      <c r="A110">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" s="1" customFormat="1">
+      <c r="A110" s="1">
         <v>143</v>
       </c>
-      <c r="C110" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3">
-      <c r="A111">
+      <c r="B110" s="7"/>
+      <c r="C110" s="20" t="s">
+        <v>535</v>
+      </c>
+      <c r="D110" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" s="1" customFormat="1">
+      <c r="A111" s="1">
         <v>144</v>
       </c>
-      <c r="C111" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3">
+      <c r="B111" s="7"/>
+      <c r="C111" s="20" t="s">
+        <v>531</v>
+      </c>
+      <c r="D111" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
       <c r="A112">
         <v>145</v>
       </c>
       <c r="C112" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
         <v>146</v>
       </c>
-      <c r="C113" t="s">
-        <v>95</v>
+      <c r="C113" s="6" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
         <v>147</v>
       </c>
-      <c r="C114" t="s">
-        <v>96</v>
+      <c r="C114" s="18" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -3729,7 +4752,7 @@
         <v>148</v>
       </c>
       <c r="C115" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -3737,7 +4760,7 @@
         <v>149</v>
       </c>
       <c r="C116" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -3750,7 +4773,7 @@
         <v>151</v>
       </c>
       <c r="C118" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -3758,15 +4781,15 @@
         <v>152</v>
       </c>
       <c r="C119" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
         <v>153</v>
       </c>
-      <c r="C120" t="s">
-        <v>101</v>
+      <c r="C120" s="18" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -3774,7 +4797,7 @@
         <v>154</v>
       </c>
       <c r="C121" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -3787,7 +4810,7 @@
         <v>156</v>
       </c>
       <c r="C123" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -3795,7 +4818,7 @@
         <v>157</v>
       </c>
       <c r="C124" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -3818,438 +4841,487 @@
         <v>161</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
+    <row r="129" spans="1:4">
       <c r="A129">
         <v>162</v>
       </c>
       <c r="C129" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
       <c r="A130">
         <v>163</v>
       </c>
       <c r="C130" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
       <c r="A131">
         <v>164</v>
       </c>
     </row>
-    <row r="132" spans="1:3">
+    <row r="132" spans="1:4">
       <c r="A132">
         <v>165</v>
       </c>
       <c r="C132" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
       <c r="A133">
         <v>166</v>
       </c>
       <c r="C133" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
       <c r="A134">
         <v>167</v>
       </c>
       <c r="C134" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
       <c r="A135">
         <v>168</v>
       </c>
-    </row>
-    <row r="136" spans="1:3">
-      <c r="A136">
+      <c r="C135" s="18" t="s">
+        <v>501</v>
+      </c>
+      <c r="D135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" s="1" customFormat="1">
+      <c r="A136" s="1">
         <v>169</v>
       </c>
-      <c r="C136" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3">
-      <c r="A137">
+      <c r="B136" s="7"/>
+      <c r="C136" s="20" t="s">
+        <v>500</v>
+      </c>
+      <c r="D136" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" s="1" customFormat="1">
+      <c r="A137" s="1">
         <v>170</v>
       </c>
-      <c r="C137" s="4">
-        <v>100.1</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3">
-      <c r="A138">
+      <c r="B137" s="21" t="s">
+        <v>519</v>
+      </c>
+      <c r="C137" s="23" t="s">
+        <v>520</v>
+      </c>
+      <c r="D137" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" s="1" customFormat="1">
+      <c r="A138" s="1">
         <v>171</v>
       </c>
-      <c r="C138" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3">
+      <c r="B138" s="21" t="s">
+        <v>526</v>
+      </c>
+      <c r="C138" s="20" t="s">
+        <v>525</v>
+      </c>
+      <c r="D138" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
       <c r="A139">
         <v>172</v>
       </c>
     </row>
-    <row r="140" spans="1:3">
+    <row r="140" spans="1:4">
       <c r="A140">
         <v>173</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="C140" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
       <c r="A141">
         <v>174</v>
       </c>
       <c r="C141" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
       <c r="A142">
         <v>175</v>
       </c>
       <c r="C142" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
       <c r="A143">
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:3">
+    <row r="144" spans="1:4">
       <c r="A144">
         <v>177</v>
       </c>
     </row>
-    <row r="145" spans="1:3">
+    <row r="145" spans="1:4">
       <c r="A145">
         <v>178</v>
       </c>
     </row>
-    <row r="146" spans="1:3">
+    <row r="146" spans="1:4">
       <c r="A146">
         <v>179</v>
       </c>
     </row>
-    <row r="147" spans="1:3">
+    <row r="147" spans="1:4">
       <c r="A147">
         <v>180</v>
       </c>
     </row>
-    <row r="148" spans="1:3">
-      <c r="A148">
+    <row r="148" spans="1:4" s="1" customFormat="1">
+      <c r="A148" s="1">
         <v>181</v>
       </c>
-    </row>
-    <row r="149" spans="1:3">
+      <c r="B148" s="7"/>
+      <c r="C148" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="D148" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
       <c r="A149">
         <v>182</v>
       </c>
     </row>
-    <row r="150" spans="1:3">
+    <row r="150" spans="1:4">
       <c r="A150">
         <v>183</v>
       </c>
     </row>
-    <row r="151" spans="1:3">
+    <row r="151" spans="1:4">
       <c r="A151">
         <v>184</v>
       </c>
     </row>
-    <row r="152" spans="1:3">
+    <row r="152" spans="1:4">
       <c r="A152">
         <v>185</v>
       </c>
     </row>
-    <row r="153" spans="1:3">
+    <row r="153" spans="1:4">
       <c r="A153">
         <v>186</v>
       </c>
     </row>
-    <row r="154" spans="1:3">
+    <row r="154" spans="1:4">
       <c r="A154">
         <v>187</v>
       </c>
     </row>
-    <row r="155" spans="1:3">
+    <row r="155" spans="1:4">
       <c r="A155">
         <v>188</v>
       </c>
     </row>
-    <row r="156" spans="1:3">
+    <row r="156" spans="1:4">
       <c r="A156">
         <v>189</v>
       </c>
-    </row>
-    <row r="157" spans="1:3">
+      <c r="B156" s="19" t="s">
+        <v>516</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="D156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
       <c r="A157">
         <v>190</v>
       </c>
     </row>
-    <row r="158" spans="1:3">
+    <row r="158" spans="1:4">
       <c r="A158">
         <v>191</v>
       </c>
     </row>
-    <row r="159" spans="1:3">
+    <row r="159" spans="1:4">
       <c r="A159">
         <v>192</v>
       </c>
       <c r="C159" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
       <c r="A160">
         <v>193</v>
       </c>
       <c r="C160" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
       <c r="A161">
         <v>194</v>
       </c>
       <c r="C161" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3">
-      <c r="A162">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" s="1" customFormat="1">
+      <c r="A162" s="1">
         <v>195</v>
       </c>
-      <c r="C162" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3">
+      <c r="B162" s="7"/>
+      <c r="C162" s="20" t="s">
+        <v>530</v>
+      </c>
+      <c r="D162" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
       <c r="A163">
         <v>196</v>
       </c>
     </row>
-    <row r="164" spans="1:3">
+    <row r="164" spans="1:4">
       <c r="A164">
         <v>197</v>
       </c>
       <c r="C164" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
       <c r="A165">
         <v>198</v>
       </c>
       <c r="C165" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
       <c r="A166">
         <v>199</v>
       </c>
       <c r="C166" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
       <c r="A167">
         <v>200</v>
       </c>
     </row>
-    <row r="168" spans="1:3">
+    <row r="168" spans="1:4">
       <c r="A168">
         <v>201</v>
       </c>
     </row>
-    <row r="169" spans="1:3">
+    <row r="169" spans="1:4">
       <c r="A169">
         <v>202</v>
       </c>
     </row>
-    <row r="170" spans="1:3">
+    <row r="170" spans="1:4">
       <c r="A170">
         <v>203</v>
       </c>
     </row>
-    <row r="171" spans="1:3">
+    <row r="171" spans="1:4">
       <c r="A171">
         <v>204</v>
       </c>
       <c r="C171" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4">
       <c r="A172">
         <v>205</v>
       </c>
       <c r="C172" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
       <c r="A173">
         <v>206</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C173" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
       <c r="A174">
         <v>207</v>
       </c>
     </row>
-    <row r="175" spans="1:3">
+    <row r="175" spans="1:4">
       <c r="A175">
         <v>208</v>
       </c>
     </row>
-    <row r="176" spans="1:3">
+    <row r="176" spans="1:4">
       <c r="A176">
         <v>209</v>
       </c>
     </row>
-    <row r="177" spans="1:3">
+    <row r="177" spans="1:4">
       <c r="A177">
         <v>210</v>
       </c>
       <c r="C177" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4">
       <c r="A178">
         <v>211</v>
       </c>
       <c r="C178" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4">
       <c r="A179">
         <v>212</v>
       </c>
       <c r="C179" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4">
       <c r="A180">
         <v>213</v>
       </c>
       <c r="C180" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4">
       <c r="A181">
         <v>214</v>
       </c>
       <c r="C181" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4">
       <c r="A182">
         <v>215</v>
       </c>
-      <c r="C182" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3">
-      <c r="A183">
+      <c r="B182" s="19" t="s">
+        <v>509</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" s="1" customFormat="1">
+      <c r="A183" s="1">
         <v>216</v>
       </c>
-      <c r="C183" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3">
+      <c r="B183" s="7"/>
+      <c r="C183" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="D183" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4">
       <c r="A184">
         <v>217</v>
       </c>
     </row>
-    <row r="185" spans="1:3">
+    <row r="185" spans="1:4">
       <c r="A185">
         <v>218</v>
       </c>
       <c r="C185" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4">
       <c r="A186">
         <v>219</v>
       </c>
     </row>
-    <row r="187" spans="1:3">
+    <row r="187" spans="1:4">
       <c r="A187">
         <v>220</v>
       </c>
       <c r="C187" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" ht="28.8">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="28.8">
       <c r="A188">
         <v>221</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="C188" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
       <c r="A189">
         <v>222</v>
       </c>
       <c r="C189" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4">
       <c r="A190">
         <v>223</v>
       </c>
       <c r="C190" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" ht="28.8">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="28.8">
       <c r="A191">
         <v>224</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4">
       <c r="A192">
         <v>225</v>
       </c>
       <c r="C192" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -4261,13 +5333,16 @@
       <c r="A194">
         <v>227</v>
       </c>
+      <c r="C194" s="6" t="s">
+        <v>521</v>
+      </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195">
         <v>228</v>
       </c>
       <c r="C195" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -4275,10 +5350,10 @@
         <v>229</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="C196" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -4286,7 +5361,7 @@
         <v>230</v>
       </c>
       <c r="C197" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -4294,7 +5369,7 @@
         <v>231</v>
       </c>
       <c r="C198" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -4302,7 +5377,7 @@
         <v>232</v>
       </c>
       <c r="C199" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -4315,7 +5390,7 @@
         <v>234</v>
       </c>
       <c r="C201" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -4323,7 +5398,7 @@
         <v>235</v>
       </c>
       <c r="C202" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -4336,10 +5411,10 @@
         <v>237</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="C204" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -4347,7 +5422,7 @@
         <v>238</v>
       </c>
       <c r="C205" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -4355,7 +5430,7 @@
         <v>239</v>
       </c>
       <c r="C206" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -4363,7 +5438,7 @@
         <v>240</v>
       </c>
       <c r="C207" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -4371,371 +5446,389 @@
         <v>241</v>
       </c>
       <c r="C208" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4">
       <c r="A209">
         <v>242</v>
       </c>
       <c r="C209" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4">
       <c r="A210">
         <v>243</v>
       </c>
       <c r="C210" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3">
-      <c r="A211">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" s="1" customFormat="1">
+      <c r="A211" s="1">
         <v>244</v>
       </c>
-      <c r="C211" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3">
+      <c r="B211" s="7"/>
+      <c r="C211" s="20" t="s">
+        <v>543</v>
+      </c>
+      <c r="D211" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4">
       <c r="A212">
         <v>245</v>
       </c>
       <c r="C212" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4">
       <c r="A213">
         <v>246</v>
       </c>
     </row>
-    <row r="214" spans="1:3">
+    <row r="214" spans="1:4">
       <c r="A214">
         <v>247</v>
       </c>
     </row>
-    <row r="215" spans="1:3">
+    <row r="215" spans="1:4">
       <c r="A215">
         <v>248</v>
       </c>
-      <c r="C215" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3">
+      <c r="C215" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4">
       <c r="A216">
         <v>249</v>
       </c>
       <c r="C216" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4">
       <c r="A217">
         <v>250</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="C217" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4">
       <c r="A218">
         <v>251</v>
       </c>
       <c r="C218" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4">
       <c r="A219">
         <v>252</v>
       </c>
       <c r="C219" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
       <c r="A220">
         <v>253</v>
       </c>
       <c r="C220" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4">
       <c r="A221">
         <v>254</v>
       </c>
     </row>
-    <row r="222" spans="1:3">
+    <row r="222" spans="1:4">
       <c r="A222">
         <v>255</v>
       </c>
       <c r="C222" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4">
       <c r="A223">
         <v>256</v>
       </c>
     </row>
-    <row r="224" spans="1:3">
+    <row r="224" spans="1:4">
       <c r="A224">
         <v>257</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="C224" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
       <c r="A225">
         <v>258</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="C225" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4">
       <c r="A226">
         <v>259</v>
       </c>
-      <c r="C226" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3">
+      <c r="C226" s="6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4">
       <c r="A227">
         <v>260</v>
       </c>
       <c r="C227" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4">
       <c r="A228">
         <v>261</v>
       </c>
-      <c r="C228" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3">
+      <c r="C228" s="18" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4">
       <c r="A229">
         <v>262</v>
       </c>
       <c r="C229" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3">
-      <c r="A230">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" s="1" customFormat="1">
+      <c r="A230" s="1">
         <v>263</v>
       </c>
-      <c r="C230" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3">
+      <c r="B230" s="7"/>
+      <c r="C230" s="20" t="s">
+        <v>544</v>
+      </c>
+      <c r="D230" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
       <c r="A231">
         <v>264</v>
       </c>
       <c r="C231" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3">
-      <c r="A232">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" s="1" customFormat="1">
+      <c r="A232" s="1">
         <v>265</v>
       </c>
-      <c r="C232" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3">
+      <c r="B232" s="21" t="s">
+        <v>507</v>
+      </c>
+      <c r="C232" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="D232" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4">
       <c r="A233">
         <v>266</v>
       </c>
       <c r="C233" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4">
       <c r="A234">
         <v>267</v>
       </c>
       <c r="C234" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4">
       <c r="A235">
         <v>268</v>
       </c>
       <c r="C235" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4">
       <c r="A236">
         <v>269</v>
       </c>
       <c r="C236" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
       <c r="A237">
         <v>270</v>
       </c>
       <c r="C237" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4">
       <c r="A238">
         <v>271</v>
       </c>
       <c r="C238" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
       <c r="A239">
         <v>272</v>
       </c>
       <c r="C239" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
       <c r="A240">
         <v>273</v>
       </c>
     </row>
-    <row r="241" spans="1:3">
+    <row r="241" spans="1:4">
       <c r="A241">
         <v>274</v>
       </c>
       <c r="C241" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
       <c r="A242">
         <v>275</v>
       </c>
       <c r="C242" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4">
       <c r="A243">
         <v>276</v>
       </c>
       <c r="C243" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3">
-      <c r="A244">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" s="1" customFormat="1">
+      <c r="A244" s="1">
         <v>277</v>
       </c>
-      <c r="C244" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3">
+      <c r="B244" s="7"/>
+      <c r="C244" s="20" t="s">
+        <v>538</v>
+      </c>
+      <c r="D244" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4">
       <c r="A245">
         <v>278</v>
       </c>
       <c r="C245" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4">
       <c r="A246">
         <v>279</v>
       </c>
     </row>
-    <row r="247" spans="1:3">
+    <row r="247" spans="1:4">
       <c r="A247">
         <v>280</v>
       </c>
       <c r="C247" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4">
       <c r="A248">
         <v>281</v>
       </c>
       <c r="C248" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4">
       <c r="A249">
         <v>282</v>
       </c>
     </row>
-    <row r="250" spans="1:3">
+    <row r="250" spans="1:4">
       <c r="A250">
         <v>283</v>
       </c>
       <c r="C250" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4">
       <c r="A251">
         <v>284</v>
       </c>
       <c r="C251" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4">
       <c r="A252">
         <v>285</v>
       </c>
     </row>
-    <row r="253" spans="1:3">
+    <row r="253" spans="1:4">
       <c r="A253">
         <v>286</v>
       </c>
       <c r="C253" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4">
       <c r="A254">
         <v>287</v>
       </c>
       <c r="C254" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4">
       <c r="A255">
         <v>288</v>
       </c>
       <c r="C255" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4">
       <c r="A256">
         <v>289</v>
       </c>
@@ -4745,7 +5838,7 @@
         <v>290</v>
       </c>
       <c r="C257" t="s">
-        <v>196</v>
+        <v>173</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -4753,7 +5846,7 @@
         <v>291</v>
       </c>
       <c r="C258" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
     </row>
     <row r="259" spans="1:3">
@@ -4761,7 +5854,7 @@
         <v>292</v>
       </c>
       <c r="C259" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -4769,7 +5862,7 @@
         <v>293</v>
       </c>
       <c r="C260" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -4777,7 +5870,7 @@
         <v>294</v>
       </c>
       <c r="C261" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -4785,7 +5878,7 @@
         <v>295</v>
       </c>
       <c r="C262" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -4793,10 +5886,10 @@
         <v>296</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="C263" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -4804,7 +5897,7 @@
         <v>297</v>
       </c>
       <c r="C264" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -4812,7 +5905,7 @@
         <v>298</v>
       </c>
       <c r="C265" t="s">
-        <v>205</v>
+        <v>182</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -4835,7 +5928,7 @@
         <v>302</v>
       </c>
       <c r="C269" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -4843,10 +5936,10 @@
         <v>303</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>207</v>
+        <v>184</v>
       </c>
       <c r="C270" t="s">
-        <v>208</v>
+        <v>185</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -4854,7 +5947,7 @@
         <v>304</v>
       </c>
       <c r="C271" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
     </row>
     <row r="272" spans="1:3">
@@ -4867,7 +5960,7 @@
         <v>306</v>
       </c>
       <c r="C273" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -4875,7 +5968,7 @@
         <v>307</v>
       </c>
       <c r="C274" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
     </row>
     <row r="275" spans="1:3">
@@ -4883,7 +5976,7 @@
         <v>308</v>
       </c>
       <c r="C275" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
     </row>
     <row r="276" spans="1:3">
@@ -4896,7 +5989,7 @@
         <v>310</v>
       </c>
       <c r="C277" t="s">
-        <v>213</v>
+        <v>190</v>
       </c>
     </row>
     <row r="278" spans="1:3">
@@ -4904,7 +5997,7 @@
         <v>311</v>
       </c>
       <c r="C278" t="s">
-        <v>214</v>
+        <v>191</v>
       </c>
     </row>
     <row r="279" spans="1:3">
@@ -4912,7 +6005,7 @@
         <v>312</v>
       </c>
       <c r="C279" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="280" spans="1:3">
@@ -4920,10 +6013,10 @@
         <v>313</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>216</v>
+        <v>193</v>
       </c>
       <c r="C280" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -4936,7 +6029,7 @@
         <v>315</v>
       </c>
       <c r="C282" t="s">
-        <v>218</v>
+        <v>195</v>
       </c>
     </row>
     <row r="283" spans="1:3">
@@ -4949,7 +6042,7 @@
         <v>317</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -4961,8 +6054,11 @@
       <c r="A286">
         <v>319</v>
       </c>
-      <c r="C286" s="4">
-        <v>25</v>
+      <c r="B286" s="24" t="s">
+        <v>523</v>
+      </c>
+      <c r="C286" s="22" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -4970,7 +6066,7 @@
         <v>320</v>
       </c>
       <c r="C287" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -4978,525 +6074,555 @@
         <v>321</v>
       </c>
       <c r="C288" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
       <c r="A289">
         <v>322</v>
       </c>
       <c r="C289" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="290" spans="1:3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
       <c r="A290">
         <v>323</v>
       </c>
       <c r="C290" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="291" spans="1:3">
-      <c r="A291">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" s="1" customFormat="1">
+      <c r="A291" s="1">
         <v>324</v>
       </c>
-    </row>
-    <row r="292" spans="1:3">
+      <c r="B291" s="7"/>
+      <c r="C291" s="20" t="s">
+        <v>539</v>
+      </c>
+      <c r="D291" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
       <c r="A292">
         <v>325</v>
       </c>
       <c r="C292" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="293" spans="1:3">
-      <c r="A293">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" s="1" customFormat="1">
+      <c r="A293" s="1">
         <v>326</v>
       </c>
-      <c r="B293" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C293" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="294" spans="1:3">
+      <c r="B293" s="21" t="s">
+        <v>513</v>
+      </c>
+      <c r="C293" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="D293" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
       <c r="A294">
         <v>327</v>
       </c>
       <c r="C294" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="295" spans="1:3">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
       <c r="A295">
         <v>328</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="296" spans="1:3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
       <c r="A296">
         <v>329</v>
       </c>
       <c r="C296" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="297" spans="1:3">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
       <c r="A297">
         <v>330</v>
       </c>
       <c r="C297" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="298" spans="1:3">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
       <c r="A298">
         <v>331</v>
       </c>
       <c r="C298" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="299" spans="1:3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
       <c r="A299">
         <v>332</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="C299" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="300" spans="1:3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
       <c r="A300">
         <v>333</v>
       </c>
       <c r="C300" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="301" spans="1:3">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
       <c r="A301">
         <v>334</v>
       </c>
-      <c r="C301" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="302" spans="1:3">
+      <c r="B301" s="19" t="s">
+        <v>533</v>
+      </c>
+      <c r="C301" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
       <c r="A302">
         <v>335</v>
       </c>
       <c r="C302" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="303" spans="1:3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
       <c r="A303">
         <v>336</v>
       </c>
       <c r="C303" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
       <c r="A304">
         <v>337</v>
       </c>
     </row>
-    <row r="305" spans="1:3">
+    <row r="305" spans="1:4">
       <c r="A305">
         <v>338</v>
       </c>
     </row>
-    <row r="306" spans="1:3">
+    <row r="306" spans="1:4">
       <c r="A306">
         <v>339</v>
       </c>
       <c r="C306" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4">
       <c r="A307">
         <v>340</v>
       </c>
       <c r="C307" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3">
-      <c r="A308">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" s="1" customFormat="1">
+      <c r="A308" s="1">
         <v>341</v>
       </c>
-      <c r="C308" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3">
+      <c r="B308" s="7"/>
+      <c r="C308" s="20" t="s">
+        <v>542</v>
+      </c>
+      <c r="D308" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4">
       <c r="A309">
         <v>342</v>
       </c>
       <c r="C309" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4">
       <c r="A310">
         <v>343</v>
       </c>
       <c r="C310" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4">
       <c r="A311">
         <v>344</v>
       </c>
       <c r="C311" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4">
       <c r="A312">
         <v>345</v>
       </c>
       <c r="C312" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4">
       <c r="A313">
         <v>346</v>
       </c>
     </row>
-    <row r="314" spans="1:3">
-      <c r="A314">
+    <row r="314" spans="1:4" s="1" customFormat="1">
+      <c r="A314" s="1">
         <v>347</v>
       </c>
-      <c r="C314" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3">
+      <c r="B314" s="10" t="s">
+        <v>503</v>
+      </c>
+      <c r="C314" s="20" t="s">
+        <v>502</v>
+      </c>
+      <c r="D314" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4">
       <c r="A315">
         <v>348</v>
       </c>
-      <c r="C315" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3">
+      <c r="C315" s="6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4">
       <c r="A316">
         <v>349</v>
       </c>
       <c r="C316" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4">
       <c r="A317">
         <v>350</v>
       </c>
       <c r="C317" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4">
       <c r="A318">
         <v>351</v>
       </c>
       <c r="C318" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="319" spans="1:3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4">
       <c r="A319">
         <v>352</v>
       </c>
       <c r="C319" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4">
       <c r="A320">
         <v>353</v>
       </c>
       <c r="C320" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4">
       <c r="A321">
         <v>354</v>
       </c>
     </row>
-    <row r="322" spans="1:3">
+    <row r="322" spans="1:4">
       <c r="A322">
         <v>355</v>
       </c>
       <c r="C322" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="323" spans="1:3">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4">
       <c r="A323">
         <v>356</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>254</v>
+        <v>228</v>
       </c>
       <c r="C323" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="324" spans="1:3">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4">
       <c r="A324">
         <v>357</v>
       </c>
       <c r="C324" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4">
       <c r="A325">
         <v>358</v>
       </c>
-      <c r="C325" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3">
+      <c r="C325" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="D325">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4">
       <c r="A326">
         <v>359</v>
       </c>
       <c r="C326" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4">
       <c r="A327">
         <v>360</v>
       </c>
       <c r="C327" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="328" spans="1:3">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4">
       <c r="A328">
         <v>361</v>
       </c>
       <c r="C328" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4">
       <c r="A329">
         <v>362</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
       <c r="C329" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4">
       <c r="A330">
         <v>363</v>
       </c>
       <c r="C330" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4">
       <c r="A331">
         <v>364</v>
       </c>
       <c r="C331" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="332" spans="1:3">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4">
       <c r="A332">
         <v>365</v>
       </c>
       <c r="C332" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="333" spans="1:3">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4">
       <c r="A333">
         <v>366</v>
       </c>
       <c r="C333" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="334" spans="1:3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4">
       <c r="A334">
         <v>367</v>
       </c>
     </row>
-    <row r="335" spans="1:3">
+    <row r="335" spans="1:4">
       <c r="A335">
         <v>368</v>
       </c>
       <c r="C335" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="336" spans="1:3">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4">
       <c r="A336">
         <v>369</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>268</v>
+        <v>242</v>
       </c>
       <c r="C336" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="337" spans="1:3">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4">
       <c r="A337">
         <v>370</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="C337" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="338" spans="1:3">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4">
       <c r="A338">
         <v>371</v>
       </c>
       <c r="C338" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4">
       <c r="A339">
         <v>372</v>
       </c>
       <c r="C339" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4">
       <c r="A340">
         <v>373</v>
       </c>
       <c r="C340" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="341" spans="1:3">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4">
       <c r="A341">
         <v>374</v>
       </c>
       <c r="C341" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="342" spans="1:3">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4">
       <c r="A342">
         <v>375</v>
       </c>
-      <c r="C342" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3">
-      <c r="A343">
+      <c r="C342" s="18" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" s="1" customFormat="1">
+      <c r="A343" s="1">
         <v>376</v>
       </c>
-      <c r="C343" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="344" spans="1:3">
+      <c r="B343" s="7"/>
+      <c r="C343" s="20" t="s">
+        <v>498</v>
+      </c>
+      <c r="D343" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4">
       <c r="A344">
         <v>377</v>
       </c>
       <c r="C344" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="345" spans="1:3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4">
       <c r="A345">
         <v>378</v>
       </c>
       <c r="C345" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="346" spans="1:3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4">
       <c r="A346">
         <v>379</v>
       </c>
       <c r="C346" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="347" spans="1:3">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4">
       <c r="A347">
         <v>380</v>
       </c>
       <c r="C347" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="348" spans="1:3">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4">
       <c r="A348">
         <v>381</v>
       </c>
       <c r="C348" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="349" spans="1:3">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4">
       <c r="A349">
         <v>382</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>283</v>
+        <v>255</v>
       </c>
       <c r="C349" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="350" spans="1:3">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4">
       <c r="A350">
         <v>383</v>
       </c>
       <c r="C350" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4">
       <c r="A351">
         <v>384</v>
       </c>
       <c r="C351" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="352" spans="1:3">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4">
       <c r="A352">
         <v>385</v>
       </c>
       <c r="C352" t="s">
-        <v>286</v>
+        <v>258</v>
       </c>
     </row>
     <row r="353" spans="1:3">
@@ -5509,7 +6635,7 @@
         <v>387</v>
       </c>
       <c r="C354" t="s">
-        <v>287</v>
+        <v>259</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -5517,7 +6643,7 @@
         <v>388</v>
       </c>
       <c r="C355" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
     </row>
     <row r="356" spans="1:3">
@@ -5525,7 +6651,7 @@
         <v>389</v>
       </c>
       <c r="C356" t="s">
-        <v>289</v>
+        <v>261</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -5533,7 +6659,7 @@
         <v>390</v>
       </c>
       <c r="C357" t="s">
-        <v>290</v>
+        <v>262</v>
       </c>
     </row>
     <row r="358" spans="1:3">
@@ -5546,7 +6672,7 @@
         <v>392</v>
       </c>
       <c r="C359" t="s">
-        <v>291</v>
+        <v>263</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -5560,7 +6686,7 @@
       </c>
       <c r="B361" s="7"/>
       <c r="C361" s="8" t="s">
-        <v>292</v>
+        <v>264</v>
       </c>
     </row>
     <row r="362" spans="1:3">
@@ -5568,7 +6694,7 @@
         <v>395</v>
       </c>
       <c r="C362" t="s">
-        <v>293</v>
+        <v>265</v>
       </c>
     </row>
     <row r="363" spans="1:3">
@@ -5576,7 +6702,7 @@
         <v>396</v>
       </c>
       <c r="C363" t="s">
-        <v>294</v>
+        <v>266</v>
       </c>
     </row>
     <row r="364" spans="1:3">
@@ -5584,7 +6710,7 @@
         <v>397</v>
       </c>
       <c r="C364" t="s">
-        <v>295</v>
+        <v>267</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -5597,7 +6723,7 @@
         <v>399</v>
       </c>
       <c r="C366" t="s">
-        <v>296</v>
+        <v>268</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -5605,7 +6731,7 @@
         <v>400</v>
       </c>
       <c r="C367" t="s">
-        <v>297</v>
+        <v>269</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -5613,135 +6739,138 @@
         <v>401</v>
       </c>
       <c r="C368" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="369" spans="1:3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4">
       <c r="A369">
         <v>402</v>
       </c>
       <c r="C369" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="370" spans="1:3">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4">
       <c r="A370">
         <v>403</v>
       </c>
     </row>
-    <row r="371" spans="1:3">
+    <row r="371" spans="1:4">
       <c r="A371">
         <v>404</v>
       </c>
       <c r="C371" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="372" spans="1:3" s="1" customFormat="1">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" s="1" customFormat="1">
       <c r="A372" s="1">
         <v>405</v>
       </c>
       <c r="B372" s="16" t="s">
-        <v>521</v>
+        <v>489</v>
       </c>
       <c r="C372" s="13" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="373" spans="1:3">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4">
       <c r="A373">
         <v>406</v>
       </c>
       <c r="C373" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="374" spans="1:3">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4">
       <c r="A374">
         <v>407</v>
       </c>
       <c r="C374" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="375" spans="1:3">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4">
       <c r="A375">
         <v>408</v>
       </c>
       <c r="C375" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="376" spans="1:3">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4">
       <c r="A376">
         <v>409</v>
       </c>
       <c r="C376" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="377" spans="1:3">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4">
       <c r="A377">
         <v>410</v>
       </c>
       <c r="C377" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="378" spans="1:3">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4">
       <c r="A378">
         <v>411</v>
       </c>
     </row>
-    <row r="379" spans="1:3" s="1" customFormat="1">
+    <row r="379" spans="1:4" s="1" customFormat="1">
       <c r="A379" s="1">
         <v>412</v>
       </c>
       <c r="B379" s="7" t="s">
-        <v>307</v>
+        <v>279</v>
       </c>
       <c r="C379" s="8" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="380" spans="1:3">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4">
       <c r="A380">
         <v>413</v>
       </c>
       <c r="C380" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="381" spans="1:3">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4">
       <c r="A381">
         <v>414</v>
       </c>
       <c r="C381" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="382" spans="1:3">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4">
       <c r="A382">
         <v>415</v>
       </c>
       <c r="C382" s="6" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="383" spans="1:3">
+        <v>524</v>
+      </c>
+      <c r="D382">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4">
       <c r="A383">
         <v>416</v>
       </c>
       <c r="C383" s="6" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="384" spans="1:3">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4">
       <c r="A384">
         <v>417</v>
       </c>
       <c r="C384" t="s">
-        <v>313</v>
+        <v>284</v>
       </c>
     </row>
     <row r="385" spans="1:3">
@@ -5764,7 +6893,7 @@
         <v>421</v>
       </c>
       <c r="C388" t="s">
-        <v>314</v>
+        <v>285</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="43.2">
@@ -5772,7 +6901,7 @@
         <v>422</v>
       </c>
       <c r="C389" s="3" t="s">
-        <v>315</v>
+        <v>286</v>
       </c>
     </row>
     <row r="390" spans="1:3">
@@ -5780,7 +6909,7 @@
         <v>423</v>
       </c>
       <c r="C390" t="s">
-        <v>316</v>
+        <v>287</v>
       </c>
     </row>
     <row r="391" spans="1:3">
@@ -5788,7 +6917,7 @@
         <v>424</v>
       </c>
       <c r="C391" t="s">
-        <v>317</v>
+        <v>288</v>
       </c>
     </row>
     <row r="392" spans="1:3">
@@ -5796,7 +6925,7 @@
         <v>425</v>
       </c>
       <c r="C392" t="s">
-        <v>318</v>
+        <v>289</v>
       </c>
     </row>
     <row r="393" spans="1:3">
@@ -5804,7 +6933,7 @@
         <v>426</v>
       </c>
       <c r="C393" s="6" t="s">
-        <v>319</v>
+        <v>290</v>
       </c>
     </row>
     <row r="394" spans="1:3">
@@ -5812,7 +6941,7 @@
         <v>427</v>
       </c>
       <c r="C394" t="s">
-        <v>320</v>
+        <v>291</v>
       </c>
     </row>
     <row r="395" spans="1:3">
@@ -5825,7 +6954,7 @@
         <v>429</v>
       </c>
       <c r="C396" t="s">
-        <v>321</v>
+        <v>292</v>
       </c>
     </row>
     <row r="397" spans="1:3">
@@ -5833,7 +6962,7 @@
         <v>430</v>
       </c>
       <c r="C397" t="s">
-        <v>322</v>
+        <v>293</v>
       </c>
     </row>
     <row r="398" spans="1:3">
@@ -5846,7 +6975,7 @@
         <v>432</v>
       </c>
       <c r="C399" t="s">
-        <v>323</v>
+        <v>294</v>
       </c>
     </row>
     <row r="400" spans="1:3">
@@ -5854,127 +6983,131 @@
         <v>433</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>324</v>
+        <v>295</v>
       </c>
       <c r="C400" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="401" spans="1:3">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4">
       <c r="A401">
         <v>434</v>
       </c>
     </row>
-    <row r="402" spans="1:3">
+    <row r="402" spans="1:4">
       <c r="A402">
         <v>435</v>
       </c>
       <c r="C402" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="403" spans="1:3" s="1" customFormat="1" ht="13.05" customHeight="1">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" s="1" customFormat="1" ht="13.05" customHeight="1">
       <c r="A403" s="1">
         <v>436</v>
       </c>
       <c r="B403" s="7"/>
       <c r="C403" s="1" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="404" spans="1:3">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4">
       <c r="A404">
         <v>437</v>
       </c>
     </row>
-    <row r="405" spans="1:3">
+    <row r="405" spans="1:4">
       <c r="A405">
         <v>438</v>
       </c>
       <c r="C405" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="406" spans="1:3">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4">
       <c r="A406">
         <v>439</v>
       </c>
       <c r="C406" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="407" spans="1:3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4">
       <c r="A407">
         <v>440</v>
       </c>
       <c r="C407" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="408" spans="1:3">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4">
       <c r="A408">
         <v>441</v>
       </c>
       <c r="C408" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="409" spans="1:3">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4">
       <c r="A409">
         <v>442</v>
       </c>
     </row>
-    <row r="410" spans="1:3">
+    <row r="410" spans="1:4">
       <c r="A410">
         <v>443</v>
       </c>
       <c r="C410" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="411" spans="1:3">
-      <c r="A411">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" s="1" customFormat="1">
+      <c r="A411" s="1">
         <v>444</v>
       </c>
-      <c r="C411" s="6" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="412" spans="1:3">
+      <c r="B411" s="7"/>
+      <c r="C411" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="D411" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4">
       <c r="A412">
         <v>445</v>
       </c>
       <c r="C412" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="413" spans="1:3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4">
       <c r="A413">
         <v>446</v>
       </c>
     </row>
-    <row r="414" spans="1:3">
+    <row r="414" spans="1:4">
       <c r="A414">
         <v>447</v>
       </c>
       <c r="C414" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="415" spans="1:3">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4">
       <c r="A415">
         <v>448</v>
       </c>
       <c r="C415" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="416" spans="1:3">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4">
       <c r="A416">
         <v>449</v>
       </c>
       <c r="C416" t="s">
-        <v>337</v>
+        <v>308</v>
       </c>
     </row>
     <row r="417" spans="1:3">
@@ -5982,7 +7115,7 @@
         <v>450</v>
       </c>
       <c r="C417" s="6" t="s">
-        <v>338</v>
+        <v>309</v>
       </c>
     </row>
     <row r="418" spans="1:3">
@@ -5995,7 +7128,7 @@
         <v>452</v>
       </c>
       <c r="C419" t="s">
-        <v>339</v>
+        <v>310</v>
       </c>
     </row>
     <row r="420" spans="1:3">
@@ -6003,7 +7136,7 @@
         <v>453</v>
       </c>
       <c r="C420" s="6" t="s">
-        <v>340</v>
+        <v>311</v>
       </c>
     </row>
     <row r="421" spans="1:3">
@@ -6011,7 +7144,7 @@
         <v>454</v>
       </c>
       <c r="C421" t="s">
-        <v>341</v>
+        <v>312</v>
       </c>
     </row>
     <row r="422" spans="1:3">
@@ -6019,7 +7152,7 @@
         <v>455</v>
       </c>
       <c r="C422" t="s">
-        <v>342</v>
+        <v>313</v>
       </c>
     </row>
     <row r="423" spans="1:3">
@@ -6027,10 +7160,10 @@
         <v>456</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="C423" t="s">
-        <v>344</v>
+        <v>315</v>
       </c>
     </row>
     <row r="424" spans="1:3">
@@ -6043,10 +7176,10 @@
         <v>458</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>345</v>
+        <v>316</v>
       </c>
       <c r="C425" t="s">
-        <v>346</v>
+        <v>317</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -6054,7 +7187,7 @@
         <v>459</v>
       </c>
       <c r="C426" t="s">
-        <v>347</v>
+        <v>318</v>
       </c>
     </row>
     <row r="427" spans="1:3">
@@ -6067,7 +7200,7 @@
         <v>461</v>
       </c>
       <c r="C428" t="s">
-        <v>348</v>
+        <v>319</v>
       </c>
     </row>
     <row r="429" spans="1:3">
@@ -6075,7 +7208,7 @@
         <v>462</v>
       </c>
       <c r="C429" t="s">
-        <v>349</v>
+        <v>320</v>
       </c>
     </row>
     <row r="430" spans="1:3">
@@ -6083,10 +7216,10 @@
         <v>463</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>350</v>
+        <v>321</v>
       </c>
       <c r="C430" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
     </row>
     <row r="431" spans="1:3">
@@ -6104,7 +7237,7 @@
         <v>466</v>
       </c>
       <c r="C433" t="s">
-        <v>351</v>
+        <v>322</v>
       </c>
     </row>
     <row r="434" spans="1:3">
@@ -6112,7 +7245,7 @@
         <v>467</v>
       </c>
       <c r="C434" t="s">
-        <v>352</v>
+        <v>323</v>
       </c>
     </row>
     <row r="435" spans="1:3">
@@ -6120,7 +7253,7 @@
         <v>468</v>
       </c>
       <c r="C435" t="s">
-        <v>353</v>
+        <v>324</v>
       </c>
     </row>
     <row r="436" spans="1:3">
@@ -6133,7 +7266,7 @@
         <v>470</v>
       </c>
       <c r="C437" t="s">
-        <v>354</v>
+        <v>325</v>
       </c>
     </row>
     <row r="438" spans="1:3">
@@ -6141,7 +7274,7 @@
         <v>471</v>
       </c>
       <c r="C438" t="s">
-        <v>355</v>
+        <v>326</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -6149,7 +7282,7 @@
         <v>472</v>
       </c>
       <c r="C439" t="s">
-        <v>356</v>
+        <v>327</v>
       </c>
     </row>
     <row r="440" spans="1:3">
@@ -6157,10 +7290,10 @@
         <v>473</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="C440" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
     </row>
     <row r="441" spans="1:3">
@@ -6168,7 +7301,7 @@
         <v>474</v>
       </c>
       <c r="C441" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
     </row>
     <row r="442" spans="1:3">
@@ -6176,7 +7309,7 @@
         <v>475</v>
       </c>
       <c r="C442" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
     </row>
     <row r="443" spans="1:3">
@@ -6184,7 +7317,7 @@
         <v>476</v>
       </c>
       <c r="C443" t="s">
-        <v>361</v>
+        <v>332</v>
       </c>
     </row>
     <row r="444" spans="1:3">
@@ -6192,7 +7325,7 @@
         <v>477</v>
       </c>
       <c r="C444" t="s">
-        <v>362</v>
+        <v>333</v>
       </c>
     </row>
     <row r="445" spans="1:3">
@@ -6200,7 +7333,7 @@
         <v>478</v>
       </c>
       <c r="C445" t="s">
-        <v>363</v>
+        <v>334</v>
       </c>
     </row>
     <row r="446" spans="1:3">
@@ -6208,7 +7341,7 @@
         <v>479</v>
       </c>
       <c r="C446" s="12" t="s">
-        <v>515</v>
+        <v>483</v>
       </c>
     </row>
     <row r="447" spans="1:3">
@@ -6216,7 +7349,7 @@
         <v>480</v>
       </c>
       <c r="C447" t="s">
-        <v>364</v>
+        <v>335</v>
       </c>
     </row>
     <row r="448" spans="1:3">
@@ -6224,7 +7357,7 @@
         <v>481</v>
       </c>
       <c r="C448" t="s">
-        <v>365</v>
+        <v>336</v>
       </c>
     </row>
     <row r="449" spans="1:5" s="1" customFormat="1">
@@ -6233,10 +7366,10 @@
       </c>
       <c r="B449" s="7"/>
       <c r="C449" s="1" t="s">
-        <v>366</v>
+        <v>337</v>
       </c>
       <c r="E449" s="1" t="s">
-        <v>367</v>
+        <v>338</v>
       </c>
     </row>
     <row r="450" spans="1:5">
@@ -6244,7 +7377,7 @@
         <v>483</v>
       </c>
       <c r="C450" t="s">
-        <v>368</v>
+        <v>339</v>
       </c>
     </row>
     <row r="451" spans="1:5">
@@ -6252,7 +7385,7 @@
         <v>484</v>
       </c>
       <c r="C451" t="s">
-        <v>369</v>
+        <v>340</v>
       </c>
     </row>
     <row r="452" spans="1:5">
@@ -6260,7 +7393,7 @@
         <v>485</v>
       </c>
       <c r="C452" t="s">
-        <v>370</v>
+        <v>341</v>
       </c>
     </row>
     <row r="453" spans="1:5">
@@ -6273,10 +7406,10 @@
         <v>487</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C454" t="s">
-        <v>371</v>
+        <v>342</v>
       </c>
     </row>
     <row r="455" spans="1:5">
@@ -6284,10 +7417,10 @@
         <v>488</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="C455" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="456" spans="1:5">
@@ -6300,10 +7433,10 @@
         <v>490</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>373</v>
+        <v>344</v>
       </c>
       <c r="C457" t="s">
-        <v>374</v>
+        <v>345</v>
       </c>
     </row>
     <row r="458" spans="1:5">
@@ -6316,7 +7449,7 @@
         <v>492</v>
       </c>
       <c r="C459" t="s">
-        <v>375</v>
+        <v>346</v>
       </c>
     </row>
     <row r="460" spans="1:5">
@@ -6324,7 +7457,7 @@
         <v>493</v>
       </c>
       <c r="C460" t="s">
-        <v>376</v>
+        <v>347</v>
       </c>
     </row>
     <row r="461" spans="1:5">
@@ -6332,7 +7465,7 @@
         <v>494</v>
       </c>
       <c r="C461" t="s">
-        <v>377</v>
+        <v>348</v>
       </c>
     </row>
     <row r="462" spans="1:5">
@@ -6345,7 +7478,7 @@
         <v>496</v>
       </c>
       <c r="C463" t="s">
-        <v>378</v>
+        <v>349</v>
       </c>
     </row>
     <row r="464" spans="1:5">
@@ -6361,7 +7494,7 @@
         <v>498</v>
       </c>
       <c r="C465" t="s">
-        <v>379</v>
+        <v>350</v>
       </c>
     </row>
     <row r="466" spans="1:3">
@@ -6374,7 +7507,7 @@
         <v>500</v>
       </c>
       <c r="C467" t="s">
-        <v>380</v>
+        <v>351</v>
       </c>
     </row>
     <row r="468" spans="1:3">
@@ -6382,7 +7515,7 @@
         <v>501</v>
       </c>
       <c r="C468" t="s">
-        <v>381</v>
+        <v>352</v>
       </c>
     </row>
     <row r="469" spans="1:3">
@@ -6406,7 +7539,7 @@
       </c>
       <c r="B472" s="7"/>
       <c r="C472" s="1" t="s">
-        <v>382</v>
+        <v>353</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="28.8">
@@ -6414,7 +7547,7 @@
         <v>506</v>
       </c>
       <c r="C473" s="3" t="s">
-        <v>383</v>
+        <v>354</v>
       </c>
     </row>
     <row r="474" spans="1:3">
@@ -6422,7 +7555,7 @@
         <v>507</v>
       </c>
       <c r="C474" t="s">
-        <v>384</v>
+        <v>355</v>
       </c>
     </row>
     <row r="475" spans="1:3">
@@ -6430,7 +7563,7 @@
         <v>508</v>
       </c>
       <c r="C475" t="s">
-        <v>385</v>
+        <v>356</v>
       </c>
     </row>
     <row r="476" spans="1:3">
@@ -6438,7 +7571,7 @@
         <v>509</v>
       </c>
       <c r="C476" t="s">
-        <v>386</v>
+        <v>357</v>
       </c>
     </row>
     <row r="477" spans="1:3">
@@ -6446,10 +7579,10 @@
         <v>510</v>
       </c>
       <c r="B477" s="9" t="s">
-        <v>387</v>
+        <v>358</v>
       </c>
       <c r="C477" s="6" t="s">
-        <v>388</v>
+        <v>359</v>
       </c>
     </row>
     <row r="478" spans="1:3">
@@ -6457,7 +7590,7 @@
         <v>511</v>
       </c>
       <c r="C478" t="s">
-        <v>389</v>
+        <v>360</v>
       </c>
     </row>
     <row r="479" spans="1:3">
@@ -6480,7 +7613,7 @@
         <v>515</v>
       </c>
       <c r="C482" t="s">
-        <v>390</v>
+        <v>361</v>
       </c>
     </row>
     <row r="483" spans="1:3">
@@ -6493,10 +7626,10 @@
         <v>517</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>391</v>
+        <v>362</v>
       </c>
       <c r="C484" t="s">
-        <v>392</v>
+        <v>363</v>
       </c>
     </row>
     <row r="485" spans="1:3">
@@ -6509,10 +7642,10 @@
         <v>519</v>
       </c>
       <c r="B486" s="10" t="s">
-        <v>393</v>
+        <v>364</v>
       </c>
       <c r="C486" s="1" t="s">
-        <v>394</v>
+        <v>365</v>
       </c>
     </row>
     <row r="487" spans="1:3">
@@ -6520,7 +7653,7 @@
         <v>520</v>
       </c>
       <c r="C487" t="s">
-        <v>395</v>
+        <v>366</v>
       </c>
     </row>
     <row r="488" spans="1:3">
@@ -6528,7 +7661,7 @@
         <v>521</v>
       </c>
       <c r="C488" t="s">
-        <v>396</v>
+        <v>367</v>
       </c>
     </row>
     <row r="489" spans="1:3">
@@ -6542,7 +7675,7 @@
       </c>
       <c r="B490" s="7"/>
       <c r="C490" s="1" t="s">
-        <v>397</v>
+        <v>368</v>
       </c>
     </row>
     <row r="491" spans="1:3">
@@ -6550,7 +7683,7 @@
         <v>524</v>
       </c>
       <c r="C491" t="s">
-        <v>398</v>
+        <v>369</v>
       </c>
     </row>
     <row r="492" spans="1:3">
@@ -6558,10 +7691,10 @@
         <v>525</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>399</v>
+        <v>370</v>
       </c>
       <c r="C492" t="s">
-        <v>400</v>
+        <v>371</v>
       </c>
     </row>
     <row r="493" spans="1:3" s="1" customFormat="1">
@@ -6569,10 +7702,10 @@
         <v>526</v>
       </c>
       <c r="B493" s="7" t="s">
-        <v>401</v>
+        <v>372</v>
       </c>
       <c r="C493" s="1" t="s">
-        <v>402</v>
+        <v>373</v>
       </c>
     </row>
     <row r="494" spans="1:3">
@@ -6580,7 +7713,7 @@
         <v>527</v>
       </c>
       <c r="C494" t="s">
-        <v>403</v>
+        <v>374</v>
       </c>
     </row>
     <row r="495" spans="1:3">
@@ -6588,7 +7721,7 @@
         <v>528</v>
       </c>
       <c r="C495" t="s">
-        <v>404</v>
+        <v>375</v>
       </c>
     </row>
     <row r="496" spans="1:3">
@@ -6596,7 +7729,7 @@
         <v>529</v>
       </c>
       <c r="C496" t="s">
-        <v>405</v>
+        <v>376</v>
       </c>
     </row>
     <row r="497" spans="1:3" s="1" customFormat="1">
@@ -6605,7 +7738,7 @@
       </c>
       <c r="B497" s="7"/>
       <c r="C497" s="8" t="s">
-        <v>406</v>
+        <v>377</v>
       </c>
     </row>
     <row r="498" spans="1:3">
@@ -6613,7 +7746,7 @@
         <v>531</v>
       </c>
       <c r="C498" t="s">
-        <v>407</v>
+        <v>378</v>
       </c>
     </row>
     <row r="499" spans="1:3">
@@ -6621,10 +7754,10 @@
         <v>532</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>408</v>
+        <v>379</v>
       </c>
       <c r="C499" t="s">
-        <v>409</v>
+        <v>380</v>
       </c>
     </row>
     <row r="500" spans="1:3">
@@ -6637,7 +7770,7 @@
         <v>534</v>
       </c>
       <c r="C501" t="s">
-        <v>410</v>
+        <v>381</v>
       </c>
     </row>
     <row r="502" spans="1:3">
@@ -6645,7 +7778,7 @@
         <v>535</v>
       </c>
       <c r="C502" s="6" t="s">
-        <v>411</v>
+        <v>382</v>
       </c>
     </row>
     <row r="503" spans="1:3">
@@ -6653,7 +7786,7 @@
         <v>536</v>
       </c>
       <c r="C503" t="s">
-        <v>412</v>
+        <v>383</v>
       </c>
     </row>
     <row r="504" spans="1:3">
@@ -6661,7 +7794,7 @@
         <v>537</v>
       </c>
       <c r="C504" t="s">
-        <v>413</v>
+        <v>384</v>
       </c>
     </row>
     <row r="505" spans="1:3">
@@ -6669,7 +7802,7 @@
         <v>538</v>
       </c>
       <c r="C505" t="s">
-        <v>414</v>
+        <v>385</v>
       </c>
     </row>
     <row r="506" spans="1:3">
@@ -6702,7 +7835,7 @@
         <v>544</v>
       </c>
       <c r="C511" t="s">
-        <v>415</v>
+        <v>386</v>
       </c>
     </row>
     <row r="512" spans="1:3">
@@ -6710,7 +7843,7 @@
         <v>545</v>
       </c>
       <c r="C512" s="6" t="s">
-        <v>416</v>
+        <v>387</v>
       </c>
     </row>
     <row r="513" spans="1:3">
@@ -6718,7 +7851,7 @@
         <v>546</v>
       </c>
       <c r="C513" s="6" t="s">
-        <v>417</v>
+        <v>514</v>
       </c>
     </row>
     <row r="514" spans="1:3">
@@ -6726,7 +7859,7 @@
         <v>547</v>
       </c>
       <c r="C514" t="s">
-        <v>418</v>
+        <v>388</v>
       </c>
     </row>
     <row r="515" spans="1:3">
@@ -6734,7 +7867,7 @@
         <v>548</v>
       </c>
       <c r="C515" t="s">
-        <v>419</v>
+        <v>389</v>
       </c>
     </row>
     <row r="516" spans="1:3">
@@ -6752,7 +7885,7 @@
         <v>551</v>
       </c>
       <c r="C518" t="s">
-        <v>420</v>
+        <v>390</v>
       </c>
     </row>
     <row r="519" spans="1:3">
@@ -6765,7 +7898,7 @@
         <v>553</v>
       </c>
       <c r="C520" t="s">
-        <v>421</v>
+        <v>391</v>
       </c>
     </row>
     <row r="521" spans="1:3">
@@ -6773,7 +7906,7 @@
         <v>554</v>
       </c>
       <c r="C521" s="6" t="s">
-        <v>422</v>
+        <v>392</v>
       </c>
     </row>
     <row r="522" spans="1:3">
@@ -6781,7 +7914,7 @@
         <v>555</v>
       </c>
       <c r="C522" t="s">
-        <v>423</v>
+        <v>393</v>
       </c>
     </row>
     <row r="523" spans="1:3">
@@ -6789,7 +7922,7 @@
         <v>556</v>
       </c>
       <c r="C523" t="s">
-        <v>424</v>
+        <v>394</v>
       </c>
     </row>
     <row r="524" spans="1:3">
@@ -6797,7 +7930,7 @@
         <v>557</v>
       </c>
       <c r="C524" t="s">
-        <v>425</v>
+        <v>395</v>
       </c>
     </row>
     <row r="525" spans="1:3">
@@ -6805,7 +7938,7 @@
         <v>558</v>
       </c>
       <c r="C525" t="s">
-        <v>426</v>
+        <v>396</v>
       </c>
     </row>
     <row r="526" spans="1:3">
@@ -6813,7 +7946,7 @@
         <v>559</v>
       </c>
       <c r="C526" t="s">
-        <v>427</v>
+        <v>397</v>
       </c>
     </row>
     <row r="527" spans="1:3">
@@ -6821,7 +7954,7 @@
         <v>560</v>
       </c>
       <c r="C527" t="s">
-        <v>428</v>
+        <v>398</v>
       </c>
     </row>
     <row r="528" spans="1:3">
@@ -6829,112 +7962,119 @@
         <v>561</v>
       </c>
     </row>
-    <row r="529" spans="1:3">
+    <row r="529" spans="1:4">
       <c r="A529">
         <v>562</v>
       </c>
       <c r="C529" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="530" spans="1:3">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4">
       <c r="A530">
         <v>563</v>
       </c>
       <c r="C530" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="531" spans="1:3">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4">
       <c r="A531">
         <v>564</v>
       </c>
       <c r="C531" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="532" spans="1:3">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4">
       <c r="A532">
         <v>565</v>
       </c>
     </row>
-    <row r="533" spans="1:3">
+    <row r="533" spans="1:4">
       <c r="A533">
         <v>566</v>
       </c>
       <c r="C533" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="534" spans="1:3">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4">
       <c r="A534">
         <v>567</v>
       </c>
     </row>
-    <row r="535" spans="1:3">
-      <c r="A535">
+    <row r="535" spans="1:4" s="1" customFormat="1">
+      <c r="A535" s="1">
         <v>568</v>
       </c>
-    </row>
-    <row r="536" spans="1:3">
+      <c r="B535" s="7"/>
+      <c r="C535" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="D535" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4">
       <c r="A536">
         <v>569</v>
       </c>
-      <c r="C536" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="537" spans="1:3">
+      <c r="C536" s="6" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4">
       <c r="A537">
         <v>570</v>
       </c>
       <c r="C537" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="538" spans="1:3">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4">
       <c r="A538">
         <v>571</v>
       </c>
       <c r="C538" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="539" spans="1:3">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4">
       <c r="A539">
         <v>572</v>
       </c>
     </row>
-    <row r="540" spans="1:3">
+    <row r="540" spans="1:4">
       <c r="A540">
         <v>573</v>
       </c>
       <c r="C540" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="541" spans="1:3">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="541" spans="1:4">
       <c r="A541">
         <v>574</v>
       </c>
       <c r="C541" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="542" spans="1:3">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4">
       <c r="A542">
         <v>575</v>
       </c>
     </row>
-    <row r="543" spans="1:3">
+    <row r="543" spans="1:4">
       <c r="A543">
         <v>576</v>
       </c>
       <c r="C543" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="544" spans="1:3">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="544" spans="1:4">
       <c r="A544">
         <v>577</v>
       </c>
@@ -6944,7 +8084,7 @@
         <v>578</v>
       </c>
       <c r="B545" s="9" t="s">
-        <v>439</v>
+        <v>409</v>
       </c>
     </row>
     <row r="546" spans="1:5">
@@ -6952,7 +8092,7 @@
         <v>579</v>
       </c>
       <c r="C546" s="4" t="s">
-        <v>440</v>
+        <v>410</v>
       </c>
     </row>
     <row r="547" spans="1:5" s="1" customFormat="1">
@@ -6961,10 +8101,10 @@
       </c>
       <c r="B547" s="7"/>
       <c r="C547" s="15" t="s">
-        <v>518</v>
+        <v>486</v>
       </c>
       <c r="E547" s="1" t="s">
-        <v>441</v>
+        <v>411</v>
       </c>
     </row>
     <row r="548" spans="1:5">
@@ -6997,7 +8137,7 @@
         <v>586</v>
       </c>
       <c r="C553" t="s">
-        <v>442</v>
+        <v>412</v>
       </c>
     </row>
     <row r="554" spans="1:5" s="1" customFormat="1">
@@ -7006,7 +8146,7 @@
       </c>
       <c r="B554" s="7"/>
       <c r="C554" s="1" t="s">
-        <v>443</v>
+        <v>413</v>
       </c>
     </row>
     <row r="555" spans="1:5">
@@ -7019,7 +8159,7 @@
         <v>589</v>
       </c>
       <c r="C556" t="s">
-        <v>444</v>
+        <v>414</v>
       </c>
     </row>
     <row r="557" spans="1:5">
@@ -7027,7 +8167,7 @@
         <v>590</v>
       </c>
       <c r="C557" t="s">
-        <v>445</v>
+        <v>415</v>
       </c>
     </row>
     <row r="558" spans="1:5">
@@ -7040,7 +8180,7 @@
         <v>592</v>
       </c>
       <c r="C559" t="s">
-        <v>446</v>
+        <v>416</v>
       </c>
     </row>
     <row r="560" spans="1:5">
@@ -7048,7 +8188,7 @@
         <v>593</v>
       </c>
       <c r="C560" t="s">
-        <v>447</v>
+        <v>417</v>
       </c>
     </row>
     <row r="561" spans="1:3">
@@ -7056,10 +8196,10 @@
         <v>594</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>448</v>
+        <v>418</v>
       </c>
       <c r="C561" s="11" t="s">
-        <v>449</v>
+        <v>419</v>
       </c>
     </row>
     <row r="562" spans="1:3">
@@ -7077,10 +8217,10 @@
         <v>597</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="C564" t="s">
-        <v>451</v>
+        <v>421</v>
       </c>
     </row>
     <row r="565" spans="1:3">
@@ -7088,7 +8228,7 @@
         <v>598</v>
       </c>
       <c r="C565" t="s">
-        <v>452</v>
+        <v>422</v>
       </c>
     </row>
     <row r="566" spans="1:3">
@@ -7096,7 +8236,7 @@
         <v>599</v>
       </c>
       <c r="C566" t="s">
-        <v>453</v>
+        <v>423</v>
       </c>
     </row>
     <row r="567" spans="1:3">
@@ -7114,7 +8254,7 @@
         <v>602</v>
       </c>
       <c r="C569" t="s">
-        <v>454</v>
+        <v>424</v>
       </c>
     </row>
     <row r="570" spans="1:3">
@@ -7147,7 +8287,7 @@
         <v>608</v>
       </c>
       <c r="C575" t="s">
-        <v>455</v>
+        <v>425</v>
       </c>
     </row>
     <row r="576" spans="1:3">
@@ -7155,7 +8295,7 @@
         <v>609</v>
       </c>
       <c r="C576" t="s">
-        <v>456</v>
+        <v>426</v>
       </c>
     </row>
     <row r="577" spans="1:5">
@@ -7169,10 +8309,10 @@
       </c>
       <c r="B578" s="7"/>
       <c r="C578" s="8" t="s">
-        <v>457</v>
+        <v>427</v>
       </c>
       <c r="E578" s="1" t="s">
-        <v>441</v>
+        <v>411</v>
       </c>
     </row>
     <row r="579" spans="1:5">
@@ -7180,7 +8320,7 @@
         <v>612</v>
       </c>
       <c r="C579" t="s">
-        <v>458</v>
+        <v>428</v>
       </c>
     </row>
     <row r="580" spans="1:5">
@@ -7198,7 +8338,7 @@
         <v>615</v>
       </c>
       <c r="C582" t="s">
-        <v>459</v>
+        <v>429</v>
       </c>
     </row>
     <row r="583" spans="1:5">
@@ -7211,7 +8351,7 @@
         <v>617</v>
       </c>
       <c r="C584" t="s">
-        <v>460</v>
+        <v>430</v>
       </c>
     </row>
     <row r="585" spans="1:5">
@@ -7219,7 +8359,7 @@
         <v>618</v>
       </c>
       <c r="C585" t="s">
-        <v>461</v>
+        <v>431</v>
       </c>
     </row>
     <row r="586" spans="1:5" s="1" customFormat="1">
@@ -7228,7 +8368,7 @@
       </c>
       <c r="B586" s="7"/>
       <c r="C586" s="17" t="s">
-        <v>522</v>
+        <v>490</v>
       </c>
     </row>
     <row r="587" spans="1:5">
@@ -7236,7 +8376,7 @@
         <v>620</v>
       </c>
       <c r="C587" t="s">
-        <v>462</v>
+        <v>432</v>
       </c>
     </row>
     <row r="588" spans="1:5">
@@ -7244,7 +8384,7 @@
         <v>621</v>
       </c>
       <c r="C588" t="s">
-        <v>463</v>
+        <v>433</v>
       </c>
     </row>
     <row r="589" spans="1:5">
@@ -7252,7 +8392,7 @@
         <v>622</v>
       </c>
       <c r="C589" t="s">
-        <v>464</v>
+        <v>434</v>
       </c>
     </row>
     <row r="590" spans="1:5">
@@ -7260,7 +8400,7 @@
         <v>623</v>
       </c>
       <c r="C590" t="s">
-        <v>465</v>
+        <v>435</v>
       </c>
     </row>
     <row r="591" spans="1:5">
@@ -7268,7 +8408,7 @@
         <v>624</v>
       </c>
       <c r="C591" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="592" spans="1:5">
@@ -7276,134 +8416,138 @@
         <v>625</v>
       </c>
     </row>
-    <row r="593" spans="1:3">
+    <row r="593" spans="1:4">
       <c r="A593">
         <v>626</v>
       </c>
       <c r="C593" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="594" spans="1:3">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="594" spans="1:4">
       <c r="A594">
         <v>627</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>467</v>
+        <v>437</v>
       </c>
       <c r="C594" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="595" spans="1:3">
-      <c r="A595">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4" s="1" customFormat="1">
+      <c r="A595" s="1">
         <v>628</v>
       </c>
-      <c r="C595" s="12" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="596" spans="1:3">
+      <c r="B595" s="7"/>
+      <c r="C595" s="8" t="s">
+        <v>529</v>
+      </c>
+      <c r="D595" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4">
       <c r="A596">
         <v>629</v>
       </c>
       <c r="C596" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="597" spans="1:3">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4">
       <c r="A597">
         <v>630</v>
       </c>
       <c r="C597" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="598" spans="1:3" s="1" customFormat="1">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4" s="1" customFormat="1">
       <c r="A598" s="1">
         <v>631</v>
       </c>
       <c r="B598" s="7"/>
       <c r="C598" s="13" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="599" spans="1:3" s="1" customFormat="1">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4" s="1" customFormat="1">
       <c r="A599" s="1">
         <v>632</v>
       </c>
       <c r="B599" s="16" t="s">
-        <v>519</v>
+        <v>487</v>
       </c>
       <c r="C599" s="13" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="600" spans="1:3">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="600" spans="1:4">
       <c r="A600">
         <v>633</v>
       </c>
     </row>
-    <row r="601" spans="1:3">
+    <row r="601" spans="1:4">
       <c r="A601">
         <v>634</v>
       </c>
       <c r="C601" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="602" spans="1:3">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4">
       <c r="A602">
         <v>635</v>
       </c>
     </row>
-    <row r="603" spans="1:3">
+    <row r="603" spans="1:4">
       <c r="A603">
         <v>636</v>
       </c>
       <c r="C603" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="604" spans="1:3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="604" spans="1:4">
       <c r="A604">
         <v>637</v>
       </c>
       <c r="C604" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="605" spans="1:3">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="605" spans="1:4">
       <c r="A605">
         <v>638</v>
       </c>
       <c r="C605" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="606" spans="1:3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="606" spans="1:4">
       <c r="A606">
         <v>639</v>
       </c>
       <c r="C606" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="607" spans="1:3">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="607" spans="1:4">
       <c r="A607">
         <v>640</v>
       </c>
       <c r="C607" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="608" spans="1:3" s="1" customFormat="1">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="608" spans="1:4" s="1" customFormat="1">
       <c r="A608" s="1">
         <v>641</v>
       </c>
       <c r="B608" s="7"/>
       <c r="C608" s="8" t="s">
-        <v>478</v>
+        <v>448</v>
       </c>
     </row>
     <row r="609" spans="1:3">
@@ -7411,7 +8555,7 @@
         <v>642</v>
       </c>
       <c r="C609" t="s">
-        <v>479</v>
+        <v>449</v>
       </c>
     </row>
     <row r="610" spans="1:3">
@@ -7419,7 +8563,7 @@
         <v>643</v>
       </c>
       <c r="C610" t="s">
-        <v>480</v>
+        <v>450</v>
       </c>
     </row>
     <row r="611" spans="1:3" ht="43.2">
@@ -7427,7 +8571,7 @@
         <v>644</v>
       </c>
       <c r="C611" s="3" t="s">
-        <v>481</v>
+        <v>451</v>
       </c>
     </row>
     <row r="612" spans="1:3">
@@ -7435,7 +8579,7 @@
         <v>645</v>
       </c>
       <c r="C612" t="s">
-        <v>482</v>
+        <v>452</v>
       </c>
     </row>
     <row r="613" spans="1:3">
@@ -7443,7 +8587,7 @@
         <v>646</v>
       </c>
       <c r="C613" s="6" t="s">
-        <v>483</v>
+        <v>453</v>
       </c>
     </row>
     <row r="614" spans="1:3">
@@ -7451,7 +8595,7 @@
         <v>647</v>
       </c>
       <c r="C614" s="6" t="s">
-        <v>484</v>
+        <v>454</v>
       </c>
     </row>
     <row r="615" spans="1:3">
@@ -7459,7 +8603,7 @@
         <v>648</v>
       </c>
       <c r="C615" t="s">
-        <v>485</v>
+        <v>455</v>
       </c>
     </row>
     <row r="616" spans="1:3">
@@ -7467,7 +8611,7 @@
         <v>649</v>
       </c>
       <c r="C616" t="s">
-        <v>486</v>
+        <v>456</v>
       </c>
     </row>
     <row r="617" spans="1:3">
@@ -7475,7 +8619,7 @@
         <v>650</v>
       </c>
       <c r="C617" t="s">
-        <v>487</v>
+        <v>457</v>
       </c>
     </row>
     <row r="618" spans="1:3">
@@ -7483,7 +8627,7 @@
         <v>651</v>
       </c>
       <c r="C618" t="s">
-        <v>488</v>
+        <v>458</v>
       </c>
     </row>
     <row r="619" spans="1:3">
@@ -7491,10 +8635,10 @@
         <v>652</v>
       </c>
       <c r="B619" s="9" t="s">
-        <v>489</v>
+        <v>459</v>
       </c>
       <c r="C619" t="s">
-        <v>490</v>
+        <v>460</v>
       </c>
     </row>
     <row r="620" spans="1:3">
@@ -7502,7 +8646,7 @@
         <v>653</v>
       </c>
       <c r="C620" t="s">
-        <v>491</v>
+        <v>461</v>
       </c>
     </row>
     <row r="621" spans="1:3">
@@ -7510,7 +8654,7 @@
         <v>654</v>
       </c>
       <c r="C621" t="s">
-        <v>492</v>
+        <v>462</v>
       </c>
     </row>
     <row r="622" spans="1:3">
@@ -7518,7 +8662,7 @@
         <v>655</v>
       </c>
       <c r="C622" t="s">
-        <v>493</v>
+        <v>463</v>
       </c>
     </row>
     <row r="623" spans="1:3" ht="72">
@@ -7526,10 +8670,10 @@
         <v>656</v>
       </c>
       <c r="B623" s="9" t="s">
-        <v>494</v>
+        <v>464</v>
       </c>
       <c r="C623" s="3" t="s">
-        <v>495</v>
+        <v>465</v>
       </c>
     </row>
     <row r="624" spans="1:3" s="1" customFormat="1">
@@ -7538,26 +8682,26 @@
       </c>
       <c r="B624" s="7"/>
       <c r="C624" s="8" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="625" spans="1:3">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="625" spans="1:4">
       <c r="A625">
         <v>658</v>
       </c>
       <c r="C625" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="626" spans="1:3">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="626" spans="1:4">
       <c r="A626">
         <v>659</v>
       </c>
       <c r="C626" s="6" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="627" spans="1:3">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="627" spans="1:4">
       <c r="A627">
         <v>660</v>
       </c>
@@ -7565,94 +8709,98 @@
         <v>7</v>
       </c>
     </row>
-    <row r="628" spans="1:3">
+    <row r="628" spans="1:4">
       <c r="A628">
         <v>661</v>
       </c>
       <c r="C628" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="629" spans="1:3">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="629" spans="1:4">
       <c r="A629">
         <v>662</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>500</v>
+        <v>470</v>
       </c>
       <c r="C629" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="630" spans="1:3">
-      <c r="A630">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="630" spans="1:4" s="1" customFormat="1">
+      <c r="A630" s="1">
         <v>663</v>
       </c>
-      <c r="C630" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="631" spans="1:3">
+      <c r="B630" s="7"/>
+      <c r="C630" s="20" t="s">
+        <v>497</v>
+      </c>
+      <c r="D630" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="631" spans="1:4">
       <c r="A631">
         <v>664</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>503</v>
+        <v>472</v>
       </c>
       <c r="C631" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="632" spans="1:3">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="632" spans="1:4">
       <c r="A632">
         <v>665</v>
       </c>
       <c r="C632" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="633" spans="1:3">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="633" spans="1:4">
       <c r="A633">
         <v>666</v>
       </c>
     </row>
-    <row r="634" spans="1:3">
+    <row r="634" spans="1:4">
       <c r="A634">
         <v>667</v>
       </c>
       <c r="C634" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="635" spans="1:3">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="635" spans="1:4">
       <c r="A635">
         <v>668</v>
       </c>
     </row>
-    <row r="636" spans="1:3">
+    <row r="636" spans="1:4">
       <c r="A636">
         <v>669</v>
       </c>
       <c r="C636" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="637" spans="1:3">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="637" spans="1:4">
       <c r="A637">
         <v>670</v>
       </c>
     </row>
-    <row r="638" spans="1:3">
+    <row r="638" spans="1:4">
       <c r="A638">
         <v>671</v>
       </c>
     </row>
-    <row r="639" spans="1:3">
+    <row r="639" spans="1:4">
       <c r="A639">
         <v>672</v>
       </c>
     </row>
-    <row r="640" spans="1:3">
+    <row r="640" spans="1:4">
       <c r="A640">
         <v>673</v>
       </c>
@@ -7662,7 +8810,7 @@
         <v>674</v>
       </c>
       <c r="E641" t="s">
-        <v>441</v>
+        <v>411</v>
       </c>
     </row>
     <row r="642" spans="1:5">
@@ -7690,7 +8838,7 @@
         <v>679</v>
       </c>
       <c r="C646" t="s">
-        <v>508</v>
+        <v>477</v>
       </c>
     </row>
     <row r="647" spans="1:5">
@@ -7698,10 +8846,10 @@
         <v>680</v>
       </c>
       <c r="B647" s="9" t="s">
-        <v>509</v>
+        <v>478</v>
       </c>
       <c r="C647" s="6" t="s">
-        <v>510</v>
+        <v>479</v>
       </c>
     </row>
     <row r="648" spans="1:5">
@@ -7714,10 +8862,10 @@
         <v>682</v>
       </c>
       <c r="B649" s="9" t="s">
-        <v>511</v>
+        <v>480</v>
       </c>
       <c r="C649" s="6" t="s">
-        <v>512</v>
+        <v>481</v>
       </c>
     </row>
     <row r="650" spans="1:5" s="1" customFormat="1">
@@ -7725,10 +8873,10 @@
         <v>683</v>
       </c>
       <c r="B650" s="10" t="s">
-        <v>513</v>
+        <v>482</v>
       </c>
       <c r="C650" s="13" t="s">
-        <v>516</v>
+        <v>484</v>
       </c>
     </row>
     <row r="651" spans="1:5">
@@ -7736,7 +8884,7 @@
         <v>684</v>
       </c>
       <c r="C651" s="14" t="s">
-        <v>517</v>
+        <v>485</v>
       </c>
     </row>
     <row r="652" spans="1:5">

--- a/MC 685.xlsx
+++ b/MC 685.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Documents\testing tools\ccnp_mc_test_online\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF182984-A6BE-44F2-B13E-61D0910F7743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10505BF-79F6-4FA9-AB2A-DB5B85940909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="546">
   <si>
     <t>Index</t>
   </si>
@@ -167,9 +167,6 @@
   </si>
   <si>
     <t>authentication port</t>
-  </si>
-  <si>
-    <t xml:space="preserve">defining frequency </t>
   </si>
   <si>
     <t>both 1:2</t>
@@ -465,9 +462,6 @@
     <t xml:space="preserve">unique VPNv4 address </t>
   </si>
   <si>
-    <t>traffic segmentation, DMVPN</t>
-  </si>
-  <si>
     <t>MPLS</t>
   </si>
   <si>
@@ -732,9 +726,6 @@
   </si>
   <si>
     <t>hop-by-hop</t>
-  </si>
-  <si>
-    <t>2, 115</t>
   </si>
   <si>
     <t>debug dateflme localtime</t>
@@ -2267,66 +2258,1185 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> command toward </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">a domain </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SNMP</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>v2c</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SNMP</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>v3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Community</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> String, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>no encryption</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>read-only</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CNR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">sername and password, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>a</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">uthentiation, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rivileged</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>uap</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>mark</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Permit </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10.0.1.0/24 address</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>process 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>remove</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> process 10 from the global configuration</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0.0.0.0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Default metrics</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> are not configured</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">两个 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">disable-connected-check </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MP-BGP</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">components，MPLS Layer 3 VPN </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>weight value</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>200</t>
+    </r>
+  </si>
+  <si>
+    <t>LDP autoconfiguration</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OSPF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ISIS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">R1 based on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ISE</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">keyword </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>localtime</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is not defined</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">SanFrancisco and Boston </t>
+  </si>
+  <si>
+    <t>network management system tools</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>not met, changed to 172</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.16.0.0/24</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Partial updates</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Scaling</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">minimizes </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DoS attacks</t>
+    </r>
+  </si>
+  <si>
+    <t>没有only的选项</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RD，64-bit route distinguisher </t>
+  </si>
+  <si>
+    <t>purposes， IPv4 and VPNv4 address-family configurations</t>
+  </si>
+  <si>
+    <t>Change sequence 10， from permit to deny</t>
+  </si>
+  <si>
+    <t>两个选项包含LA, message-digest</t>
+  </si>
+  <si>
+    <t>floating static route</t>
+  </si>
+  <si>
+    <t>BRANCH， 192.168.100.1</t>
+  </si>
+  <si>
+    <t>CLIENT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove sequence 10 </t>
+  </si>
+  <si>
+    <t>cannot Telnet </t>
+  </si>
+  <si>
+    <r>
+      <t>seq 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, permit </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10.0.0.0/8 le 32</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DHCP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> option </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>66</t>
+    </r>
+  </si>
+  <si>
+    <t>DHCP server for Cisco IP phones</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TFTP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SNMP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> policy-map </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>control-plane</t>
+    </r>
+  </si>
+  <si>
+    <t>Remove the distance 10</t>
+  </si>
+  <si>
+    <r>
+      <t>选项包含</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>customer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>VPN</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Add the</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> control disable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> option</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">both options include </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">access list 100 </t>
+    </r>
+  </si>
+  <si>
+    <t>poison reverse</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>overlapping</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> IP addresses, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>private routing table</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>E1 and E2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> , </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>access list</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>distribute-list</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 10 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>out</t>
+    </r>
+  </si>
+  <si>
+    <t>maximum-paths ibgp 2</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">from </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>strict to loose</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Apply CoPP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>control plane interface</t>
+    </r>
+  </si>
+  <si>
+    <t>syslog level 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downstream node signals </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>in</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>area 20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>feasible distance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>greater</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> than the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>reported distance</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">5 permit icmp host </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10.10.10.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> host </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10.66.66.66</t>
+    </r>
+  </si>
+  <si>
+    <t>domain name, crypto key</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">traffic </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>segmentation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> command toward </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">a domain </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SNMP</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>v2c</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SNMP</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>v3</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Community</t>
+      <t>, DMVPN</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
     </r>
     <r>
       <rPr>
@@ -2336,27 +3446,6 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> String, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>no encryption</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">, </t>
     </r>
     <r>
@@ -2368,1042 +3457,41 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>read-only</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CNR</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>u</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">sername and password, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">uthentiation, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>p</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>rivileged</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>uap</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>mark</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Permit </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>10.0.1.0/24 address</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>process 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>remove</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> process 10 from the global configuration</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>0.0.0.0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Default metrics</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> are not configured</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">两个 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">disable-connected-check </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>MP-BGP</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">components，MPLS Layer 3 VPN </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>weight value</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>200</t>
-    </r>
-  </si>
-  <si>
-    <t>LDP autoconfiguration</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>OSPF</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ISIS</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">R1 based on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ISE</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">keyword </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>localtime</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> is not defined</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">SanFrancisco and Boston </t>
-  </si>
-  <si>
-    <t>network management system tools</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>not met, changed to 172</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.16.0.0/24</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Partial updates</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Scaling</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">minimizes </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>DoS attacks</t>
-    </r>
-  </si>
-  <si>
-    <t>没有only的选项</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RD，64-bit route distinguisher </t>
-  </si>
-  <si>
-    <t>purposes， IPv4 and VPNv4 address-family configurations</t>
-  </si>
-  <si>
-    <t>Change sequence 10， from permit to deny</t>
-  </si>
-  <si>
-    <t>两个选项包含LA, message-digest</t>
-  </si>
-  <si>
-    <t>floating static route</t>
-  </si>
-  <si>
-    <t>BRANCH， 192.168.100.1</t>
-  </si>
-  <si>
-    <t>CLIENT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remove sequence 10 </t>
-  </si>
-  <si>
-    <t>cannot Telnet </t>
-  </si>
-  <si>
-    <r>
-      <t>seq 10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, permit </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>10.0.0.0/8 le 32</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>DHCP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> option </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>66</t>
-    </r>
-  </si>
-  <si>
-    <t>DHCP server for Cisco IP phones</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>TFTP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>SNMP</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> policy-map </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>control-plane</t>
-    </r>
-  </si>
-  <si>
-    <t>Remove the distance 10</t>
-  </si>
-  <si>
-    <r>
-      <t>选项包含</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>customer</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>，</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>VPN</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Add the</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> control disable</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> option</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">both options include </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">access list 100 </t>
-    </r>
-  </si>
-  <si>
-    <t>poison reverse</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>overlapping</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> IP addresses, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>private routing table</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>E1 and E2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> , </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>access list</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>distribute-list</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 10 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>out</t>
-    </r>
-  </si>
-  <si>
-    <t>maximum-paths ibgp 2</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">from </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>strict to loose</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Apply CoPP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>control plane interface</t>
-    </r>
-  </si>
-  <si>
-    <t>syslog level 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Downstream node signals </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>in</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> of </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>area 20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>feasible distance</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>greater</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> than the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>reported distance</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">5 permit icmp host </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>10.10.10.1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> host </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>10.66.66.66</t>
+      <t>115</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>defining</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> frequency and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>scheduling</t>
     </r>
   </si>
 </sst>
@@ -3411,12 +3499,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3489,7 +3584,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3504,43 +3599,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3837,7 +3937,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3880,7 +3980,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -3999,7 +4099,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="21" spans="1:4" s="1" customFormat="1">
@@ -4008,7 +4108,7 @@
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="8" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
@@ -4020,7 +4120,7 @@
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="20" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -4061,7 +4161,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
@@ -4080,7 +4180,7 @@
         <v>51</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="29" spans="1:4" s="1" customFormat="1">
@@ -4131,7 +4231,7 @@
         <v>64</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>32</v>
@@ -4158,7 +4258,7 @@
         <v>69</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -4306,7 +4406,7 @@
         <v>92</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -4340,7 +4440,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" spans="1:4">
       <c r="A65">
         <v>98</v>
       </c>
@@ -4348,28 +4448,28 @@
         <v>47</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
+    <row r="66" spans="1:4">
       <c r="A66">
         <v>99</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
       <c r="A67">
         <v>100</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
+    <row r="68" spans="1:4">
       <c r="A68">
         <v>101</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
+    <row r="69" spans="1:4">
       <c r="A69">
         <v>102</v>
       </c>
@@ -4377,101 +4477,105 @@
         <v>48</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70">
+    <row r="70" spans="1:4" s="1" customFormat="1">
+      <c r="A70" s="1">
         <v>103</v>
       </c>
-      <c r="C70" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
+      <c r="B70" s="7"/>
+      <c r="C70" s="27" t="s">
+        <v>545</v>
+      </c>
+      <c r="D70" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
       <c r="A71">
         <v>104</v>
       </c>
       <c r="C71" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
       <c r="A72">
         <v>105</v>
       </c>
       <c r="C72" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
       <c r="A73">
         <v>106</v>
       </c>
       <c r="C73" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
       <c r="A74">
         <v>107</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
       <c r="A75">
         <v>108</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C75" s="18" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
       <c r="A76">
         <v>109</v>
       </c>
       <c r="B76" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C76" t="s">
         <v>53</v>
       </c>
-      <c r="C76" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
+    </row>
+    <row r="77" spans="1:4">
       <c r="A77">
         <v>110</v>
       </c>
       <c r="B77" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C77" t="s">
         <v>55</v>
       </c>
-      <c r="C77" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
+    </row>
+    <row r="78" spans="1:4">
       <c r="A78">
         <v>111</v>
       </c>
       <c r="C78" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
       <c r="A79">
         <v>112</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
+    <row r="80" spans="1:4">
       <c r="A80">
         <v>113</v>
       </c>
       <c r="C80" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -4479,7 +4583,7 @@
         <v>114</v>
       </c>
       <c r="C81" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="82" spans="1:3">
@@ -4495,7 +4599,7 @@
         <v>116</v>
       </c>
       <c r="C83" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -4503,7 +4607,7 @@
         <v>117</v>
       </c>
       <c r="C84" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -4511,7 +4615,7 @@
         <v>118</v>
       </c>
       <c r="C85" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -4519,7 +4623,7 @@
         <v>119</v>
       </c>
       <c r="C86" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -4527,7 +4631,7 @@
         <v>120</v>
       </c>
       <c r="C87" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -4535,7 +4639,7 @@
         <v>121</v>
       </c>
       <c r="C88" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -4548,7 +4652,7 @@
         <v>123</v>
       </c>
       <c r="C90" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -4556,7 +4660,7 @@
         <v>124</v>
       </c>
       <c r="C91" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -4564,7 +4668,7 @@
         <v>125</v>
       </c>
       <c r="C92" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -4572,7 +4676,7 @@
         <v>126</v>
       </c>
       <c r="C93" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="94" spans="1:3">
@@ -4580,7 +4684,7 @@
         <v>127</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -4588,7 +4692,7 @@
         <v>128</v>
       </c>
       <c r="C95" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -4606,7 +4710,7 @@
         <v>131</v>
       </c>
       <c r="C98" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -4620,7 +4724,7 @@
       </c>
       <c r="B100" s="7"/>
       <c r="C100" s="20" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D100" s="1">
         <v>1</v>
@@ -4632,7 +4736,7 @@
       </c>
       <c r="B101" s="7"/>
       <c r="C101" s="20" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D101" s="1">
         <v>1</v>
@@ -4643,7 +4747,7 @@
         <v>135</v>
       </c>
       <c r="C102" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -4651,7 +4755,7 @@
         <v>136</v>
       </c>
       <c r="C103" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -4659,7 +4763,7 @@
         <v>137</v>
       </c>
       <c r="C104" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -4672,7 +4776,7 @@
         <v>139</v>
       </c>
       <c r="C106" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -4680,7 +4784,7 @@
         <v>140</v>
       </c>
       <c r="C107" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -4688,7 +4792,7 @@
         <v>141</v>
       </c>
       <c r="C108" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -4696,7 +4800,7 @@
         <v>142</v>
       </c>
       <c r="C109" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="110" spans="1:4" s="1" customFormat="1">
@@ -4705,7 +4809,7 @@
       </c>
       <c r="B110" s="7"/>
       <c r="C110" s="20" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D110" s="1">
         <v>1</v>
@@ -4717,7 +4821,7 @@
       </c>
       <c r="B111" s="7"/>
       <c r="C111" s="20" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D111" s="1">
         <v>1</v>
@@ -4728,7 +4832,7 @@
         <v>145</v>
       </c>
       <c r="C112" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="113" spans="1:3">
@@ -4736,7 +4840,7 @@
         <v>146</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="114" spans="1:3">
@@ -4744,7 +4848,7 @@
         <v>147</v>
       </c>
       <c r="C114" s="18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="115" spans="1:3">
@@ -4752,7 +4856,7 @@
         <v>148</v>
       </c>
       <c r="C115" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="116" spans="1:3">
@@ -4760,7 +4864,7 @@
         <v>149</v>
       </c>
       <c r="C116" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="117" spans="1:3">
@@ -4773,7 +4877,7 @@
         <v>151</v>
       </c>
       <c r="C118" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="119" spans="1:3">
@@ -4781,7 +4885,7 @@
         <v>152</v>
       </c>
       <c r="C119" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="120" spans="1:3">
@@ -4789,7 +4893,7 @@
         <v>153</v>
       </c>
       <c r="C120" s="18" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="121" spans="1:3">
@@ -4797,7 +4901,7 @@
         <v>154</v>
       </c>
       <c r="C121" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="122" spans="1:3">
@@ -4810,7 +4914,7 @@
         <v>156</v>
       </c>
       <c r="C123" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="124" spans="1:3">
@@ -4818,7 +4922,7 @@
         <v>157</v>
       </c>
       <c r="C124" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="125" spans="1:3">
@@ -4846,7 +4950,7 @@
         <v>162</v>
       </c>
       <c r="C129" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4854,7 +4958,7 @@
         <v>163</v>
       </c>
       <c r="C130" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4867,7 +4971,7 @@
         <v>165</v>
       </c>
       <c r="C132" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4875,7 +4979,7 @@
         <v>166</v>
       </c>
       <c r="C133" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4883,7 +4987,7 @@
         <v>167</v>
       </c>
       <c r="C134" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4891,7 +4995,7 @@
         <v>168</v>
       </c>
       <c r="C135" s="18" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -4903,7 +5007,7 @@
       </c>
       <c r="B136" s="7"/>
       <c r="C136" s="20" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D136" s="1">
         <v>1</v>
@@ -4914,10 +5018,10 @@
         <v>170</v>
       </c>
       <c r="B137" s="21" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C137" s="23" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D137" s="1">
         <v>1</v>
@@ -4928,10 +5032,10 @@
         <v>171</v>
       </c>
       <c r="B138" s="21" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C138" s="20" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D138" s="1">
         <v>1</v>
@@ -4947,10 +5051,10 @@
         <v>173</v>
       </c>
       <c r="B140" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C140" t="s">
         <v>95</v>
-      </c>
-      <c r="C140" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4958,7 +5062,7 @@
         <v>174</v>
       </c>
       <c r="C141" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4966,7 +5070,7 @@
         <v>175</v>
       </c>
       <c r="C142" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -5000,7 +5104,7 @@
       </c>
       <c r="B148" s="7"/>
       <c r="C148" s="8" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D148" s="1">
         <v>1</v>
@@ -5010,6 +5114,9 @@
       <c r="A149">
         <v>182</v>
       </c>
+      <c r="C149" s="25" t="s">
+        <v>542</v>
+      </c>
     </row>
     <row r="150" spans="1:4">
       <c r="A150">
@@ -5046,10 +5153,10 @@
         <v>189</v>
       </c>
       <c r="B156" s="19" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D156">
         <v>1</v>
@@ -5070,7 +5177,7 @@
         <v>192</v>
       </c>
       <c r="C159" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -5078,7 +5185,7 @@
         <v>193</v>
       </c>
       <c r="C160" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -5086,7 +5193,7 @@
         <v>194</v>
       </c>
       <c r="C161" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="162" spans="1:4" s="1" customFormat="1">
@@ -5095,7 +5202,7 @@
       </c>
       <c r="B162" s="7"/>
       <c r="C162" s="20" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D162" s="1">
         <v>1</v>
@@ -5111,7 +5218,7 @@
         <v>197</v>
       </c>
       <c r="C164" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -5119,7 +5226,7 @@
         <v>198</v>
       </c>
       <c r="C165" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -5127,7 +5234,7 @@
         <v>199</v>
       </c>
       <c r="C166" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -5155,7 +5262,7 @@
         <v>204</v>
       </c>
       <c r="C171" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -5163,7 +5270,7 @@
         <v>205</v>
       </c>
       <c r="C172" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -5171,10 +5278,10 @@
         <v>206</v>
       </c>
       <c r="B173" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C173" t="s">
         <v>107</v>
-      </c>
-      <c r="C173" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -5197,7 +5304,7 @@
         <v>210</v>
       </c>
       <c r="C177" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -5205,7 +5312,7 @@
         <v>211</v>
       </c>
       <c r="C178" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -5213,7 +5320,7 @@
         <v>212</v>
       </c>
       <c r="C179" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -5221,7 +5328,7 @@
         <v>213</v>
       </c>
       <c r="C180" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -5229,7 +5336,7 @@
         <v>214</v>
       </c>
       <c r="C181" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -5237,10 +5344,10 @@
         <v>215</v>
       </c>
       <c r="B182" s="19" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="183" spans="1:4" s="1" customFormat="1">
@@ -5249,7 +5356,7 @@
       </c>
       <c r="B183" s="7"/>
       <c r="C183" s="8" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D183" s="1">
         <v>1</v>
@@ -5265,7 +5372,7 @@
         <v>218</v>
       </c>
       <c r="C185" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5278,7 +5385,7 @@
         <v>220</v>
       </c>
       <c r="C187" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="28.8">
@@ -5286,10 +5393,10 @@
         <v>221</v>
       </c>
       <c r="B188" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C188" t="s">
         <v>117</v>
-      </c>
-      <c r="C188" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5297,7 +5404,7 @@
         <v>222</v>
       </c>
       <c r="C189" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5305,7 +5412,7 @@
         <v>223</v>
       </c>
       <c r="C190" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="28.8">
@@ -5313,7 +5420,7 @@
         <v>224</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5321,7 +5428,7 @@
         <v>225</v>
       </c>
       <c r="C192" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -5334,7 +5441,7 @@
         <v>227</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -5342,7 +5449,7 @@
         <v>228</v>
       </c>
       <c r="C195" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -5350,10 +5457,10 @@
         <v>229</v>
       </c>
       <c r="B196" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C196" t="s">
         <v>124</v>
-      </c>
-      <c r="C196" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -5361,7 +5468,7 @@
         <v>230</v>
       </c>
       <c r="C197" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -5369,7 +5476,7 @@
         <v>231</v>
       </c>
       <c r="C198" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -5377,7 +5484,7 @@
         <v>232</v>
       </c>
       <c r="C199" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -5390,7 +5497,7 @@
         <v>234</v>
       </c>
       <c r="C201" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -5398,7 +5505,7 @@
         <v>235</v>
       </c>
       <c r="C202" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -5411,10 +5518,10 @@
         <v>237</v>
       </c>
       <c r="B204" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C204" t="s">
         <v>130</v>
-      </c>
-      <c r="C204" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -5422,7 +5529,7 @@
         <v>238</v>
       </c>
       <c r="C205" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -5430,7 +5537,7 @@
         <v>239</v>
       </c>
       <c r="C206" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -5438,7 +5545,7 @@
         <v>240</v>
       </c>
       <c r="C207" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -5446,7 +5553,7 @@
         <v>241</v>
       </c>
       <c r="C208" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5454,7 +5561,7 @@
         <v>242</v>
       </c>
       <c r="C209" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5462,7 +5569,7 @@
         <v>243</v>
       </c>
       <c r="C210" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="211" spans="1:4" s="1" customFormat="1">
@@ -5471,7 +5578,7 @@
       </c>
       <c r="B211" s="7"/>
       <c r="C211" s="20" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D211" s="1">
         <v>1</v>
@@ -5482,7 +5589,7 @@
         <v>245</v>
       </c>
       <c r="C212" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -5500,7 +5607,7 @@
         <v>248</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -5508,7 +5615,7 @@
         <v>249</v>
       </c>
       <c r="C216" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -5516,10 +5623,10 @@
         <v>250</v>
       </c>
       <c r="B217" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C217" t="s">
         <v>141</v>
-      </c>
-      <c r="C217" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5527,7 +5634,7 @@
         <v>251</v>
       </c>
       <c r="C218" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5535,7 +5642,7 @@
         <v>252</v>
       </c>
       <c r="C219" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5543,7 +5650,7 @@
         <v>253</v>
       </c>
       <c r="C220" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5556,7 +5663,7 @@
         <v>255</v>
       </c>
       <c r="C222" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5568,11 +5675,11 @@
       <c r="A224">
         <v>257</v>
       </c>
-      <c r="B224" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C224" t="s">
-        <v>148</v>
+      <c r="B224" s="26" t="s">
+        <v>543</v>
+      </c>
+      <c r="C224" s="6" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5580,10 +5687,10 @@
         <v>258</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C225" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5591,7 +5698,7 @@
         <v>259</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5599,7 +5706,7 @@
         <v>260</v>
       </c>
       <c r="C227" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5607,7 +5714,7 @@
         <v>261</v>
       </c>
       <c r="C228" s="18" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5615,7 +5722,7 @@
         <v>262</v>
       </c>
       <c r="C229" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="230" spans="1:4" s="1" customFormat="1">
@@ -5624,7 +5731,7 @@
       </c>
       <c r="B230" s="7"/>
       <c r="C230" s="20" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D230" s="1">
         <v>1</v>
@@ -5635,7 +5742,7 @@
         <v>264</v>
       </c>
       <c r="C231" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="232" spans="1:4" s="1" customFormat="1">
@@ -5643,10 +5750,10 @@
         <v>265</v>
       </c>
       <c r="B232" s="21" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="C232" s="8" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D232" s="1">
         <v>1</v>
@@ -5657,7 +5764,7 @@
         <v>266</v>
       </c>
       <c r="C233" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5665,7 +5772,7 @@
         <v>267</v>
       </c>
       <c r="C234" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5673,7 +5780,7 @@
         <v>268</v>
       </c>
       <c r="C235" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5681,7 +5788,7 @@
         <v>269</v>
       </c>
       <c r="C236" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5689,7 +5796,7 @@
         <v>270</v>
       </c>
       <c r="C237" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5697,7 +5804,7 @@
         <v>271</v>
       </c>
       <c r="C238" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5705,7 +5812,7 @@
         <v>272</v>
       </c>
       <c r="C239" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5718,7 +5825,7 @@
         <v>274</v>
       </c>
       <c r="C241" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5726,7 +5833,7 @@
         <v>275</v>
       </c>
       <c r="C242" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5734,7 +5841,7 @@
         <v>276</v>
       </c>
       <c r="C243" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="244" spans="1:4" s="1" customFormat="1">
@@ -5743,7 +5850,7 @@
       </c>
       <c r="B244" s="7"/>
       <c r="C244" s="20" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D244" s="1">
         <v>1</v>
@@ -5754,7 +5861,7 @@
         <v>278</v>
       </c>
       <c r="C245" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5767,7 +5874,7 @@
         <v>280</v>
       </c>
       <c r="C247" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5775,7 +5882,7 @@
         <v>281</v>
       </c>
       <c r="C248" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5788,7 +5895,7 @@
         <v>283</v>
       </c>
       <c r="C250" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5796,7 +5903,7 @@
         <v>284</v>
       </c>
       <c r="C251" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5809,7 +5916,7 @@
         <v>286</v>
       </c>
       <c r="C253" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5817,7 +5924,7 @@
         <v>287</v>
       </c>
       <c r="C254" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5825,7 +5932,7 @@
         <v>288</v>
       </c>
       <c r="C255" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5838,7 +5945,7 @@
         <v>290</v>
       </c>
       <c r="C257" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="258" spans="1:3">
@@ -5846,7 +5953,7 @@
         <v>291</v>
       </c>
       <c r="C258" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="259" spans="1:3">
@@ -5854,7 +5961,7 @@
         <v>292</v>
       </c>
       <c r="C259" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="260" spans="1:3">
@@ -5862,7 +5969,7 @@
         <v>293</v>
       </c>
       <c r="C260" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="261" spans="1:3">
@@ -5870,7 +5977,7 @@
         <v>294</v>
       </c>
       <c r="C261" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="262" spans="1:3">
@@ -5878,7 +5985,7 @@
         <v>295</v>
       </c>
       <c r="C262" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="263" spans="1:3">
@@ -5886,10 +5993,10 @@
         <v>296</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C263" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="264" spans="1:3">
@@ -5897,7 +6004,7 @@
         <v>297</v>
       </c>
       <c r="C264" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="265" spans="1:3">
@@ -5905,7 +6012,7 @@
         <v>298</v>
       </c>
       <c r="C265" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="266" spans="1:3">
@@ -5928,7 +6035,7 @@
         <v>302</v>
       </c>
       <c r="C269" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="270" spans="1:3">
@@ -5936,10 +6043,10 @@
         <v>303</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C270" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="271" spans="1:3">
@@ -5947,7 +6054,7 @@
         <v>304</v>
       </c>
       <c r="C271" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="272" spans="1:3">
@@ -5960,7 +6067,7 @@
         <v>306</v>
       </c>
       <c r="C273" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="274" spans="1:3">
@@ -5968,7 +6075,7 @@
         <v>307</v>
       </c>
       <c r="C274" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="275" spans="1:3">
@@ -5976,7 +6083,7 @@
         <v>308</v>
       </c>
       <c r="C275" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="276" spans="1:3">
@@ -5989,7 +6096,7 @@
         <v>310</v>
       </c>
       <c r="C277" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="278" spans="1:3">
@@ -5997,7 +6104,7 @@
         <v>311</v>
       </c>
       <c r="C278" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="279" spans="1:3">
@@ -6005,7 +6112,7 @@
         <v>312</v>
       </c>
       <c r="C279" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="280" spans="1:3">
@@ -6013,10 +6120,10 @@
         <v>313</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C280" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="281" spans="1:3">
@@ -6029,7 +6136,7 @@
         <v>315</v>
       </c>
       <c r="C282" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="283" spans="1:3">
@@ -6042,7 +6149,7 @@
         <v>317</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="285" spans="1:3">
@@ -6055,10 +6162,10 @@
         <v>319</v>
       </c>
       <c r="B286" s="24" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C286" s="22" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="287" spans="1:3">
@@ -6066,7 +6173,7 @@
         <v>320</v>
       </c>
       <c r="C287" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="288" spans="1:3">
@@ -6074,7 +6181,7 @@
         <v>321</v>
       </c>
       <c r="C288" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -6082,7 +6189,7 @@
         <v>322</v>
       </c>
       <c r="C289" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -6090,7 +6197,7 @@
         <v>323</v>
       </c>
       <c r="C290" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="291" spans="1:4" s="1" customFormat="1">
@@ -6099,7 +6206,7 @@
       </c>
       <c r="B291" s="7"/>
       <c r="C291" s="20" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D291" s="1">
         <v>1</v>
@@ -6110,7 +6217,7 @@
         <v>325</v>
       </c>
       <c r="C292" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="293" spans="1:4" s="1" customFormat="1">
@@ -6118,10 +6225,10 @@
         <v>326</v>
       </c>
       <c r="B293" s="21" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C293" s="8" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D293" s="1">
         <v>1</v>
@@ -6132,7 +6239,7 @@
         <v>327</v>
       </c>
       <c r="C294" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -6140,10 +6247,10 @@
         <v>328</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -6151,7 +6258,7 @@
         <v>329</v>
       </c>
       <c r="C296" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -6159,7 +6266,7 @@
         <v>330</v>
       </c>
       <c r="C297" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -6167,7 +6274,7 @@
         <v>331</v>
       </c>
       <c r="C298" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -6175,10 +6282,10 @@
         <v>332</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C299" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -6186,7 +6293,7 @@
         <v>333</v>
       </c>
       <c r="C300" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -6194,10 +6301,10 @@
         <v>334</v>
       </c>
       <c r="B301" s="19" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -6205,7 +6312,7 @@
         <v>335</v>
       </c>
       <c r="C302" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -6213,7 +6320,7 @@
         <v>336</v>
       </c>
       <c r="C303" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -6231,7 +6338,7 @@
         <v>339</v>
       </c>
       <c r="C306" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -6239,7 +6346,7 @@
         <v>340</v>
       </c>
       <c r="C307" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="308" spans="1:4" s="1" customFormat="1">
@@ -6248,7 +6355,7 @@
       </c>
       <c r="B308" s="7"/>
       <c r="C308" s="20" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D308" s="1">
         <v>1</v>
@@ -6259,7 +6366,7 @@
         <v>342</v>
       </c>
       <c r="C309" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -6267,7 +6374,7 @@
         <v>343</v>
       </c>
       <c r="C310" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -6275,7 +6382,7 @@
         <v>344</v>
       </c>
       <c r="C311" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -6283,7 +6390,7 @@
         <v>345</v>
       </c>
       <c r="C312" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -6296,10 +6403,10 @@
         <v>347</v>
       </c>
       <c r="B314" s="10" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C314" s="20" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D314" s="1">
         <v>1</v>
@@ -6310,7 +6417,7 @@
         <v>348</v>
       </c>
       <c r="C315" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -6318,7 +6425,7 @@
         <v>349</v>
       </c>
       <c r="C316" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -6326,7 +6433,7 @@
         <v>350</v>
       </c>
       <c r="C317" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -6334,7 +6441,7 @@
         <v>351</v>
       </c>
       <c r="C318" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -6342,7 +6449,7 @@
         <v>352</v>
       </c>
       <c r="C319" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -6350,7 +6457,7 @@
         <v>353</v>
       </c>
       <c r="C320" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -6363,7 +6470,7 @@
         <v>355</v>
       </c>
       <c r="C322" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -6371,18 +6478,22 @@
         <v>356</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C323" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="324" spans="1:4">
-      <c r="A324">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" s="1" customFormat="1">
+      <c r="A324" s="1">
         <v>357</v>
       </c>
-      <c r="C324" t="s">
-        <v>230</v>
+      <c r="B324" s="7"/>
+      <c r="C324" s="27" t="s">
+        <v>544</v>
+      </c>
+      <c r="D324" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -6390,7 +6501,7 @@
         <v>358</v>
       </c>
       <c r="C325" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D325">
         <v>1</v>
@@ -6401,7 +6512,7 @@
         <v>359</v>
       </c>
       <c r="C326" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -6409,7 +6520,7 @@
         <v>360</v>
       </c>
       <c r="C327" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -6417,7 +6528,7 @@
         <v>361</v>
       </c>
       <c r="C328" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -6425,10 +6536,10 @@
         <v>362</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C329" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -6436,7 +6547,7 @@
         <v>363</v>
       </c>
       <c r="C330" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -6444,7 +6555,7 @@
         <v>364</v>
       </c>
       <c r="C331" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -6452,7 +6563,7 @@
         <v>365</v>
       </c>
       <c r="C332" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -6460,7 +6571,7 @@
         <v>366</v>
       </c>
       <c r="C333" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -6473,7 +6584,7 @@
         <v>368</v>
       </c>
       <c r="C335" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -6481,10 +6592,10 @@
         <v>369</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C336" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -6492,10 +6603,10 @@
         <v>370</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C337" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -6503,7 +6614,7 @@
         <v>371</v>
       </c>
       <c r="C338" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -6511,7 +6622,7 @@
         <v>372</v>
       </c>
       <c r="C339" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -6519,7 +6630,7 @@
         <v>373</v>
       </c>
       <c r="C340" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -6527,7 +6638,7 @@
         <v>374</v>
       </c>
       <c r="C341" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -6535,7 +6646,7 @@
         <v>375</v>
       </c>
       <c r="C342" s="18" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="343" spans="1:4" s="1" customFormat="1">
@@ -6544,7 +6655,7 @@
       </c>
       <c r="B343" s="7"/>
       <c r="C343" s="20" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D343" s="1">
         <v>1</v>
@@ -6555,7 +6666,7 @@
         <v>377</v>
       </c>
       <c r="C344" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -6563,7 +6674,7 @@
         <v>378</v>
       </c>
       <c r="C345" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -6571,7 +6682,7 @@
         <v>379</v>
       </c>
       <c r="C346" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6579,7 +6690,7 @@
         <v>380</v>
       </c>
       <c r="C347" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6587,7 +6698,7 @@
         <v>381</v>
       </c>
       <c r="C348" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6595,10 +6706,10 @@
         <v>382</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C349" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6606,7 +6717,7 @@
         <v>383</v>
       </c>
       <c r="C350" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6614,7 +6725,7 @@
         <v>384</v>
       </c>
       <c r="C351" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6622,7 +6733,7 @@
         <v>385</v>
       </c>
       <c r="C352" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="353" spans="1:3">
@@ -6635,7 +6746,7 @@
         <v>387</v>
       </c>
       <c r="C354" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -6643,7 +6754,7 @@
         <v>388</v>
       </c>
       <c r="C355" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="356" spans="1:3">
@@ -6651,7 +6762,7 @@
         <v>389</v>
       </c>
       <c r="C356" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -6659,7 +6770,7 @@
         <v>390</v>
       </c>
       <c r="C357" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="358" spans="1:3">
@@ -6672,7 +6783,7 @@
         <v>392</v>
       </c>
       <c r="C359" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -6686,7 +6797,7 @@
       </c>
       <c r="B361" s="7"/>
       <c r="C361" s="8" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="362" spans="1:3">
@@ -6694,7 +6805,7 @@
         <v>395</v>
       </c>
       <c r="C362" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="363" spans="1:3">
@@ -6702,7 +6813,7 @@
         <v>396</v>
       </c>
       <c r="C363" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="364" spans="1:3">
@@ -6710,7 +6821,7 @@
         <v>397</v>
       </c>
       <c r="C364" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -6723,7 +6834,7 @@
         <v>399</v>
       </c>
       <c r="C366" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -6731,7 +6842,7 @@
         <v>400</v>
       </c>
       <c r="C367" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="368" spans="1:3">
@@ -6739,7 +6850,7 @@
         <v>401</v>
       </c>
       <c r="C368" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6747,7 +6858,7 @@
         <v>402</v>
       </c>
       <c r="C369" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -6760,7 +6871,7 @@
         <v>404</v>
       </c>
       <c r="C371" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="372" spans="1:4" s="1" customFormat="1">
@@ -6768,10 +6879,10 @@
         <v>405</v>
       </c>
       <c r="B372" s="16" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C372" s="13" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -6779,7 +6890,7 @@
         <v>406</v>
       </c>
       <c r="C373" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -6787,7 +6898,7 @@
         <v>407</v>
       </c>
       <c r="C374" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -6795,7 +6906,7 @@
         <v>408</v>
       </c>
       <c r="C375" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -6803,7 +6914,7 @@
         <v>409</v>
       </c>
       <c r="C376" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -6811,7 +6922,7 @@
         <v>410</v>
       </c>
       <c r="C377" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -6824,10 +6935,10 @@
         <v>412</v>
       </c>
       <c r="B379" s="7" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C379" s="8" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -6835,7 +6946,7 @@
         <v>413</v>
       </c>
       <c r="C380" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -6843,7 +6954,7 @@
         <v>414</v>
       </c>
       <c r="C381" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -6851,7 +6962,7 @@
         <v>415</v>
       </c>
       <c r="C382" s="6" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D382">
         <v>1</v>
@@ -6862,7 +6973,7 @@
         <v>416</v>
       </c>
       <c r="C383" s="6" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -6870,7 +6981,7 @@
         <v>417</v>
       </c>
       <c r="C384" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="385" spans="1:3">
@@ -6893,7 +7004,7 @@
         <v>421</v>
       </c>
       <c r="C388" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="43.2">
@@ -6901,7 +7012,7 @@
         <v>422</v>
       </c>
       <c r="C389" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="390" spans="1:3">
@@ -6909,7 +7020,7 @@
         <v>423</v>
       </c>
       <c r="C390" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="391" spans="1:3">
@@ -6917,7 +7028,7 @@
         <v>424</v>
       </c>
       <c r="C391" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="392" spans="1:3">
@@ -6925,7 +7036,7 @@
         <v>425</v>
       </c>
       <c r="C392" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="393" spans="1:3">
@@ -6933,7 +7044,7 @@
         <v>426</v>
       </c>
       <c r="C393" s="6" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="394" spans="1:3">
@@ -6941,7 +7052,7 @@
         <v>427</v>
       </c>
       <c r="C394" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="395" spans="1:3">
@@ -6954,7 +7065,7 @@
         <v>429</v>
       </c>
       <c r="C396" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="397" spans="1:3">
@@ -6962,7 +7073,7 @@
         <v>430</v>
       </c>
       <c r="C397" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="398" spans="1:3">
@@ -6975,7 +7086,7 @@
         <v>432</v>
       </c>
       <c r="C399" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="400" spans="1:3">
@@ -6983,10 +7094,10 @@
         <v>433</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C400" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -6999,7 +7110,7 @@
         <v>435</v>
       </c>
       <c r="C402" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="403" spans="1:4" s="1" customFormat="1" ht="13.05" customHeight="1">
@@ -7008,7 +7119,7 @@
       </c>
       <c r="B403" s="7"/>
       <c r="C403" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -7021,7 +7132,7 @@
         <v>438</v>
       </c>
       <c r="C405" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -7029,7 +7140,7 @@
         <v>439</v>
       </c>
       <c r="C406" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -7037,7 +7148,7 @@
         <v>440</v>
       </c>
       <c r="C407" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -7045,7 +7156,7 @@
         <v>441</v>
       </c>
       <c r="C408" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -7058,7 +7169,7 @@
         <v>443</v>
       </c>
       <c r="C410" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="411" spans="1:4" s="1" customFormat="1">
@@ -7067,7 +7178,7 @@
       </c>
       <c r="B411" s="7"/>
       <c r="C411" s="8" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D411" s="1">
         <v>1</v>
@@ -7078,7 +7189,7 @@
         <v>445</v>
       </c>
       <c r="C412" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -7091,7 +7202,7 @@
         <v>447</v>
       </c>
       <c r="C414" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -7099,7 +7210,7 @@
         <v>448</v>
       </c>
       <c r="C415" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -7107,7 +7218,7 @@
         <v>449</v>
       </c>
       <c r="C416" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="417" spans="1:3">
@@ -7115,7 +7226,7 @@
         <v>450</v>
       </c>
       <c r="C417" s="6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="418" spans="1:3">
@@ -7128,7 +7239,7 @@
         <v>452</v>
       </c>
       <c r="C419" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="420" spans="1:3">
@@ -7136,7 +7247,7 @@
         <v>453</v>
       </c>
       <c r="C420" s="6" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="421" spans="1:3">
@@ -7144,7 +7255,7 @@
         <v>454</v>
       </c>
       <c r="C421" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="422" spans="1:3">
@@ -7152,7 +7263,7 @@
         <v>455</v>
       </c>
       <c r="C422" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="423" spans="1:3">
@@ -7160,10 +7271,10 @@
         <v>456</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C423" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="424" spans="1:3">
@@ -7176,10 +7287,10 @@
         <v>458</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C425" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="426" spans="1:3">
@@ -7187,7 +7298,7 @@
         <v>459</v>
       </c>
       <c r="C426" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="427" spans="1:3">
@@ -7200,7 +7311,7 @@
         <v>461</v>
       </c>
       <c r="C428" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="429" spans="1:3">
@@ -7208,7 +7319,7 @@
         <v>462</v>
       </c>
       <c r="C429" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="430" spans="1:3">
@@ -7216,10 +7327,10 @@
         <v>463</v>
       </c>
       <c r="B430" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C430" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="431" spans="1:3">
@@ -7237,7 +7348,7 @@
         <v>466</v>
       </c>
       <c r="C433" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="434" spans="1:3">
@@ -7245,7 +7356,7 @@
         <v>467</v>
       </c>
       <c r="C434" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="435" spans="1:3">
@@ -7253,7 +7364,7 @@
         <v>468</v>
       </c>
       <c r="C435" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="436" spans="1:3">
@@ -7266,7 +7377,7 @@
         <v>470</v>
       </c>
       <c r="C437" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="438" spans="1:3">
@@ -7274,7 +7385,7 @@
         <v>471</v>
       </c>
       <c r="C438" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="439" spans="1:3">
@@ -7282,7 +7393,7 @@
         <v>472</v>
       </c>
       <c r="C439" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="440" spans="1:3">
@@ -7290,10 +7401,10 @@
         <v>473</v>
       </c>
       <c r="B440" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C440" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="441" spans="1:3">
@@ -7301,7 +7412,7 @@
         <v>474</v>
       </c>
       <c r="C441" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="442" spans="1:3">
@@ -7309,7 +7420,7 @@
         <v>475</v>
       </c>
       <c r="C442" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="443" spans="1:3">
@@ -7317,7 +7428,7 @@
         <v>476</v>
       </c>
       <c r="C443" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="444" spans="1:3">
@@ -7325,7 +7436,7 @@
         <v>477</v>
       </c>
       <c r="C444" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="445" spans="1:3">
@@ -7333,7 +7444,7 @@
         <v>478</v>
       </c>
       <c r="C445" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="446" spans="1:3">
@@ -7341,7 +7452,7 @@
         <v>479</v>
       </c>
       <c r="C446" s="12" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="447" spans="1:3">
@@ -7349,7 +7460,7 @@
         <v>480</v>
       </c>
       <c r="C447" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="448" spans="1:3">
@@ -7357,7 +7468,7 @@
         <v>481</v>
       </c>
       <c r="C448" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="449" spans="1:5" s="1" customFormat="1">
@@ -7366,10 +7477,10 @@
       </c>
       <c r="B449" s="7"/>
       <c r="C449" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E449" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="450" spans="1:5">
@@ -7377,7 +7488,7 @@
         <v>483</v>
       </c>
       <c r="C450" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="451" spans="1:5">
@@ -7385,7 +7496,7 @@
         <v>484</v>
       </c>
       <c r="C451" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="452" spans="1:5">
@@ -7393,7 +7504,7 @@
         <v>485</v>
       </c>
       <c r="C452" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="453" spans="1:5">
@@ -7406,10 +7517,10 @@
         <v>487</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C454" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="455" spans="1:5">
@@ -7417,10 +7528,10 @@
         <v>488</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C455" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="456" spans="1:5">
@@ -7433,10 +7544,10 @@
         <v>490</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C457" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="458" spans="1:5">
@@ -7449,7 +7560,7 @@
         <v>492</v>
       </c>
       <c r="C459" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="460" spans="1:5">
@@ -7457,7 +7568,7 @@
         <v>493</v>
       </c>
       <c r="C460" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="461" spans="1:5">
@@ -7465,7 +7576,7 @@
         <v>494</v>
       </c>
       <c r="C461" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="462" spans="1:5">
@@ -7478,7 +7589,7 @@
         <v>496</v>
       </c>
       <c r="C463" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="464" spans="1:5">
@@ -7494,7 +7605,7 @@
         <v>498</v>
       </c>
       <c r="C465" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="466" spans="1:3">
@@ -7507,7 +7618,7 @@
         <v>500</v>
       </c>
       <c r="C467" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="468" spans="1:3">
@@ -7515,7 +7626,7 @@
         <v>501</v>
       </c>
       <c r="C468" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="469" spans="1:3">
@@ -7539,7 +7650,7 @@
       </c>
       <c r="B472" s="7"/>
       <c r="C472" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="473" spans="1:3" ht="28.8">
@@ -7547,7 +7658,7 @@
         <v>506</v>
       </c>
       <c r="C473" s="3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="474" spans="1:3">
@@ -7555,7 +7666,7 @@
         <v>507</v>
       </c>
       <c r="C474" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="475" spans="1:3">
@@ -7563,7 +7674,7 @@
         <v>508</v>
       </c>
       <c r="C475" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="476" spans="1:3">
@@ -7571,7 +7682,7 @@
         <v>509</v>
       </c>
       <c r="C476" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="477" spans="1:3">
@@ -7579,10 +7690,10 @@
         <v>510</v>
       </c>
       <c r="B477" s="9" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C477" s="6" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="478" spans="1:3">
@@ -7590,7 +7701,7 @@
         <v>511</v>
       </c>
       <c r="C478" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="479" spans="1:3">
@@ -7613,7 +7724,7 @@
         <v>515</v>
       </c>
       <c r="C482" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="483" spans="1:3">
@@ -7626,10 +7737,10 @@
         <v>517</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C484" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="485" spans="1:3">
@@ -7642,10 +7753,10 @@
         <v>519</v>
       </c>
       <c r="B486" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C486" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="487" spans="1:3">
@@ -7653,7 +7764,7 @@
         <v>520</v>
       </c>
       <c r="C487" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="488" spans="1:3">
@@ -7661,7 +7772,7 @@
         <v>521</v>
       </c>
       <c r="C488" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="489" spans="1:3">
@@ -7675,7 +7786,7 @@
       </c>
       <c r="B490" s="7"/>
       <c r="C490" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="491" spans="1:3">
@@ -7683,7 +7794,7 @@
         <v>524</v>
       </c>
       <c r="C491" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="492" spans="1:3">
@@ -7691,10 +7802,10 @@
         <v>525</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C492" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="493" spans="1:3" s="1" customFormat="1">
@@ -7702,10 +7813,10 @@
         <v>526</v>
       </c>
       <c r="B493" s="7" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C493" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="494" spans="1:3">
@@ -7713,7 +7824,7 @@
         <v>527</v>
       </c>
       <c r="C494" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="495" spans="1:3">
@@ -7721,7 +7832,7 @@
         <v>528</v>
       </c>
       <c r="C495" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="496" spans="1:3">
@@ -7729,7 +7840,7 @@
         <v>529</v>
       </c>
       <c r="C496" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="497" spans="1:3" s="1" customFormat="1">
@@ -7738,7 +7849,7 @@
       </c>
       <c r="B497" s="7"/>
       <c r="C497" s="8" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="498" spans="1:3">
@@ -7746,7 +7857,7 @@
         <v>531</v>
       </c>
       <c r="C498" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="499" spans="1:3">
@@ -7754,10 +7865,10 @@
         <v>532</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C499" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="500" spans="1:3">
@@ -7770,7 +7881,7 @@
         <v>534</v>
       </c>
       <c r="C501" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="502" spans="1:3">
@@ -7778,7 +7889,7 @@
         <v>535</v>
       </c>
       <c r="C502" s="6" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="503" spans="1:3">
@@ -7786,7 +7897,7 @@
         <v>536</v>
       </c>
       <c r="C503" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="504" spans="1:3">
@@ -7794,7 +7905,7 @@
         <v>537</v>
       </c>
       <c r="C504" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="505" spans="1:3">
@@ -7802,7 +7913,7 @@
         <v>538</v>
       </c>
       <c r="C505" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="506" spans="1:3">
@@ -7835,7 +7946,7 @@
         <v>544</v>
       </c>
       <c r="C511" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="512" spans="1:3">
@@ -7843,7 +7954,7 @@
         <v>545</v>
       </c>
       <c r="C512" s="6" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="513" spans="1:3">
@@ -7851,7 +7962,7 @@
         <v>546</v>
       </c>
       <c r="C513" s="6" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="514" spans="1:3">
@@ -7859,7 +7970,7 @@
         <v>547</v>
       </c>
       <c r="C514" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="515" spans="1:3">
@@ -7867,7 +7978,7 @@
         <v>548</v>
       </c>
       <c r="C515" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="516" spans="1:3">
@@ -7885,7 +7996,7 @@
         <v>551</v>
       </c>
       <c r="C518" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="519" spans="1:3">
@@ -7898,7 +8009,7 @@
         <v>553</v>
       </c>
       <c r="C520" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="521" spans="1:3">
@@ -7906,7 +8017,7 @@
         <v>554</v>
       </c>
       <c r="C521" s="6" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="522" spans="1:3">
@@ -7914,7 +8025,7 @@
         <v>555</v>
       </c>
       <c r="C522" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="523" spans="1:3">
@@ -7922,7 +8033,7 @@
         <v>556</v>
       </c>
       <c r="C523" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="524" spans="1:3">
@@ -7930,7 +8041,7 @@
         <v>557</v>
       </c>
       <c r="C524" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="525" spans="1:3">
@@ -7938,7 +8049,7 @@
         <v>558</v>
       </c>
       <c r="C525" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="526" spans="1:3">
@@ -7946,7 +8057,7 @@
         <v>559</v>
       </c>
       <c r="C526" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="527" spans="1:3">
@@ -7954,7 +8065,7 @@
         <v>560</v>
       </c>
       <c r="C527" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="528" spans="1:3">
@@ -7967,7 +8078,7 @@
         <v>562</v>
       </c>
       <c r="C529" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="530" spans="1:4">
@@ -7975,7 +8086,7 @@
         <v>563</v>
       </c>
       <c r="C530" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="531" spans="1:4">
@@ -7983,7 +8094,7 @@
         <v>564</v>
       </c>
       <c r="C531" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -7996,7 +8107,7 @@
         <v>566</v>
       </c>
       <c r="C533" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -8010,7 +8121,7 @@
       </c>
       <c r="B535" s="7"/>
       <c r="C535" s="8" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D535" s="1">
         <v>1</v>
@@ -8021,7 +8132,7 @@
         <v>569</v>
       </c>
       <c r="C536" s="6" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="537" spans="1:4">
@@ -8029,7 +8140,7 @@
         <v>570</v>
       </c>
       <c r="C537" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="538" spans="1:4">
@@ -8037,7 +8148,7 @@
         <v>571</v>
       </c>
       <c r="C538" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -8050,7 +8161,7 @@
         <v>573</v>
       </c>
       <c r="C540" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -8058,7 +8169,7 @@
         <v>574</v>
       </c>
       <c r="C541" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="542" spans="1:4">
@@ -8071,7 +8182,7 @@
         <v>576</v>
       </c>
       <c r="C543" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="544" spans="1:4">
@@ -8084,7 +8195,7 @@
         <v>578</v>
       </c>
       <c r="B545" s="9" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="546" spans="1:5">
@@ -8092,7 +8203,7 @@
         <v>579</v>
       </c>
       <c r="C546" s="4" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="547" spans="1:5" s="1" customFormat="1">
@@ -8101,10 +8212,10 @@
       </c>
       <c r="B547" s="7"/>
       <c r="C547" s="15" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E547" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="548" spans="1:5">
@@ -8137,7 +8248,7 @@
         <v>586</v>
       </c>
       <c r="C553" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="554" spans="1:5" s="1" customFormat="1">
@@ -8146,7 +8257,7 @@
       </c>
       <c r="B554" s="7"/>
       <c r="C554" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="555" spans="1:5">
@@ -8159,7 +8270,7 @@
         <v>589</v>
       </c>
       <c r="C556" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="557" spans="1:5">
@@ -8167,7 +8278,7 @@
         <v>590</v>
       </c>
       <c r="C557" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="558" spans="1:5">
@@ -8180,7 +8291,7 @@
         <v>592</v>
       </c>
       <c r="C559" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="560" spans="1:5">
@@ -8188,7 +8299,7 @@
         <v>593</v>
       </c>
       <c r="C560" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="561" spans="1:3">
@@ -8196,10 +8307,10 @@
         <v>594</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C561" s="11" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="562" spans="1:3">
@@ -8217,10 +8328,10 @@
         <v>597</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C564" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="565" spans="1:3">
@@ -8228,7 +8339,7 @@
         <v>598</v>
       </c>
       <c r="C565" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="566" spans="1:3">
@@ -8236,7 +8347,7 @@
         <v>599</v>
       </c>
       <c r="C566" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="567" spans="1:3">
@@ -8254,7 +8365,7 @@
         <v>602</v>
       </c>
       <c r="C569" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="570" spans="1:3">
@@ -8287,7 +8398,7 @@
         <v>608</v>
       </c>
       <c r="C575" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="576" spans="1:3">
@@ -8295,7 +8406,7 @@
         <v>609</v>
       </c>
       <c r="C576" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="577" spans="1:5">
@@ -8309,10 +8420,10 @@
       </c>
       <c r="B578" s="7"/>
       <c r="C578" s="8" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E578" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="579" spans="1:5">
@@ -8320,7 +8431,7 @@
         <v>612</v>
       </c>
       <c r="C579" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="580" spans="1:5">
@@ -8338,7 +8449,7 @@
         <v>615</v>
       </c>
       <c r="C582" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="583" spans="1:5">
@@ -8351,7 +8462,7 @@
         <v>617</v>
       </c>
       <c r="C584" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="585" spans="1:5">
@@ -8359,7 +8470,7 @@
         <v>618</v>
       </c>
       <c r="C585" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="586" spans="1:5" s="1" customFormat="1">
@@ -8368,7 +8479,7 @@
       </c>
       <c r="B586" s="7"/>
       <c r="C586" s="17" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="587" spans="1:5">
@@ -8376,7 +8487,7 @@
         <v>620</v>
       </c>
       <c r="C587" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="588" spans="1:5">
@@ -8384,7 +8495,7 @@
         <v>621</v>
       </c>
       <c r="C588" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="589" spans="1:5">
@@ -8392,7 +8503,7 @@
         <v>622</v>
       </c>
       <c r="C589" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="590" spans="1:5">
@@ -8400,7 +8511,7 @@
         <v>623</v>
       </c>
       <c r="C590" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="591" spans="1:5">
@@ -8421,7 +8532,7 @@
         <v>626</v>
       </c>
       <c r="C593" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="594" spans="1:4">
@@ -8429,10 +8540,10 @@
         <v>627</v>
       </c>
       <c r="B594" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C594" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="595" spans="1:4" s="1" customFormat="1">
@@ -8441,7 +8552,7 @@
       </c>
       <c r="B595" s="7"/>
       <c r="C595" s="8" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D595" s="1">
         <v>1</v>
@@ -8452,7 +8563,7 @@
         <v>629</v>
       </c>
       <c r="C596" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="597" spans="1:4">
@@ -8460,7 +8571,7 @@
         <v>630</v>
       </c>
       <c r="C597" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="598" spans="1:4" s="1" customFormat="1">
@@ -8469,7 +8580,7 @@
       </c>
       <c r="B598" s="7"/>
       <c r="C598" s="13" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="599" spans="1:4" s="1" customFormat="1">
@@ -8477,10 +8588,10 @@
         <v>632</v>
       </c>
       <c r="B599" s="16" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C599" s="13" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="600" spans="1:4">
@@ -8493,7 +8604,7 @@
         <v>634</v>
       </c>
       <c r="C601" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="602" spans="1:4">
@@ -8506,7 +8617,7 @@
         <v>636</v>
       </c>
       <c r="C603" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="604" spans="1:4">
@@ -8514,7 +8625,7 @@
         <v>637</v>
       </c>
       <c r="C604" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="605" spans="1:4">
@@ -8522,7 +8633,7 @@
         <v>638</v>
       </c>
       <c r="C605" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="606" spans="1:4">
@@ -8530,7 +8641,7 @@
         <v>639</v>
       </c>
       <c r="C606" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="607" spans="1:4">
@@ -8538,7 +8649,7 @@
         <v>640</v>
       </c>
       <c r="C607" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="608" spans="1:4" s="1" customFormat="1">
@@ -8547,7 +8658,7 @@
       </c>
       <c r="B608" s="7"/>
       <c r="C608" s="8" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="609" spans="1:3">
@@ -8555,7 +8666,7 @@
         <v>642</v>
       </c>
       <c r="C609" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="610" spans="1:3">
@@ -8563,7 +8674,7 @@
         <v>643</v>
       </c>
       <c r="C610" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="611" spans="1:3" ht="43.2">
@@ -8571,7 +8682,7 @@
         <v>644</v>
       </c>
       <c r="C611" s="3" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="612" spans="1:3">
@@ -8579,7 +8690,7 @@
         <v>645</v>
       </c>
       <c r="C612" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="613" spans="1:3">
@@ -8587,7 +8698,7 @@
         <v>646</v>
       </c>
       <c r="C613" s="6" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="614" spans="1:3">
@@ -8595,7 +8706,7 @@
         <v>647</v>
       </c>
       <c r="C614" s="6" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="615" spans="1:3">
@@ -8603,7 +8714,7 @@
         <v>648</v>
       </c>
       <c r="C615" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="616" spans="1:3">
@@ -8611,7 +8722,7 @@
         <v>649</v>
       </c>
       <c r="C616" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="617" spans="1:3">
@@ -8619,7 +8730,7 @@
         <v>650</v>
       </c>
       <c r="C617" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="618" spans="1:3">
@@ -8627,7 +8738,7 @@
         <v>651</v>
       </c>
       <c r="C618" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="619" spans="1:3">
@@ -8635,10 +8746,10 @@
         <v>652</v>
       </c>
       <c r="B619" s="9" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C619" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="620" spans="1:3">
@@ -8646,7 +8757,7 @@
         <v>653</v>
       </c>
       <c r="C620" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="621" spans="1:3">
@@ -8654,7 +8765,7 @@
         <v>654</v>
       </c>
       <c r="C621" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="622" spans="1:3">
@@ -8662,7 +8773,7 @@
         <v>655</v>
       </c>
       <c r="C622" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="623" spans="1:3" ht="72">
@@ -8670,10 +8781,10 @@
         <v>656</v>
       </c>
       <c r="B623" s="9" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C623" s="3" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="624" spans="1:3" s="1" customFormat="1">
@@ -8682,7 +8793,7 @@
       </c>
       <c r="B624" s="7"/>
       <c r="C624" s="8" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="625" spans="1:4">
@@ -8690,7 +8801,7 @@
         <v>658</v>
       </c>
       <c r="C625" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="626" spans="1:4">
@@ -8698,7 +8809,7 @@
         <v>659</v>
       </c>
       <c r="C626" s="6" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="627" spans="1:4">
@@ -8714,7 +8825,7 @@
         <v>661</v>
       </c>
       <c r="C628" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="629" spans="1:4">
@@ -8722,10 +8833,10 @@
         <v>662</v>
       </c>
       <c r="B629" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C629" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="630" spans="1:4" s="1" customFormat="1">
@@ -8734,7 +8845,7 @@
       </c>
       <c r="B630" s="7"/>
       <c r="C630" s="20" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D630" s="1">
         <v>1</v>
@@ -8745,10 +8856,10 @@
         <v>664</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C631" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
     </row>
     <row r="632" spans="1:4">
@@ -8756,7 +8867,7 @@
         <v>665</v>
       </c>
       <c r="C632" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="633" spans="1:4">
@@ -8769,7 +8880,7 @@
         <v>667</v>
       </c>
       <c r="C634" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="635" spans="1:4">
@@ -8782,7 +8893,7 @@
         <v>669</v>
       </c>
       <c r="C636" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="637" spans="1:4">
@@ -8810,7 +8921,7 @@
         <v>674</v>
       </c>
       <c r="E641" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="642" spans="1:5">
@@ -8838,7 +8949,7 @@
         <v>679</v>
       </c>
       <c r="C646" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="647" spans="1:5">
@@ -8846,10 +8957,10 @@
         <v>680</v>
       </c>
       <c r="B647" s="9" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C647" s="6" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="648" spans="1:5">
@@ -8862,10 +8973,10 @@
         <v>682</v>
       </c>
       <c r="B649" s="9" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C649" s="6" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="650" spans="1:5" s="1" customFormat="1">
@@ -8873,10 +8984,10 @@
         <v>683</v>
       </c>
       <c r="B650" s="10" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C650" s="13" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="651" spans="1:5">
@@ -8884,7 +8995,7 @@
         <v>684</v>
       </c>
       <c r="C651" s="14" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="652" spans="1:5">

--- a/MC 685.xlsx
+++ b/MC 685.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="18345" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="571">
   <si>
     <t>Index</t>
   </si>
@@ -311,6 +311,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>operations subnet</t>
     </r>
     <r>
@@ -853,7 +861,19 @@
     <t>assigns labels, handles traffic</t>
   </si>
   <si>
-    <t>correct IP address.</t>
+    <r>
+      <t>correct IP address</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
   </si>
   <si>
     <r>
@@ -901,6 +921,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>distribute list,</t>
     </r>
     <r>
@@ -979,6 +1007,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">default RD </t>
     </r>
     <r>
@@ -994,6 +1030,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Packets are</t>
     </r>
     <r>
@@ -1115,6 +1158,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>extends the IP</t>
     </r>
     <r>
@@ -1129,7 +1180,30 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">both options include IP address and default gateway， default gayteway 最后 </t>
+    <r>
+      <t xml:space="preserve">both options include </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>IP address and default gateway</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">， default gayteway 最后 </t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">OSPF process 5 </t>
@@ -1321,6 +1395,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">increase </t>
     </r>
     <r>
@@ -1551,6 +1633,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Each VRF</t>
     </r>
     <r>
@@ -1582,7 +1672,20 @@
     <t>domain name, crypto key</t>
   </si>
   <si>
-    <t>permit ICMPv6</t>
+    <r>
+      <t xml:space="preserve">permit </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ICMPv6</t>
+    </r>
   </si>
   <si>
     <t>purposes， IPv4 and VPNv4 address-family configurations</t>
@@ -1690,6 +1793,9 @@
   </si>
   <si>
     <t>两个选项包含LA, message-digest</t>
+  </si>
+  <si>
+    <t>unnecessary traffic</t>
   </si>
   <si>
     <t>ipv6 traffic-filter INTERNET</t>
@@ -1727,13 +1833,57 @@
     <t>Advertise the branch WAN interface</t>
   </si>
   <si>
-    <t>VPN routing information distributed</t>
-  </si>
-  <si>
-    <t>using of VPN target communities</t>
-  </si>
-  <si>
-    <r>
+    <r>
+      <t>VPN routing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> information </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>distributed</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>using of</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> VPN target communities</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>service dhcp</t>
     </r>
     <r>
@@ -1854,6 +2004,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>R3</t>
     </r>
     <r>
@@ -2050,6 +2208,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>10.1.100.10</t>
     </r>
     <r>
@@ -2187,6 +2353,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Cisc0Us3r</t>
     </r>
     <r>
@@ -2242,6 +2416,9 @@
     <t>ipv6 address autoconfig</t>
   </si>
   <si>
+    <t>anyone can access</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2265,10 +2442,21 @@
     </r>
   </si>
   <si>
+    <t>图里show interface 只有0/1</t>
+  </si>
+  <si>
     <t>interface Ethernet0/0</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>point-to-multipoint</t>
     </r>
     <r>
@@ -2305,6 +2493,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">matching </t>
     </r>
     <r>
@@ -2326,6 +2521,13 @@
     <t>deny 10 permit 20</t>
   </si>
   <si>
+    <t>Destination ip 是 10.221.10.10</t>
+  </si>
+  <si>
+    <t>flow exporter FlowAnalyzer1 
+destination 10.221.10.11</t>
+  </si>
+  <si>
     <t>permit 10  set ip next-hop recursive</t>
   </si>
   <si>
@@ -2357,14 +2559,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>Change the R1 router ID</t>
     </r>
     <r>
@@ -2386,7 +2580,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">10.255.255.1 </t>
+      <t>10.255.255.1 ，  unique value and clear the process</t>
     </r>
   </si>
   <si>
@@ -2437,6 +2631,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">set ip </t>
     </r>
     <r>
@@ -2471,6 +2672,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">Include a </t>
     </r>
     <r>
@@ -2582,7 +2790,19 @@
     <t xml:space="preserve"> critical </t>
   </si>
   <si>
-    <t>R2 no auto-summary</t>
+    <r>
+      <t xml:space="preserve">R2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>no auto-summary</t>
+    </r>
   </si>
   <si>
     <t>lowest key-id</t>
@@ -2738,14 +2958,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve"> 65000</t>
     </r>
     <r>
@@ -2767,6 +2979,27 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
+      <t>ipv4-unicas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>ipv6 unicast</t>
     </r>
   </si>
@@ -2821,6 +3054,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>package.conf</t>
     </r>
     <r>
@@ -2847,6 +3088,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>adjust-mtu</t>
     </r>
     <r>
@@ -2876,6 +3125,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">incoming </t>
     </r>
     <r>
@@ -2958,6 +3214,9 @@
     <t>IGP does not have a route</t>
   </si>
   <si>
+    <t xml:space="preserve"> should be learning the route </t>
+  </si>
+  <si>
     <t>filter the external routes</t>
   </si>
   <si>
@@ -2971,6 +3230,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>subnets</t>
     </r>
     <r>
@@ -3020,7 +3287,7 @@
     <t>MPLS LDP targeted session</t>
   </si>
   <si>
-    <t>non-directly connected</t>
+    <t>label distributio, non-directly connected</t>
   </si>
   <si>
     <t>OSPF sham-link</t>
@@ -3176,7 +3443,20 @@
     <t>IPv6 Prefix Guard</t>
   </si>
   <si>
-    <t>distance eigrp 10 170</t>
+    <r>
+      <t xml:space="preserve">distance eigrp </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10 170</t>
+    </r>
   </si>
   <si>
     <t>trunk encapsulation dot1q</t>
@@ -3348,6 +3628,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">router </t>
     </r>
     <r>
@@ -3509,6 +3796,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>8-byte</t>
     </r>
     <r>
@@ -3773,7 +4068,42 @@
     <t xml:space="preserve"> ^300$</t>
   </si>
   <si>
-    <t>allow only devices</t>
+    <r>
+      <t xml:space="preserve">allow only devices that 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>not only have registered IP addresses</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> but are </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>also connecting</t>
+    </r>
   </si>
   <si>
     <t>Route-reflector-client</t>
@@ -3977,6 +4307,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>ipv6 unicast-routing</t>
     </r>
     <r>
@@ -4602,6 +4939,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">keyword </t>
     </r>
     <r>
@@ -4769,6 +5113,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>line console 0</t>
     </r>
     <r>
@@ -4813,6 +5165,9 @@
   </si>
   <si>
     <t>nhrp nhs</t>
+  </si>
+  <si>
+    <t>through hub with other spokes</t>
   </si>
   <si>
     <t>multicast</t>
@@ -5059,6 +5414,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>10.20.20.1</t>
     </r>
     <r>
@@ -5114,6 +5477,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>no</t>
     </r>
     <r>
@@ -5141,23 +5512,8 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="23">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -5660,205 +6016,205 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -6185,15 +6541,15 @@
   <dimension ref="A1:E654"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="47.775" style="5" customWidth="1"/>
+    <col min="2" max="2" width="63.8" style="6" customWidth="1"/>
     <col min="3" max="3" width="67.2166666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -6202,12 +6558,12 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="6">
+      <c r="A2" s="7">
         <v>3</v>
       </c>
       <c r="C2" t="s">
@@ -6218,7 +6574,7 @@
       <c r="A3">
         <v>4</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>6</v>
       </c>
       <c r="D3">
@@ -6245,7 +6601,7 @@
       <c r="A6">
         <v>8</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D6">
@@ -6272,8 +6628,8 @@
       <c r="A9" s="1">
         <v>12</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="10" t="s">
+      <c r="B9" s="10"/>
+      <c r="C9" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="1">
@@ -6292,7 +6648,7 @@
       <c r="A11">
         <v>14</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>14</v>
       </c>
     </row>
@@ -6308,7 +6664,7 @@
       <c r="A13" s="1">
         <v>16</v>
       </c>
-      <c r="B13" s="9"/>
+      <c r="B13" s="10"/>
       <c r="C13" s="2" t="s">
         <v>16</v>
       </c>
@@ -6364,19 +6720,19 @@
       <c r="A19" s="1">
         <v>23</v>
       </c>
-      <c r="B19" s="9"/>
+      <c r="B19" s="10"/>
       <c r="C19" s="4" t="s">
         <v>22</v>
       </c>
       <c r="D19" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20">
         <v>24</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="8" t="s">
         <v>23</v>
       </c>
     </row>
@@ -6424,7 +6780,7 @@
       <c r="A25">
         <v>38</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C25" t="s">
@@ -6435,7 +6791,7 @@
       <c r="A26" s="1">
         <v>44</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="10" t="s">
         <v>30</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -6457,7 +6813,7 @@
       <c r="A28">
         <v>51</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="8" t="s">
         <v>33</v>
       </c>
     </row>
@@ -6465,7 +6821,7 @@
       <c r="A29" s="1">
         <v>54</v>
       </c>
-      <c r="B29" s="9"/>
+      <c r="B29" s="10"/>
       <c r="C29" s="4" t="s">
         <v>34</v>
       </c>
@@ -6489,8 +6845,8 @@
       <c r="A31" s="1">
         <v>58</v>
       </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="10" t="s">
+      <c r="B31" s="10"/>
+      <c r="C31" s="4" t="s">
         <v>36</v>
       </c>
     </row>
@@ -6510,7 +6866,7 @@
       <c r="A33">
         <v>63</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="6" t="s">
         <v>38</v>
       </c>
       <c r="C33" t="s">
@@ -6524,7 +6880,7 @@
       <c r="B34" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="9" t="s">
         <v>41</v>
       </c>
     </row>
@@ -6540,12 +6896,12 @@
       <c r="A36" s="1">
         <v>67</v>
       </c>
-      <c r="B36" s="9"/>
+      <c r="B36" s="10"/>
       <c r="C36" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D36" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -6560,7 +6916,7 @@
       <c r="A38">
         <v>69</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="8" t="s">
         <v>45</v>
       </c>
     </row>
@@ -6568,7 +6924,7 @@
       <c r="A39" s="1">
         <v>70</v>
       </c>
-      <c r="B39" s="9"/>
+      <c r="B39" s="10"/>
       <c r="C39" s="2" t="s">
         <v>46</v>
       </c>
@@ -6585,10 +6941,10 @@
       <c r="A41" s="1">
         <v>72</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C41" s="4" t="s">
         <v>48</v>
       </c>
       <c r="D41" s="1">
@@ -6625,7 +6981,7 @@
       <c r="A46" s="1">
         <v>77</v>
       </c>
-      <c r="B46" s="9"/>
+      <c r="B46" s="10"/>
       <c r="C46" s="4" t="s">
         <v>51</v>
       </c>
@@ -6683,7 +7039,7 @@
         <v>56</v>
       </c>
       <c r="D53" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -6726,7 +7082,7 @@
       <c r="A60">
         <v>91</v>
       </c>
-      <c r="C60" s="16" t="s">
+      <c r="C60" s="9" t="s">
         <v>59</v>
       </c>
     </row>
@@ -6734,7 +7090,7 @@
       <c r="A61">
         <v>92</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="8" t="s">
         <v>60</v>
       </c>
     </row>
@@ -6781,10 +7137,10 @@
       <c r="A68">
         <v>99</v>
       </c>
-      <c r="B68" s="17" t="s">
+      <c r="B68" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="C68" s="8" t="s">
         <v>65</v>
       </c>
     </row>
@@ -6849,7 +7205,7 @@
       <c r="B76" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C76" s="7" t="s">
+      <c r="C76" s="8" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6860,7 +7216,7 @@
       <c r="B77" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="C77" s="8" t="s">
         <v>74</v>
       </c>
     </row>
@@ -6868,7 +7224,7 @@
       <c r="A78">
         <v>109</v>
       </c>
-      <c r="B78" s="5" t="s">
+      <c r="B78" s="6" t="s">
         <v>75</v>
       </c>
       <c r="C78" t="s">
@@ -6879,19 +7235,23 @@
       <c r="A79">
         <v>110</v>
       </c>
-      <c r="B79" s="5" t="s">
+      <c r="B79" s="6" t="s">
         <v>77</v>
       </c>
       <c r="C79" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
-      <c r="A80">
+    <row r="80" s="1" customFormat="1" spans="1:4">
+      <c r="A80" s="1">
         <v>111</v>
       </c>
-      <c r="C80" t="s">
+      <c r="B80" s="10"/>
+      <c r="C80" s="4" t="s">
         <v>79</v>
+      </c>
+      <c r="D80" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -6903,20 +7263,20 @@
       <c r="A82" s="1">
         <v>113</v>
       </c>
-      <c r="B82" s="9"/>
+      <c r="B82" s="10"/>
       <c r="C82" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D82" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" s="1" customFormat="1" spans="1:4">
       <c r="A83" s="1">
         <v>114</v>
       </c>
-      <c r="B83" s="9"/>
-      <c r="C83" s="10" t="s">
+      <c r="B83" s="10"/>
+      <c r="C83" s="4" t="s">
         <v>81</v>
       </c>
       <c r="D83" s="1">
@@ -6927,7 +7287,7 @@
       <c r="A84">
         <v>115</v>
       </c>
-      <c r="C84" s="18">
+      <c r="C84" s="17">
         <v>90</v>
       </c>
     </row>
@@ -6988,7 +7348,7 @@
       <c r="A92" s="1">
         <v>123</v>
       </c>
-      <c r="B92" s="9"/>
+      <c r="B92" s="10"/>
       <c r="C92" s="2" t="s">
         <v>88</v>
       </c>
@@ -7000,8 +7360,8 @@
       <c r="A93" s="1">
         <v>124</v>
       </c>
-      <c r="B93" s="9"/>
-      <c r="C93" s="10" t="s">
+      <c r="B93" s="10"/>
+      <c r="C93" s="4" t="s">
         <v>89</v>
       </c>
       <c r="D93" s="1">
@@ -7012,8 +7372,8 @@
       <c r="A94" s="1">
         <v>125</v>
       </c>
-      <c r="B94" s="9"/>
-      <c r="C94" s="19" t="s">
+      <c r="B94" s="10"/>
+      <c r="C94" s="2" t="s">
         <v>90</v>
       </c>
       <c r="D94" s="1">
@@ -7032,7 +7392,7 @@
       <c r="A96">
         <v>127</v>
       </c>
-      <c r="C96" s="8" t="s">
+      <c r="C96" s="9" t="s">
         <v>92</v>
       </c>
     </row>
@@ -7040,7 +7400,7 @@
       <c r="A97" s="1">
         <v>128</v>
       </c>
-      <c r="B97" s="9"/>
+      <c r="B97" s="10"/>
       <c r="C97" s="2" t="s">
         <v>93</v>
       </c>
@@ -7062,7 +7422,7 @@
       <c r="A100">
         <v>131</v>
       </c>
-      <c r="C100" s="8" t="s">
+      <c r="C100" s="9" t="s">
         <v>94</v>
       </c>
     </row>
@@ -7083,16 +7443,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" s="3" customFormat="1" spans="1:4">
-      <c r="A103" s="3">
+    <row r="103" s="1" customFormat="1" spans="1:4">
+      <c r="A103" s="1">
         <v>134</v>
       </c>
-      <c r="B103" s="12"/>
-      <c r="C103" s="14" t="s">
+      <c r="B103" s="10"/>
+      <c r="C103" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D103" s="3">
-        <v>1</v>
+      <c r="D103" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -7107,7 +7467,7 @@
       <c r="A105">
         <v>136</v>
       </c>
-      <c r="C105" s="7" t="s">
+      <c r="C105" s="8" t="s">
         <v>98</v>
       </c>
     </row>
@@ -7144,20 +7504,24 @@
       <c r="A110" s="1">
         <v>141</v>
       </c>
-      <c r="B110" s="9"/>
-      <c r="C110" s="10" t="s">
+      <c r="B110" s="10"/>
+      <c r="C110" s="4" t="s">
         <v>102</v>
       </c>
       <c r="D110" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4">
-      <c r="A111">
+    <row r="111" s="1" customFormat="1" spans="1:4">
+      <c r="A111" s="1">
         <v>142</v>
       </c>
-      <c r="C111" s="7" t="s">
+      <c r="B111" s="10"/>
+      <c r="C111" s="2" t="s">
         <v>103</v>
+      </c>
+      <c r="D111" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="112" s="1" customFormat="1" spans="1:4">
@@ -7178,7 +7542,7 @@
       <c r="A113" s="1">
         <v>144</v>
       </c>
-      <c r="B113" s="9"/>
+      <c r="B113" s="10"/>
       <c r="C113" s="2" t="s">
         <v>106</v>
       </c>
@@ -7190,7 +7554,7 @@
       <c r="A114">
         <v>145</v>
       </c>
-      <c r="C114" s="7" t="s">
+      <c r="C114" s="8" t="s">
         <v>107</v>
       </c>
     </row>
@@ -7198,7 +7562,7 @@
       <c r="A115">
         <v>146</v>
       </c>
-      <c r="C115" s="8" t="s">
+      <c r="C115" s="9" t="s">
         <v>108</v>
       </c>
     </row>
@@ -7206,7 +7570,7 @@
       <c r="A116">
         <v>147</v>
       </c>
-      <c r="C116" s="7" t="s">
+      <c r="C116" s="8" t="s">
         <v>109</v>
       </c>
     </row>
@@ -7214,7 +7578,7 @@
       <c r="A117" s="1">
         <v>148</v>
       </c>
-      <c r="B117" s="9"/>
+      <c r="B117" s="10"/>
       <c r="C117" s="2" t="s">
         <v>110</v>
       </c>
@@ -7226,7 +7590,7 @@
       <c r="A118" s="1">
         <v>149</v>
       </c>
-      <c r="B118" s="9"/>
+      <c r="B118" s="10"/>
       <c r="C118" s="2" t="s">
         <v>111</v>
       </c>
@@ -7259,7 +7623,7 @@
       <c r="A122">
         <v>153</v>
       </c>
-      <c r="C122" s="7" t="s">
+      <c r="C122" s="8" t="s">
         <v>114</v>
       </c>
     </row>
@@ -7280,8 +7644,8 @@
       <c r="A125" s="1">
         <v>156</v>
       </c>
-      <c r="B125" s="9"/>
-      <c r="C125" s="10" t="s">
+      <c r="B125" s="10"/>
+      <c r="C125" s="4" t="s">
         <v>116</v>
       </c>
       <c r="D125" s="1">
@@ -7328,7 +7692,7 @@
       <c r="A132" s="1">
         <v>163</v>
       </c>
-      <c r="B132" s="9"/>
+      <c r="B132" s="10"/>
       <c r="C132" s="2" t="s">
         <v>119</v>
       </c>
@@ -7341,19 +7705,23 @@
         <v>164</v>
       </c>
     </row>
-    <row r="134" spans="1:4">
-      <c r="A134">
+    <row r="134" s="1" customFormat="1" spans="1:4">
+      <c r="A134" s="1">
         <v>165</v>
       </c>
-      <c r="C134" t="s">
+      <c r="B134" s="10"/>
+      <c r="C134" s="4" t="s">
         <v>120</v>
+      </c>
+      <c r="D134" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:4">
       <c r="A135">
         <v>166</v>
       </c>
-      <c r="C135" s="8" t="s">
+      <c r="C135" s="9" t="s">
         <v>121</v>
       </c>
     </row>
@@ -7361,7 +7729,7 @@
       <c r="A136" s="1">
         <v>167</v>
       </c>
-      <c r="B136" s="9"/>
+      <c r="B136" s="10"/>
       <c r="C136" s="2" t="s">
         <v>122</v>
       </c>
@@ -7373,7 +7741,7 @@
       <c r="A137">
         <v>168</v>
       </c>
-      <c r="C137" s="7" t="s">
+      <c r="C137" s="8" t="s">
         <v>123</v>
       </c>
       <c r="D137">
@@ -7396,10 +7764,10 @@
       <c r="A139" s="3">
         <v>170</v>
       </c>
-      <c r="B139" s="20" t="s">
+      <c r="B139" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="C139" s="21" t="s">
+      <c r="C139" s="19" t="s">
         <v>126</v>
       </c>
       <c r="D139" s="3">
@@ -7410,14 +7778,14 @@
       <c r="A140" s="3">
         <v>171</v>
       </c>
-      <c r="B140" s="20" t="s">
+      <c r="B140" s="18" t="s">
         <v>127</v>
       </c>
       <c r="C140" s="14" t="s">
         <v>128</v>
       </c>
       <c r="D140" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -7429,7 +7797,7 @@
       <c r="A142">
         <v>173</v>
       </c>
-      <c r="B142" s="5" t="s">
+      <c r="B142" s="6" t="s">
         <v>129</v>
       </c>
       <c r="C142" t="s">
@@ -7461,7 +7829,7 @@
       <c r="A146">
         <v>177</v>
       </c>
-      <c r="C146" s="7" t="s">
+      <c r="C146" s="8" t="s">
         <v>133</v>
       </c>
     </row>
@@ -7469,8 +7837,8 @@
       <c r="A147" s="1">
         <v>178</v>
       </c>
-      <c r="B147" s="9"/>
-      <c r="C147" s="10" t="s">
+      <c r="B147" s="10"/>
+      <c r="C147" s="4" t="s">
         <v>134</v>
       </c>
       <c r="D147" s="1">
@@ -7503,7 +7871,7 @@
       <c r="A151">
         <v>182</v>
       </c>
-      <c r="C151" s="7" t="s">
+      <c r="C151" s="8" t="s">
         <v>136</v>
       </c>
     </row>
@@ -7511,12 +7879,12 @@
       <c r="A152" s="1">
         <v>183</v>
       </c>
-      <c r="B152" s="9"/>
+      <c r="B152" s="10"/>
       <c r="C152" s="2" t="s">
         <v>137</v>
       </c>
       <c r="D152" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -7596,7 +7964,7 @@
       <c r="A164" s="1">
         <v>195</v>
       </c>
-      <c r="B164" s="9"/>
+      <c r="B164" s="10"/>
       <c r="C164" s="2" t="s">
         <v>143</v>
       </c>
@@ -7673,7 +8041,7 @@
       <c r="A175">
         <v>206</v>
       </c>
-      <c r="B175" s="5" t="s">
+      <c r="B175" s="6" t="s">
         <v>149</v>
       </c>
       <c r="C175" t="s">
@@ -7721,8 +8089,8 @@
       <c r="A181" s="1">
         <v>212</v>
       </c>
-      <c r="B181" s="9"/>
-      <c r="C181" s="10" t="s">
+      <c r="B181" s="10"/>
+      <c r="C181" s="4" t="s">
         <v>154</v>
       </c>
       <c r="D181" s="1">
@@ -7733,7 +8101,7 @@
       <c r="A182" s="4">
         <v>213</v>
       </c>
-      <c r="B182" s="22"/>
+      <c r="B182" s="20"/>
       <c r="C182" s="4" t="s">
         <v>155</v>
       </c>
@@ -7756,7 +8124,7 @@
       <c r="B184" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="C184" s="8" t="s">
+      <c r="C184" s="9" t="s">
         <v>158</v>
       </c>
     </row>
@@ -7769,7 +8137,7 @@
         <v>159</v>
       </c>
       <c r="D185" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -7781,21 +8149,23 @@
       <c r="A187" s="1">
         <v>218</v>
       </c>
-      <c r="B187" s="9"/>
+      <c r="B187" s="10" t="s">
+        <v>160</v>
+      </c>
       <c r="C187" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D187" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188" s="1" customFormat="1" spans="1:4">
       <c r="A188" s="1">
         <v>219</v>
       </c>
-      <c r="B188" s="9"/>
+      <c r="B188" s="10"/>
       <c r="C188" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D188" s="1">
         <v>1</v>
@@ -7806,46 +8176,50 @@
         <v>220</v>
       </c>
       <c r="C189" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="190" ht="28.5" spans="1:4">
       <c r="A190">
         <v>221</v>
       </c>
-      <c r="B190" s="23" t="s">
-        <v>163</v>
+      <c r="B190" s="21" t="s">
+        <v>164</v>
       </c>
       <c r="C190" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="191" s="1" customFormat="1" spans="1:4">
       <c r="A191" s="1">
         <v>222</v>
       </c>
-      <c r="B191" s="9"/>
-      <c r="C191" s="10" t="s">
-        <v>165</v>
+      <c r="B191" s="10"/>
+      <c r="C191" s="4" t="s">
+        <v>166</v>
       </c>
       <c r="D191" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:4">
-      <c r="A192">
+    <row r="192" s="1" customFormat="1" spans="1:4">
+      <c r="A192" s="1">
         <v>223</v>
       </c>
-      <c r="C192" t="s">
-        <v>166</v>
+      <c r="B192" s="10"/>
+      <c r="C192" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D192" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="193" ht="28.5" spans="1:4">
       <c r="A193">
         <v>224</v>
       </c>
-      <c r="C193" s="6" t="s">
-        <v>167</v>
+      <c r="C193" s="7" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -7853,7 +8227,7 @@
         <v>225</v>
       </c>
       <c r="C194" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -7865,8 +8239,8 @@
       <c r="A196">
         <v>227</v>
       </c>
-      <c r="C196" s="8" t="s">
-        <v>169</v>
+      <c r="C196" s="9" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -7874,27 +8248,30 @@
         <v>228</v>
       </c>
       <c r="C197" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4">
-      <c r="A198">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="198" s="1" customFormat="1" spans="1:4">
+      <c r="A198" s="1">
         <v>229</v>
       </c>
-      <c r="B198" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C198" t="s">
+      <c r="B198" s="20" t="s">
         <v>172</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D198" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="199" s="1" customFormat="1" spans="1:4">
       <c r="A199" s="1">
         <v>230</v>
       </c>
-      <c r="B199" s="9"/>
-      <c r="C199" s="10" t="s">
-        <v>173</v>
+      <c r="B199" s="10"/>
+      <c r="C199" s="4" t="s">
+        <v>174</v>
       </c>
       <c r="D199" s="1">
         <v>1</v>
@@ -7905,7 +8282,7 @@
         <v>231</v>
       </c>
       <c r="C200" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -7926,7 +8303,7 @@
         <v>234</v>
       </c>
       <c r="C203" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -7934,16 +8311,16 @@
         <v>235</v>
       </c>
       <c r="C204" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="205" s="1" customFormat="1" spans="1:4">
       <c r="A205" s="1">
         <v>236</v>
       </c>
-      <c r="B205" s="9"/>
+      <c r="B205" s="10"/>
       <c r="C205" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D205" s="1">
         <v>1</v>
@@ -7953,11 +8330,11 @@
       <c r="A206">
         <v>237</v>
       </c>
-      <c r="B206" s="5" t="s">
-        <v>178</v>
+      <c r="B206" s="6" t="s">
+        <v>179</v>
       </c>
       <c r="C206" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -7965,24 +8342,24 @@
         <v>238</v>
       </c>
       <c r="C207" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="208" spans="1:4">
       <c r="A208">
         <v>239</v>
       </c>
-      <c r="C208" s="16" t="s">
-        <v>181</v>
+      <c r="C208" s="9" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="209" s="1" customFormat="1" spans="1:4">
       <c r="A209" s="1">
         <v>240</v>
       </c>
-      <c r="B209" s="9"/>
+      <c r="B209" s="10"/>
       <c r="C209" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D209" s="1">
         <v>1</v>
@@ -7993,7 +8370,7 @@
         <v>241</v>
       </c>
       <c r="C210" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -8001,7 +8378,7 @@
         <v>242</v>
       </c>
       <c r="C211" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -8009,7 +8386,7 @@
         <v>243</v>
       </c>
       <c r="C212" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="213" s="3" customFormat="1" spans="1:4">
@@ -8018,7 +8395,7 @@
       </c>
       <c r="B213" s="12"/>
       <c r="C213" s="14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D213" s="3">
         <v>1</v>
@@ -8028,9 +8405,9 @@
       <c r="A214" s="1">
         <v>245</v>
       </c>
-      <c r="B214" s="9"/>
+      <c r="B214" s="10"/>
       <c r="C214" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D214" s="1">
         <v>1</v>
@@ -8050,8 +8427,8 @@
       <c r="A217">
         <v>248</v>
       </c>
-      <c r="C217" s="8" t="s">
-        <v>188</v>
+      <c r="C217" s="9" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -8059,18 +8436,18 @@
         <v>249</v>
       </c>
       <c r="C218" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="219" s="1" customFormat="1" spans="1:4">
       <c r="A219" s="1">
         <v>250</v>
       </c>
-      <c r="B219" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="C219" s="10" t="s">
+      <c r="B219" s="10" t="s">
         <v>191</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>192</v>
       </c>
       <c r="D219" s="1">
         <v>1</v>
@@ -8081,7 +8458,7 @@
         <v>251</v>
       </c>
       <c r="C220" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -8089,16 +8466,16 @@
         <v>252</v>
       </c>
       <c r="C221" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="222" s="1" customFormat="1" spans="1:4">
       <c r="A222" s="1">
         <v>253</v>
       </c>
-      <c r="B222" s="9"/>
-      <c r="C222" s="10" t="s">
-        <v>194</v>
+      <c r="B222" s="10"/>
+      <c r="C222" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="D222" s="1">
         <v>1</v>
@@ -8114,7 +8491,7 @@
         <v>255</v>
       </c>
       <c r="C224" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -8127,38 +8504,38 @@
         <v>257</v>
       </c>
       <c r="B226" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="C226" s="8" t="s">
         <v>197</v>
+      </c>
+      <c r="C226" s="9" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="227" spans="1:4">
       <c r="A227">
         <v>258</v>
       </c>
-      <c r="B227" s="5" t="s">
-        <v>198</v>
+      <c r="B227" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="C227" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="228" spans="1:4">
       <c r="A228">
         <v>259</v>
       </c>
-      <c r="C228" s="8" t="s">
-        <v>200</v>
+      <c r="C228" s="9" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="229" s="1" customFormat="1" spans="1:4">
       <c r="A229" s="1">
         <v>260</v>
       </c>
-      <c r="B229" s="9"/>
-      <c r="C229" s="10" t="s">
-        <v>201</v>
+      <c r="B229" s="10"/>
+      <c r="C229" s="4" t="s">
+        <v>202</v>
       </c>
       <c r="D229" s="1">
         <v>1</v>
@@ -8168,8 +8545,8 @@
       <c r="A230">
         <v>261</v>
       </c>
-      <c r="C230" s="7" t="s">
-        <v>202</v>
+      <c r="C230" s="8" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -8177,19 +8554,19 @@
         <v>262</v>
       </c>
       <c r="C231" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="232" s="3" customFormat="1" spans="1:4">
-      <c r="A232" s="3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="232" s="1" customFormat="1" spans="1:4">
+      <c r="A232" s="1">
         <v>263</v>
       </c>
-      <c r="B232" s="12"/>
-      <c r="C232" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="D232" s="3">
-        <v>1</v>
+      <c r="B232" s="10"/>
+      <c r="C232" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D232" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -8197,18 +8574,18 @@
         <v>264</v>
       </c>
       <c r="C233" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="234" s="3" customFormat="1" spans="1:4">
       <c r="A234" s="3">
         <v>265</v>
       </c>
-      <c r="B234" s="20" t="s">
-        <v>206</v>
+      <c r="B234" s="18" t="s">
+        <v>207</v>
       </c>
       <c r="C234" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D234" s="3">
         <v>1</v>
@@ -8219,7 +8596,7 @@
         <v>266</v>
       </c>
       <c r="C235" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -8227,7 +8604,7 @@
         <v>267</v>
       </c>
       <c r="C236" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -8235,7 +8612,7 @@
         <v>268</v>
       </c>
       <c r="C237" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -8243,16 +8620,16 @@
         <v>269</v>
       </c>
       <c r="C238" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="239" s="1" customFormat="1" spans="1:4">
       <c r="A239" s="1">
         <v>270</v>
       </c>
-      <c r="B239" s="9"/>
-      <c r="C239" s="10" t="s">
-        <v>212</v>
+      <c r="B239" s="10"/>
+      <c r="C239" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="D239" s="1">
         <v>1</v>
@@ -8262,9 +8639,9 @@
       <c r="A240" s="1">
         <v>271</v>
       </c>
-      <c r="B240" s="9"/>
+      <c r="B240" s="10"/>
       <c r="C240" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D240" s="1">
         <v>1</v>
@@ -8275,7 +8652,7 @@
         <v>272</v>
       </c>
       <c r="C241" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -8288,7 +8665,7 @@
         <v>274</v>
       </c>
       <c r="C243" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -8296,7 +8673,7 @@
         <v>275</v>
       </c>
       <c r="C244" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -8304,7 +8681,7 @@
         <v>276</v>
       </c>
       <c r="C245" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="246" s="3" customFormat="1" spans="1:4">
@@ -8313,7 +8690,7 @@
       </c>
       <c r="B246" s="12"/>
       <c r="C246" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D246" s="3">
         <v>1</v>
@@ -8324,7 +8701,7 @@
         <v>278</v>
       </c>
       <c r="C247" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -8337,19 +8714,21 @@
         <v>280</v>
       </c>
       <c r="C249" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="250" s="1" customFormat="1" spans="1:4">
       <c r="A250" s="1">
         <v>281</v>
       </c>
-      <c r="B250" s="9"/>
+      <c r="B250" s="10" t="s">
+        <v>221</v>
+      </c>
       <c r="C250" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D250" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -8357,21 +8736,27 @@
         <v>282</v>
       </c>
     </row>
-    <row r="252" spans="1:4">
-      <c r="A252">
+    <row r="252" s="5" customFormat="1" spans="1:4">
+      <c r="A252" s="5">
         <v>283</v>
       </c>
-      <c r="C252" t="s">
-        <v>221</v>
+      <c r="B252" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="C252" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D252" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="253" s="1" customFormat="1" spans="1:4">
       <c r="A253" s="1">
         <v>284</v>
       </c>
-      <c r="B253" s="9"/>
-      <c r="C253" s="10" t="s">
-        <v>222</v>
+      <c r="B253" s="10"/>
+      <c r="C253" s="4" t="s">
+        <v>225</v>
       </c>
       <c r="D253" s="1">
         <v>1</v>
@@ -8386,9 +8771,9 @@
       <c r="A255" s="1">
         <v>286</v>
       </c>
-      <c r="B255" s="9"/>
-      <c r="C255" s="19" t="s">
-        <v>223</v>
+      <c r="B255" s="10"/>
+      <c r="C255" s="2" t="s">
+        <v>226</v>
       </c>
       <c r="D255" s="1">
         <v>1</v>
@@ -8399,24 +8784,33 @@
         <v>287</v>
       </c>
       <c r="C256" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="257" s="1" customFormat="1" spans="1:4">
       <c r="A257" s="1">
         <v>288</v>
       </c>
-      <c r="B257" s="9"/>
-      <c r="C257" s="10" t="s">
-        <v>225</v>
+      <c r="B257" s="10"/>
+      <c r="C257" s="4" t="s">
+        <v>228</v>
       </c>
       <c r="D257" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:4">
-      <c r="A258">
+    <row r="258" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A258" s="1">
         <v>289</v>
+      </c>
+      <c r="B258" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="C258" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="D258" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -8424,7 +8818,7 @@
         <v>290</v>
       </c>
       <c r="C259" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -8432,7 +8826,7 @@
         <v>291</v>
       </c>
       <c r="C260" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -8440,7 +8834,7 @@
         <v>292</v>
       </c>
       <c r="C261" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -8448,7 +8842,7 @@
         <v>293</v>
       </c>
       <c r="C262" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -8456,7 +8850,7 @@
         <v>294</v>
       </c>
       <c r="C263" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -8464,18 +8858,18 @@
         <v>295</v>
       </c>
       <c r="C264" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="265" spans="1:4">
       <c r="A265">
         <v>296</v>
       </c>
-      <c r="B265" s="5" t="s">
-        <v>232</v>
+      <c r="B265" s="6" t="s">
+        <v>237</v>
       </c>
       <c r="C265" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -8483,7 +8877,7 @@
         <v>297</v>
       </c>
       <c r="C266" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -8491,7 +8885,7 @@
         <v>298</v>
       </c>
       <c r="C267" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -8509,23 +8903,27 @@
         <v>301</v>
       </c>
     </row>
-    <row r="271" spans="1:4">
-      <c r="A271">
+    <row r="271" s="1" customFormat="1" spans="1:4">
+      <c r="A271" s="1">
         <v>302</v>
       </c>
-      <c r="C271" s="7" t="s">
-        <v>236</v>
+      <c r="B271" s="10"/>
+      <c r="C271" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D271" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="272" spans="1:4">
       <c r="A272">
         <v>303</v>
       </c>
-      <c r="B272" s="5" t="s">
-        <v>237</v>
+      <c r="B272" s="6" t="s">
+        <v>242</v>
       </c>
       <c r="C272" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -8533,7 +8931,7 @@
         <v>304</v>
       </c>
       <c r="C273" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -8546,10 +8944,10 @@
         <v>306</v>
       </c>
       <c r="B275" s="11" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="D275" s="1">
         <v>1</v>
@@ -8559,9 +8957,9 @@
       <c r="A276" s="1">
         <v>307</v>
       </c>
-      <c r="B276" s="9"/>
-      <c r="C276" s="19" t="s">
-        <v>242</v>
+      <c r="B276" s="10"/>
+      <c r="C276" s="2" t="s">
+        <v>247</v>
       </c>
       <c r="D276" s="1">
         <v>1</v>
@@ -8572,7 +8970,7 @@
         <v>308</v>
       </c>
       <c r="C277" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -8585,7 +8983,7 @@
         <v>310</v>
       </c>
       <c r="C279" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -8593,7 +8991,7 @@
         <v>311</v>
       </c>
       <c r="C280" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -8601,18 +8999,18 @@
         <v>312</v>
       </c>
       <c r="C281" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="282" spans="1:4">
       <c r="A282">
         <v>313</v>
       </c>
-      <c r="B282" s="5" t="s">
-        <v>247</v>
+      <c r="B282" s="6" t="s">
+        <v>252</v>
       </c>
       <c r="C282" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -8624,9 +9022,9 @@
       <c r="A284" s="1">
         <v>315</v>
       </c>
-      <c r="B284" s="9"/>
-      <c r="C284" s="19" t="s">
-        <v>249</v>
+      <c r="B284" s="10"/>
+      <c r="C284" s="2" t="s">
+        <v>254</v>
       </c>
       <c r="D284" s="1">
         <v>1</v>
@@ -8641,8 +9039,8 @@
       <c r="A286">
         <v>317</v>
       </c>
-      <c r="C286" s="8" t="s">
-        <v>250</v>
+      <c r="C286" s="9" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -8654,11 +9052,11 @@
       <c r="A288">
         <v>319</v>
       </c>
-      <c r="B288" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="C288" s="25" t="s">
-        <v>252</v>
+      <c r="B288" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="C288" s="24" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -8666,7 +9064,7 @@
         <v>320</v>
       </c>
       <c r="C289" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -8674,16 +9072,16 @@
         <v>321</v>
       </c>
       <c r="C290" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="291" s="1" customFormat="1" spans="1:4">
       <c r="A291" s="1">
         <v>322</v>
       </c>
-      <c r="B291" s="9"/>
-      <c r="C291" s="10" t="s">
-        <v>255</v>
+      <c r="B291" s="10"/>
+      <c r="C291" s="4" t="s">
+        <v>260</v>
       </c>
       <c r="D291" s="1">
         <v>1</v>
@@ -8694,7 +9092,7 @@
         <v>323</v>
       </c>
       <c r="C292" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
     </row>
     <row r="293" s="3" customFormat="1" spans="1:4">
@@ -8703,7 +9101,7 @@
       </c>
       <c r="B293" s="12"/>
       <c r="C293" s="14" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="D293" s="3">
         <v>1</v>
@@ -8714,18 +9112,18 @@
         <v>325</v>
       </c>
       <c r="C294" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="295" s="3" customFormat="1" spans="1:4">
       <c r="A295" s="3">
         <v>326</v>
       </c>
-      <c r="B295" s="20" t="s">
-        <v>259</v>
+      <c r="B295" s="18" t="s">
+        <v>264</v>
       </c>
       <c r="C295" s="13" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D295" s="3">
         <v>1</v>
@@ -8736,18 +9134,18 @@
         <v>327</v>
       </c>
       <c r="C296" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
     </row>
     <row r="297" s="1" customFormat="1" spans="1:4">
       <c r="A297" s="1">
         <v>328</v>
       </c>
-      <c r="B297" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="C297" s="26" t="s">
-        <v>263</v>
+      <c r="B297" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="C297" s="25" t="s">
+        <v>268</v>
       </c>
       <c r="D297" s="1">
         <v>1</v>
@@ -8758,24 +9156,28 @@
         <v>329</v>
       </c>
       <c r="C298" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="299" spans="1:4">
-      <c r="A299">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="299" s="1" customFormat="1" spans="1:4">
+      <c r="A299" s="1">
         <v>330</v>
       </c>
-      <c r="C299" t="s">
-        <v>265</v>
+      <c r="B299" s="10"/>
+      <c r="C299" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D299" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="300" s="1" customFormat="1" spans="1:4">
       <c r="A300" s="1">
         <v>331</v>
       </c>
-      <c r="B300" s="9"/>
-      <c r="C300" s="10" t="s">
-        <v>266</v>
+      <c r="B300" s="10"/>
+      <c r="C300" s="4" t="s">
+        <v>271</v>
       </c>
       <c r="D300" s="1">
         <v>1</v>
@@ -8785,20 +9187,20 @@
       <c r="A301">
         <v>332</v>
       </c>
-      <c r="B301" s="5" t="s">
-        <v>267</v>
+      <c r="B301" s="6" t="s">
+        <v>272</v>
       </c>
       <c r="C301" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="302" s="1" customFormat="1" spans="1:4">
       <c r="A302" s="1">
         <v>333</v>
       </c>
-      <c r="B302" s="9"/>
+      <c r="B302" s="10"/>
       <c r="C302" s="2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="D302" s="1">
         <v>1</v>
@@ -8809,10 +9211,10 @@
         <v>334</v>
       </c>
       <c r="B303" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="C303" s="8" t="s">
-        <v>271</v>
+        <v>275</v>
+      </c>
+      <c r="C303" s="9" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -8820,16 +9222,16 @@
         <v>335</v>
       </c>
       <c r="C304" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="305" s="1" customFormat="1" spans="1:4">
       <c r="A305" s="1">
         <v>336</v>
       </c>
-      <c r="B305" s="9"/>
+      <c r="B305" s="10"/>
       <c r="C305" s="2" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="D305" s="1">
         <v>1</v>
@@ -8850,15 +9252,15 @@
         <v>339</v>
       </c>
       <c r="C308" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="309" spans="1:4">
       <c r="A309">
         <v>340</v>
       </c>
-      <c r="C309" s="16" t="s">
-        <v>275</v>
+      <c r="C309" s="9" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="310" s="3" customFormat="1" spans="1:4">
@@ -8867,7 +9269,7 @@
       </c>
       <c r="B310" s="12"/>
       <c r="C310" s="14" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D310" s="3">
         <v>1</v>
@@ -8878,7 +9280,7 @@
         <v>342</v>
       </c>
       <c r="C311" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -8886,27 +9288,27 @@
         <v>343</v>
       </c>
       <c r="C312" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="313" s="1" customFormat="1" spans="1:4">
       <c r="A313" s="1">
         <v>344</v>
       </c>
-      <c r="B313" s="9"/>
-      <c r="C313" s="2" t="s">
-        <v>279</v>
+      <c r="B313" s="10"/>
+      <c r="C313" s="4" t="s">
+        <v>284</v>
       </c>
       <c r="D313" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314" spans="1:4">
       <c r="A314">
         <v>345</v>
       </c>
-      <c r="C314" s="8" t="s">
-        <v>280</v>
+      <c r="C314" s="9" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -8918,11 +9320,11 @@
       <c r="A316" s="3">
         <v>347</v>
       </c>
-      <c r="B316" s="27" t="s">
-        <v>281</v>
+      <c r="B316" s="26" t="s">
+        <v>286</v>
       </c>
       <c r="C316" s="14" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="D316" s="3">
         <v>1</v>
@@ -8932,8 +9334,8 @@
       <c r="A317">
         <v>348</v>
       </c>
-      <c r="C317" s="8" t="s">
-        <v>283</v>
+      <c r="C317" s="9" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -8941,7 +9343,7 @@
         <v>349</v>
       </c>
       <c r="C318" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -8949,16 +9351,16 @@
         <v>350</v>
       </c>
       <c r="C319" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="320" s="1" customFormat="1" spans="1:4">
       <c r="A320" s="1">
         <v>351</v>
       </c>
-      <c r="B320" s="9"/>
-      <c r="C320" s="10" t="s">
-        <v>286</v>
+      <c r="B320" s="10"/>
+      <c r="C320" s="4" t="s">
+        <v>291</v>
       </c>
       <c r="D320" s="1">
         <v>1</v>
@@ -8968,9 +9370,9 @@
       <c r="A321" s="1">
         <v>352</v>
       </c>
-      <c r="B321" s="9"/>
-      <c r="C321" s="10" t="s">
-        <v>287</v>
+      <c r="B321" s="10"/>
+      <c r="C321" s="4" t="s">
+        <v>292</v>
       </c>
       <c r="D321" s="1">
         <v>1</v>
@@ -8981,7 +9383,7 @@
         <v>353</v>
       </c>
       <c r="C322" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -8993,9 +9395,9 @@
       <c r="A324" s="1">
         <v>355</v>
       </c>
-      <c r="B324" s="9"/>
-      <c r="C324" s="19" t="s">
-        <v>289</v>
+      <c r="B324" s="10"/>
+      <c r="C324" s="2" t="s">
+        <v>294</v>
       </c>
       <c r="D324" s="1">
         <v>1</v>
@@ -9005,31 +9407,31 @@
       <c r="A325">
         <v>356</v>
       </c>
-      <c r="B325" s="5" t="s">
-        <v>290</v>
+      <c r="B325" s="6" t="s">
+        <v>295</v>
       </c>
       <c r="C325" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="326" s="1" customFormat="1" spans="1:4">
       <c r="A326" s="1">
         <v>357</v>
       </c>
-      <c r="B326" s="9"/>
+      <c r="B326" s="10"/>
       <c r="C326" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="D326" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="327" spans="1:4">
       <c r="A327">
         <v>358</v>
       </c>
-      <c r="C327" s="8" t="s">
-        <v>293</v>
+      <c r="C327" s="9" t="s">
+        <v>298</v>
       </c>
       <c r="D327">
         <v>1</v>
@@ -9040,19 +9442,21 @@
         <v>359</v>
       </c>
       <c r="C328" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="329" s="1" customFormat="1" spans="1:4">
       <c r="A329" s="1">
         <v>360</v>
       </c>
-      <c r="B329" s="9"/>
+      <c r="B329" s="10" t="s">
+        <v>300</v>
+      </c>
       <c r="C329" s="4" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="D329" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -9060,27 +9464,27 @@
         <v>361</v>
       </c>
       <c r="C330" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
     </row>
     <row r="331" spans="1:4">
       <c r="A331">
         <v>362</v>
       </c>
-      <c r="B331" s="5" t="s">
-        <v>297</v>
+      <c r="B331" s="6" t="s">
+        <v>303</v>
       </c>
       <c r="C331" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="332" s="1" customFormat="1" spans="1:4">
       <c r="A332" s="1">
         <v>363</v>
       </c>
-      <c r="B332" s="9"/>
-      <c r="C332" s="10" t="s">
-        <v>299</v>
+      <c r="B332" s="10"/>
+      <c r="C332" s="4" t="s">
+        <v>305</v>
       </c>
       <c r="D332" s="1">
         <v>1</v>
@@ -9090,9 +9494,9 @@
       <c r="A333" s="1">
         <v>364</v>
       </c>
-      <c r="B333" s="9"/>
+      <c r="B333" s="10"/>
       <c r="C333" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="D333" s="1">
         <v>1</v>
@@ -9103,7 +9507,7 @@
         <v>365</v>
       </c>
       <c r="C334" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -9111,7 +9515,7 @@
         <v>366</v>
       </c>
       <c r="C335" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -9123,9 +9527,9 @@
       <c r="A337" s="1">
         <v>368</v>
       </c>
-      <c r="B337" s="9"/>
+      <c r="B337" s="10"/>
       <c r="C337" s="4" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="D337" s="1">
         <v>1</v>
@@ -9135,25 +9539,25 @@
       <c r="A338" s="1">
         <v>369</v>
       </c>
-      <c r="B338" s="9" t="s">
-        <v>304</v>
+      <c r="B338" s="10" t="s">
+        <v>310</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="D338" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="339" spans="1:4">
       <c r="A339">
         <v>370</v>
       </c>
-      <c r="B339" s="5" t="s">
-        <v>306</v>
+      <c r="B339" s="6" t="s">
+        <v>312</v>
       </c>
       <c r="C339" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -9161,16 +9565,16 @@
         <v>371</v>
       </c>
       <c r="C340" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="341" s="1" customFormat="1" spans="1:4">
       <c r="A341" s="1">
         <v>372</v>
       </c>
-      <c r="B341" s="9"/>
+      <c r="B341" s="10"/>
       <c r="C341" s="2" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="D341" s="1">
         <v>1</v>
@@ -9180,9 +9584,9 @@
       <c r="A342" s="1">
         <v>373</v>
       </c>
-      <c r="B342" s="9"/>
+      <c r="B342" s="10"/>
       <c r="C342" s="2" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="D342" s="1">
         <v>1</v>
@@ -9192,25 +9596,25 @@
       <c r="A343">
         <v>374</v>
       </c>
-      <c r="C343" s="8" t="s">
-        <v>311</v>
+      <c r="C343" s="9" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="344" spans="1:4">
       <c r="A344">
         <v>375</v>
       </c>
-      <c r="C344" s="7" t="s">
-        <v>312</v>
+      <c r="C344" s="8" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="345" s="1" customFormat="1" spans="1:4">
       <c r="A345" s="1">
         <v>376</v>
       </c>
-      <c r="B345" s="9"/>
+      <c r="B345" s="10"/>
       <c r="C345" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D345" s="1">
         <v>1</v>
@@ -9221,7 +9625,7 @@
         <v>377</v>
       </c>
       <c r="C346" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -9229,15 +9633,19 @@
         <v>378</v>
       </c>
       <c r="C347" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="348" spans="1:4">
-      <c r="A348">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="348" s="1" customFormat="1" ht="13" customHeight="1" spans="1:4">
+      <c r="A348" s="1">
         <v>379</v>
       </c>
-      <c r="C348" t="s">
-        <v>316</v>
+      <c r="B348" s="10"/>
+      <c r="C348" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D348" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -9245,7 +9653,7 @@
         <v>380</v>
       </c>
       <c r="C349" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -9253,18 +9661,18 @@
         <v>381</v>
       </c>
       <c r="C350" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="351" s="1" customFormat="1" spans="1:4">
       <c r="A351" s="1">
         <v>382</v>
       </c>
-      <c r="B351" s="9" t="s">
-        <v>319</v>
+      <c r="B351" s="10" t="s">
+        <v>325</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="D351" s="1">
         <v>1</v>
@@ -9275,7 +9683,7 @@
         <v>383</v>
       </c>
       <c r="C352" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
     </row>
     <row r="353" spans="1:3">
@@ -9283,7 +9691,7 @@
         <v>384</v>
       </c>
       <c r="C353" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="354" spans="1:3">
@@ -9291,7 +9699,7 @@
         <v>385</v>
       </c>
       <c r="C354" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="355" spans="1:3">
@@ -9304,7 +9712,7 @@
         <v>387</v>
       </c>
       <c r="C356" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
     </row>
     <row r="357" spans="1:3">
@@ -9312,7 +9720,7 @@
         <v>388</v>
       </c>
       <c r="C357" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
     </row>
     <row r="358" spans="1:3">
@@ -9320,7 +9728,7 @@
         <v>389</v>
       </c>
       <c r="C358" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
     </row>
     <row r="359" spans="1:3">
@@ -9328,7 +9736,7 @@
         <v>390</v>
       </c>
       <c r="C359" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -9341,7 +9749,7 @@
         <v>392</v>
       </c>
       <c r="C361" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="362" spans="1:3">
@@ -9355,7 +9763,7 @@
       </c>
       <c r="B363" s="12"/>
       <c r="C363" s="13" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="364" spans="1:3">
@@ -9363,7 +9771,7 @@
         <v>395</v>
       </c>
       <c r="C364" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
     </row>
     <row r="365" spans="1:3">
@@ -9371,7 +9779,7 @@
         <v>396</v>
       </c>
       <c r="C365" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
     </row>
     <row r="366" spans="1:3">
@@ -9379,7 +9787,7 @@
         <v>397</v>
       </c>
       <c r="C366" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
     </row>
     <row r="367" spans="1:3">
@@ -9392,7 +9800,7 @@
         <v>399</v>
       </c>
       <c r="C368" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -9400,7 +9808,7 @@
         <v>400</v>
       </c>
       <c r="C369" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -9408,16 +9816,16 @@
         <v>401</v>
       </c>
       <c r="C370" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="371" s="1" customFormat="1" spans="1:4">
       <c r="A371" s="1">
         <v>402</v>
       </c>
-      <c r="B371" s="9"/>
+      <c r="B371" s="10"/>
       <c r="C371" s="2" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="D371" s="1">
         <v>1</v>
@@ -9432,8 +9840,8 @@
       <c r="A373">
         <v>404</v>
       </c>
-      <c r="C373" s="8" t="s">
-        <v>336</v>
+      <c r="C373" s="9" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="374" s="1" customFormat="1" spans="1:4">
@@ -9441,10 +9849,10 @@
         <v>405</v>
       </c>
       <c r="B374" s="11" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="D374" s="1">
         <v>1</v>
@@ -9454,9 +9862,9 @@
       <c r="A375" s="1">
         <v>406</v>
       </c>
-      <c r="B375" s="9"/>
-      <c r="C375" s="19" t="s">
-        <v>339</v>
+      <c r="B375" s="10"/>
+      <c r="C375" s="2" t="s">
+        <v>345</v>
       </c>
       <c r="D375" s="1">
         <v>1</v>
@@ -9467,7 +9875,7 @@
         <v>407</v>
       </c>
       <c r="C376" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -9475,7 +9883,7 @@
         <v>408</v>
       </c>
       <c r="C377" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -9483,7 +9891,7 @@
         <v>409</v>
       </c>
       <c r="C378" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -9491,7 +9899,7 @@
         <v>410</v>
       </c>
       <c r="C379" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -9504,18 +9912,18 @@
         <v>412</v>
       </c>
       <c r="B381" s="12" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="C381" s="13" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
     </row>
     <row r="382" spans="1:4">
       <c r="A382">
         <v>413</v>
       </c>
-      <c r="C382" s="8" t="s">
-        <v>346</v>
+      <c r="C382" s="9" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -9523,15 +9931,15 @@
         <v>414</v>
       </c>
       <c r="C383" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
     </row>
     <row r="384" spans="1:4">
       <c r="A384">
         <v>415</v>
       </c>
-      <c r="C384" s="8" t="s">
-        <v>348</v>
+      <c r="C384" s="9" t="s">
+        <v>354</v>
       </c>
       <c r="D384">
         <v>1</v>
@@ -9541,8 +9949,8 @@
       <c r="A385">
         <v>416</v>
       </c>
-      <c r="C385" s="8" t="s">
-        <v>349</v>
+      <c r="C385" s="9" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -9550,7 +9958,7 @@
         <v>417</v>
       </c>
       <c r="C386" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -9573,27 +9981,27 @@
         <v>421</v>
       </c>
       <c r="C390" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
     </row>
     <row r="391" ht="42.75" spans="1:4">
       <c r="A391">
         <v>422</v>
       </c>
-      <c r="C391" s="6" t="s">
-        <v>352</v>
+      <c r="C391" s="7" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="392" s="1" customFormat="1" spans="1:4">
       <c r="A392" s="1">
         <v>423</v>
       </c>
-      <c r="B392" s="9"/>
-      <c r="C392" s="10" t="s">
-        <v>353</v>
+      <c r="B392" s="10"/>
+      <c r="C392" s="4" t="s">
+        <v>359</v>
       </c>
       <c r="D392" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -9601,7 +10009,7 @@
         <v>424</v>
       </c>
       <c r="C393" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -9609,27 +10017,27 @@
         <v>425</v>
       </c>
       <c r="C394" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="395" spans="1:4">
       <c r="A395">
         <v>426</v>
       </c>
-      <c r="C395" s="8" t="s">
-        <v>356</v>
+      <c r="C395" s="9" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="396" s="1" customFormat="1" spans="1:4">
       <c r="A396" s="1">
         <v>427</v>
       </c>
-      <c r="B396" s="9"/>
-      <c r="C396" s="10" t="s">
-        <v>357</v>
+      <c r="B396" s="10"/>
+      <c r="C396" s="4" t="s">
+        <v>363</v>
       </c>
       <c r="D396" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -9642,7 +10050,7 @@
         <v>429</v>
       </c>
       <c r="C398" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -9650,7 +10058,7 @@
         <v>430</v>
       </c>
       <c r="C399" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -9663,18 +10071,18 @@
         <v>432</v>
       </c>
       <c r="C401" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="402" spans="1:4">
       <c r="A402">
         <v>433</v>
       </c>
-      <c r="B402" s="5" t="s">
-        <v>361</v>
+      <c r="B402" s="6" t="s">
+        <v>367</v>
       </c>
       <c r="C402" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -9686,9 +10094,9 @@
       <c r="A404" s="1">
         <v>435</v>
       </c>
-      <c r="B404" s="9"/>
+      <c r="B404" s="10"/>
       <c r="C404" s="2" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
     </row>
     <row r="405" s="3" customFormat="1" ht="13.05" customHeight="1" spans="1:4">
@@ -9697,7 +10105,7 @@
       </c>
       <c r="B405" s="12"/>
       <c r="C405" s="3" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -9710,7 +10118,7 @@
         <v>438</v>
       </c>
       <c r="C407" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -9718,7 +10126,7 @@
         <v>439</v>
       </c>
       <c r="C408" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -9726,7 +10134,7 @@
         <v>440</v>
       </c>
       <c r="C409" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -9734,7 +10142,7 @@
         <v>441</v>
       </c>
       <c r="C410" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -9747,7 +10155,7 @@
         <v>443</v>
       </c>
       <c r="C412" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="413" s="3" customFormat="1" spans="1:4">
@@ -9756,7 +10164,7 @@
       </c>
       <c r="B413" s="12"/>
       <c r="C413" s="13" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="D413" s="3">
         <v>1</v>
@@ -9767,7 +10175,7 @@
         <v>445</v>
       </c>
       <c r="C414" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -9780,7 +10188,7 @@
         <v>447</v>
       </c>
       <c r="C416" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -9788,7 +10196,7 @@
         <v>448</v>
       </c>
       <c r="C417" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -9796,15 +10204,15 @@
         <v>449</v>
       </c>
       <c r="C418" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="419" spans="1:4">
       <c r="A419">
         <v>450</v>
       </c>
-      <c r="C419" s="8" t="s">
-        <v>375</v>
+      <c r="C419" s="9" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -9816,9 +10224,9 @@
       <c r="A421" s="1">
         <v>452</v>
       </c>
-      <c r="B421" s="9"/>
+      <c r="B421" s="10"/>
       <c r="C421" s="1" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="D421" s="1">
         <v>1</v>
@@ -9828,8 +10236,8 @@
       <c r="A422">
         <v>453</v>
       </c>
-      <c r="C422" s="8" t="s">
-        <v>377</v>
+      <c r="C422" s="9" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -9837,7 +10245,7 @@
         <v>454</v>
       </c>
       <c r="C423" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -9845,18 +10253,18 @@
         <v>455</v>
       </c>
       <c r="C424" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="425" spans="1:4">
       <c r="A425">
         <v>456</v>
       </c>
-      <c r="B425" s="5" t="s">
-        <v>380</v>
+      <c r="B425" s="6" t="s">
+        <v>386</v>
       </c>
       <c r="C425" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -9868,11 +10276,11 @@
       <c r="A427">
         <v>458</v>
       </c>
-      <c r="B427" s="5" t="s">
-        <v>382</v>
+      <c r="B427" s="6" t="s">
+        <v>388</v>
       </c>
       <c r="C427" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -9880,7 +10288,7 @@
         <v>459</v>
       </c>
       <c r="C428" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -9893,7 +10301,7 @@
         <v>461</v>
       </c>
       <c r="C430" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -9901,18 +10309,21 @@
         <v>462</v>
       </c>
       <c r="C431" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="432" spans="1:4">
-      <c r="A432">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="432" s="1" customFormat="1" ht="28.5" spans="1:4">
+      <c r="A432" s="1">
         <v>463</v>
       </c>
-      <c r="B432" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="C432" t="s">
-        <v>315</v>
+      <c r="B432" s="27" t="s">
+        <v>393</v>
+      </c>
+      <c r="C432" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="D432" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="433" spans="1:3">
@@ -9930,7 +10341,7 @@
         <v>466</v>
       </c>
       <c r="C435" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="436" spans="1:3">
@@ -9938,7 +10349,7 @@
         <v>467</v>
       </c>
       <c r="C436" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
     </row>
     <row r="437" spans="1:3">
@@ -9946,7 +10357,7 @@
         <v>468</v>
       </c>
       <c r="C437" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="438" spans="1:3">
@@ -9959,7 +10370,7 @@
         <v>470</v>
       </c>
       <c r="C439" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
     </row>
     <row r="440" spans="1:3">
@@ -9967,7 +10378,7 @@
         <v>471</v>
       </c>
       <c r="C440" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="441" spans="1:3">
@@ -9975,18 +10386,18 @@
         <v>472</v>
       </c>
       <c r="C441" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="442" spans="1:3">
       <c r="A442">
         <v>473</v>
       </c>
-      <c r="B442" s="5" t="s">
-        <v>394</v>
+      <c r="B442" s="6" t="s">
+        <v>400</v>
       </c>
       <c r="C442" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="443" spans="1:3">
@@ -9994,7 +10405,7 @@
         <v>474</v>
       </c>
       <c r="C443" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="444" spans="1:3">
@@ -10002,7 +10413,7 @@
         <v>475</v>
       </c>
       <c r="C444" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="445" spans="1:3">
@@ -10010,7 +10421,7 @@
         <v>476</v>
       </c>
       <c r="C445" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="446" spans="1:3">
@@ -10018,7 +10429,7 @@
         <v>477</v>
       </c>
       <c r="C446" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="447" spans="1:3">
@@ -10026,15 +10437,15 @@
         <v>478</v>
       </c>
       <c r="C447" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="448" spans="1:3">
       <c r="A448">
         <v>479</v>
       </c>
-      <c r="C448" s="7" t="s">
-        <v>401</v>
+      <c r="C448" s="8" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="449" spans="1:5">
@@ -10042,7 +10453,7 @@
         <v>480</v>
       </c>
       <c r="C449" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="450" spans="1:5">
@@ -10050,22 +10461,22 @@
         <v>481</v>
       </c>
       <c r="C450" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="451" s="1" customFormat="1" spans="1:5">
       <c r="A451" s="1">
         <v>482</v>
       </c>
-      <c r="B451" s="9"/>
+      <c r="B451" s="10"/>
       <c r="C451" s="2" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="D451" s="1">
         <v>1</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
     </row>
     <row r="452" spans="1:5">
@@ -10073,7 +10484,7 @@
         <v>483</v>
       </c>
       <c r="C452" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="453" spans="1:5">
@@ -10081,7 +10492,7 @@
         <v>484</v>
       </c>
       <c r="C453" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
     </row>
     <row r="454" spans="1:5">
@@ -10089,7 +10500,7 @@
         <v>485</v>
       </c>
       <c r="C454" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
     </row>
     <row r="455" spans="1:5">
@@ -10101,19 +10512,19 @@
       <c r="A456">
         <v>487</v>
       </c>
-      <c r="B456" s="5" t="s">
+      <c r="B456" s="6" t="s">
         <v>75</v>
       </c>
       <c r="C456" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
     </row>
     <row r="457" spans="1:5">
       <c r="A457">
         <v>488</v>
       </c>
-      <c r="B457" s="5" t="s">
-        <v>410</v>
+      <c r="B457" s="6" t="s">
+        <v>416</v>
       </c>
       <c r="C457" t="s">
         <v>78</v>
@@ -10128,11 +10539,11 @@
       <c r="A459">
         <v>490</v>
       </c>
-      <c r="B459" s="5" t="s">
-        <v>411</v>
+      <c r="B459" s="6" t="s">
+        <v>417</v>
       </c>
       <c r="C459" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="460" spans="1:5">
@@ -10145,7 +10556,7 @@
         <v>492</v>
       </c>
       <c r="C461" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="462" spans="1:5">
@@ -10153,7 +10564,7 @@
         <v>493</v>
       </c>
       <c r="C462" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="463" spans="1:5">
@@ -10161,7 +10572,7 @@
         <v>494</v>
       </c>
       <c r="C463" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="464" spans="1:5">
@@ -10174,14 +10585,14 @@
         <v>496</v>
       </c>
       <c r="C465" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="466" spans="1:4">
       <c r="A466">
         <v>497</v>
       </c>
-      <c r="C466" s="18">
+      <c r="C466" s="17">
         <v>200</v>
       </c>
     </row>
@@ -10189,9 +10600,9 @@
       <c r="A467" s="1">
         <v>498</v>
       </c>
-      <c r="B467" s="9"/>
-      <c r="C467" s="10" t="s">
-        <v>417</v>
+      <c r="B467" s="10"/>
+      <c r="C467" s="4" t="s">
+        <v>423</v>
       </c>
       <c r="D467" s="1">
         <v>1</v>
@@ -10207,7 +10618,7 @@
         <v>500</v>
       </c>
       <c r="C469" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -10215,7 +10626,7 @@
         <v>501</v>
       </c>
       <c r="C470" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -10239,16 +10650,16 @@
       </c>
       <c r="B474" s="12"/>
       <c r="C474" s="3" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="475" s="1" customFormat="1" ht="28.5" spans="1:4">
       <c r="A475" s="1">
         <v>506</v>
       </c>
-      <c r="B475" s="9"/>
+      <c r="B475" s="10"/>
       <c r="C475" s="28" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="D475" s="1">
         <v>1</v>
@@ -10259,7 +10670,7 @@
         <v>507</v>
       </c>
       <c r="C476" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="477" spans="1:4">
@@ -10267,7 +10678,7 @@
         <v>508</v>
       </c>
       <c r="C477" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="478" spans="1:4">
@@ -10275,18 +10686,18 @@
         <v>509</v>
       </c>
       <c r="C478" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="479" spans="1:4">
       <c r="A479">
         <v>510</v>
       </c>
-      <c r="B479" s="17" t="s">
-        <v>425</v>
-      </c>
-      <c r="C479" s="8" t="s">
-        <v>426</v>
+      <c r="B479" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="C479" s="9" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="480" spans="1:4">
@@ -10294,7 +10705,7 @@
         <v>511</v>
       </c>
       <c r="C480" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
     </row>
     <row r="481" spans="1:4">
@@ -10317,7 +10728,7 @@
         <v>515</v>
       </c>
       <c r="C484" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="485" spans="1:4">
@@ -10329,11 +10740,11 @@
       <c r="A486">
         <v>517</v>
       </c>
-      <c r="B486" s="5" t="s">
-        <v>429</v>
+      <c r="B486" s="6" t="s">
+        <v>435</v>
       </c>
       <c r="C486" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
     </row>
     <row r="487" spans="1:4">
@@ -10345,11 +10756,11 @@
       <c r="A488" s="3">
         <v>519</v>
       </c>
-      <c r="B488" s="27" t="s">
-        <v>431</v>
+      <c r="B488" s="26" t="s">
+        <v>437</v>
       </c>
       <c r="C488" s="3" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="489" spans="1:4">
@@ -10357,7 +10768,7 @@
         <v>520</v>
       </c>
       <c r="C489" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="490" spans="1:4">
@@ -10365,7 +10776,7 @@
         <v>521</v>
       </c>
       <c r="C490" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="491" spans="1:4">
@@ -10379,7 +10790,7 @@
       </c>
       <c r="B492" s="12"/>
       <c r="C492" s="3" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
     </row>
     <row r="493" spans="1:4">
@@ -10387,29 +10798,29 @@
         <v>524</v>
       </c>
       <c r="C493" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
     </row>
     <row r="494" spans="1:4">
       <c r="A494">
         <v>525</v>
       </c>
-      <c r="B494" s="5" t="s">
-        <v>437</v>
+      <c r="B494" s="6" t="s">
+        <v>443</v>
       </c>
       <c r="C494" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="495" s="1" customFormat="1" spans="1:4">
       <c r="A495" s="1">
         <v>526</v>
       </c>
-      <c r="B495" s="9" t="s">
-        <v>439</v>
+      <c r="B495" s="10" t="s">
+        <v>445</v>
       </c>
       <c r="C495" s="1" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="D495" s="1">
         <v>1</v>
@@ -10420,7 +10831,7 @@
         <v>527</v>
       </c>
       <c r="C496" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="497" spans="1:4">
@@ -10428,7 +10839,7 @@
         <v>528</v>
       </c>
       <c r="C497" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="498" spans="1:4">
@@ -10436,7 +10847,7 @@
         <v>529</v>
       </c>
       <c r="C498" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
     </row>
     <row r="499" s="3" customFormat="1" spans="1:4">
@@ -10445,7 +10856,7 @@
       </c>
       <c r="B499" s="12"/>
       <c r="C499" s="13" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="500" spans="1:4">
@@ -10453,18 +10864,18 @@
         <v>531</v>
       </c>
       <c r="C500" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
     </row>
     <row r="501" spans="1:4">
       <c r="A501">
         <v>532</v>
       </c>
-      <c r="B501" s="5" t="s">
-        <v>446</v>
+      <c r="B501" s="6" t="s">
+        <v>452</v>
       </c>
       <c r="C501" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
     </row>
     <row r="502" spans="1:4">
@@ -10477,16 +10888,16 @@
         <v>534</v>
       </c>
       <c r="C503" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
     </row>
     <row r="504" s="1" customFormat="1" spans="1:4">
       <c r="A504" s="1">
         <v>535</v>
       </c>
-      <c r="B504" s="9"/>
+      <c r="B504" s="10"/>
       <c r="C504" s="4" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D504" s="1">
         <v>1</v>
@@ -10497,7 +10908,7 @@
         <v>536</v>
       </c>
       <c r="C505" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="506" spans="1:4">
@@ -10505,7 +10916,7 @@
         <v>537</v>
       </c>
       <c r="C506" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
     </row>
     <row r="507" spans="1:4">
@@ -10513,7 +10924,7 @@
         <v>538</v>
       </c>
       <c r="C507" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="508" spans="1:4">
@@ -10546,7 +10957,7 @@
         <v>544</v>
       </c>
       <c r="C513" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
     </row>
     <row r="514" s="1" customFormat="1" spans="1:4">
@@ -10554,21 +10965,25 @@
         <v>545</v>
       </c>
       <c r="B514" s="11" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="C514" s="4" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="D514" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="515" spans="1:4">
-      <c r="A515">
+    <row r="515" s="1" customFormat="1" spans="1:4">
+      <c r="A515" s="1">
         <v>546</v>
       </c>
-      <c r="C515" s="8" t="s">
-        <v>456</v>
+      <c r="B515" s="10"/>
+      <c r="C515" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="D515" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="516" spans="1:4">
@@ -10576,7 +10991,7 @@
         <v>547</v>
       </c>
       <c r="C516" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
     </row>
     <row r="517" spans="1:4">
@@ -10584,7 +10999,7 @@
         <v>548</v>
       </c>
       <c r="C517" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
     <row r="518" spans="1:4">
@@ -10602,7 +11017,7 @@
         <v>551</v>
       </c>
       <c r="C520" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -10615,15 +11030,15 @@
         <v>553</v>
       </c>
       <c r="C522" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
     </row>
     <row r="523" spans="1:4">
       <c r="A523">
         <v>554</v>
       </c>
-      <c r="C523" s="8" t="s">
-        <v>461</v>
+      <c r="C523" s="9" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -10631,7 +11046,7 @@
         <v>555</v>
       </c>
       <c r="C524" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -10639,7 +11054,7 @@
         <v>556</v>
       </c>
       <c r="C525" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -10647,7 +11062,7 @@
         <v>557</v>
       </c>
       <c r="C526" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
     </row>
     <row r="527" spans="1:4">
@@ -10655,7 +11070,7 @@
         <v>558</v>
       </c>
       <c r="C527" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
     </row>
     <row r="528" spans="1:4">
@@ -10663,16 +11078,16 @@
         <v>559</v>
       </c>
       <c r="C528" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="529" s="1" customFormat="1" spans="1:4">
       <c r="A529" s="1">
         <v>560</v>
       </c>
-      <c r="B529" s="9"/>
+      <c r="B529" s="10"/>
       <c r="C529" s="2" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="D529" s="1">
         <v>1</v>
@@ -10688,7 +11103,7 @@
         <v>562</v>
       </c>
       <c r="C531" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
     </row>
     <row r="532" spans="1:4">
@@ -10696,15 +11111,19 @@
         <v>563</v>
       </c>
       <c r="C532" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="533" spans="1:4">
-      <c r="A533">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="533" s="1" customFormat="1" spans="1:4">
+      <c r="A533" s="1">
         <v>564</v>
       </c>
-      <c r="C533" t="s">
-        <v>470</v>
+      <c r="B533" s="10"/>
+      <c r="C533" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="D533" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="534" spans="1:4">
@@ -10717,7 +11136,7 @@
         <v>566</v>
       </c>
       <c r="C535" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
     </row>
     <row r="536" spans="1:4">
@@ -10731,7 +11150,7 @@
       </c>
       <c r="B537" s="12"/>
       <c r="C537" s="13" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="D537" s="3">
         <v>1</v>
@@ -10741,8 +11160,8 @@
       <c r="A538">
         <v>569</v>
       </c>
-      <c r="C538" s="8" t="s">
-        <v>473</v>
+      <c r="C538" s="9" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="539" spans="1:4">
@@ -10750,7 +11169,7 @@
         <v>570</v>
       </c>
       <c r="C539" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="540" spans="1:4">
@@ -10758,7 +11177,7 @@
         <v>571</v>
       </c>
       <c r="C540" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="541" spans="1:4">
@@ -10771,16 +11190,16 @@
         <v>573</v>
       </c>
       <c r="C542" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="543" s="1" customFormat="1" spans="1:4">
       <c r="A543" s="1">
         <v>574</v>
       </c>
-      <c r="B543" s="9"/>
+      <c r="B543" s="10"/>
       <c r="C543" s="2" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="D543" s="1">
         <v>1</v>
@@ -10796,7 +11215,7 @@
         <v>576</v>
       </c>
       <c r="C545" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="546" spans="1:5">
@@ -10808,31 +11227,31 @@
       <c r="A547">
         <v>578</v>
       </c>
-      <c r="B547" s="17" t="s">
-        <v>479</v>
+      <c r="B547" s="16" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="548" spans="1:5">
       <c r="A548">
         <v>579</v>
       </c>
-      <c r="C548" s="18" t="s">
-        <v>480</v>
+      <c r="C548" s="17" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="549" s="1" customFormat="1" spans="1:5">
       <c r="A549" s="1">
         <v>580</v>
       </c>
-      <c r="B549" s="9"/>
+      <c r="B549" s="10"/>
       <c r="C549" s="2" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="D549" s="1">
         <v>1</v>
       </c>
       <c r="E549" s="1" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="550" spans="1:5">
@@ -10865,7 +11284,7 @@
         <v>586</v>
       </c>
       <c r="C555" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="556" s="3" customFormat="1" spans="1:5">
@@ -10874,7 +11293,7 @@
       </c>
       <c r="B556" s="12"/>
       <c r="C556" s="3" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="557" spans="1:5">
@@ -10887,16 +11306,16 @@
         <v>589</v>
       </c>
       <c r="C558" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
     </row>
     <row r="559" s="1" customFormat="1" spans="1:5">
       <c r="A559" s="1">
         <v>590</v>
       </c>
-      <c r="B559" s="9"/>
+      <c r="B559" s="10"/>
       <c r="C559" s="4" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="D559" s="1">
         <v>1</v>
@@ -10912,7 +11331,7 @@
         <v>592</v>
       </c>
       <c r="C561" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
     </row>
     <row r="562" spans="1:4">
@@ -10920,18 +11339,18 @@
         <v>593</v>
       </c>
       <c r="C562" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="563" spans="1:4">
       <c r="A563">
         <v>594</v>
       </c>
-      <c r="B563" s="5" t="s">
-        <v>489</v>
-      </c>
-      <c r="C563" s="33" t="s">
-        <v>490</v>
+      <c r="B563" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="C563" s="31" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="564" spans="1:4">
@@ -10948,11 +11367,11 @@
       <c r="A566">
         <v>597</v>
       </c>
-      <c r="B566" s="5" t="s">
-        <v>491</v>
+      <c r="B566" s="6" t="s">
+        <v>497</v>
       </c>
       <c r="C566" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
     </row>
     <row r="567" spans="1:4">
@@ -10960,7 +11379,7 @@
         <v>598</v>
       </c>
       <c r="C567" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
     </row>
     <row r="568" spans="1:4">
@@ -10968,7 +11387,7 @@
         <v>599</v>
       </c>
       <c r="C568" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
     </row>
     <row r="569" spans="1:4">
@@ -10986,7 +11405,7 @@
         <v>602</v>
       </c>
       <c r="C571" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -10998,9 +11417,9 @@
       <c r="A573" s="1">
         <v>604</v>
       </c>
-      <c r="B573" s="9"/>
+      <c r="B573" s="10"/>
       <c r="C573" s="2" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="D573" s="1">
         <v>1</v>
@@ -11026,7 +11445,7 @@
         <v>608</v>
       </c>
       <c r="C577" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
     </row>
     <row r="578" spans="1:5">
@@ -11034,7 +11453,7 @@
         <v>609</v>
       </c>
       <c r="C578" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
     </row>
     <row r="579" spans="1:5">
@@ -11046,12 +11465,12 @@
       <c r="A580" s="1">
         <v>611</v>
       </c>
-      <c r="B580" s="9"/>
+      <c r="B580" s="10"/>
       <c r="C580" s="4" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="E580" s="1" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="581" spans="1:5">
@@ -11059,7 +11478,7 @@
         <v>612</v>
       </c>
       <c r="C581" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
     </row>
     <row r="582" spans="1:5">
@@ -11077,7 +11496,7 @@
         <v>615</v>
       </c>
       <c r="C584" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="585" spans="1:5">
@@ -11090,7 +11509,7 @@
         <v>617</v>
       </c>
       <c r="C586" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
     </row>
     <row r="587" spans="1:5">
@@ -11098,7 +11517,7 @@
         <v>618</v>
       </c>
       <c r="C587" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
     </row>
     <row r="588" s="3" customFormat="1" spans="1:5">
@@ -11107,7 +11526,7 @@
       </c>
       <c r="B588" s="12"/>
       <c r="C588" s="14" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
     </row>
     <row r="589" spans="1:5">
@@ -11115,7 +11534,7 @@
         <v>620</v>
       </c>
       <c r="C589" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
     </row>
     <row r="590" spans="1:5">
@@ -11123,15 +11542,15 @@
         <v>621</v>
       </c>
       <c r="C590" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
     </row>
     <row r="591" spans="1:5">
       <c r="A591">
         <v>622</v>
       </c>
-      <c r="C591" s="30" t="s">
-        <v>507</v>
+      <c r="C591" s="8" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="592" spans="1:5">
@@ -11139,7 +11558,7 @@
         <v>623</v>
       </c>
       <c r="C592" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
     </row>
     <row r="593" spans="1:4">
@@ -11159,19 +11578,19 @@
       <c r="A595">
         <v>626</v>
       </c>
-      <c r="C595" s="7" t="s">
-        <v>509</v>
+      <c r="C595" s="8" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="596" spans="1:4">
       <c r="A596">
         <v>627</v>
       </c>
-      <c r="B596" s="5" t="s">
-        <v>510</v>
+      <c r="B596" s="6" t="s">
+        <v>516</v>
       </c>
       <c r="C596" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
     </row>
     <row r="597" s="3" customFormat="1" spans="1:4">
@@ -11180,7 +11599,7 @@
       </c>
       <c r="B597" s="12"/>
       <c r="C597" s="13" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="D597" s="3">
         <v>1</v>
@@ -11191,7 +11610,7 @@
         <v>629</v>
       </c>
       <c r="C598" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
     </row>
     <row r="599" spans="1:4">
@@ -11199,7 +11618,7 @@
         <v>630</v>
       </c>
       <c r="C599" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
     </row>
     <row r="600" s="3" customFormat="1" spans="1:4">
@@ -11208,7 +11627,7 @@
       </c>
       <c r="B600" s="12"/>
       <c r="C600" s="13" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
     </row>
     <row r="601" s="1" customFormat="1" spans="1:4">
@@ -11216,13 +11635,13 @@
         <v>632</v>
       </c>
       <c r="B601" s="11" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C601" s="4" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="D601" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="602" spans="1:4">
@@ -11235,7 +11654,7 @@
         <v>634</v>
       </c>
       <c r="C603" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
     </row>
     <row r="604" spans="1:4">
@@ -11248,16 +11667,16 @@
         <v>636</v>
       </c>
       <c r="C605" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
     </row>
     <row r="606" s="1" customFormat="1" spans="1:4">
       <c r="A606" s="1">
         <v>637</v>
       </c>
-      <c r="B606" s="9"/>
+      <c r="B606" s="10"/>
       <c r="C606" s="1" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="D606" s="1">
         <v>1</v>
@@ -11268,16 +11687,16 @@
         <v>638</v>
       </c>
       <c r="C607" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
     </row>
     <row r="608" s="1" customFormat="1" spans="1:4">
       <c r="A608" s="1">
         <v>639</v>
       </c>
-      <c r="B608" s="9"/>
+      <c r="B608" s="10"/>
       <c r="C608" s="2" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="D608" s="1">
         <v>1</v>
@@ -11288,7 +11707,7 @@
         <v>640</v>
       </c>
       <c r="C609" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
     </row>
     <row r="610" s="1" customFormat="1" spans="1:4">
@@ -11296,10 +11715,10 @@
         <v>641</v>
       </c>
       <c r="B610" s="11" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="C610" s="4" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="D610" s="1">
         <v>1</v>
@@ -11310,7 +11729,7 @@
         <v>642</v>
       </c>
       <c r="C611" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
     </row>
     <row r="612" spans="1:4">
@@ -11318,16 +11737,16 @@
         <v>643</v>
       </c>
       <c r="C612" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
     </row>
     <row r="613" s="1" customFormat="1" ht="42.75" spans="1:4">
       <c r="A613" s="1">
         <v>644</v>
       </c>
-      <c r="B613" s="9"/>
-      <c r="C613" s="31" t="s">
-        <v>528</v>
+      <c r="B613" s="10"/>
+      <c r="C613" s="25" t="s">
+        <v>534</v>
       </c>
       <c r="D613" s="1">
         <v>1</v>
@@ -11338,31 +11757,37 @@
         <v>645</v>
       </c>
       <c r="C614" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
     </row>
     <row r="615" spans="1:4">
       <c r="A615">
         <v>646</v>
       </c>
-      <c r="C615" s="8" t="s">
-        <v>530</v>
+      <c r="C615" s="9" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="616" spans="1:4">
       <c r="A616">
         <v>647</v>
       </c>
-      <c r="C616" s="8" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="617" spans="1:4">
-      <c r="A617">
+      <c r="C616" s="9" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="617" s="1" customFormat="1" spans="1:4">
+      <c r="A617" s="1">
         <v>648</v>
       </c>
-      <c r="C617" t="s">
-        <v>532</v>
+      <c r="B617" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="C617" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="D617" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="618" spans="1:4">
@@ -11370,16 +11795,16 @@
         <v>649</v>
       </c>
       <c r="C618" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
     </row>
     <row r="619" s="1" customFormat="1" spans="1:4">
       <c r="A619" s="1">
         <v>650</v>
       </c>
-      <c r="B619" s="9"/>
+      <c r="B619" s="10"/>
       <c r="C619" s="4" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="D619" s="1">
         <v>1</v>
@@ -11390,18 +11815,18 @@
         <v>651</v>
       </c>
       <c r="C620" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
     </row>
     <row r="621" spans="1:4">
       <c r="A621">
         <v>652</v>
       </c>
-      <c r="B621" s="17" t="s">
-        <v>536</v>
+      <c r="B621" s="16" t="s">
+        <v>543</v>
       </c>
       <c r="C621" t="s">
-        <v>537</v>
+        <v>544</v>
       </c>
     </row>
     <row r="622" spans="1:4">
@@ -11409,7 +11834,7 @@
         <v>653</v>
       </c>
       <c r="C622" t="s">
-        <v>538</v>
+        <v>545</v>
       </c>
     </row>
     <row r="623" spans="1:4">
@@ -11417,7 +11842,7 @@
         <v>654</v>
       </c>
       <c r="C623" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
     </row>
     <row r="624" spans="1:4">
@@ -11425,18 +11850,18 @@
         <v>655</v>
       </c>
       <c r="C624" t="s">
-        <v>540</v>
+        <v>547</v>
       </c>
     </row>
     <row r="625" ht="71.25" spans="1:4">
       <c r="A625">
         <v>656</v>
       </c>
-      <c r="B625" s="17" t="s">
-        <v>541</v>
-      </c>
-      <c r="C625" s="6" t="s">
-        <v>542</v>
+      <c r="B625" s="16" t="s">
+        <v>548</v>
+      </c>
+      <c r="C625" s="7" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="626" s="3" customFormat="1" spans="1:4">
@@ -11445,7 +11870,7 @@
       </c>
       <c r="B626" s="12"/>
       <c r="C626" s="13" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
     </row>
     <row r="627" spans="1:4">
@@ -11453,22 +11878,22 @@
         <v>658</v>
       </c>
       <c r="C627" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
     </row>
     <row r="628" spans="1:4">
       <c r="A628">
         <v>659</v>
       </c>
-      <c r="C628" s="8" t="s">
-        <v>545</v>
+      <c r="C628" s="9" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="629" spans="1:4">
       <c r="A629">
         <v>660</v>
       </c>
-      <c r="C629" s="18">
+      <c r="C629" s="17">
         <v>7</v>
       </c>
     </row>
@@ -11477,18 +11902,18 @@
         <v>661</v>
       </c>
       <c r="C630" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
     </row>
     <row r="631" spans="1:4">
       <c r="A631">
         <v>662</v>
       </c>
-      <c r="B631" s="5" t="s">
-        <v>547</v>
+      <c r="B631" s="6" t="s">
+        <v>554</v>
       </c>
       <c r="C631" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
     </row>
     <row r="632" s="3" customFormat="1" spans="1:4">
@@ -11497,7 +11922,7 @@
       </c>
       <c r="B632" s="12"/>
       <c r="C632" s="14" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="D632" s="3">
         <v>1</v>
@@ -11507,11 +11932,11 @@
       <c r="A633">
         <v>664</v>
       </c>
-      <c r="B633" s="5" t="s">
-        <v>550</v>
+      <c r="B633" s="6" t="s">
+        <v>557</v>
       </c>
       <c r="C633" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
     </row>
     <row r="634" spans="1:4">
@@ -11519,7 +11944,7 @@
         <v>665</v>
       </c>
       <c r="C634" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
     </row>
     <row r="635" spans="1:4">
@@ -11532,7 +11957,7 @@
         <v>667</v>
       </c>
       <c r="C636" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
     </row>
     <row r="637" spans="1:4">
@@ -11545,7 +11970,7 @@
         <v>669</v>
       </c>
       <c r="C638" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
     </row>
     <row r="639" spans="1:4">
@@ -11562,8 +11987,8 @@
       <c r="A641" s="1">
         <v>672</v>
       </c>
-      <c r="B641" s="9"/>
-      <c r="C641" s="32">
+      <c r="B641" s="10"/>
+      <c r="C641" s="30">
         <v>2</v>
       </c>
       <c r="D641" s="1">
@@ -11580,7 +12005,7 @@
         <v>674</v>
       </c>
       <c r="E643" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="644" spans="1:5">
@@ -11608,18 +12033,18 @@
         <v>679</v>
       </c>
       <c r="C648" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
     </row>
     <row r="649" s="1" customFormat="1" spans="1:5">
       <c r="A649" s="1">
         <v>680</v>
       </c>
-      <c r="B649" s="22" t="s">
-        <v>556</v>
+      <c r="B649" s="20" t="s">
+        <v>563</v>
       </c>
       <c r="C649" s="4" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="D649" s="1">
         <v>1</v>
@@ -11629,9 +12054,9 @@
       <c r="A650" s="1">
         <v>681</v>
       </c>
-      <c r="B650" s="9"/>
-      <c r="C650" s="10" t="s">
-        <v>558</v>
+      <c r="B650" s="10"/>
+      <c r="C650" s="4" t="s">
+        <v>565</v>
       </c>
       <c r="D650" s="1">
         <v>1</v>
@@ -11641,11 +12066,11 @@
       <c r="A651" s="1">
         <v>682</v>
       </c>
-      <c r="B651" s="22" t="s">
-        <v>559</v>
+      <c r="B651" s="20" t="s">
+        <v>566</v>
       </c>
       <c r="C651" s="4" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="D651" s="1">
         <v>1</v>
@@ -11655,22 +12080,22 @@
       <c r="A652" s="1">
         <v>683</v>
       </c>
-      <c r="B652" s="22" t="s">
-        <v>561</v>
+      <c r="B652" s="20" t="s">
+        <v>568</v>
       </c>
       <c r="C652" s="4" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="D652" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="653" spans="1:5">
       <c r="A653">
         <v>684</v>
       </c>
-      <c r="C653" s="8" t="s">
-        <v>563</v>
+      <c r="C653" s="9" t="s">
+        <v>570</v>
       </c>
     </row>
     <row r="654" spans="1:5">
